--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -1830,13 +1830,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46160.48557077546</v>
+        <v>46160.65223744213</v>
       </c>
       <c r="C4" s="5">
-        <v>46167.39169478009</v>
+        <v>46167.55836144676</v>
       </c>
       <c r="D4" s="5">
-        <v>46181.512122534725</v>
+        <v>46181.67878920139</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1879,13 +1879,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46160.48568386574</v>
+        <v>46160.65235053241</v>
       </c>
       <c r="C5" s="8">
-        <v>46167.39166763889</v>
+        <v>46167.558334305555</v>
       </c>
       <c r="D5" s="8">
-        <v>46167.391668703705</v>
+        <v>46167.55833537037</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1942,13 +1942,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46160.48568737268</v>
+        <v>46160.652354039354</v>
       </c>
       <c r="C6" s="5">
-        <v>46167.39148954861</v>
+        <v>46167.55815621528</v>
       </c>
       <c r="D6" s="5">
-        <v>46167.39149064815</v>
+        <v>46167.558157314816</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2005,13 +2005,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46160.48569023148</v>
+        <v>46160.65235689815</v>
       </c>
       <c r="C7" s="8">
-        <v>46167.391522743055</v>
+        <v>46167.55818940973</v>
       </c>
       <c r="D7" s="8">
-        <v>46167.39152376157</v>
+        <v>46167.558190428244</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -2068,13 +2068,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46160.48569302083</v>
+        <v>46160.652359687505</v>
       </c>
       <c r="C8" s="5">
-        <v>46167.39156736111</v>
+        <v>46167.558234027776</v>
       </c>
       <c r="D8" s="5">
-        <v>46167.39156875</v>
+        <v>46167.55823541667</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -2131,13 +2131,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46160.48569648148</v>
+        <v>46160.65236314815</v>
       </c>
       <c r="C9" s="8">
-        <v>46167.391679444445</v>
+        <v>46167.55834611111</v>
       </c>
       <c r="D9" s="8">
-        <v>46167.391680636574</v>
+        <v>46167.558347303246</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2194,11 +2194,11 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46160.48702451389</v>
+        <v>46160.65369118056</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46167.391623668984</v>
+        <v>46167.55829033565</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2247,13 +2247,13 @@
         <v>52</v>
       </c>
       <c r="B11" s="8">
-        <v>46160.48742520833</v>
+        <v>46160.654091874996</v>
       </c>
       <c r="C11" s="8">
-        <v>46167.391617326386</v>
+        <v>46167.55828399306</v>
       </c>
       <c r="D11" s="8">
-        <v>46167.39162951389</v>
+        <v>46167.558296180556</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>53</v>
@@ -2312,11 +2312,11 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46160.48750545139</v>
+        <v>46160.654172118055</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46160.64728152778</v>
+        <v>46160.813948194445</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2375,11 +2375,11 @@
         <v>63</v>
       </c>
       <c r="B13" s="8">
-        <v>46160.485575405095</v>
+        <v>46160.65224207176</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46167.39227378472</v>
+        <v>46167.55894045139</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>64</v>
@@ -2422,13 +2422,13 @@
         <v>66</v>
       </c>
       <c r="B14" s="5">
-        <v>46160.48569984954</v>
+        <v>46160.6523665162</v>
       </c>
       <c r="C14" s="5">
-        <v>46167.39225503472</v>
+        <v>46167.55892170139</v>
       </c>
       <c r="D14" s="5">
-        <v>46167.39226771991</v>
+        <v>46167.55893438657</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>67</v>
@@ -2487,13 +2487,13 @@
         <v>70</v>
       </c>
       <c r="B15" s="8">
-        <v>46160.48570503472</v>
+        <v>46160.65237170139</v>
       </c>
       <c r="C15" s="8">
-        <v>46167.392260057866</v>
+        <v>46167.55892672454</v>
       </c>
       <c r="D15" s="8">
-        <v>46167.39227575231</v>
+        <v>46167.55894241898</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>71</v>
@@ -2552,13 +2552,13 @@
         <v>74</v>
       </c>
       <c r="B16" s="5">
-        <v>46160.48571020833</v>
+        <v>46160.652376875005</v>
       </c>
       <c r="C16" s="5">
-        <v>46167.39226748842</v>
+        <v>46167.558934155095</v>
       </c>
       <c r="D16" s="5">
-        <v>46167.392280879634</v>
+        <v>46167.55894754629</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>75</v>
@@ -2617,11 +2617,11 @@
         <v>77</v>
       </c>
       <c r="B17" s="8">
-        <v>46160.48571533565</v>
+        <v>46160.652382002314</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46167.39227512731</v>
+        <v>46167.55894179398</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>78</v>
@@ -2680,13 +2680,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46160.485579479166</v>
+        <v>46160.65224614584</v>
       </c>
       <c r="C18" s="5">
-        <v>46181.446006122686</v>
+        <v>46181.61267278936</v>
       </c>
       <c r="D18" s="5">
-        <v>46181.512035567124</v>
+        <v>46181.678702233796</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2729,13 +2729,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46160.485722893514</v>
+        <v>46160.652389560186</v>
       </c>
       <c r="C19" s="8">
-        <v>46167.39229795139</v>
+        <v>46167.55896461806</v>
       </c>
       <c r="D19" s="8">
-        <v>46167.39231096065</v>
+        <v>46167.55897762731</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2794,13 +2794,13 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46160.485728252315</v>
+        <v>46160.65239491899</v>
       </c>
       <c r="C20" s="5">
-        <v>46167.39232921296</v>
+        <v>46167.55899587963</v>
       </c>
       <c r="D20" s="5">
-        <v>46167.392345995366</v>
+        <v>46167.55901266204</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2859,13 +2859,13 @@
         <v>91</v>
       </c>
       <c r="B21" s="8">
-        <v>46160.485733622685</v>
+        <v>46160.65240028936</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.445580381944</v>
+        <v>46181.612247048615</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.445597997685</v>
+        <v>46181.61226466435</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>92</v>
@@ -2924,13 +2924,13 @@
         <v>95</v>
       </c>
       <c r="B22" s="5">
-        <v>46160.4857389699</v>
+        <v>46160.652405636574</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.446068969904</v>
+        <v>46181.612735636576</v>
       </c>
       <c r="D22" s="5">
-        <v>46181.509123125</v>
+        <v>46181.67578979167</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>96</v>
@@ -2989,13 +2989,13 @@
         <v>102</v>
       </c>
       <c r="B23" s="8">
-        <v>46160.48574392361</v>
+        <v>46160.65241059028</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.509155694446</v>
+        <v>46181.67582236111</v>
       </c>
       <c r="D23" s="8">
-        <v>46181.50917122685</v>
+        <v>46181.67583789352</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>103</v>
@@ -3054,13 +3054,13 @@
         <v>105</v>
       </c>
       <c r="B24" s="5">
-        <v>46160.485747824074</v>
+        <v>46160.652414490745</v>
       </c>
       <c r="C24" s="5">
-        <v>46181.509193645834</v>
+        <v>46181.675860312505</v>
       </c>
       <c r="D24" s="5">
-        <v>46181.50920886574</v>
+        <v>46181.67587553241</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>106</v>
@@ -3119,13 +3119,13 @@
         <v>108</v>
       </c>
       <c r="B25" s="8">
-        <v>46160.48575173611</v>
+        <v>46160.65241840278</v>
       </c>
       <c r="C25" s="8">
-        <v>46181.50920561343</v>
+        <v>46181.67587228009</v>
       </c>
       <c r="D25" s="8">
-        <v>46181.50922108797</v>
+        <v>46181.67588775463</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>109</v>
@@ -3184,13 +3184,13 @@
         <v>111</v>
       </c>
       <c r="B26" s="5">
-        <v>46160.49191201389</v>
+        <v>46160.65857868055</v>
       </c>
       <c r="C26" s="5">
-        <v>46167.39236136574</v>
+        <v>46167.55902803241</v>
       </c>
       <c r="D26" s="5">
-        <v>46167.392375868054</v>
+        <v>46167.55904253472</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>112</v>
@@ -3249,11 +3249,11 @@
         <v>114</v>
       </c>
       <c r="B27" s="8">
-        <v>46160.48558396991</v>
+        <v>46160.65225063657</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46181.51197298611</v>
+        <v>46181.678639652775</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>115</v>
@@ -3296,13 +3296,13 @@
         <v>117</v>
       </c>
       <c r="B28" s="5">
-        <v>46160.48575607639</v>
+        <v>46160.65242274306</v>
       </c>
       <c r="C28" s="5">
-        <v>46181.50902550926</v>
+        <v>46181.67569217592</v>
       </c>
       <c r="D28" s="5">
-        <v>46181.50904247686</v>
+        <v>46181.675709143514</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>118</v>
@@ -3361,13 +3361,13 @@
         <v>122</v>
       </c>
       <c r="B29" s="8">
-        <v>46160.48576053241</v>
+        <v>46160.65242719908</v>
       </c>
       <c r="C29" s="8">
-        <v>46181.50896636574</v>
+        <v>46181.675633032406</v>
       </c>
       <c r="D29" s="8">
-        <v>46181.50896782408</v>
+        <v>46181.67563449074</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>123</v>
@@ -3422,13 +3422,13 @@
         <v>125</v>
       </c>
       <c r="B30" s="5">
-        <v>46160.485765150464</v>
+        <v>46160.65243181713</v>
       </c>
       <c r="C30" s="5">
-        <v>46181.509009664354</v>
+        <v>46181.67567633102</v>
       </c>
       <c r="D30" s="5">
-        <v>46181.50901123842</v>
+        <v>46181.67567790509</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>126</v>
@@ -3483,13 +3483,13 @@
         <v>128</v>
       </c>
       <c r="B31" s="8">
-        <v>46160.485770011575</v>
+        <v>46160.65243667824</v>
       </c>
       <c r="C31" s="8">
-        <v>46181.508945995374</v>
+        <v>46181.67561266204</v>
       </c>
       <c r="D31" s="8">
-        <v>46181.5089566088</v>
+        <v>46181.67562327546</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>129</v>
@@ -3548,13 +3548,13 @@
         <v>131</v>
       </c>
       <c r="B32" s="5">
-        <v>46160.485774409724</v>
+        <v>46160.65244107639</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.508886006945</v>
+        <v>46181.67555267361</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.50888729167</v>
+        <v>46181.67555395833</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>132</v>
@@ -3609,13 +3609,13 @@
         <v>134</v>
       </c>
       <c r="B33" s="8">
-        <v>46160.48577912037</v>
+        <v>46160.65244578704</v>
       </c>
       <c r="C33" s="8">
-        <v>46181.50893012731</v>
+        <v>46181.67559679398</v>
       </c>
       <c r="D33" s="8">
-        <v>46181.50893173611</v>
+        <v>46181.67559840278</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>135</v>
@@ -3670,13 +3670,13 @@
         <v>137</v>
       </c>
       <c r="B34" s="5">
-        <v>46160.485783958335</v>
+        <v>46160.652450625</v>
       </c>
       <c r="C34" s="5">
-        <v>46181.508813252316</v>
+        <v>46181.67547991898</v>
       </c>
       <c r="D34" s="5">
-        <v>46181.508827025464</v>
+        <v>46181.67549369213</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>138</v>
@@ -3735,13 +3735,13 @@
         <v>140</v>
       </c>
       <c r="B35" s="8">
-        <v>46160.48578885417</v>
+        <v>46160.65245552083</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.508744583334</v>
+        <v>46181.67541125</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.50874601852</v>
+        <v>46181.67541268519</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>141</v>
@@ -3796,13 +3796,13 @@
         <v>143</v>
       </c>
       <c r="B36" s="5">
-        <v>46160.48579381945</v>
+        <v>46160.65246048611</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.50878599537</v>
+        <v>46181.675452662035</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.50878724537</v>
+        <v>46181.67545391204</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>144</v>
@@ -3857,13 +3857,13 @@
         <v>146</v>
       </c>
       <c r="B37" s="8">
-        <v>46160.485798865746</v>
+        <v>46160.6524655324</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.50879839121</v>
+        <v>46181.675465057866</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.508799814816</v>
+        <v>46181.67546648148</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>147</v>
@@ -3918,11 +3918,11 @@
         <v>149</v>
       </c>
       <c r="B38" s="5">
-        <v>46160.49000302084</v>
+        <v>46160.6566696875</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46185.53827590278</v>
+        <v>46185.70494256944</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3981,13 +3981,13 @@
         <v>152</v>
       </c>
       <c r="B39" s="8">
-        <v>46160.49009685185</v>
+        <v>46160.65676351852</v>
       </c>
       <c r="C39" s="8">
-        <v>46182.510074641206</v>
+        <v>46182.67674130787</v>
       </c>
       <c r="D39" s="8">
-        <v>46182.510076666666</v>
+        <v>46182.67674333333</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>113</v>
@@ -4036,11 +4036,11 @@
         <v>154</v>
       </c>
       <c r="B40" s="5">
-        <v>46160.49021748843</v>
+        <v>46160.65688415509</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46182.51008091435</v>
+        <v>46182.67674758102</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>155</v>
@@ -4089,13 +4089,13 @@
         <v>157</v>
       </c>
       <c r="B41" s="8">
-        <v>46160.485803483796</v>
+        <v>46160.65247015047</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.50956585648</v>
+        <v>46181.67623252315</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.5095777199</v>
+        <v>46181.676244386574</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>158</v>
@@ -4154,13 +4154,13 @@
         <v>162</v>
       </c>
       <c r="B42" s="5">
-        <v>46160.48580815972</v>
+        <v>46160.65247482639</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.50948204861</v>
+        <v>46181.676148715276</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.50948341435</v>
+        <v>46181.67615008102</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>163</v>
@@ -4215,13 +4215,13 @@
         <v>165</v>
       </c>
       <c r="B43" s="8">
-        <v>46160.48581292824</v>
+        <v>46160.65247959491</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.509552268515</v>
+        <v>46181.67621893519</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.50955349537</v>
+        <v>46181.67622016204</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>166</v>
@@ -4276,13 +4276,13 @@
         <v>168</v>
       </c>
       <c r="B44" s="5">
-        <v>46160.485874039354</v>
+        <v>46160.65254070602</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.50968824074</v>
+        <v>46181.67635490741</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.509699953705</v>
+        <v>46181.67636662037</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>169</v>
@@ -4341,13 +4341,13 @@
         <v>171</v>
       </c>
       <c r="B45" s="8">
-        <v>46160.4858790625</v>
+        <v>46160.65254572917</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.50963344907</v>
+        <v>46181.67630011574</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.509634953705</v>
+        <v>46181.67630162037</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>104</v>
@@ -4396,13 +4396,13 @@
         <v>173</v>
       </c>
       <c r="B46" s="5">
-        <v>46160.48588471065</v>
+        <v>46160.652551377316</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.50967270833</v>
+        <v>46181.676339375</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.50967423611</v>
+        <v>46181.67634090278</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>174</v>
@@ -4451,13 +4451,13 @@
         <v>176</v>
       </c>
       <c r="B47" s="8">
-        <v>46160.48589048611</v>
+        <v>46160.652557152775</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.509813854165</v>
+        <v>46181.67648052084</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.509825057874</v>
+        <v>46181.67649172454</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>177</v>
@@ -4516,13 +4516,13 @@
         <v>181</v>
       </c>
       <c r="B48" s="5">
-        <v>46160.4858949537</v>
+        <v>46160.65256162037</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.50972081019</v>
+        <v>46181.67638747685</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.50972233796</v>
+        <v>46181.67638900463</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>110</v>
@@ -4571,13 +4571,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46160.48590677083</v>
+        <v>46160.6525734375</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.509760891204</v>
+        <v>46181.676427557875</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.50976267361</v>
+        <v>46181.67642934028</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4626,13 +4626,13 @@
         <v>186</v>
       </c>
       <c r="B50" s="5">
-        <v>46160.48591256945</v>
+        <v>46160.652579236106</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.509799259264</v>
+        <v>46181.67646592592</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.50980063657</v>
+        <v>46181.676467303245</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>187</v>
@@ -4681,13 +4681,13 @@
         <v>190</v>
       </c>
       <c r="B51" s="8">
-        <v>46160.485916377314</v>
+        <v>46160.65258304398</v>
       </c>
       <c r="C51" s="8">
-        <v>46181.509901122685</v>
+        <v>46181.676567789356</v>
       </c>
       <c r="D51" s="8">
-        <v>46181.509912187496</v>
+        <v>46181.67657885417</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>191</v>
@@ -4746,13 +4746,13 @@
         <v>193</v>
       </c>
       <c r="B52" s="5">
-        <v>46160.485920879626</v>
+        <v>46160.6525875463</v>
       </c>
       <c r="C52" s="5">
-        <v>46181.50984517361</v>
+        <v>46181.676511840276</v>
       </c>
       <c r="D52" s="5">
-        <v>46181.50984648148</v>
+        <v>46181.67651314815</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>107</v>
@@ -4801,13 +4801,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46160.48592640046</v>
+        <v>46160.652593067134</v>
       </c>
       <c r="C53" s="8">
-        <v>46181.50988571759</v>
+        <v>46181.67655238426</v>
       </c>
       <c r="D53" s="8">
-        <v>46181.50988701389</v>
+        <v>46181.676553680554</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4856,13 +4856,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46160.48558849537</v>
+        <v>46160.65225516204</v>
       </c>
       <c r="C54" s="5">
-        <v>46181.445746921294</v>
+        <v>46181.612413587965</v>
       </c>
       <c r="D54" s="5">
-        <v>46181.51191784722</v>
+        <v>46181.67858451389</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4905,13 +4905,13 @@
         <v>201</v>
       </c>
       <c r="B55" s="8">
-        <v>46160.4859325463</v>
+        <v>46160.65259921296</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.445661516205</v>
+        <v>46181.61232818287</v>
       </c>
       <c r="D55" s="8">
-        <v>46181.44567918981</v>
+        <v>46181.61234585648</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>202</v>
@@ -4970,13 +4970,13 @@
         <v>206</v>
       </c>
       <c r="B56" s="5">
-        <v>46160.48593934027</v>
+        <v>46160.652606006945</v>
       </c>
       <c r="C56" s="5">
-        <v>46181.50905496528</v>
+        <v>46181.675721631946</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.50907157407</v>
+        <v>46181.67573824074</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>207</v>
@@ -5035,13 +5035,13 @@
         <v>210</v>
       </c>
       <c r="B57" s="8">
-        <v>46160.485947430556</v>
+        <v>46160.65261409723</v>
       </c>
       <c r="C57" s="8">
-        <v>46181.50909756945</v>
+        <v>46181.67576423611</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.50911381944</v>
+        <v>46181.67578048611</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>99</v>
@@ -5100,11 +5100,11 @@
         <v>212</v>
       </c>
       <c r="B58" s="5">
-        <v>46160.48596431713</v>
+        <v>46160.652630983794</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46184.73020696759</v>
+        <v>46184.89687363426</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>213</v>
@@ -5163,11 +5163,11 @@
         <v>217</v>
       </c>
       <c r="B59" s="8">
-        <v>46160.485968657405</v>
+        <v>46160.65263532408</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46181.51123409723</v>
+        <v>46181.67790076389</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>218</v>
@@ -5216,11 +5216,11 @@
         <v>220</v>
       </c>
       <c r="B60" s="5">
-        <v>46160.485974027775</v>
+        <v>46160.65264069445</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46181.5112465625</v>
+        <v>46181.67791322917</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>218</v>
@@ -5269,13 +5269,13 @@
         <v>222</v>
       </c>
       <c r="B61" s="8">
-        <v>46160.48601025463</v>
+        <v>46160.652676921294</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.44612966436</v>
+        <v>46181.612796331014</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.51150304398</v>
+        <v>46181.67816971065</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>223</v>
@@ -5318,13 +5318,13 @@
         <v>225</v>
       </c>
       <c r="B62" s="5">
-        <v>46160.486014166665</v>
+        <v>46160.65268083333</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.50992280093</v>
+        <v>46181.67658946759</v>
       </c>
       <c r="D62" s="5">
-        <v>46182.03195226852</v>
+        <v>46182.19861893519</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>226</v>
@@ -5383,13 +5383,13 @@
         <v>230</v>
       </c>
       <c r="B63" s="8">
-        <v>46160.486019143515</v>
+        <v>46160.652685810186</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.510016527776</v>
+        <v>46181.67668319444</v>
       </c>
       <c r="D63" s="8">
-        <v>46184.005462326386</v>
+        <v>46184.17212899306</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>231</v>
@@ -5448,13 +5448,13 @@
         <v>234</v>
       </c>
       <c r="B64" s="5">
-        <v>46160.48602430556</v>
+        <v>46160.65269097222</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.50994024306</v>
+        <v>46181.67660690972</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.50995578704</v>
+        <v>46181.6766224537</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>235</v>
@@ -5513,13 +5513,13 @@
         <v>237</v>
       </c>
       <c r="B65" s="8">
-        <v>46160.48602966435</v>
+        <v>46160.65269633102</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.51003130787</v>
+        <v>46181.67669797454</v>
       </c>
       <c r="D65" s="8">
-        <v>46184.005462326386</v>
+        <v>46184.17212899306</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>238</v>
@@ -5578,13 +5578,13 @@
         <v>239</v>
       </c>
       <c r="B66" s="5">
-        <v>46160.48603313658</v>
+        <v>46160.65269980324</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.51000043981</v>
+        <v>46181.67666710648</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.51000200232</v>
+        <v>46181.67666866898</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5643,13 +5643,13 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46160.48603726852</v>
+        <v>46160.652703935186</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.510049247685</v>
+        <v>46181.67671591435</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.00546233796</v>
+        <v>46184.172129004626</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>241</v>
@@ -5708,13 +5708,13 @@
         <v>243</v>
       </c>
       <c r="B68" s="5">
-        <v>46160.486041006945</v>
+        <v>46160.65270767361</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.44619803241</v>
+        <v>46181.61286469907</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.51144181713</v>
+        <v>46181.6781084838</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>244</v>
@@ -5757,13 +5757,13 @@
         <v>246</v>
       </c>
       <c r="B69" s="8">
-        <v>46160.48604394676</v>
+        <v>46160.65271061343</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.51018964121</v>
+        <v>46181.676856307866</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.510466886575</v>
+        <v>46181.67713355324</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>247</v>
@@ -5822,13 +5822,13 @@
         <v>252</v>
       </c>
       <c r="B70" s="5">
-        <v>46160.486049837964</v>
+        <v>46160.65271650463</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.51015998842</v>
+        <v>46181.67682665509</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.51046767361</v>
+        <v>46181.67713434028</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>218</v>
@@ -5877,13 +5877,13 @@
         <v>255</v>
       </c>
       <c r="B71" s="8">
-        <v>46160.4860555787</v>
+        <v>46160.65272224537</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.51017574074</v>
+        <v>46181.67684240741</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.51046842593</v>
+        <v>46181.67713509259</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>218</v>
@@ -5932,13 +5932,13 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46160.48606023148</v>
+        <v>46160.652726898144</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.51055939815</v>
+        <v>46181.677226064814</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.51057105324</v>
+        <v>46181.67723771991</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5997,13 +5997,13 @@
         <v>261</v>
       </c>
       <c r="B73" s="8">
-        <v>46160.486063854165</v>
+        <v>46160.65273052083</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.51053046296</v>
+        <v>46181.677197129626</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.510531875</v>
+        <v>46181.67719854167</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>218</v>
@@ -6052,13 +6052,13 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46160.486074953704</v>
+        <v>46160.652741620375</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.51054616898</v>
+        <v>46181.67721283565</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.51054769676</v>
+        <v>46181.67721436343</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>257</v>
@@ -6107,13 +6107,13 @@
         <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46160.4860796412</v>
+        <v>46160.65274630787</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.51062046296</v>
+        <v>46181.67728712963</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.51063304398</v>
+        <v>46181.677299710645</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>266</v>
@@ -6172,13 +6172,13 @@
         <v>267</v>
       </c>
       <c r="B76" s="5">
-        <v>46160.4860833912</v>
+        <v>46160.65275005787</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.51059667824</v>
+        <v>46181.67726334491</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.51059846065</v>
+        <v>46181.67726512731</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>218</v>
@@ -6227,13 +6227,13 @@
         <v>269</v>
       </c>
       <c r="B77" s="8">
-        <v>46160.486088819445</v>
+        <v>46160.65275548611</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.510606365744</v>
+        <v>46181.67727303241</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.51060799768</v>
+        <v>46181.677274664355</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>218</v>
@@ -6282,13 +6282,13 @@
         <v>272</v>
       </c>
       <c r="B78" s="5">
-        <v>46160.48609395833</v>
+        <v>46160.652760625</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.44636556713</v>
+        <v>46181.6130322338</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.510851875</v>
+        <v>46181.67751854166</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>223</v>
@@ -6331,13 +6331,13 @@
         <v>274</v>
       </c>
       <c r="B79" s="8">
-        <v>46160.48609673612</v>
+        <v>46160.65276340277</v>
       </c>
       <c r="C79" s="8">
-        <v>46181.51064849537</v>
+        <v>46181.67731516204</v>
       </c>
       <c r="D79" s="8">
-        <v>46184.03611842592</v>
+        <v>46184.202785092595</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>275</v>
@@ -6396,13 +6396,13 @@
         <v>277</v>
       </c>
       <c r="B80" s="5">
-        <v>46160.48610216435</v>
+        <v>46160.652768831016</v>
       </c>
       <c r="C80" s="5">
-        <v>46181.510658576386</v>
+        <v>46181.67732524306</v>
       </c>
       <c r="D80" s="5">
-        <v>46181.51067836805</v>
+        <v>46181.677345034725</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>278</v>
@@ -6461,13 +6461,13 @@
         <v>279</v>
       </c>
       <c r="B81" s="8">
-        <v>46160.486107743054</v>
+        <v>46160.652774409726</v>
       </c>
       <c r="C81" s="8">
-        <v>46181.51066972222</v>
+        <v>46181.67733638889</v>
       </c>
       <c r="D81" s="8">
-        <v>46181.51068952546</v>
+        <v>46181.67735619213</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>280</v>
@@ -6526,13 +6526,13 @@
         <v>281</v>
       </c>
       <c r="B82" s="5">
-        <v>46160.4861130787</v>
+        <v>46160.652779745375</v>
       </c>
       <c r="C82" s="5">
-        <v>46181.510678935185</v>
+        <v>46181.677345601856</v>
       </c>
       <c r="D82" s="5">
-        <v>46181.51069646991</v>
+        <v>46181.67736313658</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>282</v>
@@ -6591,11 +6591,11 @@
         <v>284</v>
       </c>
       <c r="B83" s="8">
-        <v>46160.49040090278</v>
+        <v>46160.657067569446</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46181.451854479164</v>
+        <v>46181.618521145836</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>61</v>
@@ -6654,13 +6654,13 @@
         <v>285</v>
       </c>
       <c r="B84" s="5">
-        <v>46160.48611752315</v>
+        <v>46160.65278418981</v>
       </c>
       <c r="C84" s="5">
-        <v>46181.45112766203</v>
+        <v>46181.617794328704</v>
       </c>
       <c r="D84" s="5">
-        <v>46181.51159185186</v>
+        <v>46181.678258518514</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>286</v>
@@ -6703,13 +6703,13 @@
         <v>288</v>
       </c>
       <c r="B85" s="8">
-        <v>46160.486120347225</v>
+        <v>46160.65278701389</v>
       </c>
       <c r="C85" s="8">
-        <v>46181.51093371528</v>
+        <v>46181.67760038194</v>
       </c>
       <c r="D85" s="8">
-        <v>46181.51095034722</v>
+        <v>46181.67761701389</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>289</v>
@@ -6768,13 +6768,13 @@
         <v>291</v>
       </c>
       <c r="B86" s="5">
-        <v>46160.486126909724</v>
+        <v>46160.65279357639</v>
       </c>
       <c r="C86" s="5">
-        <v>46181.51100827546</v>
+        <v>46181.677674942126</v>
       </c>
       <c r="D86" s="5">
-        <v>46181.51100951389</v>
+        <v>46181.67767618055</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>218</v>
@@ -6823,13 +6823,13 @@
         <v>293</v>
       </c>
       <c r="B87" s="8">
-        <v>46160.4861306713</v>
+        <v>46160.65279733796</v>
       </c>
       <c r="C87" s="8">
-        <v>46181.511020844904</v>
+        <v>46181.677687511576</v>
       </c>
       <c r="D87" s="8">
-        <v>46181.51102258102</v>
+        <v>46181.677689247685</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>218</v>
@@ -6878,13 +6878,13 @@
         <v>294</v>
       </c>
       <c r="B88" s="5">
-        <v>46160.4861344213</v>
+        <v>46160.65280108796</v>
       </c>
       <c r="C88" s="5">
-        <v>46181.5110999537</v>
+        <v>46181.67776662037</v>
       </c>
       <c r="D88" s="5">
-        <v>46181.51111119213</v>
+        <v>46181.6777778588</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>295</v>
@@ -6943,13 +6943,13 @@
         <v>296</v>
       </c>
       <c r="B89" s="8">
-        <v>46160.48613832176</v>
+        <v>46160.65280498842</v>
       </c>
       <c r="C89" s="8">
-        <v>46181.51107460648</v>
+        <v>46181.677741273146</v>
       </c>
       <c r="D89" s="8">
-        <v>46181.51107620371</v>
+        <v>46181.67774287037</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>218</v>
@@ -6998,13 +6998,13 @@
         <v>299</v>
       </c>
       <c r="B90" s="5">
-        <v>46160.486143472226</v>
+        <v>46160.65281013889</v>
       </c>
       <c r="C90" s="5">
-        <v>46181.51108667824</v>
+        <v>46181.677753344906</v>
       </c>
       <c r="D90" s="5">
-        <v>46181.511088217594</v>
+        <v>46181.67775488426</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>218</v>
@@ -7053,13 +7053,13 @@
         <v>300</v>
       </c>
       <c r="B91" s="8">
-        <v>46160.48614836806</v>
+        <v>46160.65281503472</v>
       </c>
       <c r="C91" s="8">
-        <v>46181.51117106482</v>
+        <v>46181.67783773148</v>
       </c>
       <c r="D91" s="8">
-        <v>46181.51118509259</v>
+        <v>46181.67785175926</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>301</v>
@@ -7118,13 +7118,13 @@
         <v>302</v>
       </c>
       <c r="B92" s="5">
-        <v>46160.48615216435</v>
+        <v>46160.65281883102</v>
       </c>
       <c r="C92" s="5">
-        <v>46181.511129328705</v>
+        <v>46181.67779599537</v>
       </c>
       <c r="D92" s="5">
-        <v>46181.511130960644</v>
+        <v>46181.677797627315</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>218</v>
@@ -7171,13 +7171,13 @@
         <v>304</v>
       </c>
       <c r="B93" s="8">
-        <v>46160.486209421295</v>
+        <v>46160.65287608796</v>
       </c>
       <c r="C93" s="8">
-        <v>46181.51113912037</v>
+        <v>46181.67780578704</v>
       </c>
       <c r="D93" s="8">
-        <v>46181.51114059028</v>
+        <v>46181.67780725694</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>218</v>
@@ -7224,13 +7224,13 @@
         <v>305</v>
       </c>
       <c r="B94" s="5">
-        <v>46160.486217812504</v>
+        <v>46160.65288447917</v>
       </c>
       <c r="C94" s="5">
-        <v>46181.51119900463</v>
+        <v>46181.6778656713</v>
       </c>
       <c r="D94" s="5">
-        <v>46181.511212060184</v>
+        <v>46181.677878726856</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>306</v>
@@ -7289,13 +7289,13 @@
         <v>307</v>
       </c>
       <c r="B95" s="8">
-        <v>46160.48622303241</v>
+        <v>46160.65288969908</v>
       </c>
       <c r="C95" s="8">
-        <v>46181.51117568287</v>
+        <v>46181.67784234954</v>
       </c>
       <c r="D95" s="8">
-        <v>46181.51117745371</v>
+        <v>46181.67784412037</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>218</v>
@@ -7344,13 +7344,13 @@
         <v>310</v>
       </c>
       <c r="B96" s="5">
-        <v>46160.48622869213</v>
+        <v>46160.6528953588</v>
       </c>
       <c r="C96" s="5">
-        <v>46181.511182581016</v>
+        <v>46181.67784924769</v>
       </c>
       <c r="D96" s="5">
-        <v>46181.51118395833</v>
+        <v>46181.677850625</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>218</v>
@@ -7399,13 +7399,13 @@
         <v>311</v>
       </c>
       <c r="B97" s="8">
-        <v>46160.48623403935</v>
+        <v>46160.652900706016</v>
       </c>
       <c r="C97" s="8">
-        <v>46181.5112519213</v>
+        <v>46181.677918587964</v>
       </c>
       <c r="D97" s="8">
-        <v>46181.51126422454</v>
+        <v>46181.67793089121</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>312</v>
@@ -7464,13 +7464,13 @@
         <v>313</v>
       </c>
       <c r="B98" s="5">
-        <v>46160.48623902778</v>
+        <v>46160.65290569444</v>
       </c>
       <c r="C98" s="5">
-        <v>46181.51122587963</v>
+        <v>46181.6778925463</v>
       </c>
       <c r="D98" s="5">
-        <v>46181.51122771991</v>
+        <v>46181.67789438658</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>218</v>
@@ -7519,13 +7519,13 @@
         <v>315</v>
       </c>
       <c r="B99" s="8">
-        <v>46160.48624449074</v>
+        <v>46160.652911157405</v>
       </c>
       <c r="C99" s="8">
-        <v>46181.511236307866</v>
+        <v>46181.67790297454</v>
       </c>
       <c r="D99" s="8">
-        <v>46181.51123834491</v>
+        <v>46181.67790501157</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>218</v>
@@ -7574,11 +7574,11 @@
         <v>316</v>
       </c>
       <c r="B100" s="5">
-        <v>46160.48624990741</v>
+        <v>46160.65291657408</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46160.65071959491</v>
+        <v>46160.81738626157</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>317</v>
@@ -7637,11 +7637,11 @@
         <v>319</v>
       </c>
       <c r="B101" s="8">
-        <v>46160.48625489583</v>
+        <v>46160.652921562505</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46160.65071988426</v>
+        <v>46160.81738655093</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>218</v>
@@ -7688,11 +7688,11 @@
         <v>321</v>
       </c>
       <c r="B102" s="5">
-        <v>46160.486259537036</v>
+        <v>46160.65292620371</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46160.650720624995</v>
+        <v>46160.81738729167</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>218</v>
@@ -7739,11 +7739,11 @@
         <v>323</v>
       </c>
       <c r="B103" s="8">
-        <v>46160.48626417824</v>
+        <v>46160.65293084491</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46181.51174920139</v>
+        <v>46181.67841586805</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>324</v>
@@ -7786,11 +7786,11 @@
         <v>326</v>
       </c>
       <c r="B104" s="5">
-        <v>46160.48626765046</v>
+        <v>46160.65293431713</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46181.511745254626</v>
+        <v>46181.6784119213</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>327</v>
@@ -7849,11 +7849,11 @@
         <v>331</v>
       </c>
       <c r="B105" s="8">
-        <v>46160.48627299769</v>
+        <v>46160.65293966435</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46160.6510640625</v>
+        <v>46160.81773072916</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>218</v>
@@ -7902,11 +7902,11 @@
         <v>333</v>
       </c>
       <c r="B106" s="5">
-        <v>46160.48627753472</v>
+        <v>46160.652944201385</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46160.651064722224</v>
+        <v>46160.81773138889</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>218</v>
@@ -7955,11 +7955,11 @@
         <v>335</v>
       </c>
       <c r="B107" s="8">
-        <v>46160.64149819444</v>
+        <v>46160.80816486111</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46160.65106541666</v>
+        <v>46160.817732083335</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>336</v>
@@ -8008,11 +8008,11 @@
         <v>338</v>
       </c>
       <c r="B108" s="5">
-        <v>46160.641878587965</v>
+        <v>46160.80854525463</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46160.65106607639</v>
+        <v>46160.81773274306</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>336</v>
@@ -8061,11 +8061,11 @@
         <v>340</v>
       </c>
       <c r="B109" s="8">
-        <v>46160.486281840276</v>
+        <v>46160.65294850695</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46181.511733611114</v>
+        <v>46181.67840027778</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>341</v>
@@ -8124,11 +8124,11 @@
         <v>343</v>
       </c>
       <c r="B110" s="5">
-        <v>46160.48628592593</v>
+        <v>46160.652952592594</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46160.65133898148</v>
+        <v>46160.81800564815</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>218</v>
@@ -8177,11 +8177,11 @@
         <v>345</v>
       </c>
       <c r="B111" s="8">
-        <v>46160.48629032407</v>
+        <v>46160.65295699074</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46160.65133636574</v>
+        <v>46160.81800303241</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>218</v>
@@ -8230,11 +8230,11 @@
         <v>346</v>
       </c>
       <c r="B112" s="5">
-        <v>46160.642455497684</v>
+        <v>46160.809122164355</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46160.65133309028</v>
+        <v>46160.817999756946</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>336</v>
@@ -8283,11 +8283,11 @@
         <v>348</v>
       </c>
       <c r="B113" s="8">
-        <v>46160.64247096065</v>
+        <v>46160.809137627315</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46160.6513296875</v>
+        <v>46160.81799635416</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>349</v>
@@ -8336,11 +8336,11 @@
         <v>350</v>
       </c>
       <c r="B114" s="5">
-        <v>46160.48629453704</v>
+        <v>46160.652961203705</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46181.51172226852</v>
+        <v>46181.67838893519</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>351</v>
@@ -8399,11 +8399,11 @@
         <v>353</v>
       </c>
       <c r="B115" s="8">
-        <v>46160.48629865741</v>
+        <v>46160.65296532407</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46160.65164520833</v>
+        <v>46160.818311875</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>218</v>
@@ -8448,11 +8448,11 @@
         <v>355</v>
       </c>
       <c r="B116" s="5">
-        <v>46160.48630600695</v>
+        <v>46160.65297267361</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46160.65164244213</v>
+        <v>46160.8183091088</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>218</v>
@@ -8497,11 +8497,11 @@
         <v>357</v>
       </c>
       <c r="B117" s="8">
-        <v>46160.644220671296</v>
+        <v>46160.81088733797</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46160.65163960648</v>
+        <v>46160.81830627315</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>336</v>
@@ -8546,11 +8546,11 @@
         <v>359</v>
       </c>
       <c r="B118" s="5">
-        <v>46160.64422939815</v>
+        <v>46160.81089606481</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46160.651635347225</v>
+        <v>46160.81830201389</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>336</v>
@@ -8595,11 +8595,11 @@
         <v>360</v>
       </c>
       <c r="B119" s="8">
-        <v>46160.48631179398</v>
+        <v>46160.65297846065</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46183.72898115741</v>
+        <v>46183.89564782407</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>361</v>
@@ -8658,11 +8658,11 @@
         <v>363</v>
       </c>
       <c r="B120" s="5">
-        <v>46160.486317268515</v>
+        <v>46160.652983935186</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46160.65204771991</v>
+        <v>46160.81871438657</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>218</v>
@@ -8711,11 +8711,11 @@
         <v>364</v>
       </c>
       <c r="B121" s="8">
-        <v>46160.48632146991</v>
+        <v>46160.65298813657</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46160.652045069444</v>
+        <v>46160.81871173611</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>218</v>
@@ -8764,11 +8764,11 @@
         <v>365</v>
       </c>
       <c r="B122" s="5">
-        <v>46160.64549171296</v>
+        <v>46160.81215837963</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46160.65204233796</v>
+        <v>46160.81870900463</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>336</v>
@@ -8817,11 +8817,11 @@
         <v>366</v>
       </c>
       <c r="B123" s="8">
-        <v>46160.645541018515</v>
+        <v>46160.81220768519</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46160.6520385301</v>
+        <v>46160.818705196754</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>336</v>
@@ -8870,11 +8870,11 @@
         <v>367</v>
       </c>
       <c r="B124" s="5">
-        <v>46160.486358877315</v>
+        <v>46160.65302554399</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46160.65262292824</v>
+        <v>46160.8192895949</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>368</v>
@@ -8917,11 +8917,11 @@
         <v>370</v>
       </c>
       <c r="B125" s="8">
-        <v>46160.48636229167</v>
+        <v>46160.65302895833</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46160.65253305556</v>
+        <v>46160.819199722224</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>371</v>
@@ -8980,11 +8980,11 @@
         <v>374</v>
       </c>
       <c r="B126" s="5">
-        <v>46160.486367199075</v>
+        <v>46160.65303386574</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46160.652711284725</v>
+        <v>46160.81937795139</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>375</v>
@@ -9043,11 +9043,11 @@
         <v>377</v>
       </c>
       <c r="B127" s="8">
-        <v>46160.49142284722</v>
+        <v>46160.65808951389</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46160.65314284722</v>
+        <v>46160.819809513894</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>378</v>
@@ -9096,11 +9096,11 @@
         <v>380</v>
       </c>
       <c r="B128" s="5">
-        <v>46160.49428493055</v>
+        <v>46160.66095159722</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46160.65305790509</v>
+        <v>46160.81972457176</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>381</v>
@@ -9159,11 +9159,11 @@
         <v>383</v>
       </c>
       <c r="B129" s="8">
-        <v>46160.494408715276</v>
+        <v>46160.66107538194</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46160.653279942126</v>
+        <v>46160.8199466088</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>384</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -5938,7 +5938,7 @@
         <v>46181.677226064814</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.67723771991</v>
+        <v>46188.17617141204</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5982,8 +5982,8 @@
       <c r="R72" s="5">
         <v>46195</v>
       </c>
-      <c r="S72" s="10" t="s">
-        <v>32</v>
+      <c r="S72" s="12" t="s">
+        <v>251</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -507,6 +507,9 @@
     <t>Generación OC ot 4314 ,fabricación tableros  ot 4314</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214889077215097</t>
   </si>
   <si>
@@ -802,9 +805,6 @@
   </si>
   <si>
     <t>OT2 4232 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46185.70494256944</v>
+        <v>46189.16763457176</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>150</v>
@@ -3966,8 +3966,8 @@
       <c r="R38" s="5">
         <v>46196</v>
       </c>
-      <c r="S38" s="10" t="s">
-        <v>32</v>
+      <c r="S38" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
@@ -3978,7 +3978,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B39" s="8">
         <v>46160.65676351852</v>
@@ -4023,7 +4023,7 @@
         <v>112</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4033,7 +4033,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B40" s="5">
         <v>46160.65688415509</v>
@@ -4043,7 +4043,7 @@
         <v>46182.67674758102</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4076,7 +4076,7 @@
         <v>113</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4086,7 +4086,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B41" s="8">
         <v>46160.65247015047</v>
@@ -4098,16 +4098,16 @@
         <v>46181.676244386574</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I41" s="8">
         <v>46167</v>
@@ -4128,7 +4128,7 @@
         <v>115</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P41" s="9" t="s">
         <v>115</v>
@@ -4151,7 +4151,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B42" s="5">
         <v>46160.65247482639</v>
@@ -4163,16 +4163,16 @@
         <v>46181.67615008102</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I42" s="5">
         <v>46167</v>
@@ -4190,13 +4190,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>96</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4212,7 +4212,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B43" s="8">
         <v>46160.65247959491</v>
@@ -4224,16 +4224,16 @@
         <v>46181.67622016204</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I43" s="8">
         <v>46169</v>
@@ -4251,13 +4251,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4273,7 +4273,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B44" s="5">
         <v>46160.65254070602</v>
@@ -4285,16 +4285,16 @@
         <v>46181.67636662037</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I44" s="5">
         <v>46167</v>
@@ -4315,7 +4315,7 @@
         <v>115</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4338,7 +4338,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B45" s="8">
         <v>46160.65254572917</v>
@@ -4356,10 +4356,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I45" s="8">
         <v>46167</v>
@@ -4377,13 +4377,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>103</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4393,7 +4393,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B46" s="5">
         <v>46160.652551377316</v>
@@ -4405,16 +4405,16 @@
         <v>46181.67634090278</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I46" s="5">
         <v>46169</v>
@@ -4432,13 +4432,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>104</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B47" s="8">
         <v>46160.652557152775</v>
@@ -4460,16 +4460,16 @@
         <v>46181.67649172454</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4490,7 +4490,7 @@
         <v>115</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4513,7 +4513,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B48" s="5">
         <v>46160.65256162037</v>
@@ -4531,10 +4531,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4552,13 +4552,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4568,7 +4568,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B49" s="8">
         <v>46160.6525734375</v>
@@ -4580,16 +4580,16 @@
         <v>46181.67642934028</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I49" s="8">
         <v>46176</v>
@@ -4607,13 +4607,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>110</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4623,7 +4623,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46160.652579236106</v>
@@ -4635,16 +4635,16 @@
         <v>46181.676467303245</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I50" s="5">
         <v>46205</v>
@@ -4662,10 +4662,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B51" s="8">
         <v>46160.65258304398</v>
@@ -4690,16 +4690,16 @@
         <v>46181.67657885417</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I51" s="8">
         <v>46167</v>
@@ -4720,7 +4720,7 @@
         <v>115</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>26</v>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B52" s="5">
         <v>46160.6525875463</v>
@@ -4761,10 +4761,10 @@
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I52" s="5">
         <v>46167</v>
@@ -4782,13 +4782,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>106</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B53" s="8">
         <v>46160.652593067134</v>
@@ -4810,16 +4810,16 @@
         <v>46181.676553680554</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I53" s="8">
         <v>46169</v>
@@ -4837,13 +4837,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>107</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4853,7 +4853,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B54" s="5">
         <v>46160.65225516204</v>
@@ -4865,7 +4865,7 @@
         <v>46181.67858451389</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>25</v>
@@ -4889,7 +4889,7 @@
         <v>26</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>26</v>
@@ -4902,7 +4902,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="8">
         <v>46160.65259921296</v>
@@ -4914,16 +4914,16 @@
         <v>46181.61234585648</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I55" s="8">
         <v>46140</v>
@@ -4941,13 +4941,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>75</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q55" s="8">
         <v>46140</v>
@@ -4967,7 +4967,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46160.652606006945</v>
@@ -4979,16 +4979,16 @@
         <v>46181.67573824074</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I56" s="5">
         <v>46153</v>
@@ -5006,13 +5006,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46153</v>
@@ -5032,7 +5032,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46160.65261409723</v>
@@ -5050,10 +5050,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I57" s="8">
         <v>46160</v>
@@ -5071,13 +5071,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q57" s="8">
         <v>46160</v>
@@ -5097,7 +5097,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46160.652630983794</v>
@@ -5107,16 +5107,16 @@
         <v>46184.89687363426</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I58" s="5">
         <v>46210</v>
@@ -5134,10 +5134,10 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5160,7 +5160,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B59" s="8">
         <v>46160.65263532408</v>
@@ -5170,16 +5170,16 @@
         <v>46181.67790076389</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I59" s="8">
         <v>46210</v>
@@ -5197,13 +5197,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5213,7 +5213,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B60" s="5">
         <v>46160.65264069445</v>
@@ -5223,16 +5223,16 @@
         <v>46181.67791322917</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="I60" s="5">
         <v>46210</v>
@@ -5250,13 +5250,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5266,7 +5266,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
         <v>46160.652676921294</v>
@@ -5278,7 +5278,7 @@
         <v>46181.67816971065</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5302,7 +5302,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5315,7 +5315,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46160.65268083333</v>
@@ -5327,16 +5327,16 @@
         <v>46182.19861893519</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I62" s="5">
         <v>46178</v>
@@ -5354,13 +5354,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q62" s="5">
         <v>46178</v>
@@ -5380,7 +5380,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B63" s="8">
         <v>46160.652685810186</v>
@@ -5392,16 +5392,16 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I63" s="8">
         <v>46182</v>
@@ -5419,13 +5419,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q63" s="8">
         <v>46182</v>
@@ -5445,7 +5445,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B64" s="5">
         <v>46160.65269097222</v>
@@ -5457,16 +5457,16 @@
         <v>46181.6766224537</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I64" s="5">
         <v>46178</v>
@@ -5484,13 +5484,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q64" s="5">
         <v>46147</v>
@@ -5510,7 +5510,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B65" s="8">
         <v>46160.65269633102</v>
@@ -5522,16 +5522,16 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I65" s="8">
         <v>46182</v>
@@ -5549,13 +5549,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q65" s="8">
         <v>46182</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5">
         <v>46160.65269980324</v>
@@ -5587,16 +5587,16 @@
         <v>46181.67666866898</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I66" s="5">
         <v>46178</v>
@@ -5614,13 +5614,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q66" s="5">
         <v>46147</v>
@@ -5640,7 +5640,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B67" s="8">
         <v>46160.652703935186</v>
@@ -5652,16 +5652,16 @@
         <v>46184.172129004626</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I67" s="8">
         <v>46182</v>
@@ -5679,13 +5679,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q67" s="8">
         <v>46182</v>
@@ -5705,7 +5705,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B68" s="5">
         <v>46160.65270767361</v>
@@ -5717,7 +5717,7 @@
         <v>46181.6781084838</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5741,7 +5741,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5754,7 +5754,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B69" s="8">
         <v>46160.65271061343</v>
@@ -5763,19 +5763,19 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.67713355324</v>
+        <v>46189.195743599535</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I69" s="8">
         <v>46184</v>
@@ -5793,13 +5793,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q69" s="8">
         <v>46184</v>
@@ -5807,8 +5807,8 @@
       <c r="R69" s="8">
         <v>46188</v>
       </c>
-      <c r="S69" s="12" t="s">
-        <v>251</v>
+      <c r="S69" s="11" t="s">
+        <v>101</v>
       </c>
       <c r="T69" s="9">
         <v>1</v>
@@ -5831,16 +5831,16 @@
         <v>46181.67713434028</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I70" s="5">
         <v>46184</v>
@@ -5858,7 +5858,7 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>253</v>
@@ -5886,16 +5886,16 @@
         <v>46181.67713509259</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I71" s="8">
         <v>46184</v>
@@ -5913,7 +5913,7 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>256</v>
@@ -5947,10 +5947,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I72" s="5">
         <v>46189</v>
@@ -5968,13 +5968,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>260</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q72" s="5">
         <v>46189</v>
@@ -5983,7 +5983,7 @@
         <v>46195</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>251</v>
+        <v>152</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6006,16 +6006,16 @@
         <v>46181.67719854167</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I73" s="8">
         <v>46189</v>
@@ -6067,10 +6067,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I74" s="5">
         <v>46189</v>
@@ -6113,7 +6113,7 @@
         <v>46181.67728712963</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.677299710645</v>
+        <v>46189.167635439815</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>266</v>
@@ -6122,10 +6122,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I75" s="8">
         <v>46196</v>
@@ -6143,13 +6143,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q75" s="8">
         <v>46196</v>
@@ -6157,8 +6157,8 @@
       <c r="R75" s="8">
         <v>46196</v>
       </c>
-      <c r="S75" s="10" t="s">
-        <v>32</v>
+      <c r="S75" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="T75" s="9">
         <v>1</v>
@@ -6181,16 +6181,16 @@
         <v>46181.67726512731</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I76" s="5">
         <v>46196</v>
@@ -6236,16 +6236,16 @@
         <v>46181.677274664355</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I77" s="8">
         <v>46196</v>
@@ -6291,7 +6291,7 @@
         <v>46181.67751854166</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6346,10 +6346,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I79" s="8">
         <v>46160</v>
@@ -6367,7 +6367,7 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O79" s="9" t="s">
         <v>135</v>
@@ -6382,7 +6382,7 @@
         <v>46191</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>251</v>
+        <v>152</v>
       </c>
       <c r="T79" s="9">
         <v>1</v>
@@ -6411,10 +6411,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I80" s="5">
         <v>46141</v>
@@ -6432,7 +6432,7 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>126</v>
@@ -6476,10 +6476,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I81" s="8">
         <v>46174</v>
@@ -6497,13 +6497,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>144</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q81" s="8">
         <v>46174</v>
@@ -6541,10 +6541,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I82" s="5">
         <v>46206</v>
@@ -6562,10 +6562,10 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>283</v>
@@ -6604,10 +6604,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I83" s="8">
         <v>46197</v>
@@ -6625,10 +6625,10 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>58</v>
@@ -6777,7 +6777,7 @@
         <v>46181.67767618055</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6832,7 +6832,7 @@
         <v>46181.677689247685</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6917,7 +6917,7 @@
         <v>286</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>286</v>
@@ -6952,7 +6952,7 @@
         <v>46181.67774287037</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -7007,7 +7007,7 @@
         <v>46181.67775488426</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7092,7 +7092,7 @@
         <v>286</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>286</v>
@@ -7127,7 +7127,7 @@
         <v>46181.677797627315</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7180,7 +7180,7 @@
         <v>46181.67780725694</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7263,7 +7263,7 @@
         <v>286</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>286</v>
@@ -7298,7 +7298,7 @@
         <v>46181.67784412037</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7353,7 +7353,7 @@
         <v>46181.677850625</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7438,7 +7438,7 @@
         <v>286</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P97" s="9" t="s">
         <v>286</v>
@@ -7473,7 +7473,7 @@
         <v>46181.67789438658</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7503,7 +7503,7 @@
         <v>312</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P98" s="6" t="s">
         <v>314</v>
@@ -7528,7 +7528,7 @@
         <v>46181.67790501157</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7558,7 +7558,7 @@
         <v>312</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>314</v>
@@ -7611,7 +7611,7 @@
         <v>286</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>318</v>
@@ -7644,7 +7644,7 @@
         <v>46160.81738655093</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7672,7 +7672,7 @@
         <v>317</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P101" s="9" t="s">
         <v>320</v>
@@ -7695,7 +7695,7 @@
         <v>46160.81738729167</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7723,7 +7723,7 @@
         <v>317</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>322</v>
@@ -7856,7 +7856,7 @@
         <v>46160.81773072916</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7886,7 +7886,7 @@
         <v>327</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>332</v>
@@ -7909,7 +7909,7 @@
         <v>46160.81773138889</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7939,7 +7939,7 @@
         <v>327</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P106" s="6" t="s">
         <v>334</v>
@@ -8131,7 +8131,7 @@
         <v>46160.81800564815</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8161,7 +8161,7 @@
         <v>341</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>344</v>
@@ -8184,7 +8184,7 @@
         <v>46160.81800303241</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8214,7 +8214,7 @@
         <v>341</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>344</v>
@@ -8349,10 +8349,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I114" s="5">
         <v>46216</v>
@@ -8406,16 +8406,16 @@
         <v>46160.818311875</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="9"/>
@@ -8432,7 +8432,7 @@
         <v>351</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>354</v>
@@ -8455,16 +8455,16 @@
         <v>46160.8183091088</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="6"/>
@@ -8481,7 +8481,7 @@
         <v>351</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>356</v>
@@ -8510,10 +8510,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="9"/>
@@ -8559,10 +8559,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
@@ -8608,10 +8608,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I119" s="8">
         <v>46217</v>
@@ -8665,16 +8665,16 @@
         <v>46160.81871438657</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I120" s="5">
         <v>46217</v>
@@ -8695,7 +8695,7 @@
         <v>361</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>361</v>
@@ -8718,16 +8718,16 @@
         <v>46160.81871173611</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I121" s="8">
         <v>46217</v>
@@ -8748,7 +8748,7 @@
         <v>361</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>361</v>
@@ -8777,10 +8777,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I122" s="5">
         <v>46217</v>
@@ -8830,10 +8830,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I123" s="8">
         <v>46217</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -6595,7 +6595,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46181.618521145836</v>
+        <v>46190.17135600695</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>61</v>
@@ -6639,8 +6639,8 @@
       <c r="R83" s="8">
         <v>46197</v>
       </c>
-      <c r="S83" s="10" t="s">
-        <v>32</v>
+      <c r="S83" s="12" t="s">
+        <v>152</v>
       </c>
       <c r="T83" s="9">
         <v>0</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -234,6 +234,9 @@
     <t>Coordinacion Entrega con Cliente,Ingenieria Servicios ,OT 4314 - VDF VLT  FC 102,OT 4314 - VDF VLT  FC 102</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1214892476594829</t>
   </si>
   <si>
@@ -505,9 +508,6 @@
   </si>
   <si>
     <t>Generación OC ot 4314 ,fabricación tableros  ot 4314</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214889077215097</t>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46160.813948194445</v>
+        <v>46191.18605898148</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2360,8 +2360,8 @@
       <c r="R12" s="5">
         <v>46198</v>
       </c>
-      <c r="S12" s="10" t="s">
-        <v>32</v>
+      <c r="S12" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="T12" s="6">
         <v>0</v>
@@ -2372,7 +2372,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B13" s="8">
         <v>46160.65224207176</v>
@@ -2382,7 +2382,7 @@
         <v>46167.55894045139</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2406,7 +2406,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B14" s="5">
         <v>46160.6523665162</v>
@@ -2431,7 +2431,7 @@
         <v>46167.55893438657</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2452,19 +2452,19 @@
         <v>26</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>42</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q14" s="5">
         <v>46129</v>
@@ -2484,7 +2484,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15" s="8">
         <v>46160.65237170139</v>
@@ -2496,7 +2496,7 @@
         <v>46167.55894241898</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2517,19 +2517,19 @@
         <v>26</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>42</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="8">
         <v>46129</v>
@@ -2549,7 +2549,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B16" s="5">
         <v>46160.652376875005</v>
@@ -2561,7 +2561,7 @@
         <v>46167.55894754629</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2588,13 +2588,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>42</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="Q16" s="5">
         <v>46129</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B17" s="8">
         <v>46160.652382002314</v>
@@ -2624,7 +2624,7 @@
         <v>46167.55894179398</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -2651,13 +2651,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q17" s="8">
         <v>46129</v>
@@ -2672,12 +2672,12 @@
         <v>0</v>
       </c>
       <c r="U17" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B18" s="5">
         <v>46160.65224614584</v>
@@ -2689,7 +2689,7 @@
         <v>46181.678702233796</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>25</v>
@@ -2713,7 +2713,7 @@
         <v>26</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>26</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B19" s="8">
         <v>46160.652389560186</v>
@@ -2738,7 +2738,7 @@
         <v>46167.55897762731</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2765,13 +2765,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q19" s="8">
         <v>46133</v>
@@ -2791,7 +2791,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" s="5">
         <v>46160.65239491899</v>
@@ -2803,7 +2803,7 @@
         <v>46167.55901266204</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -2830,13 +2830,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q20" s="5">
         <v>46133</v>
@@ -2856,7 +2856,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B21" s="8">
         <v>46160.65240028936</v>
@@ -2868,16 +2868,16 @@
         <v>46181.61226466435</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I21" s="8">
         <v>46133</v>
@@ -2895,13 +2895,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q21" s="8">
         <v>46133</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B22" s="5">
         <v>46160.652405636574</v>
@@ -2933,16 +2933,16 @@
         <v>46181.67578979167</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I22" s="5">
         <v>46162</v>
@@ -2960,13 +2960,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -2975,18 +2975,18 @@
         <v>46164</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
       </c>
       <c r="U22" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B23" s="8">
         <v>46160.65241059028</v>
@@ -2998,16 +2998,16 @@
         <v>46181.67583789352</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I23" s="8">
         <v>46162</v>
@@ -3025,13 +3025,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q23" s="8">
         <v>46162</v>
@@ -3040,7 +3040,7 @@
         <v>46164</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T23" s="9">
         <v>1</v>
@@ -3051,7 +3051,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B24" s="5">
         <v>46160.652414490745</v>
@@ -3063,16 +3063,16 @@
         <v>46181.67587553241</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I24" s="5">
         <v>46162</v>
@@ -3090,13 +3090,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q24" s="5">
         <v>46162</v>
@@ -3105,7 +3105,7 @@
         <v>46164</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T24" s="6">
         <v>1</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B25" s="8">
         <v>46160.65241840278</v>
@@ -3128,16 +3128,16 @@
         <v>46181.67588775463</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I25" s="8">
         <v>46162</v>
@@ -3155,13 +3155,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q25" s="8">
         <v>46162</v>
@@ -3170,7 +3170,7 @@
         <v>46164</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T25" s="9">
         <v>1</v>
@@ -3181,7 +3181,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B26" s="5">
         <v>46160.65857868055</v>
@@ -3193,7 +3193,7 @@
         <v>46167.55904253472</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3220,13 +3220,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>53</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q26" s="5">
         <v>46134</v>
@@ -3246,7 +3246,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B27" s="8">
         <v>46160.65225063657</v>
@@ -3256,7 +3256,7 @@
         <v>46181.678639652775</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -3280,7 +3280,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>26</v>
@@ -3293,7 +3293,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B28" s="5">
         <v>46160.65242274306</v>
@@ -3305,16 +3305,16 @@
         <v>46181.675709143514</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I28" s="5">
         <v>46135</v>
@@ -3332,13 +3332,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q28" s="5">
         <v>46135</v>
@@ -3358,7 +3358,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B29" s="8">
         <v>46160.65242719908</v>
@@ -3370,16 +3370,16 @@
         <v>46181.67563449074</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I29" s="8">
         <v>46135</v>
@@ -3397,13 +3397,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B30" s="5">
         <v>46160.65243181713</v>
@@ -3431,16 +3431,16 @@
         <v>46181.67567790509</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I30" s="5">
         <v>46139</v>
@@ -3458,13 +3458,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3480,7 +3480,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B31" s="8">
         <v>46160.65243667824</v>
@@ -3492,16 +3492,16 @@
         <v>46181.67562327546</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I31" s="8">
         <v>46135</v>
@@ -3519,13 +3519,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q31" s="8">
         <v>46135</v>
@@ -3545,7 +3545,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B32" s="5">
         <v>46160.65244107639</v>
@@ -3557,16 +3557,16 @@
         <v>46181.67555395833</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I32" s="5">
         <v>46135</v>
@@ -3584,13 +3584,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3606,7 +3606,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B33" s="8">
         <v>46160.65244578704</v>
@@ -3618,16 +3618,16 @@
         <v>46181.67559840278</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I33" s="8">
         <v>46139</v>
@@ -3645,13 +3645,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3667,7 +3667,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B34" s="5">
         <v>46160.652450625</v>
@@ -3679,16 +3679,16 @@
         <v>46181.67549369213</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I34" s="5">
         <v>46133</v>
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q34" s="5">
         <v>46133</v>
@@ -3721,7 +3721,7 @@
         <v>46171</v>
       </c>
       <c r="S34" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T34" s="6">
         <v>1</v>
@@ -3732,7 +3732,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B35" s="8">
         <v>46160.65245552083</v>
@@ -3744,16 +3744,16 @@
         <v>46181.67541268519</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I35" s="8">
         <v>46133</v>
@@ -3771,13 +3771,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B36" s="5">
         <v>46160.65246048611</v>
@@ -3805,16 +3805,16 @@
         <v>46181.67545391204</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I36" s="5">
         <v>46142</v>
@@ -3832,13 +3832,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3854,7 +3854,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B37" s="8">
         <v>46160.6524655324</v>
@@ -3866,16 +3866,16 @@
         <v>46181.67546648148</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I37" s="8">
         <v>46141</v>
@@ -3893,13 +3893,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B38" s="5">
         <v>46160.6566696875</v>
@@ -3925,16 +3925,16 @@
         <v>46189.16763457176</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I38" s="5">
         <v>46136</v>
@@ -3952,10 +3952,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3967,7 +3967,7 @@
         <v>46196</v>
       </c>
       <c r="S38" s="12" t="s">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
@@ -3990,16 +3990,16 @@
         <v>46182.67674333333</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I39" s="8">
         <v>46136</v>
@@ -4017,10 +4017,10 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P39" s="9" t="s">
         <v>154</v>
@@ -4049,10 +4049,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I40" s="5">
         <v>46148</v>
@@ -4070,10 +4070,10 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>157</v>
@@ -4125,13 +4125,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>162</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q41" s="8">
         <v>46167</v>
@@ -4140,7 +4140,7 @@
         <v>46177</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -4193,7 +4193,7 @@
         <v>159</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>165</v>
@@ -4312,7 +4312,7 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>171</v>
@@ -4327,7 +4327,7 @@
         <v>46177</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4350,7 +4350,7 @@
         <v>46181.67630162037</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4380,7 +4380,7 @@
         <v>170</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>173</v>
@@ -4435,7 +4435,7 @@
         <v>170</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>176</v>
@@ -4487,7 +4487,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>181</v>
@@ -4525,7 +4525,7 @@
         <v>46181.67638900463</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4555,7 +4555,7 @@
         <v>178</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>183</v>
@@ -4610,7 +4610,7 @@
         <v>178</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>186</v>
@@ -4717,7 +4717,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>193</v>
@@ -4732,7 +4732,7 @@
         <v>46177</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T51" s="9">
         <v>1</v>
@@ -4755,7 +4755,7 @@
         <v>46181.67651314815</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4785,7 +4785,7 @@
         <v>192</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>195</v>
@@ -4840,7 +4840,7 @@
         <v>192</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>198</v>
@@ -4944,7 +4944,7 @@
         <v>200</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>206</v>
@@ -5044,7 +5044,7 @@
         <v>46181.67578048611</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5086,7 +5086,7 @@
         <v>46161</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T57" s="9">
         <v>1</v>
@@ -5369,7 +5369,7 @@
         <v>46181</v>
       </c>
       <c r="S62" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
@@ -5434,7 +5434,7 @@
         <v>46183</v>
       </c>
       <c r="S63" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T63" s="9">
         <v>1</v>
@@ -5564,7 +5564,7 @@
         <v>46183</v>
       </c>
       <c r="S65" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T65" s="9">
         <v>1</v>
@@ -5694,7 +5694,7 @@
         <v>46183</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>
@@ -5808,7 +5808,7 @@
         <v>46188</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T69" s="9">
         <v>1</v>
@@ -5983,7 +5983,7 @@
         <v>46195</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6158,7 +6158,7 @@
         <v>46196</v>
       </c>
       <c r="S75" s="12" t="s">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="T75" s="9">
         <v>1</v>
@@ -6370,7 +6370,7 @@
         <v>224</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>276</v>
@@ -6382,7 +6382,7 @@
         <v>46191</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="T79" s="9">
         <v>1</v>
@@ -6435,7 +6435,7 @@
         <v>224</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>276</v>
@@ -6500,7 +6500,7 @@
         <v>224</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>234</v>
@@ -6512,7 +6512,7 @@
         <v>46174</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>
@@ -6640,7 +6640,7 @@
         <v>46197</v>
       </c>
       <c r="S83" s="12" t="s">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="T83" s="9">
         <v>0</v>
@@ -6718,10 +6718,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6783,10 +6783,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I86" s="5">
         <v>46197</v>
@@ -6838,10 +6838,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I87" s="8">
         <v>46197</v>
@@ -6893,10 +6893,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I88" s="5">
         <v>46204</v>
@@ -6958,10 +6958,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I89" s="8">
         <v>46204</v>
@@ -7013,10 +7013,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I90" s="5">
         <v>46204</v>
@@ -7068,10 +7068,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I91" s="8">
         <v>46205</v>
@@ -7133,10 +7133,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -7186,10 +7186,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="8">
@@ -7239,10 +7239,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I94" s="5">
         <v>46206</v>
@@ -7304,10 +7304,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I95" s="8">
         <v>46206</v>
@@ -7359,10 +7359,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I96" s="5">
         <v>46206</v>
@@ -7414,10 +7414,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I97" s="8">
         <v>46209</v>
@@ -7479,10 +7479,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I98" s="5">
         <v>46209</v>
@@ -7534,10 +7534,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I99" s="8">
         <v>46209</v>
@@ -7587,10 +7587,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I100" s="5">
         <v>46211</v>
@@ -7650,10 +7650,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="8">
@@ -7701,10 +7701,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I102" s="6"/>
       <c r="J102" s="5">
@@ -8074,10 +8074,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I109" s="8">
         <v>46213</v>
@@ -8137,10 +8137,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I110" s="5">
         <v>46213</v>
@@ -8190,10 +8190,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I111" s="8">
         <v>46213</v>
@@ -8243,10 +8243,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I112" s="5">
         <v>46213</v>
@@ -8296,10 +8296,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I113" s="8">
         <v>46213</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -6337,7 +6337,7 @@
         <v>46181.67731516204</v>
       </c>
       <c r="D79" s="8">
-        <v>46184.202785092595</v>
+        <v>46192.20460657407</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>275</v>
@@ -6381,8 +6381,8 @@
       <c r="R79" s="8">
         <v>46191</v>
       </c>
-      <c r="S79" s="12" t="s">
-        <v>63</v>
+      <c r="S79" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="T79" s="9">
         <v>1</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -8340,7 +8340,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46181.67838893519</v>
+        <v>46194.05666876158</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>351</v>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46160.818311875</v>
+        <v>46194.05454135417</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>219</v>
@@ -8418,7 +8418,9 @@
         <v>250</v>
       </c>
       <c r="I115" s="9"/>
-      <c r="J115" s="9"/>
+      <c r="J115" s="8">
+        <v>46216</v>
+      </c>
       <c r="K115" s="9" t="s">
         <v>26</v>
       </c>
@@ -8452,7 +8454,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46160.8183091088</v>
+        <v>46194.054542060185</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>219</v>
@@ -8467,7 +8469,9 @@
         <v>250</v>
       </c>
       <c r="I116" s="6"/>
-      <c r="J116" s="6"/>
+      <c r="J116" s="5">
+        <v>46216</v>
+      </c>
       <c r="K116" s="6" t="s">
         <v>26</v>
       </c>
@@ -8501,7 +8505,7 @@
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46160.81830627315</v>
+        <v>46194.05454275463</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>336</v>
@@ -8516,7 +8520,9 @@
         <v>250</v>
       </c>
       <c r="I117" s="9"/>
-      <c r="J117" s="9"/>
+      <c r="J117" s="8">
+        <v>46216</v>
+      </c>
       <c r="K117" s="9" t="s">
         <v>26</v>
       </c>
@@ -8550,7 +8556,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46160.81830201389</v>
+        <v>46194.05454344908</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>336</v>
@@ -8565,7 +8571,9 @@
         <v>250</v>
       </c>
       <c r="I118" s="6"/>
-      <c r="J118" s="6"/>
+      <c r="J118" s="5">
+        <v>46216</v>
+      </c>
       <c r="K118" s="6" t="s">
         <v>26</v>
       </c>
@@ -8662,7 +8670,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46160.81871438657</v>
+        <v>46194.054542048616</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>219</v>
@@ -8715,7 +8723,7 @@
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46160.81871173611</v>
+        <v>46194.056669247686</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>219</v>
@@ -8768,7 +8776,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46160.81870900463</v>
+        <v>46194.05454575231</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>336</v>
@@ -8821,7 +8829,7 @@
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46160.818705196754</v>
+        <v>46194.05454428241</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>336</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -3922,7 +3922,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46189.16763457176</v>
+        <v>46196.168987083336</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -4040,7 +4040,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46182.67674758102</v>
+        <v>46196.16898914352</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>156</v>
@@ -5938,7 +5938,7 @@
         <v>46181.677226064814</v>
       </c>
       <c r="D72" s="5">
-        <v>46188.17617141204</v>
+        <v>46196.198199756946</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5982,8 +5982,8 @@
       <c r="R72" s="5">
         <v>46195</v>
       </c>
-      <c r="S72" s="12" t="s">
-        <v>63</v>
+      <c r="S72" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6709,7 +6709,7 @@
         <v>46181.67760038194</v>
       </c>
       <c r="D85" s="8">
-        <v>46181.67761701389</v>
+        <v>46196.17484756945</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>289</v>
@@ -6753,8 +6753,8 @@
       <c r="R85" s="8">
         <v>46203</v>
       </c>
-      <c r="S85" s="10" t="s">
-        <v>32</v>
+      <c r="S85" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -804,7 +804,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4232 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2</t>
   </si>
   <si>
     <t>1214909353651671</t>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="385">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -3922,7 +3922,7 @@
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46196.168987083336</v>
+        <v>46197.19306372685</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3966,8 +3966,8 @@
       <c r="R38" s="5">
         <v>46196</v>
       </c>
-      <c r="S38" s="12" t="s">
-        <v>63</v>
+      <c r="S38" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>46181.67728712963</v>
       </c>
       <c r="D75" s="8">
-        <v>46189.167635439815</v>
+        <v>46197.19306369213</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>266</v>
@@ -6157,8 +6157,8 @@
       <c r="R75" s="8">
         <v>46196</v>
       </c>
-      <c r="S75" s="12" t="s">
-        <v>63</v>
+      <c r="S75" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="T75" s="9">
         <v>1</v>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46190.17135600695</v>
+        <v>46197.16928957176</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>61</v>
@@ -6660,7 +6660,7 @@
         <v>46181.617794328704</v>
       </c>
       <c r="D84" s="5">
-        <v>46181.678258518514</v>
+        <v>46197.49724974537</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>286</v>
@@ -6696,7 +6696,9 @@
       <c r="R84" s="6"/>
       <c r="S84" s="6"/>
       <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
+      <c r="U84" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
@@ -6884,7 +6886,7 @@
         <v>46181.67776662037</v>
       </c>
       <c r="D88" s="5">
-        <v>46181.6777778588</v>
+        <v>46197.19052525463</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>295</v>
@@ -6928,8 +6930,8 @@
       <c r="R88" s="5">
         <v>46204</v>
       </c>
-      <c r="S88" s="10" t="s">
-        <v>32</v>
+      <c r="S88" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="T88" s="6">
         <v>1</v>
@@ -7576,9 +7578,11 @@
       <c r="B100" s="5">
         <v>46160.65291657408</v>
       </c>
-      <c r="C100" s="6"/>
+      <c r="C100" s="5">
+        <v>46197.49723263889</v>
+      </c>
       <c r="D100" s="5">
-        <v>46160.81738626157</v>
+        <v>46197.497295243054</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>317</v>
@@ -7626,10 +7630,10 @@
         <v>32</v>
       </c>
       <c r="T100" s="6">
-        <v>0</v>
-      </c>
-      <c r="U100" s="11" t="s">
-        <v>51</v>
+        <v>1</v>
+      </c>
+      <c r="U100" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7690,9 +7694,11 @@
       <c r="B102" s="5">
         <v>46160.65292620371</v>
       </c>
-      <c r="C102" s="6"/>
+      <c r="C102" s="5">
+        <v>46197.4972891088</v>
+      </c>
       <c r="D102" s="5">
-        <v>46160.81738729167</v>
+        <v>46197.49729054398</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>219</v>
@@ -7743,7 +7749,7 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46181.67841586805</v>
+        <v>46197.49766417824</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>324</v>
@@ -7790,7 +7796,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46181.6784119213</v>
+        <v>46197.49724334491</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>327</v>
@@ -7906,7 +7912,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46160.81773138889</v>
+        <v>46197.49729465278</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>219</v>
@@ -8063,9 +8069,11 @@
       <c r="B109" s="8">
         <v>46160.65294850695</v>
       </c>
-      <c r="C109" s="9"/>
+      <c r="C109" s="8">
+        <v>46197.49765626158</v>
+      </c>
       <c r="D109" s="8">
-        <v>46181.67840027778</v>
+        <v>46197.497765231485</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>341</v>
@@ -8115,8 +8123,8 @@
       <c r="T109" s="9">
         <v>1</v>
       </c>
-      <c r="U109" s="10" t="s">
-        <v>33</v>
+      <c r="U109" s="12" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
@@ -8126,9 +8134,11 @@
       <c r="B110" s="5">
         <v>46160.652952592594</v>
       </c>
-      <c r="C110" s="6"/>
+      <c r="C110" s="5">
+        <v>46197.497369351855</v>
+      </c>
       <c r="D110" s="5">
-        <v>46160.81800564815</v>
+        <v>46197.497371261576</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>219</v>
@@ -8179,9 +8189,11 @@
       <c r="B111" s="8">
         <v>46160.65295699074</v>
       </c>
-      <c r="C111" s="9"/>
+      <c r="C111" s="8">
+        <v>46197.497530023145</v>
+      </c>
       <c r="D111" s="8">
-        <v>46160.81800303241</v>
+        <v>46197.49753173611</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>219</v>
@@ -8234,7 +8246,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46160.817999756946</v>
+        <v>46197.4977528125</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>336</v>
@@ -8287,7 +8299,7 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46160.81799635416</v>
+        <v>46197.497759895836</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>349</v>
@@ -8403,7 +8415,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46194.05454135417</v>
+        <v>46197.49737577546</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>219</v>
@@ -8454,7 +8466,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46194.054542060185</v>
+        <v>46197.49753788194</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>219</v>
@@ -8505,7 +8517,7 @@
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46194.05454275463</v>
+        <v>46197.49775597222</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>336</v>
@@ -8556,7 +8568,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46194.05454344908</v>
+        <v>46197.49776570602</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>336</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -7582,7 +7582,7 @@
         <v>46197.49723263889</v>
       </c>
       <c r="D100" s="5">
-        <v>46197.497295243054</v>
+        <v>46197.60306288194</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>317</v>
@@ -7632,8 +7632,8 @@
       <c r="T100" s="6">
         <v>1</v>
       </c>
-      <c r="U100" s="10" t="s">
-        <v>33</v>
+      <c r="U100" s="12" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
@@ -7643,9 +7643,11 @@
       <c r="B101" s="8">
         <v>46160.652921562505</v>
       </c>
-      <c r="C101" s="9"/>
+      <c r="C101" s="8">
+        <v>46197.60304642361</v>
+      </c>
       <c r="D101" s="8">
-        <v>46160.81738655093</v>
+        <v>46197.60304800926</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>219</v>
@@ -7859,7 +7861,7 @@
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46160.81773072916</v>
+        <v>46197.60305672453</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>219</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -1830,13 +1830,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46160.65223744213</v>
+        <v>46160.48557077546</v>
       </c>
       <c r="C4" s="5">
-        <v>46167.55836144676</v>
+        <v>46167.39169478009</v>
       </c>
       <c r="D4" s="5">
-        <v>46181.67878920139</v>
+        <v>46181.512122534725</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1879,13 +1879,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46160.65235053241</v>
+        <v>46160.48568386574</v>
       </c>
       <c r="C5" s="8">
-        <v>46167.558334305555</v>
+        <v>46167.39166763889</v>
       </c>
       <c r="D5" s="8">
-        <v>46167.55833537037</v>
+        <v>46167.391668703705</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1942,13 +1942,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46160.652354039354</v>
+        <v>46160.48568737268</v>
       </c>
       <c r="C6" s="5">
-        <v>46167.55815621528</v>
+        <v>46167.39148954861</v>
       </c>
       <c r="D6" s="5">
-        <v>46167.558157314816</v>
+        <v>46167.39149064815</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2005,13 +2005,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46160.65235689815</v>
+        <v>46160.48569023148</v>
       </c>
       <c r="C7" s="8">
-        <v>46167.55818940973</v>
+        <v>46167.391522743055</v>
       </c>
       <c r="D7" s="8">
-        <v>46167.558190428244</v>
+        <v>46167.39152376157</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -2068,13 +2068,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46160.652359687505</v>
+        <v>46160.48569302083</v>
       </c>
       <c r="C8" s="5">
-        <v>46167.558234027776</v>
+        <v>46167.39156736111</v>
       </c>
       <c r="D8" s="5">
-        <v>46167.55823541667</v>
+        <v>46167.39156875</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -2131,13 +2131,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46160.65236314815</v>
+        <v>46160.48569648148</v>
       </c>
       <c r="C9" s="8">
-        <v>46167.55834611111</v>
+        <v>46167.391679444445</v>
       </c>
       <c r="D9" s="8">
-        <v>46167.558347303246</v>
+        <v>46167.391680636574</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2194,11 +2194,11 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46160.65369118056</v>
+        <v>46160.48702451389</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46167.55829033565</v>
+        <v>46167.391623668984</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2247,13 +2247,13 @@
         <v>52</v>
       </c>
       <c r="B11" s="8">
-        <v>46160.654091874996</v>
+        <v>46160.48742520833</v>
       </c>
       <c r="C11" s="8">
-        <v>46167.55828399306</v>
+        <v>46167.391617326386</v>
       </c>
       <c r="D11" s="8">
-        <v>46167.558296180556</v>
+        <v>46167.39162951389</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>53</v>
@@ -2312,11 +2312,11 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46160.654172118055</v>
+        <v>46160.48750545139</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46191.18605898148</v>
+        <v>46191.01939231482</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2375,11 +2375,11 @@
         <v>64</v>
       </c>
       <c r="B13" s="8">
-        <v>46160.65224207176</v>
+        <v>46160.485575405095</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46167.55894045139</v>
+        <v>46167.39227378472</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>65</v>
@@ -2422,13 +2422,13 @@
         <v>67</v>
       </c>
       <c r="B14" s="5">
-        <v>46160.6523665162</v>
+        <v>46160.48569984954</v>
       </c>
       <c r="C14" s="5">
-        <v>46167.55892170139</v>
+        <v>46167.39225503472</v>
       </c>
       <c r="D14" s="5">
-        <v>46167.55893438657</v>
+        <v>46167.39226771991</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>68</v>
@@ -2487,13 +2487,13 @@
         <v>71</v>
       </c>
       <c r="B15" s="8">
-        <v>46160.65237170139</v>
+        <v>46160.48570503472</v>
       </c>
       <c r="C15" s="8">
-        <v>46167.55892672454</v>
+        <v>46167.392260057866</v>
       </c>
       <c r="D15" s="8">
-        <v>46167.55894241898</v>
+        <v>46167.39227575231</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>72</v>
@@ -2552,13 +2552,13 @@
         <v>75</v>
       </c>
       <c r="B16" s="5">
-        <v>46160.652376875005</v>
+        <v>46160.48571020833</v>
       </c>
       <c r="C16" s="5">
-        <v>46167.558934155095</v>
+        <v>46167.39226748842</v>
       </c>
       <c r="D16" s="5">
-        <v>46167.55894754629</v>
+        <v>46167.392280879634</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>76</v>
@@ -2617,11 +2617,11 @@
         <v>78</v>
       </c>
       <c r="B17" s="8">
-        <v>46160.652382002314</v>
+        <v>46160.48571533565</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46167.55894179398</v>
+        <v>46167.39227512731</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>79</v>
@@ -2680,13 +2680,13 @@
         <v>83</v>
       </c>
       <c r="B18" s="5">
-        <v>46160.65224614584</v>
+        <v>46160.485579479166</v>
       </c>
       <c r="C18" s="5">
-        <v>46181.61267278936</v>
+        <v>46181.446006122686</v>
       </c>
       <c r="D18" s="5">
-        <v>46181.678702233796</v>
+        <v>46181.512035567124</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>84</v>
@@ -2729,13 +2729,13 @@
         <v>86</v>
       </c>
       <c r="B19" s="8">
-        <v>46160.652389560186</v>
+        <v>46160.485722893514</v>
       </c>
       <c r="C19" s="8">
-        <v>46167.55896461806</v>
+        <v>46167.39229795139</v>
       </c>
       <c r="D19" s="8">
-        <v>46167.55897762731</v>
+        <v>46167.39231096065</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>87</v>
@@ -2794,13 +2794,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46160.65239491899</v>
+        <v>46160.485728252315</v>
       </c>
       <c r="C20" s="5">
-        <v>46167.55899587963</v>
+        <v>46167.39232921296</v>
       </c>
       <c r="D20" s="5">
-        <v>46167.55901266204</v>
+        <v>46167.392345995366</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2859,13 +2859,13 @@
         <v>92</v>
       </c>
       <c r="B21" s="8">
-        <v>46160.65240028936</v>
+        <v>46160.485733622685</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.612247048615</v>
+        <v>46181.445580381944</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.61226466435</v>
+        <v>46181.445597997685</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>93</v>
@@ -2924,13 +2924,13 @@
         <v>96</v>
       </c>
       <c r="B22" s="5">
-        <v>46160.652405636574</v>
+        <v>46160.4857389699</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.612735636576</v>
+        <v>46181.446068969904</v>
       </c>
       <c r="D22" s="5">
-        <v>46181.67578979167</v>
+        <v>46181.509123125</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>97</v>
@@ -2989,13 +2989,13 @@
         <v>103</v>
       </c>
       <c r="B23" s="8">
-        <v>46160.65241059028</v>
+        <v>46160.48574392361</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.67582236111</v>
+        <v>46181.509155694446</v>
       </c>
       <c r="D23" s="8">
-        <v>46181.67583789352</v>
+        <v>46181.50917122685</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>104</v>
@@ -3054,13 +3054,13 @@
         <v>106</v>
       </c>
       <c r="B24" s="5">
-        <v>46160.652414490745</v>
+        <v>46160.485747824074</v>
       </c>
       <c r="C24" s="5">
-        <v>46181.675860312505</v>
+        <v>46181.509193645834</v>
       </c>
       <c r="D24" s="5">
-        <v>46181.67587553241</v>
+        <v>46181.50920886574</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>107</v>
@@ -3119,13 +3119,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46160.65241840278</v>
+        <v>46160.48575173611</v>
       </c>
       <c r="C25" s="8">
-        <v>46181.67587228009</v>
+        <v>46181.50920561343</v>
       </c>
       <c r="D25" s="8">
-        <v>46181.67588775463</v>
+        <v>46181.50922108797</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -3184,13 +3184,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46160.65857868055</v>
+        <v>46160.49191201389</v>
       </c>
       <c r="C26" s="5">
-        <v>46167.55902803241</v>
+        <v>46167.39236136574</v>
       </c>
       <c r="D26" s="5">
-        <v>46167.55904253472</v>
+        <v>46167.392375868054</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3249,11 +3249,11 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46160.65225063657</v>
+        <v>46160.48558396991</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46181.678639652775</v>
+        <v>46181.51197298611</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3296,13 +3296,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46160.65242274306</v>
+        <v>46160.48575607639</v>
       </c>
       <c r="C28" s="5">
-        <v>46181.67569217592</v>
+        <v>46181.50902550926</v>
       </c>
       <c r="D28" s="5">
-        <v>46181.675709143514</v>
+        <v>46181.50904247686</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3361,13 +3361,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46160.65242719908</v>
+        <v>46160.48576053241</v>
       </c>
       <c r="C29" s="8">
-        <v>46181.675633032406</v>
+        <v>46181.50896636574</v>
       </c>
       <c r="D29" s="8">
-        <v>46181.67563449074</v>
+        <v>46181.50896782408</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3422,13 +3422,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46160.65243181713</v>
+        <v>46160.485765150464</v>
       </c>
       <c r="C30" s="5">
-        <v>46181.67567633102</v>
+        <v>46181.509009664354</v>
       </c>
       <c r="D30" s="5">
-        <v>46181.67567790509</v>
+        <v>46181.50901123842</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3483,13 +3483,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46160.65243667824</v>
+        <v>46160.485770011575</v>
       </c>
       <c r="C31" s="8">
-        <v>46181.67561266204</v>
+        <v>46181.508945995374</v>
       </c>
       <c r="D31" s="8">
-        <v>46181.67562327546</v>
+        <v>46181.5089566088</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3548,13 +3548,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46160.65244107639</v>
+        <v>46160.485774409724</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.67555267361</v>
+        <v>46181.508886006945</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.67555395833</v>
+        <v>46181.50888729167</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3609,13 +3609,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46160.65244578704</v>
+        <v>46160.48577912037</v>
       </c>
       <c r="C33" s="8">
-        <v>46181.67559679398</v>
+        <v>46181.50893012731</v>
       </c>
       <c r="D33" s="8">
-        <v>46181.67559840278</v>
+        <v>46181.50893173611</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3670,13 +3670,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46160.652450625</v>
+        <v>46160.485783958335</v>
       </c>
       <c r="C34" s="5">
-        <v>46181.67547991898</v>
+        <v>46181.508813252316</v>
       </c>
       <c r="D34" s="5">
-        <v>46181.67549369213</v>
+        <v>46181.508827025464</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3735,13 +3735,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46160.65245552083</v>
+        <v>46160.48578885417</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.67541125</v>
+        <v>46181.508744583334</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.67541268519</v>
+        <v>46181.50874601852</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3796,13 +3796,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46160.65246048611</v>
+        <v>46160.48579381945</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.675452662035</v>
+        <v>46181.50878599537</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.67545391204</v>
+        <v>46181.50878724537</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3857,13 +3857,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46160.6524655324</v>
+        <v>46160.485798865746</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.675465057866</v>
+        <v>46181.50879839121</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.67546648148</v>
+        <v>46181.508799814816</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3918,11 +3918,11 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46160.6566696875</v>
+        <v>46160.49000302084</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46197.19306372685</v>
+        <v>46197.02639706018</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3981,13 +3981,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46160.65676351852</v>
+        <v>46160.49009685185</v>
       </c>
       <c r="C39" s="8">
-        <v>46182.67674130787</v>
+        <v>46182.510074641206</v>
       </c>
       <c r="D39" s="8">
-        <v>46182.67674333333</v>
+        <v>46182.510076666666</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>114</v>
@@ -4036,11 +4036,11 @@
         <v>155</v>
       </c>
       <c r="B40" s="5">
-        <v>46160.65688415509</v>
+        <v>46160.49021748843</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46196.16898914352</v>
+        <v>46196.00232247685</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>156</v>
@@ -4089,13 +4089,13 @@
         <v>158</v>
       </c>
       <c r="B41" s="8">
-        <v>46160.65247015047</v>
+        <v>46160.485803483796</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.67623252315</v>
+        <v>46181.50956585648</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.676244386574</v>
+        <v>46181.5095777199</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>159</v>
@@ -4154,13 +4154,13 @@
         <v>163</v>
       </c>
       <c r="B42" s="5">
-        <v>46160.65247482639</v>
+        <v>46160.48580815972</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.676148715276</v>
+        <v>46181.50948204861</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.67615008102</v>
+        <v>46181.50948341435</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>164</v>
@@ -4215,13 +4215,13 @@
         <v>166</v>
       </c>
       <c r="B43" s="8">
-        <v>46160.65247959491</v>
+        <v>46160.48581292824</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.67621893519</v>
+        <v>46181.509552268515</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.67622016204</v>
+        <v>46181.50955349537</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>167</v>
@@ -4276,13 +4276,13 @@
         <v>169</v>
       </c>
       <c r="B44" s="5">
-        <v>46160.65254070602</v>
+        <v>46160.485874039354</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.67635490741</v>
+        <v>46181.50968824074</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.67636662037</v>
+        <v>46181.509699953705</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>170</v>
@@ -4341,13 +4341,13 @@
         <v>172</v>
       </c>
       <c r="B45" s="8">
-        <v>46160.65254572917</v>
+        <v>46160.4858790625</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.67630011574</v>
+        <v>46181.50963344907</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.67630162037</v>
+        <v>46181.509634953705</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>105</v>
@@ -4396,13 +4396,13 @@
         <v>174</v>
       </c>
       <c r="B46" s="5">
-        <v>46160.652551377316</v>
+        <v>46160.48588471065</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.676339375</v>
+        <v>46181.50967270833</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.67634090278</v>
+        <v>46181.50967423611</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>175</v>
@@ -4451,13 +4451,13 @@
         <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46160.652557152775</v>
+        <v>46160.48589048611</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.67648052084</v>
+        <v>46181.509813854165</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.67649172454</v>
+        <v>46181.509825057874</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>178</v>
@@ -4516,13 +4516,13 @@
         <v>182</v>
       </c>
       <c r="B48" s="5">
-        <v>46160.65256162037</v>
+        <v>46160.4858949537</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.67638747685</v>
+        <v>46181.50972081019</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.67638900463</v>
+        <v>46181.50972233796</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>111</v>
@@ -4571,13 +4571,13 @@
         <v>184</v>
       </c>
       <c r="B49" s="8">
-        <v>46160.6525734375</v>
+        <v>46160.48590677083</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.676427557875</v>
+        <v>46181.509760891204</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.67642934028</v>
+        <v>46181.50976267361</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>185</v>
@@ -4626,13 +4626,13 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46160.652579236106</v>
+        <v>46160.48591256945</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.67646592592</v>
+        <v>46181.509799259264</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.676467303245</v>
+        <v>46181.50980063657</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4681,13 +4681,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46160.65258304398</v>
+        <v>46160.485916377314</v>
       </c>
       <c r="C51" s="8">
-        <v>46181.676567789356</v>
+        <v>46181.509901122685</v>
       </c>
       <c r="D51" s="8">
-        <v>46181.67657885417</v>
+        <v>46181.509912187496</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4746,13 +4746,13 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46160.6525875463</v>
+        <v>46160.485920879626</v>
       </c>
       <c r="C52" s="5">
-        <v>46181.676511840276</v>
+        <v>46181.50984517361</v>
       </c>
       <c r="D52" s="5">
-        <v>46181.67651314815</v>
+        <v>46181.50984648148</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4801,13 +4801,13 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46160.652593067134</v>
+        <v>46160.48592640046</v>
       </c>
       <c r="C53" s="8">
-        <v>46181.67655238426</v>
+        <v>46181.50988571759</v>
       </c>
       <c r="D53" s="8">
-        <v>46181.676553680554</v>
+        <v>46181.50988701389</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4856,13 +4856,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46160.65225516204</v>
+        <v>46160.48558849537</v>
       </c>
       <c r="C54" s="5">
-        <v>46181.612413587965</v>
+        <v>46181.445746921294</v>
       </c>
       <c r="D54" s="5">
-        <v>46181.67858451389</v>
+        <v>46181.51191784722</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4905,13 +4905,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46160.65259921296</v>
+        <v>46160.4859325463</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.61232818287</v>
+        <v>46181.445661516205</v>
       </c>
       <c r="D55" s="8">
-        <v>46181.61234585648</v>
+        <v>46181.44567918981</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4970,13 +4970,13 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46160.652606006945</v>
+        <v>46160.48593934027</v>
       </c>
       <c r="C56" s="5">
-        <v>46181.675721631946</v>
+        <v>46181.50905496528</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.67573824074</v>
+        <v>46181.50907157407</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>208</v>
@@ -5035,13 +5035,13 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46160.65261409723</v>
+        <v>46160.485947430556</v>
       </c>
       <c r="C57" s="8">
-        <v>46181.67576423611</v>
+        <v>46181.50909756945</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.67578048611</v>
+        <v>46181.50911381944</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>100</v>
@@ -5100,11 +5100,11 @@
         <v>213</v>
       </c>
       <c r="B58" s="5">
-        <v>46160.652630983794</v>
+        <v>46160.48596431713</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46184.89687363426</v>
+        <v>46184.73020696759</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>214</v>
@@ -5163,11 +5163,11 @@
         <v>218</v>
       </c>
       <c r="B59" s="8">
-        <v>46160.65263532408</v>
+        <v>46160.485968657405</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46181.67790076389</v>
+        <v>46181.51123409723</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>219</v>
@@ -5216,11 +5216,11 @@
         <v>221</v>
       </c>
       <c r="B60" s="5">
-        <v>46160.65264069445</v>
+        <v>46160.485974027775</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46181.67791322917</v>
+        <v>46181.5112465625</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>219</v>
@@ -5269,13 +5269,13 @@
         <v>223</v>
       </c>
       <c r="B61" s="8">
-        <v>46160.652676921294</v>
+        <v>46160.48601025463</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.612796331014</v>
+        <v>46181.44612966436</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.67816971065</v>
+        <v>46181.51150304398</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>224</v>
@@ -5318,13 +5318,13 @@
         <v>226</v>
       </c>
       <c r="B62" s="5">
-        <v>46160.65268083333</v>
+        <v>46160.486014166665</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.67658946759</v>
+        <v>46181.50992280093</v>
       </c>
       <c r="D62" s="5">
-        <v>46182.19861893519</v>
+        <v>46182.03195226852</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>227</v>
@@ -5383,13 +5383,13 @@
         <v>231</v>
       </c>
       <c r="B63" s="8">
-        <v>46160.652685810186</v>
+        <v>46160.486019143515</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.67668319444</v>
+        <v>46181.510016527776</v>
       </c>
       <c r="D63" s="8">
-        <v>46184.17212899306</v>
+        <v>46184.005462326386</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>232</v>
@@ -5448,13 +5448,13 @@
         <v>235</v>
       </c>
       <c r="B64" s="5">
-        <v>46160.65269097222</v>
+        <v>46160.48602430556</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.67660690972</v>
+        <v>46181.50994024306</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.6766224537</v>
+        <v>46181.50995578704</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>236</v>
@@ -5513,13 +5513,13 @@
         <v>238</v>
       </c>
       <c r="B65" s="8">
-        <v>46160.65269633102</v>
+        <v>46160.48602966435</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.67669797454</v>
+        <v>46181.51003130787</v>
       </c>
       <c r="D65" s="8">
-        <v>46184.17212899306</v>
+        <v>46184.005462326386</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>239</v>
@@ -5578,13 +5578,13 @@
         <v>240</v>
       </c>
       <c r="B66" s="5">
-        <v>46160.65269980324</v>
+        <v>46160.48603313658</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.67666710648</v>
+        <v>46181.51000043981</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.67666866898</v>
+        <v>46181.51000200232</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>241</v>
@@ -5643,13 +5643,13 @@
         <v>243</v>
       </c>
       <c r="B67" s="8">
-        <v>46160.652703935186</v>
+        <v>46160.48603726852</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.67671591435</v>
+        <v>46181.510049247685</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.172129004626</v>
+        <v>46184.00546233796</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>242</v>
@@ -5708,13 +5708,13 @@
         <v>244</v>
       </c>
       <c r="B68" s="5">
-        <v>46160.65270767361</v>
+        <v>46160.486041006945</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.61286469907</v>
+        <v>46181.44619803241</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.6781084838</v>
+        <v>46181.51144181713</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>
@@ -5757,13 +5757,13 @@
         <v>247</v>
       </c>
       <c r="B69" s="8">
-        <v>46160.65271061343</v>
+        <v>46160.48604394676</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.676856307866</v>
+        <v>46181.51018964121</v>
       </c>
       <c r="D69" s="8">
-        <v>46189.195743599535</v>
+        <v>46189.02907693287</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>248</v>
@@ -5822,13 +5822,13 @@
         <v>252</v>
       </c>
       <c r="B70" s="5">
-        <v>46160.65271650463</v>
+        <v>46160.486049837964</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.67682665509</v>
+        <v>46181.51015998842</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.67713434028</v>
+        <v>46181.51046767361</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>219</v>
@@ -5877,13 +5877,13 @@
         <v>255</v>
       </c>
       <c r="B71" s="8">
-        <v>46160.65272224537</v>
+        <v>46160.4860555787</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.67684240741</v>
+        <v>46181.51017574074</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.67713509259</v>
+        <v>46181.51046842593</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>219</v>
@@ -5932,13 +5932,13 @@
         <v>258</v>
       </c>
       <c r="B72" s="5">
-        <v>46160.652726898144</v>
+        <v>46160.48606023148</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.677226064814</v>
+        <v>46181.51055939815</v>
       </c>
       <c r="D72" s="5">
-        <v>46196.198199756946</v>
+        <v>46196.03153309028</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>259</v>
@@ -5997,13 +5997,13 @@
         <v>261</v>
       </c>
       <c r="B73" s="8">
-        <v>46160.65273052083</v>
+        <v>46160.486063854165</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.677197129626</v>
+        <v>46181.51053046296</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.67719854167</v>
+        <v>46181.510531875</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>219</v>
@@ -6052,13 +6052,13 @@
         <v>264</v>
       </c>
       <c r="B74" s="5">
-        <v>46160.652741620375</v>
+        <v>46160.486074953704</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.67721283565</v>
+        <v>46181.51054616898</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.67721436343</v>
+        <v>46181.51054769676</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>257</v>
@@ -6107,13 +6107,13 @@
         <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46160.65274630787</v>
+        <v>46160.4860796412</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.67728712963</v>
+        <v>46181.51062046296</v>
       </c>
       <c r="D75" s="8">
-        <v>46197.19306369213</v>
+        <v>46197.02639702546</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>266</v>
@@ -6172,13 +6172,13 @@
         <v>267</v>
       </c>
       <c r="B76" s="5">
-        <v>46160.65275005787</v>
+        <v>46160.4860833912</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.67726334491</v>
+        <v>46181.51059667824</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.67726512731</v>
+        <v>46181.51059846065</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>219</v>
@@ -6227,13 +6227,13 @@
         <v>269</v>
       </c>
       <c r="B77" s="8">
-        <v>46160.65275548611</v>
+        <v>46160.486088819445</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.67727303241</v>
+        <v>46181.510606365744</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.677274664355</v>
+        <v>46181.51060799768</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>219</v>
@@ -6282,13 +6282,13 @@
         <v>272</v>
       </c>
       <c r="B78" s="5">
-        <v>46160.652760625</v>
+        <v>46160.48609395833</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.6130322338</v>
+        <v>46181.44636556713</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.67751854166</v>
+        <v>46181.510851875</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>224</v>
@@ -6331,13 +6331,13 @@
         <v>274</v>
       </c>
       <c r="B79" s="8">
-        <v>46160.65276340277</v>
+        <v>46160.48609673612</v>
       </c>
       <c r="C79" s="8">
-        <v>46181.67731516204</v>
+        <v>46181.51064849537</v>
       </c>
       <c r="D79" s="8">
-        <v>46192.20460657407</v>
+        <v>46192.03793990741</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>275</v>
@@ -6396,13 +6396,13 @@
         <v>277</v>
       </c>
       <c r="B80" s="5">
-        <v>46160.652768831016</v>
+        <v>46160.48610216435</v>
       </c>
       <c r="C80" s="5">
-        <v>46181.67732524306</v>
+        <v>46181.510658576386</v>
       </c>
       <c r="D80" s="5">
-        <v>46181.677345034725</v>
+        <v>46181.51067836805</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>278</v>
@@ -6461,13 +6461,13 @@
         <v>279</v>
       </c>
       <c r="B81" s="8">
-        <v>46160.652774409726</v>
+        <v>46160.486107743054</v>
       </c>
       <c r="C81" s="8">
-        <v>46181.67733638889</v>
+        <v>46181.51066972222</v>
       </c>
       <c r="D81" s="8">
-        <v>46181.67735619213</v>
+        <v>46181.51068952546</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>280</v>
@@ -6526,13 +6526,13 @@
         <v>281</v>
       </c>
       <c r="B82" s="5">
-        <v>46160.652779745375</v>
+        <v>46160.4861130787</v>
       </c>
       <c r="C82" s="5">
-        <v>46181.677345601856</v>
+        <v>46181.510678935185</v>
       </c>
       <c r="D82" s="5">
-        <v>46181.67736313658</v>
+        <v>46181.51069646991</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>282</v>
@@ -6591,11 +6591,11 @@
         <v>284</v>
       </c>
       <c r="B83" s="8">
-        <v>46160.657067569446</v>
+        <v>46160.49040090278</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46197.16928957176</v>
+        <v>46197.00262290509</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>61</v>
@@ -6654,13 +6654,13 @@
         <v>285</v>
       </c>
       <c r="B84" s="5">
-        <v>46160.65278418981</v>
+        <v>46160.48611752315</v>
       </c>
       <c r="C84" s="5">
-        <v>46181.617794328704</v>
+        <v>46181.45112766203</v>
       </c>
       <c r="D84" s="5">
-        <v>46197.49724974537</v>
+        <v>46197.3305830787</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>286</v>
@@ -6705,13 +6705,13 @@
         <v>288</v>
       </c>
       <c r="B85" s="8">
-        <v>46160.65278701389</v>
+        <v>46160.486120347225</v>
       </c>
       <c r="C85" s="8">
-        <v>46181.67760038194</v>
+        <v>46181.51093371528</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.17484756945</v>
+        <v>46196.008180902776</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>289</v>
@@ -6770,13 +6770,13 @@
         <v>291</v>
       </c>
       <c r="B86" s="5">
-        <v>46160.65279357639</v>
+        <v>46160.486126909724</v>
       </c>
       <c r="C86" s="5">
-        <v>46181.677674942126</v>
+        <v>46181.51100827546</v>
       </c>
       <c r="D86" s="5">
-        <v>46181.67767618055</v>
+        <v>46181.51100951389</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>219</v>
@@ -6825,13 +6825,13 @@
         <v>293</v>
       </c>
       <c r="B87" s="8">
-        <v>46160.65279733796</v>
+        <v>46160.4861306713</v>
       </c>
       <c r="C87" s="8">
-        <v>46181.677687511576</v>
+        <v>46181.511020844904</v>
       </c>
       <c r="D87" s="8">
-        <v>46181.677689247685</v>
+        <v>46181.51102258102</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>219</v>
@@ -6880,13 +6880,13 @@
         <v>294</v>
       </c>
       <c r="B88" s="5">
-        <v>46160.65280108796</v>
+        <v>46160.4861344213</v>
       </c>
       <c r="C88" s="5">
-        <v>46181.67776662037</v>
+        <v>46181.5110999537</v>
       </c>
       <c r="D88" s="5">
-        <v>46197.19052525463</v>
+        <v>46197.02385858796</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>295</v>
@@ -6945,13 +6945,13 @@
         <v>296</v>
       </c>
       <c r="B89" s="8">
-        <v>46160.65280498842</v>
+        <v>46160.48613832176</v>
       </c>
       <c r="C89" s="8">
-        <v>46181.677741273146</v>
+        <v>46181.51107460648</v>
       </c>
       <c r="D89" s="8">
-        <v>46181.67774287037</v>
+        <v>46181.51107620371</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>219</v>
@@ -7000,13 +7000,13 @@
         <v>299</v>
       </c>
       <c r="B90" s="5">
-        <v>46160.65281013889</v>
+        <v>46160.486143472226</v>
       </c>
       <c r="C90" s="5">
-        <v>46181.677753344906</v>
+        <v>46181.51108667824</v>
       </c>
       <c r="D90" s="5">
-        <v>46181.67775488426</v>
+        <v>46181.511088217594</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>219</v>
@@ -7055,13 +7055,13 @@
         <v>300</v>
       </c>
       <c r="B91" s="8">
-        <v>46160.65281503472</v>
+        <v>46160.48614836806</v>
       </c>
       <c r="C91" s="8">
-        <v>46181.67783773148</v>
+        <v>46181.51117106482</v>
       </c>
       <c r="D91" s="8">
-        <v>46181.67785175926</v>
+        <v>46181.51118509259</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>301</v>
@@ -7120,13 +7120,13 @@
         <v>302</v>
       </c>
       <c r="B92" s="5">
-        <v>46160.65281883102</v>
+        <v>46160.48615216435</v>
       </c>
       <c r="C92" s="5">
-        <v>46181.67779599537</v>
+        <v>46181.511129328705</v>
       </c>
       <c r="D92" s="5">
-        <v>46181.677797627315</v>
+        <v>46181.511130960644</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>219</v>
@@ -7173,13 +7173,13 @@
         <v>304</v>
       </c>
       <c r="B93" s="8">
-        <v>46160.65287608796</v>
+        <v>46160.486209421295</v>
       </c>
       <c r="C93" s="8">
-        <v>46181.67780578704</v>
+        <v>46181.51113912037</v>
       </c>
       <c r="D93" s="8">
-        <v>46181.67780725694</v>
+        <v>46181.51114059028</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>219</v>
@@ -7226,13 +7226,13 @@
         <v>305</v>
       </c>
       <c r="B94" s="5">
-        <v>46160.65288447917</v>
+        <v>46160.486217812504</v>
       </c>
       <c r="C94" s="5">
-        <v>46181.6778656713</v>
+        <v>46181.51119900463</v>
       </c>
       <c r="D94" s="5">
-        <v>46181.677878726856</v>
+        <v>46181.511212060184</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>306</v>
@@ -7291,13 +7291,13 @@
         <v>307</v>
       </c>
       <c r="B95" s="8">
-        <v>46160.65288969908</v>
+        <v>46160.48622303241</v>
       </c>
       <c r="C95" s="8">
-        <v>46181.67784234954</v>
+        <v>46181.51117568287</v>
       </c>
       <c r="D95" s="8">
-        <v>46181.67784412037</v>
+        <v>46181.51117745371</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>219</v>
@@ -7346,13 +7346,13 @@
         <v>310</v>
       </c>
       <c r="B96" s="5">
-        <v>46160.6528953588</v>
+        <v>46160.48622869213</v>
       </c>
       <c r="C96" s="5">
-        <v>46181.67784924769</v>
+        <v>46181.511182581016</v>
       </c>
       <c r="D96" s="5">
-        <v>46181.677850625</v>
+        <v>46181.51118395833</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>219</v>
@@ -7401,13 +7401,13 @@
         <v>311</v>
       </c>
       <c r="B97" s="8">
-        <v>46160.652900706016</v>
+        <v>46160.48623403935</v>
       </c>
       <c r="C97" s="8">
-        <v>46181.677918587964</v>
+        <v>46181.5112519213</v>
       </c>
       <c r="D97" s="8">
-        <v>46181.67793089121</v>
+        <v>46181.51126422454</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>312</v>
@@ -7466,13 +7466,13 @@
         <v>313</v>
       </c>
       <c r="B98" s="5">
-        <v>46160.65290569444</v>
+        <v>46160.48623902778</v>
       </c>
       <c r="C98" s="5">
-        <v>46181.6778925463</v>
+        <v>46181.51122587963</v>
       </c>
       <c r="D98" s="5">
-        <v>46181.67789438658</v>
+        <v>46181.51122771991</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>219</v>
@@ -7521,13 +7521,13 @@
         <v>315</v>
       </c>
       <c r="B99" s="8">
-        <v>46160.652911157405</v>
+        <v>46160.48624449074</v>
       </c>
       <c r="C99" s="8">
-        <v>46181.67790297454</v>
+        <v>46181.511236307866</v>
       </c>
       <c r="D99" s="8">
-        <v>46181.67790501157</v>
+        <v>46181.51123834491</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>219</v>
@@ -7576,13 +7576,13 @@
         <v>316</v>
       </c>
       <c r="B100" s="5">
-        <v>46160.65291657408</v>
+        <v>46160.48624990741</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.49723263889</v>
+        <v>46197.330565972225</v>
       </c>
       <c r="D100" s="5">
-        <v>46197.60306288194</v>
+        <v>46197.43639621528</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>317</v>
@@ -7641,13 +7641,13 @@
         <v>319</v>
       </c>
       <c r="B101" s="8">
-        <v>46160.652921562505</v>
+        <v>46160.48625489583</v>
       </c>
       <c r="C101" s="8">
-        <v>46197.60304642361</v>
+        <v>46197.436379756946</v>
       </c>
       <c r="D101" s="8">
-        <v>46197.60304800926</v>
+        <v>46197.43638134259</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>219</v>
@@ -7694,13 +7694,13 @@
         <v>321</v>
       </c>
       <c r="B102" s="5">
-        <v>46160.65292620371</v>
+        <v>46160.486259537036</v>
       </c>
       <c r="C102" s="5">
-        <v>46197.4972891088</v>
+        <v>46197.330622442125</v>
       </c>
       <c r="D102" s="5">
-        <v>46197.49729054398</v>
+        <v>46197.330623877315</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>219</v>
@@ -7747,11 +7747,11 @@
         <v>323</v>
       </c>
       <c r="B103" s="8">
-        <v>46160.65293084491</v>
+        <v>46160.48626417824</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46197.49766417824</v>
+        <v>46197.33099751157</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>324</v>
@@ -7794,11 +7794,11 @@
         <v>326</v>
       </c>
       <c r="B104" s="5">
-        <v>46160.65293431713</v>
+        <v>46160.48626765046</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46197.49724334491</v>
+        <v>46197.33057667824</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>327</v>
@@ -7857,11 +7857,11 @@
         <v>331</v>
       </c>
       <c r="B105" s="8">
-        <v>46160.65293966435</v>
+        <v>46160.48627299769</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46197.60305672453</v>
+        <v>46197.436390057876</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>219</v>
@@ -7910,11 +7910,11 @@
         <v>333</v>
       </c>
       <c r="B106" s="5">
-        <v>46160.652944201385</v>
+        <v>46160.48627753472</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46197.49729465278</v>
+        <v>46197.33062798611</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>219</v>
@@ -7963,11 +7963,11 @@
         <v>335</v>
       </c>
       <c r="B107" s="8">
-        <v>46160.80816486111</v>
+        <v>46160.64149819444</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46160.817732083335</v>
+        <v>46160.65106541666</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>336</v>
@@ -8016,11 +8016,11 @@
         <v>338</v>
       </c>
       <c r="B108" s="5">
-        <v>46160.80854525463</v>
+        <v>46160.641878587965</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46160.81773274306</v>
+        <v>46160.65106607639</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>336</v>
@@ -8069,13 +8069,13 @@
         <v>340</v>
       </c>
       <c r="B109" s="8">
-        <v>46160.65294850695</v>
+        <v>46160.486281840276</v>
       </c>
       <c r="C109" s="8">
-        <v>46197.49765626158</v>
+        <v>46197.330989594906</v>
       </c>
       <c r="D109" s="8">
-        <v>46197.497765231485</v>
+        <v>46197.33109856481</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>341</v>
@@ -8134,13 +8134,13 @@
         <v>343</v>
       </c>
       <c r="B110" s="5">
-        <v>46160.652952592594</v>
+        <v>46160.48628592593</v>
       </c>
       <c r="C110" s="5">
-        <v>46197.497369351855</v>
+        <v>46197.33070268518</v>
       </c>
       <c r="D110" s="5">
-        <v>46197.497371261576</v>
+        <v>46197.330704594904</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>219</v>
@@ -8189,13 +8189,13 @@
         <v>345</v>
       </c>
       <c r="B111" s="8">
-        <v>46160.65295699074</v>
+        <v>46160.48629032407</v>
       </c>
       <c r="C111" s="8">
-        <v>46197.497530023145</v>
+        <v>46197.33086335648</v>
       </c>
       <c r="D111" s="8">
-        <v>46197.49753173611</v>
+        <v>46197.330865069445</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>219</v>
@@ -8244,11 +8244,11 @@
         <v>346</v>
       </c>
       <c r="B112" s="5">
-        <v>46160.809122164355</v>
+        <v>46160.642455497684</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46197.4977528125</v>
+        <v>46197.33108614583</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>336</v>
@@ -8297,11 +8297,11 @@
         <v>348</v>
       </c>
       <c r="B113" s="8">
-        <v>46160.809137627315</v>
+        <v>46160.64247096065</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46197.497759895836</v>
+        <v>46197.331093229164</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>349</v>
@@ -8350,11 +8350,11 @@
         <v>350</v>
       </c>
       <c r="B114" s="5">
-        <v>46160.652961203705</v>
+        <v>46160.48629453704</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46194.05666876158</v>
+        <v>46193.89000209491</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>351</v>
@@ -8413,11 +8413,11 @@
         <v>353</v>
       </c>
       <c r="B115" s="8">
-        <v>46160.65296532407</v>
+        <v>46160.48629865741</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46197.49737577546</v>
+        <v>46197.33070910879</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>219</v>
@@ -8464,11 +8464,11 @@
         <v>355</v>
       </c>
       <c r="B116" s="5">
-        <v>46160.65297267361</v>
+        <v>46160.48630600695</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46197.49753788194</v>
+        <v>46197.33087121528</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>219</v>
@@ -8515,11 +8515,11 @@
         <v>357</v>
       </c>
       <c r="B117" s="8">
-        <v>46160.81088733797</v>
+        <v>46160.644220671296</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46197.49775597222</v>
+        <v>46197.33108930556</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>336</v>
@@ -8566,11 +8566,11 @@
         <v>359</v>
       </c>
       <c r="B118" s="5">
-        <v>46160.81089606481</v>
+        <v>46160.64422939815</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46197.49776570602</v>
+        <v>46197.33109903935</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>336</v>
@@ -8617,11 +8617,11 @@
         <v>360</v>
       </c>
       <c r="B119" s="8">
-        <v>46160.65297846065</v>
+        <v>46160.48631179398</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46183.89564782407</v>
+        <v>46183.72898115741</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>361</v>
@@ -8680,11 +8680,11 @@
         <v>363</v>
       </c>
       <c r="B120" s="5">
-        <v>46160.652983935186</v>
+        <v>46160.486317268515</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46194.054542048616</v>
+        <v>46193.887875381944</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>219</v>
@@ -8733,11 +8733,11 @@
         <v>364</v>
       </c>
       <c r="B121" s="8">
-        <v>46160.65298813657</v>
+        <v>46160.48632146991</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46194.056669247686</v>
+        <v>46193.890002581014</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>219</v>
@@ -8786,11 +8786,11 @@
         <v>365</v>
       </c>
       <c r="B122" s="5">
-        <v>46160.81215837963</v>
+        <v>46160.64549171296</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46194.05454575231</v>
+        <v>46193.88787908565</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>336</v>
@@ -8839,11 +8839,11 @@
         <v>366</v>
       </c>
       <c r="B123" s="8">
-        <v>46160.81220768519</v>
+        <v>46160.645541018515</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46194.05454428241</v>
+        <v>46193.887877615736</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>336</v>
@@ -8892,11 +8892,11 @@
         <v>367</v>
       </c>
       <c r="B124" s="5">
-        <v>46160.65302554399</v>
+        <v>46160.486358877315</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46160.8192895949</v>
+        <v>46160.65262292824</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>368</v>
@@ -8939,11 +8939,11 @@
         <v>370</v>
       </c>
       <c r="B125" s="8">
-        <v>46160.65302895833</v>
+        <v>46160.48636229167</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46160.819199722224</v>
+        <v>46160.65253305556</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>371</v>
@@ -9002,11 +9002,11 @@
         <v>374</v>
       </c>
       <c r="B126" s="5">
-        <v>46160.65303386574</v>
+        <v>46160.486367199075</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46160.81937795139</v>
+        <v>46160.652711284725</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>375</v>
@@ -9065,11 +9065,11 @@
         <v>377</v>
       </c>
       <c r="B127" s="8">
-        <v>46160.65808951389</v>
+        <v>46160.49142284722</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46160.819809513894</v>
+        <v>46160.65314284722</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>378</v>
@@ -9118,11 +9118,11 @@
         <v>380</v>
       </c>
       <c r="B128" s="5">
-        <v>46160.66095159722</v>
+        <v>46160.49428493055</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46160.81972457176</v>
+        <v>46160.65305790509</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>381</v>
@@ -9181,11 +9181,11 @@
         <v>383</v>
       </c>
       <c r="B129" s="8">
-        <v>46160.66107538194</v>
+        <v>46160.494408715276</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46160.8199466088</v>
+        <v>46160.653279942126</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>384</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="387">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -663,28 +663,34 @@
     <t>Planos preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214909595210222</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor ot 4313</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214909462950236</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214909595210222</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor ot 4313</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214909462950236</t>
   </si>
   <si>
     <t>OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,propuesta Corte Laser ot 4313,Propuesta Corte plasma  ot 4313,Propuesta Mecanizado ot 4313 ,Propuesta Fabricación externa ot 4313,OT 4313 - ZVN 1-9-45/2,OT  4313- ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
@@ -1830,13 +1836,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46160.48557077546</v>
+        <v>46160.65223744213</v>
       </c>
       <c r="C4" s="5">
-        <v>46167.39169478009</v>
+        <v>46167.55836144676</v>
       </c>
       <c r="D4" s="5">
-        <v>46181.512122534725</v>
+        <v>46181.67878920139</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1879,13 +1885,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46160.48568386574</v>
+        <v>46160.65235053241</v>
       </c>
       <c r="C5" s="8">
-        <v>46167.39166763889</v>
+        <v>46167.558334305555</v>
       </c>
       <c r="D5" s="8">
-        <v>46167.391668703705</v>
+        <v>46167.55833537037</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1942,13 +1948,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46160.48568737268</v>
+        <v>46160.652354039354</v>
       </c>
       <c r="C6" s="5">
-        <v>46167.39148954861</v>
+        <v>46167.55815621528</v>
       </c>
       <c r="D6" s="5">
-        <v>46167.39149064815</v>
+        <v>46167.558157314816</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2005,13 +2011,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46160.48569023148</v>
+        <v>46160.65235689815</v>
       </c>
       <c r="C7" s="8">
-        <v>46167.391522743055</v>
+        <v>46167.55818940973</v>
       </c>
       <c r="D7" s="8">
-        <v>46167.39152376157</v>
+        <v>46167.558190428244</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -2068,13 +2074,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46160.48569302083</v>
+        <v>46160.652359687505</v>
       </c>
       <c r="C8" s="5">
-        <v>46167.39156736111</v>
+        <v>46167.558234027776</v>
       </c>
       <c r="D8" s="5">
-        <v>46167.39156875</v>
+        <v>46167.55823541667</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -2131,13 +2137,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46160.48569648148</v>
+        <v>46160.65236314815</v>
       </c>
       <c r="C9" s="8">
-        <v>46167.391679444445</v>
+        <v>46167.55834611111</v>
       </c>
       <c r="D9" s="8">
-        <v>46167.391680636574</v>
+        <v>46167.558347303246</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2194,11 +2200,11 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46160.48702451389</v>
+        <v>46160.65369118056</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46167.391623668984</v>
+        <v>46167.55829033565</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2247,13 +2253,13 @@
         <v>52</v>
       </c>
       <c r="B11" s="8">
-        <v>46160.48742520833</v>
+        <v>46160.654091874996</v>
       </c>
       <c r="C11" s="8">
-        <v>46167.391617326386</v>
+        <v>46167.55828399306</v>
       </c>
       <c r="D11" s="8">
-        <v>46167.39162951389</v>
+        <v>46167.558296180556</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>53</v>
@@ -2312,11 +2318,11 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46160.48750545139</v>
+        <v>46160.654172118055</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46191.01939231482</v>
+        <v>46191.18605898148</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2375,11 +2381,11 @@
         <v>64</v>
       </c>
       <c r="B13" s="8">
-        <v>46160.485575405095</v>
+        <v>46160.65224207176</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46167.39227378472</v>
+        <v>46167.55894045139</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>65</v>
@@ -2422,13 +2428,13 @@
         <v>67</v>
       </c>
       <c r="B14" s="5">
-        <v>46160.48569984954</v>
+        <v>46160.6523665162</v>
       </c>
       <c r="C14" s="5">
-        <v>46167.39225503472</v>
+        <v>46167.55892170139</v>
       </c>
       <c r="D14" s="5">
-        <v>46167.39226771991</v>
+        <v>46167.55893438657</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>68</v>
@@ -2487,13 +2493,13 @@
         <v>71</v>
       </c>
       <c r="B15" s="8">
-        <v>46160.48570503472</v>
+        <v>46160.65237170139</v>
       </c>
       <c r="C15" s="8">
-        <v>46167.392260057866</v>
+        <v>46167.55892672454</v>
       </c>
       <c r="D15" s="8">
-        <v>46167.39227575231</v>
+        <v>46167.55894241898</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>72</v>
@@ -2552,13 +2558,13 @@
         <v>75</v>
       </c>
       <c r="B16" s="5">
-        <v>46160.48571020833</v>
+        <v>46160.652376875005</v>
       </c>
       <c r="C16" s="5">
-        <v>46167.39226748842</v>
+        <v>46167.558934155095</v>
       </c>
       <c r="D16" s="5">
-        <v>46167.392280879634</v>
+        <v>46167.55894754629</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>76</v>
@@ -2617,11 +2623,11 @@
         <v>78</v>
       </c>
       <c r="B17" s="8">
-        <v>46160.48571533565</v>
+        <v>46160.652382002314</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46167.39227512731</v>
+        <v>46167.55894179398</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>79</v>
@@ -2680,13 +2686,13 @@
         <v>83</v>
       </c>
       <c r="B18" s="5">
-        <v>46160.485579479166</v>
+        <v>46160.65224614584</v>
       </c>
       <c r="C18" s="5">
-        <v>46181.446006122686</v>
+        <v>46181.61267278936</v>
       </c>
       <c r="D18" s="5">
-        <v>46181.512035567124</v>
+        <v>46181.678702233796</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>84</v>
@@ -2729,13 +2735,13 @@
         <v>86</v>
       </c>
       <c r="B19" s="8">
-        <v>46160.485722893514</v>
+        <v>46160.652389560186</v>
       </c>
       <c r="C19" s="8">
-        <v>46167.39229795139</v>
+        <v>46167.55896461806</v>
       </c>
       <c r="D19" s="8">
-        <v>46167.39231096065</v>
+        <v>46167.55897762731</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>87</v>
@@ -2794,13 +2800,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46160.485728252315</v>
+        <v>46160.65239491899</v>
       </c>
       <c r="C20" s="5">
-        <v>46167.39232921296</v>
+        <v>46167.55899587963</v>
       </c>
       <c r="D20" s="5">
-        <v>46167.392345995366</v>
+        <v>46167.55901266204</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2859,13 +2865,13 @@
         <v>92</v>
       </c>
       <c r="B21" s="8">
-        <v>46160.485733622685</v>
+        <v>46160.65240028936</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.445580381944</v>
+        <v>46181.612247048615</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.445597997685</v>
+        <v>46181.61226466435</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>93</v>
@@ -2924,13 +2930,13 @@
         <v>96</v>
       </c>
       <c r="B22" s="5">
-        <v>46160.4857389699</v>
+        <v>46160.652405636574</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.446068969904</v>
+        <v>46181.612735636576</v>
       </c>
       <c r="D22" s="5">
-        <v>46181.509123125</v>
+        <v>46181.67578979167</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>97</v>
@@ -2989,13 +2995,13 @@
         <v>103</v>
       </c>
       <c r="B23" s="8">
-        <v>46160.48574392361</v>
+        <v>46160.65241059028</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.509155694446</v>
+        <v>46181.67582236111</v>
       </c>
       <c r="D23" s="8">
-        <v>46181.50917122685</v>
+        <v>46181.67583789352</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>104</v>
@@ -3054,13 +3060,13 @@
         <v>106</v>
       </c>
       <c r="B24" s="5">
-        <v>46160.485747824074</v>
+        <v>46160.652414490745</v>
       </c>
       <c r="C24" s="5">
-        <v>46181.509193645834</v>
+        <v>46181.675860312505</v>
       </c>
       <c r="D24" s="5">
-        <v>46181.50920886574</v>
+        <v>46181.67587553241</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>107</v>
@@ -3119,13 +3125,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46160.48575173611</v>
+        <v>46160.65241840278</v>
       </c>
       <c r="C25" s="8">
-        <v>46181.50920561343</v>
+        <v>46181.67587228009</v>
       </c>
       <c r="D25" s="8">
-        <v>46181.50922108797</v>
+        <v>46181.67588775463</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -3184,13 +3190,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46160.49191201389</v>
+        <v>46160.65857868055</v>
       </c>
       <c r="C26" s="5">
-        <v>46167.39236136574</v>
+        <v>46167.55902803241</v>
       </c>
       <c r="D26" s="5">
-        <v>46167.392375868054</v>
+        <v>46167.55904253472</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3249,11 +3255,11 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46160.48558396991</v>
+        <v>46160.65225063657</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46181.51197298611</v>
+        <v>46181.678639652775</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3296,13 +3302,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46160.48575607639</v>
+        <v>46160.65242274306</v>
       </c>
       <c r="C28" s="5">
-        <v>46181.50902550926</v>
+        <v>46181.67569217592</v>
       </c>
       <c r="D28" s="5">
-        <v>46181.50904247686</v>
+        <v>46181.675709143514</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3361,13 +3367,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46160.48576053241</v>
+        <v>46160.65242719908</v>
       </c>
       <c r="C29" s="8">
-        <v>46181.50896636574</v>
+        <v>46181.675633032406</v>
       </c>
       <c r="D29" s="8">
-        <v>46181.50896782408</v>
+        <v>46181.67563449074</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3422,13 +3428,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46160.485765150464</v>
+        <v>46160.65243181713</v>
       </c>
       <c r="C30" s="5">
-        <v>46181.509009664354</v>
+        <v>46181.67567633102</v>
       </c>
       <c r="D30" s="5">
-        <v>46181.50901123842</v>
+        <v>46181.67567790509</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3483,13 +3489,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46160.485770011575</v>
+        <v>46160.65243667824</v>
       </c>
       <c r="C31" s="8">
-        <v>46181.508945995374</v>
+        <v>46181.67561266204</v>
       </c>
       <c r="D31" s="8">
-        <v>46181.5089566088</v>
+        <v>46181.67562327546</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3548,13 +3554,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46160.485774409724</v>
+        <v>46160.65244107639</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.508886006945</v>
+        <v>46181.67555267361</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.50888729167</v>
+        <v>46181.67555395833</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3609,13 +3615,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46160.48577912037</v>
+        <v>46160.65244578704</v>
       </c>
       <c r="C33" s="8">
-        <v>46181.50893012731</v>
+        <v>46181.67559679398</v>
       </c>
       <c r="D33" s="8">
-        <v>46181.50893173611</v>
+        <v>46181.67559840278</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3670,13 +3676,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46160.485783958335</v>
+        <v>46160.652450625</v>
       </c>
       <c r="C34" s="5">
-        <v>46181.508813252316</v>
+        <v>46181.67547991898</v>
       </c>
       <c r="D34" s="5">
-        <v>46181.508827025464</v>
+        <v>46181.67549369213</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3735,13 +3741,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46160.48578885417</v>
+        <v>46160.65245552083</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.508744583334</v>
+        <v>46181.67541125</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.50874601852</v>
+        <v>46181.67541268519</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3796,13 +3802,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46160.48579381945</v>
+        <v>46160.65246048611</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.50878599537</v>
+        <v>46181.675452662035</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.50878724537</v>
+        <v>46181.67545391204</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3857,13 +3863,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46160.485798865746</v>
+        <v>46160.6524655324</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.50879839121</v>
+        <v>46181.675465057866</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.508799814816</v>
+        <v>46181.67546648148</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3918,11 +3924,11 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46160.49000302084</v>
+        <v>46160.6566696875</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46197.02639706018</v>
+        <v>46197.19306372685</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3981,13 +3987,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46160.49009685185</v>
+        <v>46160.65676351852</v>
       </c>
       <c r="C39" s="8">
-        <v>46182.510074641206</v>
+        <v>46182.67674130787</v>
       </c>
       <c r="D39" s="8">
-        <v>46182.510076666666</v>
+        <v>46182.67674333333</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>114</v>
@@ -4036,11 +4042,11 @@
         <v>155</v>
       </c>
       <c r="B40" s="5">
-        <v>46160.49021748843</v>
+        <v>46160.65688415509</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46196.00232247685</v>
+        <v>46196.16898914352</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>156</v>
@@ -4089,13 +4095,13 @@
         <v>158</v>
       </c>
       <c r="B41" s="8">
-        <v>46160.485803483796</v>
+        <v>46160.65247015047</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.50956585648</v>
+        <v>46181.67623252315</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.5095777199</v>
+        <v>46181.676244386574</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>159</v>
@@ -4154,13 +4160,13 @@
         <v>163</v>
       </c>
       <c r="B42" s="5">
-        <v>46160.48580815972</v>
+        <v>46160.65247482639</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.50948204861</v>
+        <v>46181.676148715276</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.50948341435</v>
+        <v>46181.67615008102</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>164</v>
@@ -4215,13 +4221,13 @@
         <v>166</v>
       </c>
       <c r="B43" s="8">
-        <v>46160.48581292824</v>
+        <v>46160.65247959491</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.509552268515</v>
+        <v>46181.67621893519</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.50955349537</v>
+        <v>46181.67622016204</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>167</v>
@@ -4276,13 +4282,13 @@
         <v>169</v>
       </c>
       <c r="B44" s="5">
-        <v>46160.485874039354</v>
+        <v>46160.65254070602</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.50968824074</v>
+        <v>46181.67635490741</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.509699953705</v>
+        <v>46181.67636662037</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>170</v>
@@ -4341,13 +4347,13 @@
         <v>172</v>
       </c>
       <c r="B45" s="8">
-        <v>46160.4858790625</v>
+        <v>46160.65254572917</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.50963344907</v>
+        <v>46181.67630011574</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.509634953705</v>
+        <v>46181.67630162037</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>105</v>
@@ -4396,13 +4402,13 @@
         <v>174</v>
       </c>
       <c r="B46" s="5">
-        <v>46160.48588471065</v>
+        <v>46160.652551377316</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.50967270833</v>
+        <v>46181.676339375</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.50967423611</v>
+        <v>46181.67634090278</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>175</v>
@@ -4451,13 +4457,13 @@
         <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46160.48589048611</v>
+        <v>46160.652557152775</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.509813854165</v>
+        <v>46181.67648052084</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.509825057874</v>
+        <v>46181.67649172454</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>178</v>
@@ -4516,13 +4522,13 @@
         <v>182</v>
       </c>
       <c r="B48" s="5">
-        <v>46160.4858949537</v>
+        <v>46160.65256162037</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.50972081019</v>
+        <v>46181.67638747685</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.50972233796</v>
+        <v>46181.67638900463</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>111</v>
@@ -4571,13 +4577,13 @@
         <v>184</v>
       </c>
       <c r="B49" s="8">
-        <v>46160.48590677083</v>
+        <v>46160.6525734375</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.509760891204</v>
+        <v>46181.676427557875</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.50976267361</v>
+        <v>46181.67642934028</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>185</v>
@@ -4626,13 +4632,13 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46160.48591256945</v>
+        <v>46160.652579236106</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.509799259264</v>
+        <v>46181.67646592592</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.50980063657</v>
+        <v>46181.676467303245</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4681,13 +4687,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46160.485916377314</v>
+        <v>46160.65258304398</v>
       </c>
       <c r="C51" s="8">
-        <v>46181.509901122685</v>
+        <v>46181.676567789356</v>
       </c>
       <c r="D51" s="8">
-        <v>46181.509912187496</v>
+        <v>46181.67657885417</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4746,13 +4752,13 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46160.485920879626</v>
+        <v>46160.6525875463</v>
       </c>
       <c r="C52" s="5">
-        <v>46181.50984517361</v>
+        <v>46181.676511840276</v>
       </c>
       <c r="D52" s="5">
-        <v>46181.50984648148</v>
+        <v>46181.67651314815</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4801,13 +4807,13 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46160.48592640046</v>
+        <v>46160.652593067134</v>
       </c>
       <c r="C53" s="8">
-        <v>46181.50988571759</v>
+        <v>46181.67655238426</v>
       </c>
       <c r="D53" s="8">
-        <v>46181.50988701389</v>
+        <v>46181.676553680554</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4856,13 +4862,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46160.48558849537</v>
+        <v>46160.65225516204</v>
       </c>
       <c r="C54" s="5">
-        <v>46181.445746921294</v>
+        <v>46181.612413587965</v>
       </c>
       <c r="D54" s="5">
-        <v>46181.51191784722</v>
+        <v>46181.67858451389</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4905,13 +4911,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46160.4859325463</v>
+        <v>46160.65259921296</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.445661516205</v>
+        <v>46181.61232818287</v>
       </c>
       <c r="D55" s="8">
-        <v>46181.44567918981</v>
+        <v>46197.712640196754</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4970,13 +4976,13 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46160.48593934027</v>
+        <v>46160.652606006945</v>
       </c>
       <c r="C56" s="5">
-        <v>46181.50905496528</v>
+        <v>46181.675721631946</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.50907157407</v>
+        <v>46197.71267317129</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>208</v>
@@ -5035,13 +5041,13 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46160.485947430556</v>
+        <v>46160.65261409723</v>
       </c>
       <c r="C57" s="8">
-        <v>46181.50909756945</v>
+        <v>46181.67576423611</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.50911381944</v>
+        <v>46181.67578048611</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>100</v>
@@ -5050,10 +5056,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="I57" s="8">
         <v>46160</v>
@@ -5077,7 +5083,7 @@
         <v>208</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Q57" s="8">
         <v>46160</v>
@@ -5097,26 +5103,26 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46160.48596431713</v>
+        <v>46160.652630983794</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46184.73020696759</v>
+        <v>46184.89687363426</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I58" s="5">
         <v>46210</v>
@@ -5137,7 +5143,7 @@
         <v>200</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>26</v>
@@ -5160,26 +5166,26 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B59" s="8">
-        <v>46160.485968657405</v>
+        <v>46160.65263532408</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46181.51123409723</v>
+        <v>46181.67790076389</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I59" s="8">
         <v>46210</v>
@@ -5197,13 +5203,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5213,26 +5219,26 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B60" s="5">
-        <v>46160.485974027775</v>
+        <v>46160.65264069445</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46181.5112465625</v>
+        <v>46181.67791322917</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="I60" s="5">
         <v>46210</v>
@@ -5250,13 +5256,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5266,19 +5272,19 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46160.48601025463</v>
+        <v>46160.652676921294</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.44612966436</v>
+        <v>46181.612796331014</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.51150304398</v>
+        <v>46181.67816971065</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>25</v>
@@ -5302,7 +5308,7 @@
         <v>26</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>26</v>
@@ -5315,28 +5321,28 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B62" s="5">
-        <v>46160.486014166665</v>
+        <v>46160.65268083333</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.50992280093</v>
+        <v>46181.67658946759</v>
       </c>
       <c r="D62" s="5">
-        <v>46182.03195226852</v>
+        <v>46182.19861893519</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I62" s="5">
         <v>46178</v>
@@ -5354,13 +5360,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>167</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q62" s="5">
         <v>46178</v>
@@ -5380,19 +5386,19 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B63" s="8">
-        <v>46160.486019143515</v>
+        <v>46160.652685810186</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.510016527776</v>
+        <v>46181.67668319444</v>
       </c>
       <c r="D63" s="8">
-        <v>46184.005462326386</v>
+        <v>46184.17212899306</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
@@ -5419,13 +5425,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q63" s="8">
         <v>46182</v>
@@ -5445,28 +5451,28 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B64" s="5">
-        <v>46160.48602430556</v>
+        <v>46160.65269097222</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.50994024306</v>
+        <v>46181.67660690972</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.50995578704</v>
+        <v>46181.6766224537</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I64" s="5">
         <v>46178</v>
@@ -5484,13 +5490,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>175</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q64" s="5">
         <v>46147</v>
@@ -5510,19 +5516,19 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B65" s="8">
-        <v>46160.48602966435</v>
+        <v>46160.65269633102</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.51003130787</v>
+        <v>46181.67669797454</v>
       </c>
       <c r="D65" s="8">
-        <v>46184.005462326386</v>
+        <v>46184.17212899306</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5549,13 +5555,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q65" s="8">
         <v>46182</v>
@@ -5575,28 +5581,28 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B66" s="5">
-        <v>46160.48603313658</v>
+        <v>46160.65269980324</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.51000043981</v>
+        <v>46181.67666710648</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.51000200232</v>
+        <v>46181.67666866898</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I66" s="5">
         <v>46178</v>
@@ -5614,13 +5620,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>197</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q66" s="5">
         <v>46147</v>
@@ -5640,19 +5646,19 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46160.48603726852</v>
+        <v>46160.652703935186</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.510049247685</v>
+        <v>46181.67671591435</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.00546233796</v>
+        <v>46184.172129004626</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
@@ -5679,13 +5685,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Q67" s="8">
         <v>46182</v>
@@ -5705,19 +5711,19 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46160.486041006945</v>
+        <v>46160.65270767361</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.44619803241</v>
+        <v>46181.61286469907</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.51144181713</v>
+        <v>46181.6781084838</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>25</v>
@@ -5741,7 +5747,7 @@
         <v>26</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>26</v>
@@ -5754,28 +5760,28 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46160.48604394676</v>
+        <v>46160.65271061343</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.51018964121</v>
+        <v>46181.676856307866</v>
       </c>
       <c r="D69" s="8">
-        <v>46189.02907693287</v>
+        <v>46189.195743599535</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I69" s="8">
         <v>46184</v>
@@ -5793,13 +5799,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q69" s="8">
         <v>46184</v>
@@ -5819,28 +5825,28 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B70" s="5">
+        <v>46160.65271650463</v>
+      </c>
+      <c r="C70" s="5">
+        <v>46181.67682665509</v>
+      </c>
+      <c r="D70" s="5">
+        <v>46181.67713434028</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>252</v>
-      </c>
-      <c r="B70" s="5">
-        <v>46160.486049837964</v>
-      </c>
-      <c r="C70" s="5">
-        <v>46181.51015998842</v>
-      </c>
-      <c r="D70" s="5">
-        <v>46181.51046767361</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="I70" s="5">
         <v>46184</v>
@@ -5858,13 +5864,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5874,28 +5880,28 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B71" s="8">
-        <v>46160.4860555787</v>
+        <v>46160.65272224537</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.51017574074</v>
+        <v>46181.67684240741</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.51046842593</v>
+        <v>46181.67713509259</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I71" s="8">
         <v>46184</v>
@@ -5913,13 +5919,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -5929,28 +5935,28 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B72" s="5">
-        <v>46160.48606023148</v>
+        <v>46160.652726898144</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.51055939815</v>
+        <v>46181.677226064814</v>
       </c>
       <c r="D72" s="5">
-        <v>46196.03153309028</v>
+        <v>46196.198199756946</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I72" s="5">
         <v>46189</v>
@@ -5968,13 +5974,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q72" s="5">
         <v>46189</v>
@@ -5994,28 +6000,28 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46160.486063854165</v>
+        <v>46160.65273052083</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.51053046296</v>
+        <v>46181.677197129626</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.510531875</v>
+        <v>46181.67719854167</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I73" s="8">
         <v>46189</v>
@@ -6033,13 +6039,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6049,28 +6055,28 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46160.486074953704</v>
+        <v>46160.652741620375</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.51054616898</v>
+        <v>46181.67721283565</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.51054769676</v>
+        <v>46181.67721436343</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I74" s="5">
         <v>46189</v>
@@ -6088,13 +6094,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6104,19 +6110,19 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46160.4860796412</v>
+        <v>46160.65274630787</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.51062046296</v>
+        <v>46181.67728712963</v>
       </c>
       <c r="D75" s="8">
-        <v>46197.02639702546</v>
+        <v>46197.19306369213</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -6143,13 +6149,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q75" s="8">
         <v>46196</v>
@@ -6169,19 +6175,19 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46160.4860833912</v>
+        <v>46160.65275005787</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.51059667824</v>
+        <v>46181.67726334491</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.51059846065</v>
+        <v>46181.67726512731</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6208,13 +6214,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6224,19 +6230,19 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B77" s="8">
-        <v>46160.486088819445</v>
+        <v>46160.65275548611</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.510606365744</v>
+        <v>46181.67727303241</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.51060799768</v>
+        <v>46181.677274664355</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
@@ -6263,13 +6269,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6279,19 +6285,19 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B78" s="5">
-        <v>46160.48609395833</v>
+        <v>46160.652760625</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.44636556713</v>
+        <v>46181.6130322338</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.510851875</v>
+        <v>46181.67751854166</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>25</v>
@@ -6315,7 +6321,7 @@
         <v>26</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6328,28 +6334,28 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B79" s="8">
-        <v>46160.48609673612</v>
+        <v>46160.65276340277</v>
       </c>
       <c r="C79" s="8">
-        <v>46181.51064849537</v>
+        <v>46181.67731516204</v>
       </c>
       <c r="D79" s="8">
-        <v>46192.03793990741</v>
+        <v>46192.20460657407</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I79" s="8">
         <v>46160</v>
@@ -6367,13 +6373,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O79" s="9" t="s">
         <v>136</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q79" s="8">
         <v>46160</v>
@@ -6393,28 +6399,28 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B80" s="5">
-        <v>46160.48610216435</v>
+        <v>46160.652768831016</v>
       </c>
       <c r="C80" s="5">
-        <v>46181.510658576386</v>
+        <v>46181.67732524306</v>
       </c>
       <c r="D80" s="5">
-        <v>46181.51067836805</v>
+        <v>46181.677345034725</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I80" s="5">
         <v>46141</v>
@@ -6432,13 +6438,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>127</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q80" s="5">
         <v>46141</v>
@@ -6458,28 +6464,28 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B81" s="8">
-        <v>46160.486107743054</v>
+        <v>46160.652774409726</v>
       </c>
       <c r="C81" s="8">
-        <v>46181.51066972222</v>
+        <v>46181.67733638889</v>
       </c>
       <c r="D81" s="8">
-        <v>46181.51068952546</v>
+        <v>46181.67735619213</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I81" s="8">
         <v>46174</v>
@@ -6497,13 +6503,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>145</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q81" s="8">
         <v>46174</v>
@@ -6523,28 +6529,28 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B82" s="5">
-        <v>46160.4861130787</v>
+        <v>46160.652779745375</v>
       </c>
       <c r="C82" s="5">
-        <v>46181.510678935185</v>
+        <v>46181.677345601856</v>
       </c>
       <c r="D82" s="5">
-        <v>46181.51069646991</v>
+        <v>46181.67736313658</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I82" s="5">
         <v>46206</v>
@@ -6562,13 +6568,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>185</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q82" s="5">
         <v>46206</v>
@@ -6588,14 +6594,14 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B83" s="8">
-        <v>46160.49040090278</v>
+        <v>46160.657067569446</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46197.00262290509</v>
+        <v>46197.16928957176</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>61</v>
@@ -6604,10 +6610,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="I83" s="8">
         <v>46197</v>
@@ -6625,7 +6631,7 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>156</v>
@@ -6651,19 +6657,19 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B84" s="5">
-        <v>46160.48611752315</v>
+        <v>46160.65278418981</v>
       </c>
       <c r="C84" s="5">
-        <v>46181.45112766203</v>
+        <v>46181.617794328704</v>
       </c>
       <c r="D84" s="5">
-        <v>46197.3305830787</v>
+        <v>46197.49724974537</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -6687,7 +6693,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -6702,19 +6708,19 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B85" s="8">
-        <v>46160.486120347225</v>
+        <v>46160.65278701389</v>
       </c>
       <c r="C85" s="8">
-        <v>46181.51093371528</v>
+        <v>46181.67760038194</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.008180902776</v>
+        <v>46196.17484756945</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6741,13 +6747,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q85" s="8">
         <v>46197</v>
@@ -6767,19 +6773,19 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B86" s="5">
-        <v>46160.486126909724</v>
+        <v>46160.65279357639</v>
       </c>
       <c r="C86" s="5">
-        <v>46181.51100827546</v>
+        <v>46181.677674942126</v>
       </c>
       <c r="D86" s="5">
-        <v>46181.51100951389</v>
+        <v>46181.67767618055</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6806,10 +6812,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6822,19 +6828,19 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B87" s="8">
-        <v>46160.4861306713</v>
+        <v>46160.65279733796</v>
       </c>
       <c r="C87" s="8">
-        <v>46181.511020844904</v>
+        <v>46181.677687511576</v>
       </c>
       <c r="D87" s="8">
-        <v>46181.51102258102</v>
+        <v>46181.677689247685</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6861,10 +6867,10 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>26</v>
@@ -6877,19 +6883,19 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B88" s="5">
-        <v>46160.4861344213</v>
+        <v>46160.65280108796</v>
       </c>
       <c r="C88" s="5">
-        <v>46181.5110999537</v>
+        <v>46181.67776662037</v>
       </c>
       <c r="D88" s="5">
-        <v>46197.02385858796</v>
+        <v>46197.19052525463</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6916,13 +6922,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q88" s="5">
         <v>46204</v>
@@ -6942,19 +6948,19 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B89" s="8">
-        <v>46160.48613832176</v>
+        <v>46160.65280498842</v>
       </c>
       <c r="C89" s="8">
-        <v>46181.51107460648</v>
+        <v>46181.677741273146</v>
       </c>
       <c r="D89" s="8">
-        <v>46181.51107620371</v>
+        <v>46181.67774287037</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6981,13 +6987,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6997,19 +7003,19 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B90" s="5">
-        <v>46160.486143472226</v>
+        <v>46160.65281013889</v>
       </c>
       <c r="C90" s="5">
-        <v>46181.51108667824</v>
+        <v>46181.677753344906</v>
       </c>
       <c r="D90" s="5">
-        <v>46181.511088217594</v>
+        <v>46181.67775488426</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7036,13 +7042,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q90" s="6"/>
       <c r="R90" s="6"/>
@@ -7052,19 +7058,19 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B91" s="8">
-        <v>46160.48614836806</v>
+        <v>46160.65281503472</v>
       </c>
       <c r="C91" s="8">
-        <v>46181.51117106482</v>
+        <v>46181.67783773148</v>
       </c>
       <c r="D91" s="8">
-        <v>46181.51118509259</v>
+        <v>46181.67785175926</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7091,13 +7097,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q91" s="8">
         <v>46205</v>
@@ -7117,19 +7123,19 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B92" s="5">
-        <v>46160.48615216435</v>
+        <v>46160.65281883102</v>
       </c>
       <c r="C92" s="5">
-        <v>46181.511129328705</v>
+        <v>46181.67779599537</v>
       </c>
       <c r="D92" s="5">
-        <v>46181.511130960644</v>
+        <v>46181.677797627315</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7154,13 +7160,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O92" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="P92" s="6" t="s">
         <v>303</v>
-      </c>
-      <c r="P92" s="6" t="s">
-        <v>301</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7170,19 +7176,19 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B93" s="8">
-        <v>46160.486209421295</v>
+        <v>46160.65287608796</v>
       </c>
       <c r="C93" s="8">
-        <v>46181.51113912037</v>
+        <v>46181.67780578704</v>
       </c>
       <c r="D93" s="8">
-        <v>46181.51114059028</v>
+        <v>46181.67780725694</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7207,13 +7213,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="O93" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="P93" s="9" t="s">
         <v>303</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>301</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7223,19 +7229,19 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B94" s="5">
-        <v>46160.486217812504</v>
+        <v>46160.65288447917</v>
       </c>
       <c r="C94" s="5">
-        <v>46181.51119900463</v>
+        <v>46181.6778656713</v>
       </c>
       <c r="D94" s="5">
-        <v>46181.511212060184</v>
+        <v>46181.677878726856</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7262,13 +7268,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q94" s="5">
         <v>46206</v>
@@ -7288,19 +7294,19 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B95" s="8">
-        <v>46160.48622303241</v>
+        <v>46160.65288969908</v>
       </c>
       <c r="C95" s="8">
-        <v>46181.51117568287</v>
+        <v>46181.67784234954</v>
       </c>
       <c r="D95" s="8">
-        <v>46181.51117745371</v>
+        <v>46181.67784412037</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7327,13 +7333,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7343,19 +7349,19 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B96" s="5">
-        <v>46160.48622869213</v>
+        <v>46160.6528953588</v>
       </c>
       <c r="C96" s="5">
-        <v>46181.511182581016</v>
+        <v>46181.67784924769</v>
       </c>
       <c r="D96" s="5">
-        <v>46181.51118395833</v>
+        <v>46181.677850625</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7382,13 +7388,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7398,19 +7404,19 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B97" s="8">
-        <v>46160.48623403935</v>
+        <v>46160.652900706016</v>
       </c>
       <c r="C97" s="8">
-        <v>46181.5112519213</v>
+        <v>46181.677918587964</v>
       </c>
       <c r="D97" s="8">
-        <v>46181.51126422454</v>
+        <v>46181.67793089121</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7437,13 +7443,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q97" s="8">
         <v>46209</v>
@@ -7463,19 +7469,19 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B98" s="5">
-        <v>46160.48623902778</v>
+        <v>46160.65290569444</v>
       </c>
       <c r="C98" s="5">
-        <v>46181.51122587963</v>
+        <v>46181.6778925463</v>
       </c>
       <c r="D98" s="5">
-        <v>46181.51122771991</v>
+        <v>46181.67789438658</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7502,13 +7508,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7518,19 +7524,19 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B99" s="8">
-        <v>46160.48624449074</v>
+        <v>46160.652911157405</v>
       </c>
       <c r="C99" s="8">
-        <v>46181.511236307866</v>
+        <v>46181.67790297454</v>
       </c>
       <c r="D99" s="8">
-        <v>46181.51123834491</v>
+        <v>46181.67790501157</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7557,13 +7563,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7573,19 +7579,19 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B100" s="5">
-        <v>46160.48624990741</v>
+        <v>46160.65291657408</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.330565972225</v>
+        <v>46197.49723263889</v>
       </c>
       <c r="D100" s="5">
-        <v>46197.43639621528</v>
+        <v>46197.60306288194</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7612,13 +7618,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q100" s="5">
         <v>46211</v>
@@ -7638,19 +7644,19 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B101" s="8">
-        <v>46160.48625489583</v>
+        <v>46160.652921562505</v>
       </c>
       <c r="C101" s="8">
-        <v>46197.436379756946</v>
+        <v>46197.60304642361</v>
       </c>
       <c r="D101" s="8">
-        <v>46197.43638134259</v>
+        <v>46197.60304800926</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7675,13 +7681,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7691,19 +7697,19 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B102" s="5">
-        <v>46160.486259537036</v>
+        <v>46160.65292620371</v>
       </c>
       <c r="C102" s="5">
-        <v>46197.330622442125</v>
+        <v>46197.4972891088</v>
       </c>
       <c r="D102" s="5">
-        <v>46197.330623877315</v>
+        <v>46197.49729054398</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -7728,13 +7734,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7744,17 +7750,17 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B103" s="8">
-        <v>46160.48626417824</v>
+        <v>46160.65293084491</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46197.33099751157</v>
+        <v>46197.49766417824</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>25</v>
@@ -7778,7 +7784,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>26</v>
@@ -7791,26 +7797,26 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B104" s="5">
-        <v>46160.48626765046</v>
+        <v>46160.65293431713</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46197.33057667824</v>
+        <v>46197.49724334491</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I104" s="5">
         <v>46212</v>
@@ -7828,13 +7834,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q104" s="5">
         <v>46212</v>
@@ -7854,26 +7860,26 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B105" s="8">
-        <v>46160.48627299769</v>
+        <v>46160.65293966435</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46197.436390057876</v>
+        <v>46197.60305672453</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I105" s="8">
         <v>46212</v>
@@ -7891,13 +7897,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7907,26 +7913,26 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B106" s="5">
-        <v>46160.48627753472</v>
+        <v>46160.652944201385</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46197.33062798611</v>
+        <v>46197.49729465278</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I106" s="5">
         <v>46212</v>
@@ -7944,13 +7950,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7960,26 +7966,26 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B107" s="8">
-        <v>46160.64149819444</v>
+        <v>46160.80816486111</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46160.65106541666</v>
+        <v>46160.817732083335</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I107" s="8">
         <v>46212</v>
@@ -7997,13 +8003,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>58</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8013,26 +8019,26 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B108" s="5">
-        <v>46160.641878587965</v>
+        <v>46160.80854525463</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46160.65106607639</v>
+        <v>46160.81773274306</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="I108" s="5">
         <v>46212</v>
@@ -8050,13 +8056,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>58</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8066,19 +8072,19 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B109" s="8">
-        <v>46160.486281840276</v>
+        <v>46160.65294850695</v>
       </c>
       <c r="C109" s="8">
-        <v>46197.330989594906</v>
+        <v>46197.49765626158</v>
       </c>
       <c r="D109" s="8">
-        <v>46197.33109856481</v>
+        <v>46197.497765231485</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8105,13 +8111,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q109" s="8">
         <v>46213</v>
@@ -8131,19 +8137,19 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B110" s="5">
-        <v>46160.48628592593</v>
+        <v>46160.652952592594</v>
       </c>
       <c r="C110" s="5">
-        <v>46197.33070268518</v>
+        <v>46197.497369351855</v>
       </c>
       <c r="D110" s="5">
-        <v>46197.330704594904</v>
+        <v>46197.497371261576</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8170,13 +8176,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8186,19 +8192,19 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B111" s="8">
-        <v>46160.48629032407</v>
+        <v>46160.65295699074</v>
       </c>
       <c r="C111" s="8">
-        <v>46197.33086335648</v>
+        <v>46197.497530023145</v>
       </c>
       <c r="D111" s="8">
-        <v>46197.330865069445</v>
+        <v>46197.49753173611</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8225,13 +8231,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8241,17 +8247,17 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B112" s="5">
-        <v>46160.642455497684</v>
+        <v>46160.809122164355</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46197.33108614583</v>
+        <v>46197.4977528125</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8278,13 +8284,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8294,17 +8300,17 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B113" s="8">
-        <v>46160.64247096065</v>
+        <v>46160.809137627315</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46197.331093229164</v>
+        <v>46197.497759895836</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8331,13 +8337,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
@@ -8347,26 +8353,26 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B114" s="5">
-        <v>46160.48629453704</v>
+        <v>46160.652961203705</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46193.89000209491</v>
+        <v>46194.05666876158</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I114" s="5">
         <v>46216</v>
@@ -8384,13 +8390,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q114" s="5">
         <v>46216</v>
@@ -8410,26 +8416,26 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B115" s="8">
-        <v>46160.48629865741</v>
+        <v>46160.65296532407</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46197.33070910879</v>
+        <v>46197.49737577546</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="8">
@@ -8445,13 +8451,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8461,26 +8467,26 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B116" s="5">
-        <v>46160.48630600695</v>
+        <v>46160.65297267361</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46197.33087121528</v>
+        <v>46197.49753788194</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8496,13 +8502,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8512,26 +8518,26 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B117" s="8">
-        <v>46160.644220671296</v>
+        <v>46160.81088733797</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46197.33108930556</v>
+        <v>46197.49775597222</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8547,13 +8553,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8563,26 +8569,26 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B118" s="5">
-        <v>46160.64422939815</v>
+        <v>46160.81089606481</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46197.33109903935</v>
+        <v>46197.49776570602</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I118" s="6"/>
       <c r="J118" s="5">
@@ -8598,13 +8604,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="O118" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="O118" s="6" t="s">
-        <v>349</v>
-      </c>
       <c r="P118" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8614,26 +8620,26 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B119" s="8">
-        <v>46160.48631179398</v>
+        <v>46160.65297846065</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46183.72898115741</v>
+        <v>46183.89564782407</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I119" s="8">
         <v>46217</v>
@@ -8651,13 +8657,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q119" s="8">
         <v>46217</v>
@@ -8677,26 +8683,26 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B120" s="5">
-        <v>46160.486317268515</v>
+        <v>46160.652983935186</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46193.887875381944</v>
+        <v>46194.054542048616</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I120" s="5">
         <v>46217</v>
@@ -8714,13 +8720,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8730,26 +8736,26 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B121" s="8">
-        <v>46160.48632146991</v>
+        <v>46160.65298813657</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46193.890002581014</v>
+        <v>46194.056669247686</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I121" s="8">
         <v>46217</v>
@@ -8767,13 +8773,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8783,26 +8789,26 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B122" s="5">
-        <v>46160.64549171296</v>
+        <v>46160.81215837963</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46193.88787908565</v>
+        <v>46194.05454575231</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I122" s="5">
         <v>46217</v>
@@ -8820,13 +8826,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8836,26 +8842,26 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B123" s="8">
-        <v>46160.645541018515</v>
+        <v>46160.81220768519</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46193.887877615736</v>
+        <v>46194.05454428241</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="I123" s="8">
         <v>46217</v>
@@ -8873,13 +8879,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8889,17 +8895,17 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B124" s="5">
-        <v>46160.486358877315</v>
+        <v>46160.65302554399</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46160.65262292824</v>
+        <v>46160.8192895949</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>25</v>
@@ -8923,7 +8929,7 @@
         <v>26</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>26</v>
@@ -8936,26 +8942,26 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B125" s="8">
-        <v>46160.48636229167</v>
+        <v>46160.65302895833</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46160.65253305556</v>
+        <v>46160.819199722224</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I125" s="8">
         <v>46218</v>
@@ -8973,13 +8979,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q125" s="8">
         <v>46218</v>
@@ -8999,17 +9005,17 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B126" s="5">
-        <v>46160.486367199075</v>
+        <v>46160.65303386574</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46160.652711284725</v>
+        <v>46160.81937795139</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9036,13 +9042,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q126" s="5">
         <v>46218</v>
@@ -9062,17 +9068,17 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B127" s="8">
-        <v>46160.49142284722</v>
+        <v>46160.65808951389</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46160.65314284722</v>
+        <v>46160.819809513894</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>25</v>
@@ -9096,7 +9102,7 @@
         <v>26</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>26</v>
@@ -9115,17 +9121,17 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B128" s="5">
-        <v>46160.49428493055</v>
+        <v>46160.66095159722</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46160.65305790509</v>
+        <v>46160.81972457176</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9152,13 +9158,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q128" s="5">
         <v>46218</v>
@@ -9178,17 +9184,17 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B129" s="8">
-        <v>46160.494408715276</v>
+        <v>46160.66107538194</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46160.653279942126</v>
+        <v>46160.8199466088</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9215,13 +9221,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q129" s="8">
         <v>46227</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -2322,7 +2322,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46191.18605898148</v>
+        <v>46198.16902134259</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -4463,7 +4463,7 @@
         <v>46181.67648052084</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.67649172454</v>
+        <v>46198.206338171294</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>178</v>
@@ -4507,8 +4507,8 @@
       <c r="R47" s="8">
         <v>46205</v>
       </c>
-      <c r="S47" s="10" t="s">
-        <v>32</v>
+      <c r="S47" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>
@@ -6601,7 +6601,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46197.16928957176</v>
+        <v>46198.18861751157</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>61</v>
@@ -6645,8 +6645,8 @@
       <c r="R83" s="8">
         <v>46197</v>
       </c>
-      <c r="S83" s="12" t="s">
-        <v>63</v>
+      <c r="S83" s="11" t="s">
+        <v>102</v>
       </c>
       <c r="T83" s="9">
         <v>0</v>
@@ -7067,7 +7067,7 @@
         <v>46181.67783773148</v>
       </c>
       <c r="D91" s="8">
-        <v>46181.67785175926</v>
+        <v>46198.20633876158</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>303</v>
@@ -7111,8 +7111,8 @@
       <c r="R91" s="8">
         <v>46205</v>
       </c>
-      <c r="S91" s="10" t="s">
-        <v>32</v>
+      <c r="S91" s="12" t="s">
+        <v>63</v>
       </c>
       <c r="T91" s="9">
         <v>1</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -5108,9 +5108,11 @@
       <c r="B58" s="5">
         <v>46160.652630983794</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46198.56611644676</v>
+      </c>
       <c r="D58" s="5">
-        <v>46184.89687363426</v>
+        <v>46198.566261608794</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>
@@ -5158,10 +5160,10 @@
         <v>32</v>
       </c>
       <c r="T58" s="6">
-        <v>0</v>
-      </c>
-      <c r="U58" s="11" t="s">
-        <v>51</v>
+        <v>1</v>
+      </c>
+      <c r="U58" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
@@ -5171,9 +5173,11 @@
       <c r="B59" s="8">
         <v>46160.65263532408</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="8">
+        <v>46198.56608402778</v>
+      </c>
       <c r="D59" s="8">
-        <v>46181.67790076389</v>
+        <v>46198.566085625</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>221</v>
@@ -5224,9 +5228,11 @@
       <c r="B60" s="5">
         <v>46160.65264069445</v>
       </c>
-      <c r="C60" s="6"/>
+      <c r="C60" s="5">
+        <v>46198.566099675925</v>
+      </c>
       <c r="D60" s="5">
-        <v>46181.67791322917</v>
+        <v>46198.5661015625</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -7653,7 +7659,7 @@
         <v>46197.60304642361</v>
       </c>
       <c r="D101" s="8">
-        <v>46197.60304800926</v>
+        <v>46198.56608928241</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>221</v>
@@ -7706,7 +7712,7 @@
         <v>46197.4972891088</v>
       </c>
       <c r="D102" s="5">
-        <v>46197.49729054398</v>
+        <v>46198.566110405096</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>221</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -1836,13 +1836,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46160.65223744213</v>
+        <v>46160.48557077546</v>
       </c>
       <c r="C4" s="5">
-        <v>46167.55836144676</v>
+        <v>46167.39169478009</v>
       </c>
       <c r="D4" s="5">
-        <v>46181.67878920139</v>
+        <v>46181.512122534725</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1885,13 +1885,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46160.65235053241</v>
+        <v>46160.48568386574</v>
       </c>
       <c r="C5" s="8">
-        <v>46167.558334305555</v>
+        <v>46167.39166763889</v>
       </c>
       <c r="D5" s="8">
-        <v>46167.55833537037</v>
+        <v>46167.391668703705</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1948,13 +1948,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46160.652354039354</v>
+        <v>46160.48568737268</v>
       </c>
       <c r="C6" s="5">
-        <v>46167.55815621528</v>
+        <v>46167.39148954861</v>
       </c>
       <c r="D6" s="5">
-        <v>46167.558157314816</v>
+        <v>46167.39149064815</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2011,13 +2011,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46160.65235689815</v>
+        <v>46160.48569023148</v>
       </c>
       <c r="C7" s="8">
-        <v>46167.55818940973</v>
+        <v>46167.391522743055</v>
       </c>
       <c r="D7" s="8">
-        <v>46167.558190428244</v>
+        <v>46167.39152376157</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -2074,13 +2074,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46160.652359687505</v>
+        <v>46160.48569302083</v>
       </c>
       <c r="C8" s="5">
-        <v>46167.558234027776</v>
+        <v>46167.39156736111</v>
       </c>
       <c r="D8" s="5">
-        <v>46167.55823541667</v>
+        <v>46167.39156875</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -2137,13 +2137,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46160.65236314815</v>
+        <v>46160.48569648148</v>
       </c>
       <c r="C9" s="8">
-        <v>46167.55834611111</v>
+        <v>46167.391679444445</v>
       </c>
       <c r="D9" s="8">
-        <v>46167.558347303246</v>
+        <v>46167.391680636574</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2200,11 +2200,11 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46160.65369118056</v>
+        <v>46160.48702451389</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46167.55829033565</v>
+        <v>46167.391623668984</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2253,13 +2253,13 @@
         <v>52</v>
       </c>
       <c r="B11" s="8">
-        <v>46160.654091874996</v>
+        <v>46160.48742520833</v>
       </c>
       <c r="C11" s="8">
-        <v>46167.55828399306</v>
+        <v>46167.391617326386</v>
       </c>
       <c r="D11" s="8">
-        <v>46167.558296180556</v>
+        <v>46167.39162951389</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>53</v>
@@ -2318,11 +2318,11 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46160.654172118055</v>
+        <v>46160.48750545139</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46198.16902134259</v>
+        <v>46198.002354675926</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2381,11 +2381,11 @@
         <v>64</v>
       </c>
       <c r="B13" s="8">
-        <v>46160.65224207176</v>
+        <v>46160.485575405095</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46167.55894045139</v>
+        <v>46167.39227378472</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>65</v>
@@ -2428,13 +2428,13 @@
         <v>67</v>
       </c>
       <c r="B14" s="5">
-        <v>46160.6523665162</v>
+        <v>46160.48569984954</v>
       </c>
       <c r="C14" s="5">
-        <v>46167.55892170139</v>
+        <v>46167.39225503472</v>
       </c>
       <c r="D14" s="5">
-        <v>46167.55893438657</v>
+        <v>46167.39226771991</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>68</v>
@@ -2493,13 +2493,13 @@
         <v>71</v>
       </c>
       <c r="B15" s="8">
-        <v>46160.65237170139</v>
+        <v>46160.48570503472</v>
       </c>
       <c r="C15" s="8">
-        <v>46167.55892672454</v>
+        <v>46167.392260057866</v>
       </c>
       <c r="D15" s="8">
-        <v>46167.55894241898</v>
+        <v>46167.39227575231</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>72</v>
@@ -2558,13 +2558,13 @@
         <v>75</v>
       </c>
       <c r="B16" s="5">
-        <v>46160.652376875005</v>
+        <v>46160.48571020833</v>
       </c>
       <c r="C16" s="5">
-        <v>46167.558934155095</v>
+        <v>46167.39226748842</v>
       </c>
       <c r="D16" s="5">
-        <v>46167.55894754629</v>
+        <v>46167.392280879634</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>76</v>
@@ -2623,11 +2623,11 @@
         <v>78</v>
       </c>
       <c r="B17" s="8">
-        <v>46160.652382002314</v>
+        <v>46160.48571533565</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46167.55894179398</v>
+        <v>46167.39227512731</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>79</v>
@@ -2686,13 +2686,13 @@
         <v>83</v>
       </c>
       <c r="B18" s="5">
-        <v>46160.65224614584</v>
+        <v>46160.485579479166</v>
       </c>
       <c r="C18" s="5">
-        <v>46181.61267278936</v>
+        <v>46181.446006122686</v>
       </c>
       <c r="D18" s="5">
-        <v>46181.678702233796</v>
+        <v>46181.512035567124</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>84</v>
@@ -2735,13 +2735,13 @@
         <v>86</v>
       </c>
       <c r="B19" s="8">
-        <v>46160.652389560186</v>
+        <v>46160.485722893514</v>
       </c>
       <c r="C19" s="8">
-        <v>46167.55896461806</v>
+        <v>46167.39229795139</v>
       </c>
       <c r="D19" s="8">
-        <v>46167.55897762731</v>
+        <v>46167.39231096065</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>87</v>
@@ -2800,13 +2800,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46160.65239491899</v>
+        <v>46160.485728252315</v>
       </c>
       <c r="C20" s="5">
-        <v>46167.55899587963</v>
+        <v>46167.39232921296</v>
       </c>
       <c r="D20" s="5">
-        <v>46167.55901266204</v>
+        <v>46167.392345995366</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2865,13 +2865,13 @@
         <v>92</v>
       </c>
       <c r="B21" s="8">
-        <v>46160.65240028936</v>
+        <v>46160.485733622685</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.612247048615</v>
+        <v>46181.445580381944</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.61226466435</v>
+        <v>46181.445597997685</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>93</v>
@@ -2930,13 +2930,13 @@
         <v>96</v>
       </c>
       <c r="B22" s="5">
-        <v>46160.652405636574</v>
+        <v>46160.4857389699</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.612735636576</v>
+        <v>46181.446068969904</v>
       </c>
       <c r="D22" s="5">
-        <v>46181.67578979167</v>
+        <v>46181.509123125</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>97</v>
@@ -2995,13 +2995,13 @@
         <v>103</v>
       </c>
       <c r="B23" s="8">
-        <v>46160.65241059028</v>
+        <v>46160.48574392361</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.67582236111</v>
+        <v>46181.509155694446</v>
       </c>
       <c r="D23" s="8">
-        <v>46181.67583789352</v>
+        <v>46181.50917122685</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>104</v>
@@ -3060,13 +3060,13 @@
         <v>106</v>
       </c>
       <c r="B24" s="5">
-        <v>46160.652414490745</v>
+        <v>46160.485747824074</v>
       </c>
       <c r="C24" s="5">
-        <v>46181.675860312505</v>
+        <v>46181.509193645834</v>
       </c>
       <c r="D24" s="5">
-        <v>46181.67587553241</v>
+        <v>46181.50920886574</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>107</v>
@@ -3125,13 +3125,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46160.65241840278</v>
+        <v>46160.48575173611</v>
       </c>
       <c r="C25" s="8">
-        <v>46181.67587228009</v>
+        <v>46181.50920561343</v>
       </c>
       <c r="D25" s="8">
-        <v>46181.67588775463</v>
+        <v>46181.50922108797</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -3190,13 +3190,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46160.65857868055</v>
+        <v>46160.49191201389</v>
       </c>
       <c r="C26" s="5">
-        <v>46167.55902803241</v>
+        <v>46167.39236136574</v>
       </c>
       <c r="D26" s="5">
-        <v>46167.55904253472</v>
+        <v>46167.392375868054</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3255,11 +3255,11 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46160.65225063657</v>
+        <v>46160.48558396991</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46181.678639652775</v>
+        <v>46181.51197298611</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3302,13 +3302,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46160.65242274306</v>
+        <v>46160.48575607639</v>
       </c>
       <c r="C28" s="5">
-        <v>46181.67569217592</v>
+        <v>46181.50902550926</v>
       </c>
       <c r="D28" s="5">
-        <v>46181.675709143514</v>
+        <v>46181.50904247686</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3367,13 +3367,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46160.65242719908</v>
+        <v>46160.48576053241</v>
       </c>
       <c r="C29" s="8">
-        <v>46181.675633032406</v>
+        <v>46181.50896636574</v>
       </c>
       <c r="D29" s="8">
-        <v>46181.67563449074</v>
+        <v>46181.50896782408</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3428,13 +3428,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46160.65243181713</v>
+        <v>46160.485765150464</v>
       </c>
       <c r="C30" s="5">
-        <v>46181.67567633102</v>
+        <v>46181.509009664354</v>
       </c>
       <c r="D30" s="5">
-        <v>46181.67567790509</v>
+        <v>46181.50901123842</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3489,13 +3489,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46160.65243667824</v>
+        <v>46160.485770011575</v>
       </c>
       <c r="C31" s="8">
-        <v>46181.67561266204</v>
+        <v>46181.508945995374</v>
       </c>
       <c r="D31" s="8">
-        <v>46181.67562327546</v>
+        <v>46181.5089566088</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3554,13 +3554,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46160.65244107639</v>
+        <v>46160.485774409724</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.67555267361</v>
+        <v>46181.508886006945</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.67555395833</v>
+        <v>46181.50888729167</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3615,13 +3615,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46160.65244578704</v>
+        <v>46160.48577912037</v>
       </c>
       <c r="C33" s="8">
-        <v>46181.67559679398</v>
+        <v>46181.50893012731</v>
       </c>
       <c r="D33" s="8">
-        <v>46181.67559840278</v>
+        <v>46181.50893173611</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3676,13 +3676,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46160.652450625</v>
+        <v>46160.485783958335</v>
       </c>
       <c r="C34" s="5">
-        <v>46181.67547991898</v>
+        <v>46181.508813252316</v>
       </c>
       <c r="D34" s="5">
-        <v>46181.67549369213</v>
+        <v>46181.508827025464</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3741,13 +3741,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46160.65245552083</v>
+        <v>46160.48578885417</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.67541125</v>
+        <v>46181.508744583334</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.67541268519</v>
+        <v>46181.50874601852</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3802,13 +3802,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46160.65246048611</v>
+        <v>46160.48579381945</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.675452662035</v>
+        <v>46181.50878599537</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.67545391204</v>
+        <v>46181.50878724537</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3863,13 +3863,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46160.6524655324</v>
+        <v>46160.485798865746</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.675465057866</v>
+        <v>46181.50879839121</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.67546648148</v>
+        <v>46181.508799814816</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3924,11 +3924,11 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46160.6566696875</v>
+        <v>46160.49000302084</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46197.19306372685</v>
+        <v>46197.02639706018</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3987,13 +3987,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46160.65676351852</v>
+        <v>46160.49009685185</v>
       </c>
       <c r="C39" s="8">
-        <v>46182.67674130787</v>
+        <v>46182.510074641206</v>
       </c>
       <c r="D39" s="8">
-        <v>46182.67674333333</v>
+        <v>46182.510076666666</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>114</v>
@@ -4042,11 +4042,11 @@
         <v>155</v>
       </c>
       <c r="B40" s="5">
-        <v>46160.65688415509</v>
+        <v>46160.49021748843</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46196.16898914352</v>
+        <v>46196.00232247685</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>156</v>
@@ -4095,13 +4095,13 @@
         <v>158</v>
       </c>
       <c r="B41" s="8">
-        <v>46160.65247015047</v>
+        <v>46160.485803483796</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.67623252315</v>
+        <v>46181.50956585648</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.676244386574</v>
+        <v>46181.5095777199</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>159</v>
@@ -4160,13 +4160,13 @@
         <v>163</v>
       </c>
       <c r="B42" s="5">
-        <v>46160.65247482639</v>
+        <v>46160.48580815972</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.676148715276</v>
+        <v>46181.50948204861</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.67615008102</v>
+        <v>46181.50948341435</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>164</v>
@@ -4221,13 +4221,13 @@
         <v>166</v>
       </c>
       <c r="B43" s="8">
-        <v>46160.65247959491</v>
+        <v>46160.48581292824</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.67621893519</v>
+        <v>46181.509552268515</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.67622016204</v>
+        <v>46181.50955349537</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>167</v>
@@ -4282,13 +4282,13 @@
         <v>169</v>
       </c>
       <c r="B44" s="5">
-        <v>46160.65254070602</v>
+        <v>46160.485874039354</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.67635490741</v>
+        <v>46181.50968824074</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.67636662037</v>
+        <v>46181.509699953705</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>170</v>
@@ -4347,13 +4347,13 @@
         <v>172</v>
       </c>
       <c r="B45" s="8">
-        <v>46160.65254572917</v>
+        <v>46160.4858790625</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.67630011574</v>
+        <v>46181.50963344907</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.67630162037</v>
+        <v>46181.509634953705</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>105</v>
@@ -4402,13 +4402,13 @@
         <v>174</v>
       </c>
       <c r="B46" s="5">
-        <v>46160.652551377316</v>
+        <v>46160.48588471065</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.676339375</v>
+        <v>46181.50967270833</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.67634090278</v>
+        <v>46181.50967423611</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>175</v>
@@ -4457,13 +4457,13 @@
         <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46160.652557152775</v>
+        <v>46160.48589048611</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.67648052084</v>
+        <v>46181.509813854165</v>
       </c>
       <c r="D47" s="8">
-        <v>46198.206338171294</v>
+        <v>46198.03967150463</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>178</v>
@@ -4522,13 +4522,13 @@
         <v>182</v>
       </c>
       <c r="B48" s="5">
-        <v>46160.65256162037</v>
+        <v>46160.4858949537</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.67638747685</v>
+        <v>46181.50972081019</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.67638900463</v>
+        <v>46181.50972233796</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>111</v>
@@ -4577,13 +4577,13 @@
         <v>184</v>
       </c>
       <c r="B49" s="8">
-        <v>46160.6525734375</v>
+        <v>46160.48590677083</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.676427557875</v>
+        <v>46181.509760891204</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.67642934028</v>
+        <v>46181.50976267361</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>185</v>
@@ -4632,13 +4632,13 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46160.652579236106</v>
+        <v>46160.48591256945</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.67646592592</v>
+        <v>46181.509799259264</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.676467303245</v>
+        <v>46181.50980063657</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4687,13 +4687,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46160.65258304398</v>
+        <v>46160.485916377314</v>
       </c>
       <c r="C51" s="8">
-        <v>46181.676567789356</v>
+        <v>46181.509901122685</v>
       </c>
       <c r="D51" s="8">
-        <v>46181.67657885417</v>
+        <v>46181.509912187496</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4752,13 +4752,13 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46160.6525875463</v>
+        <v>46160.485920879626</v>
       </c>
       <c r="C52" s="5">
-        <v>46181.676511840276</v>
+        <v>46181.50984517361</v>
       </c>
       <c r="D52" s="5">
-        <v>46181.67651314815</v>
+        <v>46181.50984648148</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4807,13 +4807,13 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46160.652593067134</v>
+        <v>46160.48592640046</v>
       </c>
       <c r="C53" s="8">
-        <v>46181.67655238426</v>
+        <v>46181.50988571759</v>
       </c>
       <c r="D53" s="8">
-        <v>46181.676553680554</v>
+        <v>46181.50988701389</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4862,13 +4862,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46160.65225516204</v>
+        <v>46160.48558849537</v>
       </c>
       <c r="C54" s="5">
-        <v>46181.612413587965</v>
+        <v>46181.445746921294</v>
       </c>
       <c r="D54" s="5">
-        <v>46181.67858451389</v>
+        <v>46181.51191784722</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4911,13 +4911,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46160.65259921296</v>
+        <v>46160.4859325463</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.61232818287</v>
+        <v>46181.445661516205</v>
       </c>
       <c r="D55" s="8">
-        <v>46197.712640196754</v>
+        <v>46197.5459735301</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4976,13 +4976,13 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46160.652606006945</v>
+        <v>46160.48593934027</v>
       </c>
       <c r="C56" s="5">
-        <v>46181.675721631946</v>
+        <v>46181.50905496528</v>
       </c>
       <c r="D56" s="5">
-        <v>46197.71267317129</v>
+        <v>46197.54600650463</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>208</v>
@@ -5041,13 +5041,13 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46160.65261409723</v>
+        <v>46160.485947430556</v>
       </c>
       <c r="C57" s="8">
-        <v>46181.67576423611</v>
+        <v>46181.50909756945</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.67578048611</v>
+        <v>46181.50911381944</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>100</v>
@@ -5106,13 +5106,13 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46160.652630983794</v>
+        <v>46160.48596431713</v>
       </c>
       <c r="C58" s="5">
-        <v>46198.56611644676</v>
+        <v>46198.39944978009</v>
       </c>
       <c r="D58" s="5">
-        <v>46198.566261608794</v>
+        <v>46198.39959494213</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>
@@ -5171,13 +5171,13 @@
         <v>220</v>
       </c>
       <c r="B59" s="8">
-        <v>46160.65263532408</v>
+        <v>46160.485968657405</v>
       </c>
       <c r="C59" s="8">
-        <v>46198.56608402778</v>
+        <v>46198.39941736111</v>
       </c>
       <c r="D59" s="8">
-        <v>46198.566085625</v>
+        <v>46198.39941895833</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>221</v>
@@ -5226,13 +5226,13 @@
         <v>223</v>
       </c>
       <c r="B60" s="5">
-        <v>46160.65264069445</v>
+        <v>46160.485974027775</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.566099675925</v>
+        <v>46198.39943300926</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.5661015625</v>
+        <v>46198.39943489584</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5281,13 +5281,13 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46160.652676921294</v>
+        <v>46160.48601025463</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.612796331014</v>
+        <v>46181.44612966436</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.67816971065</v>
+        <v>46181.51150304398</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5330,13 +5330,13 @@
         <v>228</v>
       </c>
       <c r="B62" s="5">
-        <v>46160.65268083333</v>
+        <v>46160.486014166665</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.67658946759</v>
+        <v>46181.50992280093</v>
       </c>
       <c r="D62" s="5">
-        <v>46182.19861893519</v>
+        <v>46182.03195226852</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5395,13 +5395,13 @@
         <v>233</v>
       </c>
       <c r="B63" s="8">
-        <v>46160.652685810186</v>
+        <v>46160.486019143515</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.67668319444</v>
+        <v>46181.510016527776</v>
       </c>
       <c r="D63" s="8">
-        <v>46184.17212899306</v>
+        <v>46184.005462326386</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>234</v>
@@ -5460,13 +5460,13 @@
         <v>237</v>
       </c>
       <c r="B64" s="5">
-        <v>46160.65269097222</v>
+        <v>46160.48602430556</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.67660690972</v>
+        <v>46181.50994024306</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.6766224537</v>
+        <v>46181.50995578704</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>238</v>
@@ -5525,13 +5525,13 @@
         <v>240</v>
       </c>
       <c r="B65" s="8">
-        <v>46160.65269633102</v>
+        <v>46160.48602966435</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.67669797454</v>
+        <v>46181.51003130787</v>
       </c>
       <c r="D65" s="8">
-        <v>46184.17212899306</v>
+        <v>46184.005462326386</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>241</v>
@@ -5590,13 +5590,13 @@
         <v>242</v>
       </c>
       <c r="B66" s="5">
-        <v>46160.65269980324</v>
+        <v>46160.48603313658</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.67666710648</v>
+        <v>46181.51000043981</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.67666866898</v>
+        <v>46181.51000200232</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>243</v>
@@ -5655,13 +5655,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46160.652703935186</v>
+        <v>46160.48603726852</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.67671591435</v>
+        <v>46181.510049247685</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.172129004626</v>
+        <v>46184.00546233796</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5720,13 +5720,13 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46160.65270767361</v>
+        <v>46160.486041006945</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.61286469907</v>
+        <v>46181.44619803241</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.6781084838</v>
+        <v>46181.51144181713</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5769,13 +5769,13 @@
         <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46160.65271061343</v>
+        <v>46160.48604394676</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.676856307866</v>
+        <v>46181.51018964121</v>
       </c>
       <c r="D69" s="8">
-        <v>46189.195743599535</v>
+        <v>46189.02907693287</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5834,13 +5834,13 @@
         <v>254</v>
       </c>
       <c r="B70" s="5">
-        <v>46160.65271650463</v>
+        <v>46160.486049837964</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.67682665509</v>
+        <v>46181.51015998842</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.67713434028</v>
+        <v>46181.51046767361</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>221</v>
@@ -5889,13 +5889,13 @@
         <v>257</v>
       </c>
       <c r="B71" s="8">
-        <v>46160.65272224537</v>
+        <v>46160.4860555787</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.67684240741</v>
+        <v>46181.51017574074</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.67713509259</v>
+        <v>46181.51046842593</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>221</v>
@@ -5944,13 +5944,13 @@
         <v>260</v>
       </c>
       <c r="B72" s="5">
-        <v>46160.652726898144</v>
+        <v>46160.48606023148</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.677226064814</v>
+        <v>46181.51055939815</v>
       </c>
       <c r="D72" s="5">
-        <v>46196.198199756946</v>
+        <v>46196.03153309028</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>261</v>
@@ -6009,13 +6009,13 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46160.65273052083</v>
+        <v>46160.486063854165</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.677197129626</v>
+        <v>46181.51053046296</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.67719854167</v>
+        <v>46181.510531875</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>221</v>
@@ -6064,13 +6064,13 @@
         <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46160.652741620375</v>
+        <v>46160.486074953704</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.67721283565</v>
+        <v>46181.51054616898</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.67721436343</v>
+        <v>46181.51054769676</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>259</v>
@@ -6119,13 +6119,13 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46160.65274630787</v>
+        <v>46160.4860796412</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.67728712963</v>
+        <v>46181.51062046296</v>
       </c>
       <c r="D75" s="8">
-        <v>46197.19306369213</v>
+        <v>46197.02639702546</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>
@@ -6184,13 +6184,13 @@
         <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46160.65275005787</v>
+        <v>46160.4860833912</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.67726334491</v>
+        <v>46181.51059667824</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.67726512731</v>
+        <v>46181.51059846065</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>221</v>
@@ -6239,13 +6239,13 @@
         <v>271</v>
       </c>
       <c r="B77" s="8">
-        <v>46160.65275548611</v>
+        <v>46160.486088819445</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.67727303241</v>
+        <v>46181.510606365744</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.677274664355</v>
+        <v>46181.51060799768</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>221</v>
@@ -6294,13 +6294,13 @@
         <v>274</v>
       </c>
       <c r="B78" s="5">
-        <v>46160.652760625</v>
+        <v>46160.48609395833</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.6130322338</v>
+        <v>46181.44636556713</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.67751854166</v>
+        <v>46181.510851875</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>226</v>
@@ -6343,13 +6343,13 @@
         <v>276</v>
       </c>
       <c r="B79" s="8">
-        <v>46160.65276340277</v>
+        <v>46160.48609673612</v>
       </c>
       <c r="C79" s="8">
-        <v>46181.67731516204</v>
+        <v>46181.51064849537</v>
       </c>
       <c r="D79" s="8">
-        <v>46192.20460657407</v>
+        <v>46192.03793990741</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>277</v>
@@ -6408,13 +6408,13 @@
         <v>279</v>
       </c>
       <c r="B80" s="5">
-        <v>46160.652768831016</v>
+        <v>46160.48610216435</v>
       </c>
       <c r="C80" s="5">
-        <v>46181.67732524306</v>
+        <v>46181.510658576386</v>
       </c>
       <c r="D80" s="5">
-        <v>46181.677345034725</v>
+        <v>46181.51067836805</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>280</v>
@@ -6473,13 +6473,13 @@
         <v>281</v>
       </c>
       <c r="B81" s="8">
-        <v>46160.652774409726</v>
+        <v>46160.486107743054</v>
       </c>
       <c r="C81" s="8">
-        <v>46181.67733638889</v>
+        <v>46181.51066972222</v>
       </c>
       <c r="D81" s="8">
-        <v>46181.67735619213</v>
+        <v>46181.51068952546</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>282</v>
@@ -6538,13 +6538,13 @@
         <v>283</v>
       </c>
       <c r="B82" s="5">
-        <v>46160.652779745375</v>
+        <v>46160.4861130787</v>
       </c>
       <c r="C82" s="5">
-        <v>46181.677345601856</v>
+        <v>46181.510678935185</v>
       </c>
       <c r="D82" s="5">
-        <v>46181.67736313658</v>
+        <v>46181.51069646991</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6603,11 +6603,11 @@
         <v>286</v>
       </c>
       <c r="B83" s="8">
-        <v>46160.657067569446</v>
+        <v>46160.49040090278</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46198.18861751157</v>
+        <v>46198.02195084491</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>61</v>
@@ -6666,13 +6666,13 @@
         <v>287</v>
       </c>
       <c r="B84" s="5">
-        <v>46160.65278418981</v>
+        <v>46160.48611752315</v>
       </c>
       <c r="C84" s="5">
-        <v>46181.617794328704</v>
+        <v>46181.45112766203</v>
       </c>
       <c r="D84" s="5">
-        <v>46197.49724974537</v>
+        <v>46197.3305830787</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>288</v>
@@ -6717,13 +6717,13 @@
         <v>290</v>
       </c>
       <c r="B85" s="8">
-        <v>46160.65278701389</v>
+        <v>46160.486120347225</v>
       </c>
       <c r="C85" s="8">
-        <v>46181.67760038194</v>
+        <v>46181.51093371528</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.17484756945</v>
+        <v>46196.008180902776</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>291</v>
@@ -6782,13 +6782,13 @@
         <v>293</v>
       </c>
       <c r="B86" s="5">
-        <v>46160.65279357639</v>
+        <v>46160.486126909724</v>
       </c>
       <c r="C86" s="5">
-        <v>46181.677674942126</v>
+        <v>46181.51100827546</v>
       </c>
       <c r="D86" s="5">
-        <v>46181.67767618055</v>
+        <v>46181.51100951389</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>221</v>
@@ -6837,13 +6837,13 @@
         <v>295</v>
       </c>
       <c r="B87" s="8">
-        <v>46160.65279733796</v>
+        <v>46160.4861306713</v>
       </c>
       <c r="C87" s="8">
-        <v>46181.677687511576</v>
+        <v>46181.511020844904</v>
       </c>
       <c r="D87" s="8">
-        <v>46181.677689247685</v>
+        <v>46181.51102258102</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>221</v>
@@ -6892,13 +6892,13 @@
         <v>296</v>
       </c>
       <c r="B88" s="5">
-        <v>46160.65280108796</v>
+        <v>46160.4861344213</v>
       </c>
       <c r="C88" s="5">
-        <v>46181.67776662037</v>
+        <v>46181.5110999537</v>
       </c>
       <c r="D88" s="5">
-        <v>46197.19052525463</v>
+        <v>46197.02385858796</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>297</v>
@@ -6957,13 +6957,13 @@
         <v>298</v>
       </c>
       <c r="B89" s="8">
-        <v>46160.65280498842</v>
+        <v>46160.48613832176</v>
       </c>
       <c r="C89" s="8">
-        <v>46181.677741273146</v>
+        <v>46181.51107460648</v>
       </c>
       <c r="D89" s="8">
-        <v>46181.67774287037</v>
+        <v>46181.51107620371</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>221</v>
@@ -7012,13 +7012,13 @@
         <v>301</v>
       </c>
       <c r="B90" s="5">
-        <v>46160.65281013889</v>
+        <v>46160.486143472226</v>
       </c>
       <c r="C90" s="5">
-        <v>46181.677753344906</v>
+        <v>46181.51108667824</v>
       </c>
       <c r="D90" s="5">
-        <v>46181.67775488426</v>
+        <v>46181.511088217594</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>221</v>
@@ -7067,13 +7067,13 @@
         <v>302</v>
       </c>
       <c r="B91" s="8">
-        <v>46160.65281503472</v>
+        <v>46160.48614836806</v>
       </c>
       <c r="C91" s="8">
-        <v>46181.67783773148</v>
+        <v>46181.51117106482</v>
       </c>
       <c r="D91" s="8">
-        <v>46198.20633876158</v>
+        <v>46198.03967209491</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>303</v>
@@ -7132,13 +7132,13 @@
         <v>304</v>
       </c>
       <c r="B92" s="5">
-        <v>46160.65281883102</v>
+        <v>46160.48615216435</v>
       </c>
       <c r="C92" s="5">
-        <v>46181.67779599537</v>
+        <v>46181.511129328705</v>
       </c>
       <c r="D92" s="5">
-        <v>46181.677797627315</v>
+        <v>46181.511130960644</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>221</v>
@@ -7185,13 +7185,13 @@
         <v>306</v>
       </c>
       <c r="B93" s="8">
-        <v>46160.65287608796</v>
+        <v>46160.486209421295</v>
       </c>
       <c r="C93" s="8">
-        <v>46181.67780578704</v>
+        <v>46181.51113912037</v>
       </c>
       <c r="D93" s="8">
-        <v>46181.67780725694</v>
+        <v>46181.51114059028</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>221</v>
@@ -7238,13 +7238,13 @@
         <v>307</v>
       </c>
       <c r="B94" s="5">
-        <v>46160.65288447917</v>
+        <v>46160.486217812504</v>
       </c>
       <c r="C94" s="5">
-        <v>46181.6778656713</v>
+        <v>46181.51119900463</v>
       </c>
       <c r="D94" s="5">
-        <v>46181.677878726856</v>
+        <v>46181.511212060184</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>308</v>
@@ -7303,13 +7303,13 @@
         <v>309</v>
       </c>
       <c r="B95" s="8">
-        <v>46160.65288969908</v>
+        <v>46160.48622303241</v>
       </c>
       <c r="C95" s="8">
-        <v>46181.67784234954</v>
+        <v>46181.51117568287</v>
       </c>
       <c r="D95" s="8">
-        <v>46181.67784412037</v>
+        <v>46181.51117745371</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>221</v>
@@ -7358,13 +7358,13 @@
         <v>312</v>
       </c>
       <c r="B96" s="5">
-        <v>46160.6528953588</v>
+        <v>46160.48622869213</v>
       </c>
       <c r="C96" s="5">
-        <v>46181.67784924769</v>
+        <v>46181.511182581016</v>
       </c>
       <c r="D96" s="5">
-        <v>46181.677850625</v>
+        <v>46181.51118395833</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>221</v>
@@ -7413,13 +7413,13 @@
         <v>313</v>
       </c>
       <c r="B97" s="8">
-        <v>46160.652900706016</v>
+        <v>46160.48623403935</v>
       </c>
       <c r="C97" s="8">
-        <v>46181.677918587964</v>
+        <v>46181.5112519213</v>
       </c>
       <c r="D97" s="8">
-        <v>46181.67793089121</v>
+        <v>46181.51126422454</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>314</v>
@@ -7478,13 +7478,13 @@
         <v>315</v>
       </c>
       <c r="B98" s="5">
-        <v>46160.65290569444</v>
+        <v>46160.48623902778</v>
       </c>
       <c r="C98" s="5">
-        <v>46181.6778925463</v>
+        <v>46181.51122587963</v>
       </c>
       <c r="D98" s="5">
-        <v>46181.67789438658</v>
+        <v>46181.51122771991</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>221</v>
@@ -7533,13 +7533,13 @@
         <v>317</v>
       </c>
       <c r="B99" s="8">
-        <v>46160.652911157405</v>
+        <v>46160.48624449074</v>
       </c>
       <c r="C99" s="8">
-        <v>46181.67790297454</v>
+        <v>46181.511236307866</v>
       </c>
       <c r="D99" s="8">
-        <v>46181.67790501157</v>
+        <v>46181.51123834491</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>221</v>
@@ -7588,13 +7588,13 @@
         <v>318</v>
       </c>
       <c r="B100" s="5">
-        <v>46160.65291657408</v>
+        <v>46160.48624990741</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.49723263889</v>
+        <v>46197.330565972225</v>
       </c>
       <c r="D100" s="5">
-        <v>46197.60306288194</v>
+        <v>46197.43639621528</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>319</v>
@@ -7653,13 +7653,13 @@
         <v>321</v>
       </c>
       <c r="B101" s="8">
-        <v>46160.652921562505</v>
+        <v>46160.48625489583</v>
       </c>
       <c r="C101" s="8">
-        <v>46197.60304642361</v>
+        <v>46197.436379756946</v>
       </c>
       <c r="D101" s="8">
-        <v>46198.56608928241</v>
+        <v>46198.39942261574</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>221</v>
@@ -7706,13 +7706,13 @@
         <v>323</v>
       </c>
       <c r="B102" s="5">
-        <v>46160.65292620371</v>
+        <v>46160.486259537036</v>
       </c>
       <c r="C102" s="5">
-        <v>46197.4972891088</v>
+        <v>46197.330622442125</v>
       </c>
       <c r="D102" s="5">
-        <v>46198.566110405096</v>
+        <v>46198.399443738424</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>221</v>
@@ -7759,11 +7759,11 @@
         <v>325</v>
       </c>
       <c r="B103" s="8">
-        <v>46160.65293084491</v>
+        <v>46160.48626417824</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46197.49766417824</v>
+        <v>46197.33099751157</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>326</v>
@@ -7806,11 +7806,11 @@
         <v>328</v>
       </c>
       <c r="B104" s="5">
-        <v>46160.65293431713</v>
+        <v>46160.48626765046</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46197.49724334491</v>
+        <v>46197.33057667824</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>329</v>
@@ -7869,11 +7869,11 @@
         <v>333</v>
       </c>
       <c r="B105" s="8">
-        <v>46160.65293966435</v>
+        <v>46160.48627299769</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46197.60305672453</v>
+        <v>46197.436390057876</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>221</v>
@@ -7922,11 +7922,11 @@
         <v>335</v>
       </c>
       <c r="B106" s="5">
-        <v>46160.652944201385</v>
+        <v>46160.48627753472</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46197.49729465278</v>
+        <v>46197.33062798611</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>221</v>
@@ -7975,11 +7975,11 @@
         <v>337</v>
       </c>
       <c r="B107" s="8">
-        <v>46160.80816486111</v>
+        <v>46160.64149819444</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46160.817732083335</v>
+        <v>46160.65106541666</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>338</v>
@@ -8028,11 +8028,11 @@
         <v>340</v>
       </c>
       <c r="B108" s="5">
-        <v>46160.80854525463</v>
+        <v>46160.641878587965</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46160.81773274306</v>
+        <v>46160.65106607639</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>338</v>
@@ -8081,13 +8081,13 @@
         <v>342</v>
       </c>
       <c r="B109" s="8">
-        <v>46160.65294850695</v>
+        <v>46160.486281840276</v>
       </c>
       <c r="C109" s="8">
-        <v>46197.49765626158</v>
+        <v>46197.330989594906</v>
       </c>
       <c r="D109" s="8">
-        <v>46197.497765231485</v>
+        <v>46197.33109856481</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>343</v>
@@ -8146,13 +8146,13 @@
         <v>345</v>
       </c>
       <c r="B110" s="5">
-        <v>46160.652952592594</v>
+        <v>46160.48628592593</v>
       </c>
       <c r="C110" s="5">
-        <v>46197.497369351855</v>
+        <v>46197.33070268518</v>
       </c>
       <c r="D110" s="5">
-        <v>46197.497371261576</v>
+        <v>46197.330704594904</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>221</v>
@@ -8201,13 +8201,13 @@
         <v>347</v>
       </c>
       <c r="B111" s="8">
-        <v>46160.65295699074</v>
+        <v>46160.48629032407</v>
       </c>
       <c r="C111" s="8">
-        <v>46197.497530023145</v>
+        <v>46197.33086335648</v>
       </c>
       <c r="D111" s="8">
-        <v>46197.49753173611</v>
+        <v>46197.330865069445</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>221</v>
@@ -8256,11 +8256,11 @@
         <v>348</v>
       </c>
       <c r="B112" s="5">
-        <v>46160.809122164355</v>
+        <v>46160.642455497684</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46197.4977528125</v>
+        <v>46197.33108614583</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>338</v>
@@ -8309,11 +8309,11 @@
         <v>350</v>
       </c>
       <c r="B113" s="8">
-        <v>46160.809137627315</v>
+        <v>46160.64247096065</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46197.497759895836</v>
+        <v>46197.331093229164</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>351</v>
@@ -8362,11 +8362,11 @@
         <v>352</v>
       </c>
       <c r="B114" s="5">
-        <v>46160.652961203705</v>
+        <v>46160.48629453704</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46194.05666876158</v>
+        <v>46193.89000209491</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>353</v>
@@ -8425,11 +8425,11 @@
         <v>355</v>
       </c>
       <c r="B115" s="8">
-        <v>46160.65296532407</v>
+        <v>46160.48629865741</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46197.49737577546</v>
+        <v>46197.33070910879</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>221</v>
@@ -8476,11 +8476,11 @@
         <v>357</v>
       </c>
       <c r="B116" s="5">
-        <v>46160.65297267361</v>
+        <v>46160.48630600695</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46197.49753788194</v>
+        <v>46197.33087121528</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>221</v>
@@ -8527,11 +8527,11 @@
         <v>359</v>
       </c>
       <c r="B117" s="8">
-        <v>46160.81088733797</v>
+        <v>46160.644220671296</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46197.49775597222</v>
+        <v>46197.33108930556</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>338</v>
@@ -8578,11 +8578,11 @@
         <v>361</v>
       </c>
       <c r="B118" s="5">
-        <v>46160.81089606481</v>
+        <v>46160.64422939815</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46197.49776570602</v>
+        <v>46197.33109903935</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>338</v>
@@ -8629,11 +8629,11 @@
         <v>362</v>
       </c>
       <c r="B119" s="8">
-        <v>46160.65297846065</v>
+        <v>46160.48631179398</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46183.89564782407</v>
+        <v>46183.72898115741</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>363</v>
@@ -8692,11 +8692,11 @@
         <v>365</v>
       </c>
       <c r="B120" s="5">
-        <v>46160.652983935186</v>
+        <v>46160.486317268515</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46194.054542048616</v>
+        <v>46193.887875381944</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>221</v>
@@ -8745,11 +8745,11 @@
         <v>366</v>
       </c>
       <c r="B121" s="8">
-        <v>46160.65298813657</v>
+        <v>46160.48632146991</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46194.056669247686</v>
+        <v>46193.890002581014</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>221</v>
@@ -8798,11 +8798,11 @@
         <v>367</v>
       </c>
       <c r="B122" s="5">
-        <v>46160.81215837963</v>
+        <v>46160.64549171296</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46194.05454575231</v>
+        <v>46193.88787908565</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>338</v>
@@ -8851,11 +8851,11 @@
         <v>368</v>
       </c>
       <c r="B123" s="8">
-        <v>46160.81220768519</v>
+        <v>46160.645541018515</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46194.05454428241</v>
+        <v>46193.887877615736</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>338</v>
@@ -8904,11 +8904,11 @@
         <v>369</v>
       </c>
       <c r="B124" s="5">
-        <v>46160.65302554399</v>
+        <v>46160.486358877315</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46160.8192895949</v>
+        <v>46160.65262292824</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>370</v>
@@ -8951,11 +8951,11 @@
         <v>372</v>
       </c>
       <c r="B125" s="8">
-        <v>46160.65302895833</v>
+        <v>46160.48636229167</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46160.819199722224</v>
+        <v>46160.65253305556</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>373</v>
@@ -9014,11 +9014,11 @@
         <v>376</v>
       </c>
       <c r="B126" s="5">
-        <v>46160.65303386574</v>
+        <v>46160.486367199075</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46160.81937795139</v>
+        <v>46160.652711284725</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>377</v>
@@ -9077,11 +9077,11 @@
         <v>379</v>
       </c>
       <c r="B127" s="8">
-        <v>46160.65808951389</v>
+        <v>46160.49142284722</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46160.819809513894</v>
+        <v>46160.65314284722</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>380</v>
@@ -9130,11 +9130,11 @@
         <v>382</v>
       </c>
       <c r="B128" s="5">
-        <v>46160.66095159722</v>
+        <v>46160.49428493055</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46160.81972457176</v>
+        <v>46160.65305790509</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>383</v>
@@ -9193,11 +9193,11 @@
         <v>385</v>
       </c>
       <c r="B129" s="8">
-        <v>46160.66107538194</v>
+        <v>46160.494408715276</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46160.8199466088</v>
+        <v>46160.653279942126</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>386</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -1836,13 +1836,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46160.48557077546</v>
+        <v>46160.65223744213</v>
       </c>
       <c r="C4" s="5">
-        <v>46167.39169478009</v>
+        <v>46167.55836144676</v>
       </c>
       <c r="D4" s="5">
-        <v>46181.512122534725</v>
+        <v>46181.67878920139</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1885,13 +1885,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46160.48568386574</v>
+        <v>46160.65235053241</v>
       </c>
       <c r="C5" s="8">
-        <v>46167.39166763889</v>
+        <v>46167.558334305555</v>
       </c>
       <c r="D5" s="8">
-        <v>46167.391668703705</v>
+        <v>46167.55833537037</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1948,13 +1948,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46160.48568737268</v>
+        <v>46160.652354039354</v>
       </c>
       <c r="C6" s="5">
-        <v>46167.39148954861</v>
+        <v>46167.55815621528</v>
       </c>
       <c r="D6" s="5">
-        <v>46167.39149064815</v>
+        <v>46167.558157314816</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2011,13 +2011,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46160.48569023148</v>
+        <v>46160.65235689815</v>
       </c>
       <c r="C7" s="8">
-        <v>46167.391522743055</v>
+        <v>46167.55818940973</v>
       </c>
       <c r="D7" s="8">
-        <v>46167.39152376157</v>
+        <v>46167.558190428244</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -2074,13 +2074,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46160.48569302083</v>
+        <v>46160.652359687505</v>
       </c>
       <c r="C8" s="5">
-        <v>46167.39156736111</v>
+        <v>46167.558234027776</v>
       </c>
       <c r="D8" s="5">
-        <v>46167.39156875</v>
+        <v>46167.55823541667</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -2137,13 +2137,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46160.48569648148</v>
+        <v>46160.65236314815</v>
       </c>
       <c r="C9" s="8">
-        <v>46167.391679444445</v>
+        <v>46167.55834611111</v>
       </c>
       <c r="D9" s="8">
-        <v>46167.391680636574</v>
+        <v>46167.558347303246</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2200,11 +2200,11 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46160.48702451389</v>
+        <v>46160.65369118056</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46167.391623668984</v>
+        <v>46167.55829033565</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2253,13 +2253,13 @@
         <v>52</v>
       </c>
       <c r="B11" s="8">
-        <v>46160.48742520833</v>
+        <v>46160.654091874996</v>
       </c>
       <c r="C11" s="8">
-        <v>46167.391617326386</v>
+        <v>46167.55828399306</v>
       </c>
       <c r="D11" s="8">
-        <v>46167.39162951389</v>
+        <v>46167.558296180556</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>53</v>
@@ -2318,11 +2318,11 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46160.48750545139</v>
+        <v>46160.654172118055</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46198.002354675926</v>
+        <v>46198.16902134259</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2381,11 +2381,11 @@
         <v>64</v>
       </c>
       <c r="B13" s="8">
-        <v>46160.485575405095</v>
+        <v>46160.65224207176</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46167.39227378472</v>
+        <v>46167.55894045139</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>65</v>
@@ -2428,13 +2428,13 @@
         <v>67</v>
       </c>
       <c r="B14" s="5">
-        <v>46160.48569984954</v>
+        <v>46160.6523665162</v>
       </c>
       <c r="C14" s="5">
-        <v>46167.39225503472</v>
+        <v>46167.55892170139</v>
       </c>
       <c r="D14" s="5">
-        <v>46167.39226771991</v>
+        <v>46167.55893438657</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>68</v>
@@ -2493,13 +2493,13 @@
         <v>71</v>
       </c>
       <c r="B15" s="8">
-        <v>46160.48570503472</v>
+        <v>46160.65237170139</v>
       </c>
       <c r="C15" s="8">
-        <v>46167.392260057866</v>
+        <v>46167.55892672454</v>
       </c>
       <c r="D15" s="8">
-        <v>46167.39227575231</v>
+        <v>46167.55894241898</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>72</v>
@@ -2558,13 +2558,13 @@
         <v>75</v>
       </c>
       <c r="B16" s="5">
-        <v>46160.48571020833</v>
+        <v>46160.652376875005</v>
       </c>
       <c r="C16" s="5">
-        <v>46167.39226748842</v>
+        <v>46167.558934155095</v>
       </c>
       <c r="D16" s="5">
-        <v>46167.392280879634</v>
+        <v>46167.55894754629</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>76</v>
@@ -2623,11 +2623,11 @@
         <v>78</v>
       </c>
       <c r="B17" s="8">
-        <v>46160.48571533565</v>
+        <v>46160.652382002314</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46167.39227512731</v>
+        <v>46167.55894179398</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>79</v>
@@ -2686,13 +2686,13 @@
         <v>83</v>
       </c>
       <c r="B18" s="5">
-        <v>46160.485579479166</v>
+        <v>46160.65224614584</v>
       </c>
       <c r="C18" s="5">
-        <v>46181.446006122686</v>
+        <v>46181.61267278936</v>
       </c>
       <c r="D18" s="5">
-        <v>46181.512035567124</v>
+        <v>46181.678702233796</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>84</v>
@@ -2735,13 +2735,13 @@
         <v>86</v>
       </c>
       <c r="B19" s="8">
-        <v>46160.485722893514</v>
+        <v>46160.652389560186</v>
       </c>
       <c r="C19" s="8">
-        <v>46167.39229795139</v>
+        <v>46167.55896461806</v>
       </c>
       <c r="D19" s="8">
-        <v>46167.39231096065</v>
+        <v>46167.55897762731</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>87</v>
@@ -2800,13 +2800,13 @@
         <v>89</v>
       </c>
       <c r="B20" s="5">
-        <v>46160.485728252315</v>
+        <v>46160.65239491899</v>
       </c>
       <c r="C20" s="5">
-        <v>46167.39232921296</v>
+        <v>46167.55899587963</v>
       </c>
       <c r="D20" s="5">
-        <v>46167.392345995366</v>
+        <v>46167.55901266204</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2865,13 +2865,13 @@
         <v>92</v>
       </c>
       <c r="B21" s="8">
-        <v>46160.485733622685</v>
+        <v>46160.65240028936</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.445580381944</v>
+        <v>46181.612247048615</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.445597997685</v>
+        <v>46181.61226466435</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>93</v>
@@ -2930,13 +2930,13 @@
         <v>96</v>
       </c>
       <c r="B22" s="5">
-        <v>46160.4857389699</v>
+        <v>46160.652405636574</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.446068969904</v>
+        <v>46181.612735636576</v>
       </c>
       <c r="D22" s="5">
-        <v>46181.509123125</v>
+        <v>46181.67578979167</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>97</v>
@@ -2995,13 +2995,13 @@
         <v>103</v>
       </c>
       <c r="B23" s="8">
-        <v>46160.48574392361</v>
+        <v>46160.65241059028</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.509155694446</v>
+        <v>46181.67582236111</v>
       </c>
       <c r="D23" s="8">
-        <v>46181.50917122685</v>
+        <v>46181.67583789352</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>104</v>
@@ -3060,13 +3060,13 @@
         <v>106</v>
       </c>
       <c r="B24" s="5">
-        <v>46160.485747824074</v>
+        <v>46160.652414490745</v>
       </c>
       <c r="C24" s="5">
-        <v>46181.509193645834</v>
+        <v>46181.675860312505</v>
       </c>
       <c r="D24" s="5">
-        <v>46181.50920886574</v>
+        <v>46181.67587553241</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>107</v>
@@ -3125,13 +3125,13 @@
         <v>109</v>
       </c>
       <c r="B25" s="8">
-        <v>46160.48575173611</v>
+        <v>46160.65241840278</v>
       </c>
       <c r="C25" s="8">
-        <v>46181.50920561343</v>
+        <v>46181.67587228009</v>
       </c>
       <c r="D25" s="8">
-        <v>46181.50922108797</v>
+        <v>46181.67588775463</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>110</v>
@@ -3190,13 +3190,13 @@
         <v>112</v>
       </c>
       <c r="B26" s="5">
-        <v>46160.49191201389</v>
+        <v>46160.65857868055</v>
       </c>
       <c r="C26" s="5">
-        <v>46167.39236136574</v>
+        <v>46167.55902803241</v>
       </c>
       <c r="D26" s="5">
-        <v>46167.392375868054</v>
+        <v>46167.55904253472</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>113</v>
@@ -3255,11 +3255,11 @@
         <v>115</v>
       </c>
       <c r="B27" s="8">
-        <v>46160.48558396991</v>
+        <v>46160.65225063657</v>
       </c>
       <c r="C27" s="9"/>
       <c r="D27" s="8">
-        <v>46181.51197298611</v>
+        <v>46181.678639652775</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>116</v>
@@ -3302,13 +3302,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46160.48575607639</v>
+        <v>46160.65242274306</v>
       </c>
       <c r="C28" s="5">
-        <v>46181.50902550926</v>
+        <v>46181.67569217592</v>
       </c>
       <c r="D28" s="5">
-        <v>46181.50904247686</v>
+        <v>46181.675709143514</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3367,13 +3367,13 @@
         <v>123</v>
       </c>
       <c r="B29" s="8">
-        <v>46160.48576053241</v>
+        <v>46160.65242719908</v>
       </c>
       <c r="C29" s="8">
-        <v>46181.50896636574</v>
+        <v>46181.675633032406</v>
       </c>
       <c r="D29" s="8">
-        <v>46181.50896782408</v>
+        <v>46181.67563449074</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>124</v>
@@ -3428,13 +3428,13 @@
         <v>126</v>
       </c>
       <c r="B30" s="5">
-        <v>46160.485765150464</v>
+        <v>46160.65243181713</v>
       </c>
       <c r="C30" s="5">
-        <v>46181.509009664354</v>
+        <v>46181.67567633102</v>
       </c>
       <c r="D30" s="5">
-        <v>46181.50901123842</v>
+        <v>46181.67567790509</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>127</v>
@@ -3489,13 +3489,13 @@
         <v>129</v>
       </c>
       <c r="B31" s="8">
-        <v>46160.485770011575</v>
+        <v>46160.65243667824</v>
       </c>
       <c r="C31" s="8">
-        <v>46181.508945995374</v>
+        <v>46181.67561266204</v>
       </c>
       <c r="D31" s="8">
-        <v>46181.5089566088</v>
+        <v>46181.67562327546</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>130</v>
@@ -3554,13 +3554,13 @@
         <v>132</v>
       </c>
       <c r="B32" s="5">
-        <v>46160.485774409724</v>
+        <v>46160.65244107639</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.508886006945</v>
+        <v>46181.67555267361</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.50888729167</v>
+        <v>46181.67555395833</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>133</v>
@@ -3615,13 +3615,13 @@
         <v>135</v>
       </c>
       <c r="B33" s="8">
-        <v>46160.48577912037</v>
+        <v>46160.65244578704</v>
       </c>
       <c r="C33" s="8">
-        <v>46181.50893012731</v>
+        <v>46181.67559679398</v>
       </c>
       <c r="D33" s="8">
-        <v>46181.50893173611</v>
+        <v>46181.67559840278</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>136</v>
@@ -3676,13 +3676,13 @@
         <v>138</v>
       </c>
       <c r="B34" s="5">
-        <v>46160.485783958335</v>
+        <v>46160.652450625</v>
       </c>
       <c r="C34" s="5">
-        <v>46181.508813252316</v>
+        <v>46181.67547991898</v>
       </c>
       <c r="D34" s="5">
-        <v>46181.508827025464</v>
+        <v>46181.67549369213</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>139</v>
@@ -3741,13 +3741,13 @@
         <v>141</v>
       </c>
       <c r="B35" s="8">
-        <v>46160.48578885417</v>
+        <v>46160.65245552083</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.508744583334</v>
+        <v>46181.67541125</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.50874601852</v>
+        <v>46181.67541268519</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>142</v>
@@ -3802,13 +3802,13 @@
         <v>144</v>
       </c>
       <c r="B36" s="5">
-        <v>46160.48579381945</v>
+        <v>46160.65246048611</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.50878599537</v>
+        <v>46181.675452662035</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.50878724537</v>
+        <v>46181.67545391204</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>145</v>
@@ -3863,13 +3863,13 @@
         <v>147</v>
       </c>
       <c r="B37" s="8">
-        <v>46160.485798865746</v>
+        <v>46160.6524655324</v>
       </c>
       <c r="C37" s="8">
-        <v>46181.50879839121</v>
+        <v>46181.675465057866</v>
       </c>
       <c r="D37" s="8">
-        <v>46181.508799814816</v>
+        <v>46181.67546648148</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>148</v>
@@ -3924,11 +3924,11 @@
         <v>150</v>
       </c>
       <c r="B38" s="5">
-        <v>46160.49000302084</v>
+        <v>46160.6566696875</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="5">
-        <v>46197.02639706018</v>
+        <v>46197.19306372685</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>151</v>
@@ -3987,13 +3987,13 @@
         <v>153</v>
       </c>
       <c r="B39" s="8">
-        <v>46160.49009685185</v>
+        <v>46160.65676351852</v>
       </c>
       <c r="C39" s="8">
-        <v>46182.510074641206</v>
+        <v>46182.67674130787</v>
       </c>
       <c r="D39" s="8">
-        <v>46182.510076666666</v>
+        <v>46182.67674333333</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>114</v>
@@ -4042,11 +4042,11 @@
         <v>155</v>
       </c>
       <c r="B40" s="5">
-        <v>46160.49021748843</v>
+        <v>46160.65688415509</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46196.00232247685</v>
+        <v>46196.16898914352</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>156</v>
@@ -4095,13 +4095,13 @@
         <v>158</v>
       </c>
       <c r="B41" s="8">
-        <v>46160.485803483796</v>
+        <v>46160.65247015047</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.50956585648</v>
+        <v>46181.67623252315</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.5095777199</v>
+        <v>46181.676244386574</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>159</v>
@@ -4160,13 +4160,13 @@
         <v>163</v>
       </c>
       <c r="B42" s="5">
-        <v>46160.48580815972</v>
+        <v>46160.65247482639</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.50948204861</v>
+        <v>46181.676148715276</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.50948341435</v>
+        <v>46181.67615008102</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>164</v>
@@ -4221,13 +4221,13 @@
         <v>166</v>
       </c>
       <c r="B43" s="8">
-        <v>46160.48581292824</v>
+        <v>46160.65247959491</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.509552268515</v>
+        <v>46181.67621893519</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.50955349537</v>
+        <v>46181.67622016204</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>167</v>
@@ -4282,13 +4282,13 @@
         <v>169</v>
       </c>
       <c r="B44" s="5">
-        <v>46160.485874039354</v>
+        <v>46160.65254070602</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.50968824074</v>
+        <v>46181.67635490741</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.509699953705</v>
+        <v>46181.67636662037</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>170</v>
@@ -4347,13 +4347,13 @@
         <v>172</v>
       </c>
       <c r="B45" s="8">
-        <v>46160.4858790625</v>
+        <v>46160.65254572917</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.50963344907</v>
+        <v>46181.67630011574</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.509634953705</v>
+        <v>46181.67630162037</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>105</v>
@@ -4402,13 +4402,13 @@
         <v>174</v>
       </c>
       <c r="B46" s="5">
-        <v>46160.48588471065</v>
+        <v>46160.652551377316</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.50967270833</v>
+        <v>46181.676339375</v>
       </c>
       <c r="D46" s="5">
-        <v>46181.50967423611</v>
+        <v>46181.67634090278</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>175</v>
@@ -4457,13 +4457,13 @@
         <v>177</v>
       </c>
       <c r="B47" s="8">
-        <v>46160.48589048611</v>
+        <v>46160.652557152775</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.509813854165</v>
+        <v>46181.67648052084</v>
       </c>
       <c r="D47" s="8">
-        <v>46198.03967150463</v>
+        <v>46198.206338171294</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>178</v>
@@ -4522,13 +4522,13 @@
         <v>182</v>
       </c>
       <c r="B48" s="5">
-        <v>46160.4858949537</v>
+        <v>46160.65256162037</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.50972081019</v>
+        <v>46181.67638747685</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.50972233796</v>
+        <v>46181.67638900463</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>111</v>
@@ -4577,13 +4577,13 @@
         <v>184</v>
       </c>
       <c r="B49" s="8">
-        <v>46160.48590677083</v>
+        <v>46160.6525734375</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.509760891204</v>
+        <v>46181.676427557875</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.50976267361</v>
+        <v>46181.67642934028</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>185</v>
@@ -4632,13 +4632,13 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46160.48591256945</v>
+        <v>46160.652579236106</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.509799259264</v>
+        <v>46181.67646592592</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.50980063657</v>
+        <v>46181.676467303245</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4687,13 +4687,13 @@
         <v>191</v>
       </c>
       <c r="B51" s="8">
-        <v>46160.485916377314</v>
+        <v>46160.65258304398</v>
       </c>
       <c r="C51" s="8">
-        <v>46181.509901122685</v>
+        <v>46181.676567789356</v>
       </c>
       <c r="D51" s="8">
-        <v>46181.509912187496</v>
+        <v>46181.67657885417</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>192</v>
@@ -4752,13 +4752,13 @@
         <v>194</v>
       </c>
       <c r="B52" s="5">
-        <v>46160.485920879626</v>
+        <v>46160.6525875463</v>
       </c>
       <c r="C52" s="5">
-        <v>46181.50984517361</v>
+        <v>46181.676511840276</v>
       </c>
       <c r="D52" s="5">
-        <v>46181.50984648148</v>
+        <v>46181.67651314815</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>108</v>
@@ -4807,13 +4807,13 @@
         <v>196</v>
       </c>
       <c r="B53" s="8">
-        <v>46160.48592640046</v>
+        <v>46160.652593067134</v>
       </c>
       <c r="C53" s="8">
-        <v>46181.50988571759</v>
+        <v>46181.67655238426</v>
       </c>
       <c r="D53" s="8">
-        <v>46181.50988701389</v>
+        <v>46181.676553680554</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>197</v>
@@ -4862,13 +4862,13 @@
         <v>199</v>
       </c>
       <c r="B54" s="5">
-        <v>46160.48558849537</v>
+        <v>46160.65225516204</v>
       </c>
       <c r="C54" s="5">
-        <v>46181.445746921294</v>
+        <v>46181.612413587965</v>
       </c>
       <c r="D54" s="5">
-        <v>46181.51191784722</v>
+        <v>46181.67858451389</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>200</v>
@@ -4911,13 +4911,13 @@
         <v>202</v>
       </c>
       <c r="B55" s="8">
-        <v>46160.4859325463</v>
+        <v>46160.65259921296</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.445661516205</v>
+        <v>46181.61232818287</v>
       </c>
       <c r="D55" s="8">
-        <v>46197.5459735301</v>
+        <v>46197.712640196754</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>203</v>
@@ -4976,13 +4976,13 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46160.48593934027</v>
+        <v>46160.652606006945</v>
       </c>
       <c r="C56" s="5">
-        <v>46181.50905496528</v>
+        <v>46181.675721631946</v>
       </c>
       <c r="D56" s="5">
-        <v>46197.54600650463</v>
+        <v>46197.71267317129</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>208</v>
@@ -5041,13 +5041,13 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46160.485947430556</v>
+        <v>46160.65261409723</v>
       </c>
       <c r="C57" s="8">
-        <v>46181.50909756945</v>
+        <v>46181.67576423611</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.50911381944</v>
+        <v>46181.67578048611</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>100</v>
@@ -5106,13 +5106,13 @@
         <v>215</v>
       </c>
       <c r="B58" s="5">
-        <v>46160.48596431713</v>
+        <v>46160.652630983794</v>
       </c>
       <c r="C58" s="5">
-        <v>46198.39944978009</v>
+        <v>46198.56611644676</v>
       </c>
       <c r="D58" s="5">
-        <v>46198.39959494213</v>
+        <v>46198.566261608794</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>216</v>
@@ -5171,13 +5171,13 @@
         <v>220</v>
       </c>
       <c r="B59" s="8">
-        <v>46160.485968657405</v>
+        <v>46160.65263532408</v>
       </c>
       <c r="C59" s="8">
-        <v>46198.39941736111</v>
+        <v>46198.56608402778</v>
       </c>
       <c r="D59" s="8">
-        <v>46198.39941895833</v>
+        <v>46198.566085625</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>221</v>
@@ -5226,13 +5226,13 @@
         <v>223</v>
       </c>
       <c r="B60" s="5">
-        <v>46160.485974027775</v>
+        <v>46160.65264069445</v>
       </c>
       <c r="C60" s="5">
-        <v>46198.39943300926</v>
+        <v>46198.566099675925</v>
       </c>
       <c r="D60" s="5">
-        <v>46198.39943489584</v>
+        <v>46198.5661015625</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>221</v>
@@ -5281,13 +5281,13 @@
         <v>225</v>
       </c>
       <c r="B61" s="8">
-        <v>46160.48601025463</v>
+        <v>46160.652676921294</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.44612966436</v>
+        <v>46181.612796331014</v>
       </c>
       <c r="D61" s="8">
-        <v>46181.51150304398</v>
+        <v>46181.67816971065</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>226</v>
@@ -5330,13 +5330,13 @@
         <v>228</v>
       </c>
       <c r="B62" s="5">
-        <v>46160.486014166665</v>
+        <v>46160.65268083333</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.50992280093</v>
+        <v>46181.67658946759</v>
       </c>
       <c r="D62" s="5">
-        <v>46182.03195226852</v>
+        <v>46182.19861893519</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>229</v>
@@ -5395,13 +5395,13 @@
         <v>233</v>
       </c>
       <c r="B63" s="8">
-        <v>46160.486019143515</v>
+        <v>46160.652685810186</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.510016527776</v>
+        <v>46181.67668319444</v>
       </c>
       <c r="D63" s="8">
-        <v>46184.005462326386</v>
+        <v>46184.17212899306</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>234</v>
@@ -5460,13 +5460,13 @@
         <v>237</v>
       </c>
       <c r="B64" s="5">
-        <v>46160.48602430556</v>
+        <v>46160.65269097222</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.50994024306</v>
+        <v>46181.67660690972</v>
       </c>
       <c r="D64" s="5">
-        <v>46181.50995578704</v>
+        <v>46181.6766224537</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>238</v>
@@ -5525,13 +5525,13 @@
         <v>240</v>
       </c>
       <c r="B65" s="8">
-        <v>46160.48602966435</v>
+        <v>46160.65269633102</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.51003130787</v>
+        <v>46181.67669797454</v>
       </c>
       <c r="D65" s="8">
-        <v>46184.005462326386</v>
+        <v>46184.17212899306</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>241</v>
@@ -5590,13 +5590,13 @@
         <v>242</v>
       </c>
       <c r="B66" s="5">
-        <v>46160.48603313658</v>
+        <v>46160.65269980324</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.51000043981</v>
+        <v>46181.67666710648</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.51000200232</v>
+        <v>46181.67666866898</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>243</v>
@@ -5655,13 +5655,13 @@
         <v>245</v>
       </c>
       <c r="B67" s="8">
-        <v>46160.48603726852</v>
+        <v>46160.652703935186</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.510049247685</v>
+        <v>46181.67671591435</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.00546233796</v>
+        <v>46184.172129004626</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>244</v>
@@ -5720,13 +5720,13 @@
         <v>246</v>
       </c>
       <c r="B68" s="5">
-        <v>46160.486041006945</v>
+        <v>46160.65270767361</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.44619803241</v>
+        <v>46181.61286469907</v>
       </c>
       <c r="D68" s="5">
-        <v>46181.51144181713</v>
+        <v>46181.6781084838</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>247</v>
@@ -5769,13 +5769,13 @@
         <v>249</v>
       </c>
       <c r="B69" s="8">
-        <v>46160.48604394676</v>
+        <v>46160.65271061343</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.51018964121</v>
+        <v>46181.676856307866</v>
       </c>
       <c r="D69" s="8">
-        <v>46189.02907693287</v>
+        <v>46189.195743599535</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>250</v>
@@ -5834,13 +5834,13 @@
         <v>254</v>
       </c>
       <c r="B70" s="5">
-        <v>46160.486049837964</v>
+        <v>46160.65271650463</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.51015998842</v>
+        <v>46181.67682665509</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.51046767361</v>
+        <v>46181.67713434028</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>221</v>
@@ -5889,13 +5889,13 @@
         <v>257</v>
       </c>
       <c r="B71" s="8">
-        <v>46160.4860555787</v>
+        <v>46160.65272224537</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.51017574074</v>
+        <v>46181.67684240741</v>
       </c>
       <c r="D71" s="8">
-        <v>46181.51046842593</v>
+        <v>46181.67713509259</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>221</v>
@@ -5944,13 +5944,13 @@
         <v>260</v>
       </c>
       <c r="B72" s="5">
-        <v>46160.48606023148</v>
+        <v>46160.652726898144</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.51055939815</v>
+        <v>46181.677226064814</v>
       </c>
       <c r="D72" s="5">
-        <v>46196.03153309028</v>
+        <v>46196.198199756946</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>261</v>
@@ -6009,13 +6009,13 @@
         <v>263</v>
       </c>
       <c r="B73" s="8">
-        <v>46160.486063854165</v>
+        <v>46160.65273052083</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.51053046296</v>
+        <v>46181.677197129626</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.510531875</v>
+        <v>46181.67719854167</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>221</v>
@@ -6064,13 +6064,13 @@
         <v>266</v>
       </c>
       <c r="B74" s="5">
-        <v>46160.486074953704</v>
+        <v>46160.652741620375</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.51054616898</v>
+        <v>46181.67721283565</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.51054769676</v>
+        <v>46181.67721436343</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>259</v>
@@ -6119,13 +6119,13 @@
         <v>267</v>
       </c>
       <c r="B75" s="8">
-        <v>46160.4860796412</v>
+        <v>46160.65274630787</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.51062046296</v>
+        <v>46181.67728712963</v>
       </c>
       <c r="D75" s="8">
-        <v>46197.02639702546</v>
+        <v>46197.19306369213</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>268</v>
@@ -6184,13 +6184,13 @@
         <v>269</v>
       </c>
       <c r="B76" s="5">
-        <v>46160.4860833912</v>
+        <v>46160.65275005787</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.51059667824</v>
+        <v>46181.67726334491</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.51059846065</v>
+        <v>46181.67726512731</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>221</v>
@@ -6239,13 +6239,13 @@
         <v>271</v>
       </c>
       <c r="B77" s="8">
-        <v>46160.486088819445</v>
+        <v>46160.65275548611</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.510606365744</v>
+        <v>46181.67727303241</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.51060799768</v>
+        <v>46181.677274664355</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>221</v>
@@ -6294,13 +6294,13 @@
         <v>274</v>
       </c>
       <c r="B78" s="5">
-        <v>46160.48609395833</v>
+        <v>46160.652760625</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.44636556713</v>
+        <v>46181.6130322338</v>
       </c>
       <c r="D78" s="5">
-        <v>46181.510851875</v>
+        <v>46181.67751854166</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>226</v>
@@ -6343,13 +6343,13 @@
         <v>276</v>
       </c>
       <c r="B79" s="8">
-        <v>46160.48609673612</v>
+        <v>46160.65276340277</v>
       </c>
       <c r="C79" s="8">
-        <v>46181.51064849537</v>
+        <v>46181.67731516204</v>
       </c>
       <c r="D79" s="8">
-        <v>46192.03793990741</v>
+        <v>46192.20460657407</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>277</v>
@@ -6408,13 +6408,13 @@
         <v>279</v>
       </c>
       <c r="B80" s="5">
-        <v>46160.48610216435</v>
+        <v>46160.652768831016</v>
       </c>
       <c r="C80" s="5">
-        <v>46181.510658576386</v>
+        <v>46181.67732524306</v>
       </c>
       <c r="D80" s="5">
-        <v>46181.51067836805</v>
+        <v>46181.677345034725</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>280</v>
@@ -6473,13 +6473,13 @@
         <v>281</v>
       </c>
       <c r="B81" s="8">
-        <v>46160.486107743054</v>
+        <v>46160.652774409726</v>
       </c>
       <c r="C81" s="8">
-        <v>46181.51066972222</v>
+        <v>46181.67733638889</v>
       </c>
       <c r="D81" s="8">
-        <v>46181.51068952546</v>
+        <v>46181.67735619213</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>282</v>
@@ -6538,13 +6538,13 @@
         <v>283</v>
       </c>
       <c r="B82" s="5">
-        <v>46160.4861130787</v>
+        <v>46160.652779745375</v>
       </c>
       <c r="C82" s="5">
-        <v>46181.510678935185</v>
+        <v>46181.677345601856</v>
       </c>
       <c r="D82" s="5">
-        <v>46181.51069646991</v>
+        <v>46181.67736313658</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6603,11 +6603,11 @@
         <v>286</v>
       </c>
       <c r="B83" s="8">
-        <v>46160.49040090278</v>
+        <v>46160.657067569446</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46198.02195084491</v>
+        <v>46198.18861751157</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>61</v>
@@ -6666,13 +6666,13 @@
         <v>287</v>
       </c>
       <c r="B84" s="5">
-        <v>46160.48611752315</v>
+        <v>46160.65278418981</v>
       </c>
       <c r="C84" s="5">
-        <v>46181.45112766203</v>
+        <v>46181.617794328704</v>
       </c>
       <c r="D84" s="5">
-        <v>46197.3305830787</v>
+        <v>46197.49724974537</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>288</v>
@@ -6717,13 +6717,13 @@
         <v>290</v>
       </c>
       <c r="B85" s="8">
-        <v>46160.486120347225</v>
+        <v>46160.65278701389</v>
       </c>
       <c r="C85" s="8">
-        <v>46181.51093371528</v>
+        <v>46181.67760038194</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.008180902776</v>
+        <v>46196.17484756945</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>291</v>
@@ -6782,13 +6782,13 @@
         <v>293</v>
       </c>
       <c r="B86" s="5">
-        <v>46160.486126909724</v>
+        <v>46160.65279357639</v>
       </c>
       <c r="C86" s="5">
-        <v>46181.51100827546</v>
+        <v>46181.677674942126</v>
       </c>
       <c r="D86" s="5">
-        <v>46181.51100951389</v>
+        <v>46181.67767618055</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>221</v>
@@ -6837,13 +6837,13 @@
         <v>295</v>
       </c>
       <c r="B87" s="8">
-        <v>46160.4861306713</v>
+        <v>46160.65279733796</v>
       </c>
       <c r="C87" s="8">
-        <v>46181.511020844904</v>
+        <v>46181.677687511576</v>
       </c>
       <c r="D87" s="8">
-        <v>46181.51102258102</v>
+        <v>46181.677689247685</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>221</v>
@@ -6892,13 +6892,13 @@
         <v>296</v>
       </c>
       <c r="B88" s="5">
-        <v>46160.4861344213</v>
+        <v>46160.65280108796</v>
       </c>
       <c r="C88" s="5">
-        <v>46181.5110999537</v>
+        <v>46181.67776662037</v>
       </c>
       <c r="D88" s="5">
-        <v>46197.02385858796</v>
+        <v>46197.19052525463</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>297</v>
@@ -6957,13 +6957,13 @@
         <v>298</v>
       </c>
       <c r="B89" s="8">
-        <v>46160.48613832176</v>
+        <v>46160.65280498842</v>
       </c>
       <c r="C89" s="8">
-        <v>46181.51107460648</v>
+        <v>46181.677741273146</v>
       </c>
       <c r="D89" s="8">
-        <v>46181.51107620371</v>
+        <v>46181.67774287037</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>221</v>
@@ -7012,13 +7012,13 @@
         <v>301</v>
       </c>
       <c r="B90" s="5">
-        <v>46160.486143472226</v>
+        <v>46160.65281013889</v>
       </c>
       <c r="C90" s="5">
-        <v>46181.51108667824</v>
+        <v>46181.677753344906</v>
       </c>
       <c r="D90" s="5">
-        <v>46181.511088217594</v>
+        <v>46181.67775488426</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>221</v>
@@ -7067,13 +7067,13 @@
         <v>302</v>
       </c>
       <c r="B91" s="8">
-        <v>46160.48614836806</v>
+        <v>46160.65281503472</v>
       </c>
       <c r="C91" s="8">
-        <v>46181.51117106482</v>
+        <v>46181.67783773148</v>
       </c>
       <c r="D91" s="8">
-        <v>46198.03967209491</v>
+        <v>46198.20633876158</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>303</v>
@@ -7132,13 +7132,13 @@
         <v>304</v>
       </c>
       <c r="B92" s="5">
-        <v>46160.48615216435</v>
+        <v>46160.65281883102</v>
       </c>
       <c r="C92" s="5">
-        <v>46181.511129328705</v>
+        <v>46181.67779599537</v>
       </c>
       <c r="D92" s="5">
-        <v>46181.511130960644</v>
+        <v>46181.677797627315</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>221</v>
@@ -7185,13 +7185,13 @@
         <v>306</v>
       </c>
       <c r="B93" s="8">
-        <v>46160.486209421295</v>
+        <v>46160.65287608796</v>
       </c>
       <c r="C93" s="8">
-        <v>46181.51113912037</v>
+        <v>46181.67780578704</v>
       </c>
       <c r="D93" s="8">
-        <v>46181.51114059028</v>
+        <v>46181.67780725694</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>221</v>
@@ -7238,13 +7238,13 @@
         <v>307</v>
       </c>
       <c r="B94" s="5">
-        <v>46160.486217812504</v>
+        <v>46160.65288447917</v>
       </c>
       <c r="C94" s="5">
-        <v>46181.51119900463</v>
+        <v>46181.6778656713</v>
       </c>
       <c r="D94" s="5">
-        <v>46181.511212060184</v>
+        <v>46181.677878726856</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>308</v>
@@ -7303,13 +7303,13 @@
         <v>309</v>
       </c>
       <c r="B95" s="8">
-        <v>46160.48622303241</v>
+        <v>46160.65288969908</v>
       </c>
       <c r="C95" s="8">
-        <v>46181.51117568287</v>
+        <v>46181.67784234954</v>
       </c>
       <c r="D95" s="8">
-        <v>46181.51117745371</v>
+        <v>46181.67784412037</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>221</v>
@@ -7358,13 +7358,13 @@
         <v>312</v>
       </c>
       <c r="B96" s="5">
-        <v>46160.48622869213</v>
+        <v>46160.6528953588</v>
       </c>
       <c r="C96" s="5">
-        <v>46181.511182581016</v>
+        <v>46181.67784924769</v>
       </c>
       <c r="D96" s="5">
-        <v>46181.51118395833</v>
+        <v>46181.677850625</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>221</v>
@@ -7413,13 +7413,13 @@
         <v>313</v>
       </c>
       <c r="B97" s="8">
-        <v>46160.48623403935</v>
+        <v>46160.652900706016</v>
       </c>
       <c r="C97" s="8">
-        <v>46181.5112519213</v>
+        <v>46181.677918587964</v>
       </c>
       <c r="D97" s="8">
-        <v>46181.51126422454</v>
+        <v>46181.67793089121</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>314</v>
@@ -7478,13 +7478,13 @@
         <v>315</v>
       </c>
       <c r="B98" s="5">
-        <v>46160.48623902778</v>
+        <v>46160.65290569444</v>
       </c>
       <c r="C98" s="5">
-        <v>46181.51122587963</v>
+        <v>46181.6778925463</v>
       </c>
       <c r="D98" s="5">
-        <v>46181.51122771991</v>
+        <v>46181.67789438658</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>221</v>
@@ -7533,13 +7533,13 @@
         <v>317</v>
       </c>
       <c r="B99" s="8">
-        <v>46160.48624449074</v>
+        <v>46160.652911157405</v>
       </c>
       <c r="C99" s="8">
-        <v>46181.511236307866</v>
+        <v>46181.67790297454</v>
       </c>
       <c r="D99" s="8">
-        <v>46181.51123834491</v>
+        <v>46181.67790501157</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>221</v>
@@ -7588,13 +7588,13 @@
         <v>318</v>
       </c>
       <c r="B100" s="5">
-        <v>46160.48624990741</v>
+        <v>46160.65291657408</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.330565972225</v>
+        <v>46197.49723263889</v>
       </c>
       <c r="D100" s="5">
-        <v>46197.43639621528</v>
+        <v>46197.60306288194</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>319</v>
@@ -7653,13 +7653,13 @@
         <v>321</v>
       </c>
       <c r="B101" s="8">
-        <v>46160.48625489583</v>
+        <v>46160.652921562505</v>
       </c>
       <c r="C101" s="8">
-        <v>46197.436379756946</v>
+        <v>46197.60304642361</v>
       </c>
       <c r="D101" s="8">
-        <v>46198.39942261574</v>
+        <v>46198.56608928241</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>221</v>
@@ -7706,13 +7706,13 @@
         <v>323</v>
       </c>
       <c r="B102" s="5">
-        <v>46160.486259537036</v>
+        <v>46160.65292620371</v>
       </c>
       <c r="C102" s="5">
-        <v>46197.330622442125</v>
+        <v>46197.4972891088</v>
       </c>
       <c r="D102" s="5">
-        <v>46198.399443738424</v>
+        <v>46198.566110405096</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>221</v>
@@ -7759,11 +7759,11 @@
         <v>325</v>
       </c>
       <c r="B103" s="8">
-        <v>46160.48626417824</v>
+        <v>46160.65293084491</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46197.33099751157</v>
+        <v>46197.49766417824</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>326</v>
@@ -7806,11 +7806,11 @@
         <v>328</v>
       </c>
       <c r="B104" s="5">
-        <v>46160.48626765046</v>
+        <v>46160.65293431713</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46197.33057667824</v>
+        <v>46197.49724334491</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>329</v>
@@ -7869,11 +7869,11 @@
         <v>333</v>
       </c>
       <c r="B105" s="8">
-        <v>46160.48627299769</v>
+        <v>46160.65293966435</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46197.436390057876</v>
+        <v>46197.60305672453</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>221</v>
@@ -7922,11 +7922,11 @@
         <v>335</v>
       </c>
       <c r="B106" s="5">
-        <v>46160.48627753472</v>
+        <v>46160.652944201385</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46197.33062798611</v>
+        <v>46197.49729465278</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>221</v>
@@ -7975,11 +7975,11 @@
         <v>337</v>
       </c>
       <c r="B107" s="8">
-        <v>46160.64149819444</v>
+        <v>46160.80816486111</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46160.65106541666</v>
+        <v>46160.817732083335</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>338</v>
@@ -8028,11 +8028,11 @@
         <v>340</v>
       </c>
       <c r="B108" s="5">
-        <v>46160.641878587965</v>
+        <v>46160.80854525463</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46160.65106607639</v>
+        <v>46160.81773274306</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>338</v>
@@ -8081,13 +8081,13 @@
         <v>342</v>
       </c>
       <c r="B109" s="8">
-        <v>46160.486281840276</v>
+        <v>46160.65294850695</v>
       </c>
       <c r="C109" s="8">
-        <v>46197.330989594906</v>
+        <v>46197.49765626158</v>
       </c>
       <c r="D109" s="8">
-        <v>46197.33109856481</v>
+        <v>46197.497765231485</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>343</v>
@@ -8146,13 +8146,13 @@
         <v>345</v>
       </c>
       <c r="B110" s="5">
-        <v>46160.48628592593</v>
+        <v>46160.652952592594</v>
       </c>
       <c r="C110" s="5">
-        <v>46197.33070268518</v>
+        <v>46197.497369351855</v>
       </c>
       <c r="D110" s="5">
-        <v>46197.330704594904</v>
+        <v>46197.497371261576</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>221</v>
@@ -8201,13 +8201,13 @@
         <v>347</v>
       </c>
       <c r="B111" s="8">
-        <v>46160.48629032407</v>
+        <v>46160.65295699074</v>
       </c>
       <c r="C111" s="8">
-        <v>46197.33086335648</v>
+        <v>46197.497530023145</v>
       </c>
       <c r="D111" s="8">
-        <v>46197.330865069445</v>
+        <v>46197.49753173611</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>221</v>
@@ -8256,11 +8256,11 @@
         <v>348</v>
       </c>
       <c r="B112" s="5">
-        <v>46160.642455497684</v>
+        <v>46160.809122164355</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46197.33108614583</v>
+        <v>46197.4977528125</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>338</v>
@@ -8309,11 +8309,11 @@
         <v>350</v>
       </c>
       <c r="B113" s="8">
-        <v>46160.64247096065</v>
+        <v>46160.809137627315</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46197.331093229164</v>
+        <v>46197.497759895836</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>351</v>
@@ -8362,11 +8362,11 @@
         <v>352</v>
       </c>
       <c r="B114" s="5">
-        <v>46160.48629453704</v>
+        <v>46160.652961203705</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46193.89000209491</v>
+        <v>46194.05666876158</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>353</v>
@@ -8425,11 +8425,11 @@
         <v>355</v>
       </c>
       <c r="B115" s="8">
-        <v>46160.48629865741</v>
+        <v>46160.65296532407</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46197.33070910879</v>
+        <v>46197.49737577546</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>221</v>
@@ -8476,11 +8476,11 @@
         <v>357</v>
       </c>
       <c r="B116" s="5">
-        <v>46160.48630600695</v>
+        <v>46160.65297267361</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46197.33087121528</v>
+        <v>46197.49753788194</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>221</v>
@@ -8527,11 +8527,11 @@
         <v>359</v>
       </c>
       <c r="B117" s="8">
-        <v>46160.644220671296</v>
+        <v>46160.81088733797</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46197.33108930556</v>
+        <v>46197.49775597222</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>338</v>
@@ -8578,11 +8578,11 @@
         <v>361</v>
       </c>
       <c r="B118" s="5">
-        <v>46160.64422939815</v>
+        <v>46160.81089606481</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46197.33109903935</v>
+        <v>46197.49776570602</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>338</v>
@@ -8629,11 +8629,11 @@
         <v>362</v>
       </c>
       <c r="B119" s="8">
-        <v>46160.48631179398</v>
+        <v>46160.65297846065</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46183.72898115741</v>
+        <v>46183.89564782407</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>363</v>
@@ -8692,11 +8692,11 @@
         <v>365</v>
       </c>
       <c r="B120" s="5">
-        <v>46160.486317268515</v>
+        <v>46160.652983935186</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46193.887875381944</v>
+        <v>46194.054542048616</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>221</v>
@@ -8745,11 +8745,11 @@
         <v>366</v>
       </c>
       <c r="B121" s="8">
-        <v>46160.48632146991</v>
+        <v>46160.65298813657</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46193.890002581014</v>
+        <v>46194.056669247686</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>221</v>
@@ -8798,11 +8798,11 @@
         <v>367</v>
       </c>
       <c r="B122" s="5">
-        <v>46160.64549171296</v>
+        <v>46160.81215837963</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46193.88787908565</v>
+        <v>46194.05454575231</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>338</v>
@@ -8851,11 +8851,11 @@
         <v>368</v>
       </c>
       <c r="B123" s="8">
-        <v>46160.645541018515</v>
+        <v>46160.81220768519</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46193.887877615736</v>
+        <v>46194.05454428241</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>338</v>
@@ -8904,11 +8904,11 @@
         <v>369</v>
       </c>
       <c r="B124" s="5">
-        <v>46160.486358877315</v>
+        <v>46160.65302554399</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46160.65262292824</v>
+        <v>46160.8192895949</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>370</v>
@@ -8951,11 +8951,11 @@
         <v>372</v>
       </c>
       <c r="B125" s="8">
-        <v>46160.48636229167</v>
+        <v>46160.65302895833</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46160.65253305556</v>
+        <v>46160.819199722224</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>373</v>
@@ -9014,11 +9014,11 @@
         <v>376</v>
       </c>
       <c r="B126" s="5">
-        <v>46160.486367199075</v>
+        <v>46160.65303386574</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46160.652711284725</v>
+        <v>46160.81937795139</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>377</v>
@@ -9077,11 +9077,11 @@
         <v>379</v>
       </c>
       <c r="B127" s="8">
-        <v>46160.49142284722</v>
+        <v>46160.65808951389</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46160.65314284722</v>
+        <v>46160.819809513894</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>380</v>
@@ -9130,11 +9130,11 @@
         <v>382</v>
       </c>
       <c r="B128" s="5">
-        <v>46160.49428493055</v>
+        <v>46160.66095159722</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46160.65305790509</v>
+        <v>46160.81972457176</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>383</v>
@@ -9193,11 +9193,11 @@
         <v>385</v>
       </c>
       <c r="B129" s="8">
-        <v>46160.494408715276</v>
+        <v>46160.66107538194</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46160.653279942126</v>
+        <v>46160.8199466088</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>386</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -234,7 +234,7 @@
     <t>Coordinacion Entrega con Cliente,Ingenieria Servicios ,OT 4314 - VDF VLT  FC 102,OT 4314 - VDF VLT  FC 102</t>
   </si>
   <si>
-    <t>Media</t>
+    <t>Alta</t>
   </si>
   <si>
     <t>1214892476594829</t>
@@ -357,9 +357,6 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser ot 4313</t>
   </si>
   <si>
-    <t>Alta</t>
-  </si>
-  <si>
     <t>1214909616779628</t>
   </si>
   <si>
@@ -595,6 +592,9 @@
   </si>
   <si>
     <t>Generacion OC Fabricación Externa ot 4313,Fabricación estructura proveedor externo ot 4313</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214909353558429</t>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46198.16902134259</v>
+        <v>46199.17997571759</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2366,7 +2366,7 @@
       <c r="R12" s="5">
         <v>46198</v>
       </c>
-      <c r="S12" s="12" t="s">
+      <c r="S12" s="11" t="s">
         <v>63</v>
       </c>
       <c r="T12" s="6">
@@ -2981,7 +2981,7 @@
         <v>46164</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B23" s="8">
         <v>46160.65241059028</v>
@@ -3004,7 +3004,7 @@
         <v>46181.67583789352</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -3037,7 +3037,7 @@
         <v>100</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q23" s="8">
         <v>46162</v>
@@ -3046,7 +3046,7 @@
         <v>46164</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T23" s="9">
         <v>1</v>
@@ -3057,7 +3057,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B24" s="5">
         <v>46160.652414490745</v>
@@ -3069,7 +3069,7 @@
         <v>46181.67587553241</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3102,7 +3102,7 @@
         <v>100</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q24" s="5">
         <v>46162</v>
@@ -3111,7 +3111,7 @@
         <v>46164</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T24" s="6">
         <v>1</v>
@@ -3122,7 +3122,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B25" s="8">
         <v>46160.65241840278</v>
@@ -3134,7 +3134,7 @@
         <v>46181.67588775463</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -3167,7 +3167,7 @@
         <v>100</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q25" s="8">
         <v>46162</v>
@@ -3176,7 +3176,7 @@
         <v>46164</v>
       </c>
       <c r="S25" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T25" s="9">
         <v>1</v>
@@ -3187,7 +3187,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B26" s="5">
         <v>46160.65857868055</v>
@@ -3199,7 +3199,7 @@
         <v>46167.55904253472</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3232,7 +3232,7 @@
         <v>53</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q26" s="5">
         <v>46134</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B27" s="8">
         <v>46160.65225063657</v>
@@ -3262,7 +3262,7 @@
         <v>46181.678639652775</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>25</v>
@@ -3286,7 +3286,7 @@
         <v>26</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>26</v>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B28" s="5">
         <v>46160.65242274306</v>
@@ -3311,16 +3311,16 @@
         <v>46181.675709143514</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G28" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="H28" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="I28" s="5">
         <v>46135</v>
@@ -3338,13 +3338,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q28" s="5">
         <v>46135</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B29" s="8">
         <v>46160.65242719908</v>
@@ -3376,16 +3376,16 @@
         <v>46181.67563449074</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="I29" s="8">
         <v>46135</v>
@@ -3403,13 +3403,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3425,7 +3425,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B30" s="5">
         <v>46160.65243181713</v>
@@ -3437,16 +3437,16 @@
         <v>46181.67567790509</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H30" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="I30" s="5">
         <v>46139</v>
@@ -3464,13 +3464,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q30" s="6"/>
       <c r="R30" s="6"/>
@@ -3486,7 +3486,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B31" s="8">
         <v>46160.65243667824</v>
@@ -3498,16 +3498,16 @@
         <v>46181.67562327546</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="I31" s="8">
         <v>46135</v>
@@ -3525,13 +3525,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q31" s="8">
         <v>46135</v>
@@ -3551,7 +3551,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B32" s="5">
         <v>46160.65244107639</v>
@@ -3563,16 +3563,16 @@
         <v>46181.67555395833</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="I32" s="5">
         <v>46135</v>
@@ -3590,13 +3590,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>93</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3612,7 +3612,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B33" s="8">
         <v>46160.65244578704</v>
@@ -3624,16 +3624,16 @@
         <v>46181.67559840278</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H33" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="I33" s="8">
         <v>46139</v>
@@ -3651,13 +3651,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
@@ -3673,7 +3673,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B34" s="5">
         <v>46160.652450625</v>
@@ -3685,16 +3685,16 @@
         <v>46181.67549369213</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="I34" s="5">
         <v>46133</v>
@@ -3712,13 +3712,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q34" s="5">
         <v>46133</v>
@@ -3727,7 +3727,7 @@
         <v>46171</v>
       </c>
       <c r="S34" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T34" s="6">
         <v>1</v>
@@ -3738,7 +3738,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B35" s="8">
         <v>46160.65245552083</v>
@@ -3750,16 +3750,16 @@
         <v>46181.67541268519</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="I35" s="8">
         <v>46133</v>
@@ -3777,13 +3777,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>87</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3799,7 +3799,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B36" s="5">
         <v>46160.65246048611</v>
@@ -3811,16 +3811,16 @@
         <v>46181.67545391204</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="I36" s="5">
         <v>46142</v>
@@ -3838,13 +3838,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B37" s="8">
         <v>46160.6524655324</v>
@@ -3872,16 +3872,16 @@
         <v>46181.67546648148</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="I37" s="8">
         <v>46141</v>
@@ -3899,13 +3899,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -3921,7 +3921,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B38" s="5">
         <v>46160.6566696875</v>
@@ -3931,16 +3931,16 @@
         <v>46197.19306372685</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="I38" s="5">
         <v>46136</v>
@@ -3958,10 +3958,10 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>26</v>
@@ -3973,7 +3973,7 @@
         <v>46196</v>
       </c>
       <c r="S38" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
@@ -3984,7 +3984,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B39" s="8">
         <v>46160.65676351852</v>
@@ -3996,16 +3996,16 @@
         <v>46182.67674333333</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>120</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>121</v>
       </c>
       <c r="I39" s="8">
         <v>46136</v>
@@ -4023,13 +4023,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4039,7 +4039,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
         <v>46160.65688415509</v>
@@ -4049,16 +4049,16 @@
         <v>46196.16898914352</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>120</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>121</v>
       </c>
       <c r="I40" s="5">
         <v>46148</v>
@@ -4076,13 +4076,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4092,7 +4092,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B41" s="8">
         <v>46160.65247015047</v>
@@ -4104,16 +4104,16 @@
         <v>46181.676244386574</v>
       </c>
       <c r="E41" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="F41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="9" t="s">
+      <c r="H41" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="I41" s="8">
         <v>46167</v>
@@ -4131,13 +4131,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q41" s="8">
         <v>46167</v>
@@ -4146,7 +4146,7 @@
         <v>46177</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T41" s="9">
         <v>1</v>
@@ -4157,7 +4157,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B42" s="5">
         <v>46160.65247482639</v>
@@ -4169,16 +4169,16 @@
         <v>46181.67615008102</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I42" s="5">
         <v>46167</v>
@@ -4196,13 +4196,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>97</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4218,7 +4218,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B43" s="8">
         <v>46160.65247959491</v>
@@ -4230,16 +4230,16 @@
         <v>46181.67622016204</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="I43" s="8">
         <v>46169</v>
@@ -4257,13 +4257,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q43" s="9"/>
       <c r="R43" s="9"/>
@@ -4279,7 +4279,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B44" s="5">
         <v>46160.65254070602</v>
@@ -4291,16 +4291,16 @@
         <v>46181.67636662037</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I44" s="5">
         <v>46167</v>
@@ -4318,10 +4318,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>26</v>
@@ -4333,7 +4333,7 @@
         <v>46177</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T44" s="6">
         <v>1</v>
@@ -4344,7 +4344,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B45" s="8">
         <v>46160.65254572917</v>
@@ -4356,16 +4356,16 @@
         <v>46181.67630162037</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="I45" s="8">
         <v>46167</v>
@@ -4383,13 +4383,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4399,7 +4399,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B46" s="5">
         <v>46160.652551377316</v>
@@ -4411,16 +4411,16 @@
         <v>46181.67634090278</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H46" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I46" s="5">
         <v>46169</v>
@@ -4438,13 +4438,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Q46" s="6"/>
       <c r="R46" s="6"/>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B47" s="8">
         <v>46160.652557152775</v>
@@ -4466,16 +4466,16 @@
         <v>46198.206338171294</v>
       </c>
       <c r="E47" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="9" t="s">
+      <c r="H47" s="9" t="s">
         <v>179</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4493,10 +4493,10 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>26</v>
@@ -4508,7 +4508,7 @@
         <v>46205</v>
       </c>
       <c r="S47" s="12" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="T47" s="9">
         <v>1</v>
@@ -4531,16 +4531,16 @@
         <v>46181.67638900463</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>179</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>180</v>
       </c>
       <c r="I48" s="5">
         <v>46167</v>
@@ -4558,10 +4558,10 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>183</v>
@@ -4592,10 +4592,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>178</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>179</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>180</v>
       </c>
       <c r="I49" s="8">
         <v>46176</v>
@@ -4613,10 +4613,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>186</v>
@@ -4668,7 +4668,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>185</v>
@@ -4702,10 +4702,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="I51" s="8">
         <v>46167</v>
@@ -4723,7 +4723,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>193</v>
@@ -4738,7 +4738,7 @@
         <v>46177</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T51" s="9">
         <v>1</v>
@@ -4761,16 +4761,16 @@
         <v>46181.67651314815</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="H52" s="6" t="s">
         <v>160</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>161</v>
       </c>
       <c r="I52" s="5">
         <v>46167</v>
@@ -4791,7 +4791,7 @@
         <v>192</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>195</v>
@@ -4822,10 +4822,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>160</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="I53" s="8">
         <v>46169</v>
@@ -4846,7 +4846,7 @@
         <v>192</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>198</v>
@@ -5092,7 +5092,7 @@
         <v>46161</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T57" s="9">
         <v>1</v>
@@ -5369,7 +5369,7 @@
         <v>226</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>232</v>
@@ -5381,7 +5381,7 @@
         <v>46181</v>
       </c>
       <c r="S62" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
@@ -5446,7 +5446,7 @@
         <v>46183</v>
       </c>
       <c r="S63" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T63" s="9">
         <v>1</v>
@@ -5499,7 +5499,7 @@
         <v>226</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>239</v>
@@ -5576,7 +5576,7 @@
         <v>46183</v>
       </c>
       <c r="S65" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T65" s="9">
         <v>1</v>
@@ -5706,7 +5706,7 @@
         <v>46183</v>
       </c>
       <c r="S67" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>
@@ -5820,7 +5820,7 @@
         <v>46188</v>
       </c>
       <c r="S69" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T69" s="9">
         <v>1</v>
@@ -5995,7 +5995,7 @@
         <v>46195</v>
       </c>
       <c r="S72" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6170,7 +6170,7 @@
         <v>46196</v>
       </c>
       <c r="S75" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T75" s="9">
         <v>1</v>
@@ -6382,7 +6382,7 @@
         <v>226</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>278</v>
@@ -6394,7 +6394,7 @@
         <v>46191</v>
       </c>
       <c r="S79" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T79" s="9">
         <v>1</v>
@@ -6447,7 +6447,7 @@
         <v>226</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>278</v>
@@ -6512,7 +6512,7 @@
         <v>226</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>236</v>
@@ -6524,7 +6524,7 @@
         <v>46174</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>
@@ -6544,7 +6544,7 @@
         <v>46181.677345601856</v>
       </c>
       <c r="D82" s="5">
-        <v>46181.67736313658</v>
+        <v>46199.19357225695</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>284</v>
@@ -6588,8 +6588,8 @@
       <c r="R82" s="5">
         <v>46206</v>
       </c>
-      <c r="S82" s="10" t="s">
-        <v>32</v>
+      <c r="S82" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="T82" s="6">
         <v>1</v>
@@ -6640,7 +6640,7 @@
         <v>226</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>58</v>
@@ -6652,7 +6652,7 @@
         <v>46197</v>
       </c>
       <c r="S83" s="11" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="T83" s="9">
         <v>0</v>
@@ -6768,7 +6768,7 @@
         <v>46203</v>
       </c>
       <c r="S85" s="12" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>
@@ -6943,7 +6943,7 @@
         <v>46204</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="T88" s="6">
         <v>1</v>
@@ -7118,7 +7118,7 @@
         <v>46205</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="T91" s="9">
         <v>1</v>
@@ -7244,7 +7244,7 @@
         <v>46181.6778656713</v>
       </c>
       <c r="D94" s="5">
-        <v>46181.677878726856</v>
+        <v>46199.193572986114</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>308</v>
@@ -7288,8 +7288,8 @@
       <c r="R94" s="5">
         <v>46206</v>
       </c>
-      <c r="S94" s="10" t="s">
-        <v>32</v>
+      <c r="S94" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="T94" s="6">
         <v>1</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1537" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="382">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -243,7 +243,10 @@
     <t>Ingenieria Jefe de proyecto:</t>
   </si>
   <si>
-    <t>Ingenieria basica Rodete,Ingenieria Detalle,Analisis de costeo,Ingenieria Basica Motor</t>
+    <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214909462744422</t>
@@ -255,7 +258,7 @@
     <t>MOTOR DE STOCK WEG - 02 POLOS - IE3 FRAME 280</t>
   </si>
   <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta motor</t>
   </si>
   <si>
     <t>1214909311323558</t>
@@ -273,7 +276,7 @@
 </t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,propuesta alabes,propuesta nucleo rodete ot 4313</t>
+    <t>Ingenieria Jefe de proyecto:,propuesta alabes,propuesta nucleo rodete ot 4313</t>
   </si>
   <si>
     <t>1214909311323578</t>
@@ -282,22 +285,7 @@
     <t>Ingenieria Detalle</t>
   </si>
   <si>
-    <t>Ingenieria Jefe de proyecto:,Analisis de costeo,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1214909311326752</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
+    <t>Ingenieria Jefe de proyecto:,Planos preliminar</t>
   </si>
   <si>
     <t>1214892476594831</t>
@@ -1183,9 +1171,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>Despacho,Analisis de costeo</t>
   </si>
   <si>
     <t>1214889077215100</t>
@@ -1733,7 +1718,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U129"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -2385,7 +2370,7 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46167.55894045139</v>
+        <v>46199.75069068287</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>65</v>
@@ -2421,11 +2406,13 @@
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
       <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
+      <c r="U13" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B14" s="5">
         <v>46160.6523665162</v>
@@ -2434,10 +2421,10 @@
         <v>46167.55892170139</v>
       </c>
       <c r="D14" s="5">
-        <v>46167.55893438657</v>
+        <v>46199.75068067129</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2458,7 +2445,7 @@
         <v>26</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>26</v>
@@ -2470,7 +2457,7 @@
         <v>42</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q14" s="5">
         <v>46129</v>
@@ -2490,7 +2477,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B15" s="8">
         <v>46160.65237170139</v>
@@ -2499,10 +2486,10 @@
         <v>46167.55892672454</v>
       </c>
       <c r="D15" s="8">
-        <v>46167.55894241898</v>
+        <v>46199.75068077546</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2523,7 +2510,7 @@
         <v>26</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>26</v>
@@ -2535,7 +2522,7 @@
         <v>42</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Q15" s="8">
         <v>46129</v>
@@ -2555,7 +2542,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B16" s="5">
         <v>46160.652376875005</v>
@@ -2564,10 +2551,10 @@
         <v>46167.558934155095</v>
       </c>
       <c r="D16" s="5">
-        <v>46167.55894754629</v>
+        <v>46199.750680613426</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2600,7 +2587,7 @@
         <v>42</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="Q16" s="5">
         <v>46129</v>
@@ -2620,33 +2607,29 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B17" s="8">
-        <v>46160.652382002314</v>
-      </c>
-      <c r="C17" s="9"/>
+        <v>46160.65224614584</v>
+      </c>
+      <c r="C17" s="8">
+        <v>46181.61267278936</v>
+      </c>
       <c r="D17" s="8">
-        <v>46167.55894179398</v>
+        <v>46181.678702233796</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="I17" s="8">
-        <v>46129</v>
-      </c>
-      <c r="J17" s="8">
-        <v>46139</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
       <c r="K17" s="9" t="s">
         <v>26</v>
       </c>
@@ -2654,97 +2637,103 @@
         <v>26</v>
       </c>
       <c r="M17" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>46129</v>
-      </c>
-      <c r="R17" s="8">
-        <v>46139</v>
-      </c>
-      <c r="S17" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T17" s="9">
-        <v>0</v>
-      </c>
-      <c r="U17" s="12" t="s">
-        <v>82</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
+      <c r="S17" s="9"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="9"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="5">
+        <v>46160.652389560186</v>
+      </c>
+      <c r="C18" s="5">
+        <v>46167.55896461806</v>
+      </c>
+      <c r="D18" s="5">
+        <v>46167.55897762731</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="B18" s="5">
-        <v>46160.65224614584</v>
-      </c>
-      <c r="C18" s="5">
-        <v>46181.61267278936</v>
-      </c>
-      <c r="D18" s="5">
-        <v>46181.678702233796</v>
-      </c>
-      <c r="E18" s="6" t="s">
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="5">
+        <v>46133</v>
+      </c>
+      <c r="J18" s="5">
+        <v>46134</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="O18" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P18" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="6"/>
-      <c r="T18" s="6"/>
-      <c r="U18" s="6"/>
+      <c r="Q18" s="5">
+        <v>46133</v>
+      </c>
+      <c r="R18" s="5">
+        <v>46134</v>
+      </c>
+      <c r="S18" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T18" s="6">
+        <v>1</v>
+      </c>
+      <c r="U18" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B19" s="8">
+        <v>46160.65239491899</v>
+      </c>
+      <c r="C19" s="8">
+        <v>46167.55899587963</v>
+      </c>
+      <c r="D19" s="8">
+        <v>46167.55901266204</v>
+      </c>
+      <c r="E19" s="9" t="s">
         <v>86</v>
-      </c>
-      <c r="B19" s="8">
-        <v>46160.652389560186</v>
-      </c>
-      <c r="C19" s="8">
-        <v>46167.55896461806</v>
-      </c>
-      <c r="D19" s="8">
-        <v>46167.55897762731</v>
-      </c>
-      <c r="E19" s="9" t="s">
-        <v>87</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2771,13 +2760,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q19" s="8">
         <v>46133</v>
@@ -2797,28 +2786,28 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="5">
+        <v>46160.65240028936</v>
+      </c>
+      <c r="C20" s="5">
+        <v>46181.612247048615</v>
+      </c>
+      <c r="D20" s="5">
+        <v>46181.61226466435</v>
+      </c>
+      <c r="E20" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="5">
-        <v>46160.65239491899</v>
-      </c>
-      <c r="C20" s="5">
-        <v>46167.55899587963</v>
-      </c>
-      <c r="D20" s="5">
-        <v>46167.55901266204</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="F20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>36</v>
-      </c>
       <c r="H20" s="6" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="I20" s="5">
         <v>46133</v>
@@ -2836,10 +2825,10 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>91</v>
@@ -2865,13 +2854,13 @@
         <v>92</v>
       </c>
       <c r="B21" s="8">
-        <v>46160.65240028936</v>
+        <v>46160.652405636574</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.612247048615</v>
+        <v>46181.612735636576</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.61226466435</v>
+        <v>46181.67578979167</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>93</v>
@@ -2883,13 +2872,13 @@
         <v>94</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I21" s="8">
-        <v>46133</v>
+        <v>46162</v>
       </c>
       <c r="J21" s="8">
-        <v>46134</v>
+        <v>46164</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>26</v>
@@ -2901,54 +2890,54 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Q21" s="8">
-        <v>46133</v>
+        <v>46162</v>
       </c>
       <c r="R21" s="8">
-        <v>46134</v>
-      </c>
-      <c r="S21" s="10" t="s">
-        <v>32</v>
+        <v>46164</v>
+      </c>
+      <c r="S21" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T21" s="9">
         <v>1</v>
       </c>
-      <c r="U21" s="10" t="s">
-        <v>33</v>
+      <c r="U21" s="12" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B22" s="5">
-        <v>46160.652405636574</v>
+        <v>46160.65241059028</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.612735636576</v>
+        <v>46181.67582236111</v>
       </c>
       <c r="D22" s="5">
-        <v>46181.67578979167</v>
+        <v>46181.67583789352</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I22" s="5">
         <v>46162</v>
@@ -2966,13 +2955,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O22" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="P22" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="P22" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -2986,34 +2975,34 @@
       <c r="T22" s="6">
         <v>1</v>
       </c>
-      <c r="U22" s="12" t="s">
-        <v>82</v>
+      <c r="U22" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="8">
+        <v>46160.652414490745</v>
+      </c>
+      <c r="C23" s="8">
+        <v>46181.675860312505</v>
+      </c>
+      <c r="D23" s="8">
+        <v>46181.67587553241</v>
+      </c>
+      <c r="E23" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="B23" s="8">
-        <v>46160.65241059028</v>
-      </c>
-      <c r="C23" s="8">
-        <v>46181.67582236111</v>
-      </c>
-      <c r="D23" s="8">
-        <v>46181.67583789352</v>
-      </c>
-      <c r="E23" s="9" t="s">
-        <v>103</v>
-      </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I23" s="8">
         <v>46162</v>
@@ -3031,13 +3020,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q23" s="8">
         <v>46162</v>
@@ -3057,28 +3046,28 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="5">
+        <v>46160.65241840278</v>
+      </c>
+      <c r="C24" s="5">
+        <v>46181.67587228009</v>
+      </c>
+      <c r="D24" s="5">
+        <v>46181.67588775463</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B24" s="5">
-        <v>46160.652414490745</v>
-      </c>
-      <c r="C24" s="5">
-        <v>46181.675860312505</v>
-      </c>
-      <c r="D24" s="5">
-        <v>46181.67587553241</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>106</v>
-      </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I24" s="5">
         <v>46162</v>
@@ -3096,13 +3085,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="Q24" s="5">
         <v>46162</v>
@@ -3122,61 +3111,61 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" s="8">
+        <v>46160.65857868055</v>
+      </c>
+      <c r="C25" s="8">
+        <v>46167.55902803241</v>
+      </c>
+      <c r="D25" s="8">
+        <v>46167.55904253472</v>
+      </c>
+      <c r="E25" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B25" s="8">
-        <v>46160.65241840278</v>
-      </c>
-      <c r="C25" s="8">
-        <v>46181.67587228009</v>
-      </c>
-      <c r="D25" s="8">
-        <v>46181.67588775463</v>
-      </c>
-      <c r="E25" s="9" t="s">
+      <c r="F25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G25" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I25" s="8">
+        <v>46134</v>
+      </c>
+      <c r="J25" s="8">
+        <v>46135</v>
+      </c>
+      <c r="K25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N25" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="O25" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="P25" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="I25" s="8">
-        <v>46162</v>
-      </c>
-      <c r="J25" s="8">
-        <v>46164</v>
-      </c>
-      <c r="K25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N25" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="O25" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="P25" s="9" t="s">
-        <v>110</v>
-      </c>
       <c r="Q25" s="8">
-        <v>46162</v>
+        <v>46134</v>
       </c>
       <c r="R25" s="8">
-        <v>46164</v>
-      </c>
-      <c r="S25" s="11" t="s">
-        <v>63</v>
+        <v>46135</v>
+      </c>
+      <c r="S25" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T25" s="9">
         <v>1</v>
@@ -3187,92 +3176,82 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" s="5">
+        <v>46160.65225063657</v>
+      </c>
+      <c r="C26" s="6"/>
+      <c r="D26" s="5">
+        <v>46181.678639652775</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="5">
-        <v>46160.65857868055</v>
-      </c>
-      <c r="C26" s="5">
-        <v>46167.55902803241</v>
-      </c>
-      <c r="D26" s="5">
-        <v>46167.55904253472</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="F26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M26" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O26" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I26" s="5">
-        <v>46134</v>
-      </c>
-      <c r="J26" s="5">
-        <v>46135</v>
-      </c>
-      <c r="K26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N26" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="O26" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="P26" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q26" s="5">
-        <v>46134</v>
-      </c>
-      <c r="R26" s="5">
-        <v>46135</v>
-      </c>
-      <c r="S26" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T26" s="6">
-        <v>1</v>
-      </c>
-      <c r="U26" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="6"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46160.65242274306</v>
+      </c>
+      <c r="C27" s="8">
+        <v>46181.67569217592</v>
+      </c>
+      <c r="D27" s="8">
+        <v>46181.675709143514</v>
+      </c>
+      <c r="E27" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="B27" s="8">
-        <v>46160.65225063657</v>
-      </c>
-      <c r="C27" s="9"/>
-      <c r="D27" s="8">
-        <v>46181.678639652775</v>
-      </c>
-      <c r="E27" s="9" t="s">
+      <c r="F27" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="F27" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
+      <c r="H27" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I27" s="8">
+        <v>46135</v>
+      </c>
+      <c r="J27" s="8">
+        <v>46140</v>
+      </c>
       <c r="K27" s="9" t="s">
         <v>26</v>
       </c>
@@ -3280,53 +3259,63 @@
         <v>26</v>
       </c>
       <c r="M27" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q27" s="9"/>
-      <c r="R27" s="9"/>
-      <c r="S27" s="9"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
+        <v>111</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>46135</v>
+      </c>
+      <c r="R27" s="8">
+        <v>46140</v>
+      </c>
+      <c r="S27" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T27" s="9">
+        <v>1</v>
+      </c>
+      <c r="U27" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46160.65242274306</v>
+        <v>46160.65242719908</v>
       </c>
       <c r="C28" s="5">
-        <v>46181.67569217592</v>
+        <v>46181.675633032406</v>
       </c>
       <c r="D28" s="5">
-        <v>46181.675709143514</v>
+        <v>46181.67563449074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I28" s="5">
         <v>46135</v>
       </c>
       <c r="J28" s="5">
-        <v>46140</v>
+        <v>46136</v>
       </c>
       <c r="K28" s="6" t="s">
         <v>26</v>
@@ -3338,78 +3327,74 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q28" s="5">
-        <v>46135</v>
-      </c>
-      <c r="R28" s="5">
-        <v>46140</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
       <c r="S28" s="10" t="s">
         <v>32</v>
       </c>
       <c r="T28" s="6">
-        <v>1</v>
-      </c>
-      <c r="U28" s="10" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="U28" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46160.65243181713</v>
+      </c>
+      <c r="C29" s="8">
+        <v>46181.67567633102</v>
+      </c>
+      <c r="D29" s="8">
+        <v>46181.67567790509</v>
+      </c>
+      <c r="E29" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B29" s="8">
-        <v>46160.65242719908</v>
-      </c>
-      <c r="C29" s="8">
-        <v>46181.675633032406</v>
-      </c>
-      <c r="D29" s="8">
-        <v>46181.67563449074</v>
-      </c>
-      <c r="E29" s="9" t="s">
+      <c r="F29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I29" s="8">
+        <v>46139</v>
+      </c>
+      <c r="J29" s="8">
+        <v>46140</v>
+      </c>
+      <c r="K29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M29" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="O29" s="9" t="s">
+        <v>119</v>
+      </c>
+      <c r="P29" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I29" s="8">
-        <v>46135</v>
-      </c>
-      <c r="J29" s="8">
-        <v>46136</v>
-      </c>
-      <c r="K29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N29" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="O29" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="P29" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3425,95 +3410,99 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B30" s="5">
+        <v>46160.65243667824</v>
+      </c>
+      <c r="C30" s="5">
+        <v>46181.67561266204</v>
+      </c>
+      <c r="D30" s="5">
+        <v>46181.67562327546</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B30" s="5">
-        <v>46160.65243181713</v>
-      </c>
-      <c r="C30" s="5">
-        <v>46181.67567633102</v>
-      </c>
-      <c r="D30" s="5">
-        <v>46181.67567790509</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="F30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="I30" s="5">
+        <v>46135</v>
+      </c>
+      <c r="J30" s="5">
+        <v>46157</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M30" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="O30" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="I30" s="5">
-        <v>46139</v>
-      </c>
-      <c r="J30" s="5">
-        <v>46140</v>
-      </c>
-      <c r="K30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N30" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="O30" s="6" t="s">
-        <v>123</v>
-      </c>
       <c r="P30" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
+        <v>111</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>46135</v>
+      </c>
+      <c r="R30" s="5">
+        <v>46157</v>
+      </c>
       <c r="S30" s="10" t="s">
         <v>32</v>
       </c>
       <c r="T30" s="6">
-        <v>0</v>
-      </c>
-      <c r="U30" s="11" t="s">
-        <v>51</v>
+        <v>1</v>
+      </c>
+      <c r="U30" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46160.65244107639</v>
+      </c>
+      <c r="C31" s="8">
+        <v>46181.67555267361</v>
+      </c>
+      <c r="D31" s="8">
+        <v>46181.67555395833</v>
+      </c>
+      <c r="E31" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B31" s="8">
-        <v>46160.65243667824</v>
-      </c>
-      <c r="C31" s="8">
-        <v>46181.67561266204</v>
-      </c>
-      <c r="D31" s="8">
-        <v>46181.67562327546</v>
-      </c>
-      <c r="E31" s="9" t="s">
-        <v>129</v>
-      </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I31" s="8">
         <v>46135</v>
       </c>
       <c r="J31" s="8">
-        <v>46157</v>
+        <v>46136</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>26</v>
@@ -3525,78 +3514,74 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q31" s="8">
-        <v>46135</v>
-      </c>
-      <c r="R31" s="8">
-        <v>46157</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="Q31" s="9"/>
+      <c r="R31" s="9"/>
       <c r="S31" s="10" t="s">
         <v>32</v>
       </c>
       <c r="T31" s="9">
-        <v>1</v>
-      </c>
-      <c r="U31" s="10" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="U31" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B32" s="5">
+        <v>46160.65244578704</v>
+      </c>
+      <c r="C32" s="5">
+        <v>46181.67559679398</v>
+      </c>
+      <c r="D32" s="5">
+        <v>46181.67559840278</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B32" s="5">
-        <v>46160.65244107639</v>
-      </c>
-      <c r="C32" s="5">
-        <v>46181.67555267361</v>
-      </c>
-      <c r="D32" s="5">
-        <v>46181.67555395833</v>
-      </c>
-      <c r="E32" s="6" t="s">
+      <c r="F32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="I32" s="5">
+        <v>46139</v>
+      </c>
+      <c r="J32" s="5">
+        <v>46157</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M32" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N32" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="O32" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="P32" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="I32" s="5">
-        <v>46135</v>
-      </c>
-      <c r="J32" s="5">
-        <v>46136</v>
-      </c>
-      <c r="K32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N32" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="O32" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="P32" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3612,95 +3597,99 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46160.652450625</v>
+      </c>
+      <c r="C33" s="8">
+        <v>46181.67547991898</v>
+      </c>
+      <c r="D33" s="8">
+        <v>46181.67549369213</v>
+      </c>
+      <c r="E33" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B33" s="8">
-        <v>46160.65244578704</v>
-      </c>
-      <c r="C33" s="8">
-        <v>46181.67559679398</v>
-      </c>
-      <c r="D33" s="8">
-        <v>46181.67559840278</v>
-      </c>
-      <c r="E33" s="9" t="s">
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I33" s="8">
+        <v>46133</v>
+      </c>
+      <c r="J33" s="8">
+        <v>46171</v>
+      </c>
+      <c r="K33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N33" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="O33" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I33" s="8">
-        <v>46139</v>
-      </c>
-      <c r="J33" s="8">
-        <v>46157</v>
-      </c>
-      <c r="K33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N33" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="O33" s="9" t="s">
-        <v>132</v>
-      </c>
       <c r="P33" s="9" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q33" s="9"/>
-      <c r="R33" s="9"/>
-      <c r="S33" s="10" t="s">
-        <v>32</v>
+        <v>111</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>46133</v>
+      </c>
+      <c r="R33" s="8">
+        <v>46171</v>
+      </c>
+      <c r="S33" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T33" s="9">
-        <v>0</v>
-      </c>
-      <c r="U33" s="11" t="s">
-        <v>51</v>
+        <v>1</v>
+      </c>
+      <c r="U33" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="5">
+        <v>46160.65245552083</v>
+      </c>
+      <c r="C34" s="5">
+        <v>46181.67541125</v>
+      </c>
+      <c r="D34" s="5">
+        <v>46181.67541268519</v>
+      </c>
+      <c r="E34" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B34" s="5">
-        <v>46160.652450625</v>
-      </c>
-      <c r="C34" s="5">
-        <v>46181.67547991898</v>
-      </c>
-      <c r="D34" s="5">
-        <v>46181.67549369213</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I34" s="5">
         <v>46133</v>
       </c>
       <c r="J34" s="5">
-        <v>46171</v>
+        <v>46141</v>
       </c>
       <c r="K34" s="6" t="s">
         <v>26</v>
@@ -3712,78 +3701,74 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q34" s="5">
-        <v>46133</v>
-      </c>
-      <c r="R34" s="5">
-        <v>46171</v>
-      </c>
-      <c r="S34" s="11" t="s">
-        <v>63</v>
+        <v>138</v>
+      </c>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T34" s="6">
-        <v>1</v>
-      </c>
-      <c r="U34" s="10" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="U34" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46160.65246048611</v>
+      </c>
+      <c r="C35" s="8">
+        <v>46181.675452662035</v>
+      </c>
+      <c r="D35" s="8">
+        <v>46181.67545391204</v>
+      </c>
+      <c r="E35" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B35" s="8">
-        <v>46160.65245552083</v>
-      </c>
-      <c r="C35" s="8">
-        <v>46181.67541125</v>
-      </c>
-      <c r="D35" s="8">
-        <v>46181.67541268519</v>
-      </c>
-      <c r="E35" s="9" t="s">
+      <c r="F35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I35" s="8">
+        <v>46142</v>
+      </c>
+      <c r="J35" s="8">
+        <v>46171</v>
+      </c>
+      <c r="K35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M35" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N35" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="O35" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="P35" s="9" t="s">
         <v>141</v>
-      </c>
-      <c r="F35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I35" s="8">
-        <v>46133</v>
-      </c>
-      <c r="J35" s="8">
-        <v>46141</v>
-      </c>
-      <c r="K35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N35" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="O35" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="P35" s="9" t="s">
-        <v>142</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3799,52 +3784,52 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B36" s="5">
+        <v>46160.6524655324</v>
+      </c>
+      <c r="C36" s="5">
+        <v>46181.675465057866</v>
+      </c>
+      <c r="D36" s="5">
+        <v>46181.67546648148</v>
+      </c>
+      <c r="E36" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B36" s="5">
-        <v>46160.65246048611</v>
-      </c>
-      <c r="C36" s="5">
-        <v>46181.675452662035</v>
-      </c>
-      <c r="D36" s="5">
-        <v>46181.67545391204</v>
-      </c>
-      <c r="E36" s="6" t="s">
+      <c r="F36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="I36" s="5">
+        <v>46141</v>
+      </c>
+      <c r="J36" s="5">
+        <v>46150</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N36" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="P36" s="6" t="s">
         <v>144</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="I36" s="5">
-        <v>46142</v>
-      </c>
-      <c r="J36" s="5">
-        <v>46171</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N36" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="O36" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="P36" s="6" t="s">
-        <v>145</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3860,57 +3845,59 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46160.6566696875</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="8">
+        <v>46197.19306372685</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B37" s="8">
-        <v>46160.6524655324</v>
-      </c>
-      <c r="C37" s="8">
-        <v>46181.675465057866</v>
-      </c>
-      <c r="D37" s="8">
-        <v>46181.67546648148</v>
-      </c>
-      <c r="E37" s="9" t="s">
+      <c r="F37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I37" s="8">
+        <v>46136</v>
+      </c>
+      <c r="J37" s="8">
+        <v>46196</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M37" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="O37" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="F37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I37" s="8">
-        <v>46141</v>
-      </c>
-      <c r="J37" s="8">
-        <v>46150</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M37" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N37" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="O37" s="9" t="s">
-        <v>141</v>
-      </c>
       <c r="P37" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q37" s="9"/>
-      <c r="R37" s="9"/>
-      <c r="S37" s="10" t="s">
-        <v>32</v>
+        <v>26</v>
+      </c>
+      <c r="Q37" s="8">
+        <v>46136</v>
+      </c>
+      <c r="R37" s="8">
+        <v>46196</v>
+      </c>
+      <c r="S37" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
@@ -3921,32 +3908,34 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B38" s="5">
-        <v>46160.6566696875</v>
-      </c>
-      <c r="C38" s="6"/>
+        <v>46160.65676351852</v>
+      </c>
+      <c r="C38" s="5">
+        <v>46182.67674130787</v>
+      </c>
       <c r="D38" s="5">
-        <v>46197.19306372685</v>
+        <v>46182.67674333333</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>150</v>
+        <v>109</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="I38" s="5">
         <v>46136</v>
       </c>
       <c r="J38" s="5">
-        <v>46196</v>
+        <v>46147</v>
       </c>
       <c r="K38" s="6" t="s">
         <v>26</v>
@@ -3958,78 +3947,66 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q38" s="5">
-        <v>46136</v>
-      </c>
-      <c r="R38" s="5">
-        <v>46196</v>
-      </c>
-      <c r="S38" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="T38" s="6">
-        <v>0</v>
-      </c>
-      <c r="U38" s="11" t="s">
-        <v>51</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="Q38" s="6"/>
+      <c r="R38" s="6"/>
+      <c r="S38" s="6"/>
+      <c r="T38" s="6"/>
+      <c r="U38" s="6"/>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46160.65688415509</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="8">
+        <v>46196.16898914352</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G39" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I39" s="8">
+        <v>46148</v>
+      </c>
+      <c r="J39" s="8">
+        <v>46196</v>
+      </c>
+      <c r="K39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N39" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="O39" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="P39" s="9" t="s">
         <v>152</v>
-      </c>
-      <c r="B39" s="8">
-        <v>46160.65676351852</v>
-      </c>
-      <c r="C39" s="8">
-        <v>46182.67674130787</v>
-      </c>
-      <c r="D39" s="8">
-        <v>46182.67674333333</v>
-      </c>
-      <c r="E39" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="I39" s="8">
-        <v>46136</v>
-      </c>
-      <c r="J39" s="8">
-        <v>46147</v>
-      </c>
-      <c r="K39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N39" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="O39" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="P39" s="9" t="s">
-        <v>153</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4039,32 +4016,34 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B40" s="5">
+        <v>46160.65247015047</v>
+      </c>
+      <c r="C40" s="5">
+        <v>46181.67623252315</v>
+      </c>
+      <c r="D40" s="5">
+        <v>46181.676244386574</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="B40" s="5">
-        <v>46160.65688415509</v>
-      </c>
-      <c r="C40" s="6"/>
-      <c r="D40" s="5">
-        <v>46196.16898914352</v>
-      </c>
-      <c r="E40" s="6" t="s">
+      <c r="F40" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>119</v>
-      </c>
       <c r="H40" s="6" t="s">
-        <v>120</v>
+        <v>156</v>
       </c>
       <c r="I40" s="5">
-        <v>46148</v>
+        <v>46167</v>
       </c>
       <c r="J40" s="5">
-        <v>46196</v>
+        <v>46177</v>
       </c>
       <c r="K40" s="6" t="s">
         <v>26</v>
@@ -4076,50 +4055,60 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="6"/>
-      <c r="T40" s="6"/>
-      <c r="U40" s="6"/>
+        <v>111</v>
+      </c>
+      <c r="Q40" s="5">
+        <v>46167</v>
+      </c>
+      <c r="R40" s="5">
+        <v>46177</v>
+      </c>
+      <c r="S40" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T40" s="6">
+        <v>1</v>
+      </c>
+      <c r="U40" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B41" s="8">
-        <v>46160.65247015047</v>
+        <v>46160.65247482639</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.67623252315</v>
+        <v>46181.676148715276</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.676244386574</v>
+        <v>46181.67615008102</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I41" s="8">
         <v>46167</v>
       </c>
       <c r="J41" s="8">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>26</v>
@@ -4131,78 +4120,74 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>115</v>
+        <v>154</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>161</v>
+        <v>93</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q41" s="8">
-        <v>46167</v>
-      </c>
-      <c r="R41" s="8">
-        <v>46177</v>
-      </c>
-      <c r="S41" s="11" t="s">
-        <v>63</v>
+        <v>160</v>
+      </c>
+      <c r="Q41" s="9"/>
+      <c r="R41" s="9"/>
+      <c r="S41" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T41" s="9">
-        <v>1</v>
-      </c>
-      <c r="U41" s="10" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="U41" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B42" s="5">
+        <v>46160.65247959491</v>
+      </c>
+      <c r="C42" s="5">
+        <v>46181.67621893519</v>
+      </c>
+      <c r="D42" s="5">
+        <v>46181.67622016204</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="B42" s="5">
-        <v>46160.65247482639</v>
-      </c>
-      <c r="C42" s="5">
-        <v>46181.676148715276</v>
-      </c>
-      <c r="D42" s="5">
-        <v>46181.67615008102</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I42" s="5">
+        <v>46169</v>
+      </c>
+      <c r="J42" s="5">
+        <v>46177</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="P42" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I42" s="5">
-        <v>46167</v>
-      </c>
-      <c r="J42" s="5">
-        <v>46168</v>
-      </c>
-      <c r="K42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N42" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="O42" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="P42" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4218,31 +4203,31 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46160.65254070602</v>
+      </c>
+      <c r="C43" s="8">
+        <v>46181.67635490741</v>
+      </c>
+      <c r="D43" s="8">
+        <v>46181.67636662037</v>
+      </c>
+      <c r="E43" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B43" s="8">
-        <v>46160.65247959491</v>
-      </c>
-      <c r="C43" s="8">
-        <v>46181.67621893519</v>
-      </c>
-      <c r="D43" s="8">
-        <v>46181.67622016204</v>
-      </c>
-      <c r="E43" s="9" t="s">
-        <v>166</v>
-      </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I43" s="8">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="J43" s="8">
         <v>46177</v>
@@ -4257,56 +4242,60 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>158</v>
+        <v>111</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="Q43" s="9"/>
-      <c r="R43" s="9"/>
-      <c r="S43" s="10" t="s">
-        <v>32</v>
+        <v>26</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>46167</v>
+      </c>
+      <c r="R43" s="8">
+        <v>46177</v>
+      </c>
+      <c r="S43" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T43" s="9">
-        <v>0</v>
-      </c>
-      <c r="U43" s="11" t="s">
-        <v>51</v>
+        <v>1</v>
+      </c>
+      <c r="U43" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B44" s="5">
-        <v>46160.65254070602</v>
+        <v>46160.65254572917</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.67635490741</v>
+        <v>46181.67630011574</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.67636662037</v>
+        <v>46181.67630162037</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I44" s="5">
         <v>46167</v>
       </c>
       <c r="J44" s="5">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="K44" s="6" t="s">
         <v>26</v>
@@ -4318,78 +4307,68 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>170</v>
+        <v>99</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q44" s="5">
-        <v>46167</v>
-      </c>
-      <c r="R44" s="5">
-        <v>46177</v>
-      </c>
-      <c r="S44" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="T44" s="6">
-        <v>1</v>
-      </c>
-      <c r="U44" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6"/>
+      <c r="T44" s="6"/>
+      <c r="U44" s="6"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46160.652551377316</v>
+      </c>
+      <c r="C45" s="8">
+        <v>46181.676339375</v>
+      </c>
+      <c r="D45" s="8">
+        <v>46181.67634090278</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="I45" s="8">
+        <v>46169</v>
+      </c>
+      <c r="J45" s="8">
+        <v>46177</v>
+      </c>
+      <c r="K45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M45" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N45" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="O45" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="P45" s="9" t="s">
         <v>171</v>
-      </c>
-      <c r="B45" s="8">
-        <v>46160.65254572917</v>
-      </c>
-      <c r="C45" s="8">
-        <v>46181.67630011574</v>
-      </c>
-      <c r="D45" s="8">
-        <v>46181.67630162037</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="I45" s="8">
-        <v>46167</v>
-      </c>
-      <c r="J45" s="8">
-        <v>46168</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M45" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N45" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="O45" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="P45" s="9" t="s">
-        <v>172</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4399,34 +4378,34 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B46" s="5">
+        <v>46160.652557152775</v>
+      </c>
+      <c r="C46" s="5">
+        <v>46181.67648052084</v>
+      </c>
+      <c r="D46" s="5">
+        <v>46198.206338171294</v>
+      </c>
+      <c r="E46" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B46" s="5">
-        <v>46160.652551377316</v>
-      </c>
-      <c r="C46" s="5">
-        <v>46181.676339375</v>
-      </c>
-      <c r="D46" s="5">
-        <v>46181.67634090278</v>
-      </c>
-      <c r="E46" s="6" t="s">
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="H46" s="6" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="I46" s="5">
-        <v>46169</v>
+        <v>46167</v>
       </c>
       <c r="J46" s="5">
-        <v>46177</v>
+        <v>46205</v>
       </c>
       <c r="K46" s="6" t="s">
         <v>26</v>
@@ -4438,50 +4417,60 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q46" s="5">
+        <v>46167</v>
+      </c>
+      <c r="R46" s="5">
+        <v>46205</v>
+      </c>
+      <c r="S46" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="T46" s="6">
+        <v>1</v>
+      </c>
+      <c r="U46" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B47" s="8">
-        <v>46160.652557152775</v>
+        <v>46160.65256162037</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.67648052084</v>
+        <v>46181.67638747685</v>
       </c>
       <c r="D47" s="8">
-        <v>46198.206338171294</v>
+        <v>46181.67638900463</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
       </c>
       <c r="J47" s="8">
-        <v>46205</v>
+        <v>46175</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>26</v>
@@ -4493,78 +4482,68 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>180</v>
+        <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q47" s="8">
-        <v>46167</v>
-      </c>
-      <c r="R47" s="8">
-        <v>46205</v>
-      </c>
-      <c r="S47" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="T47" s="9">
-        <v>1</v>
-      </c>
-      <c r="U47" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Q47" s="9"/>
+      <c r="R47" s="9"/>
+      <c r="S47" s="9"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B48" s="5">
+        <v>46160.6525734375</v>
+      </c>
+      <c r="C48" s="5">
+        <v>46181.676427557875</v>
+      </c>
+      <c r="D48" s="5">
+        <v>46181.67642934028</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I48" s="5">
+        <v>46176</v>
+      </c>
+      <c r="J48" s="5">
+        <v>46204</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N48" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="P48" s="6" t="s">
         <v>182</v>
-      </c>
-      <c r="B48" s="5">
-        <v>46160.65256162037</v>
-      </c>
-      <c r="C48" s="5">
-        <v>46181.67638747685</v>
-      </c>
-      <c r="D48" s="5">
-        <v>46181.67638900463</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="I48" s="5">
-        <v>46167</v>
-      </c>
-      <c r="J48" s="5">
-        <v>46175</v>
-      </c>
-      <c r="K48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N48" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="O48" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P48" s="6" t="s">
-        <v>183</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4574,34 +4553,34 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B49" s="8">
+        <v>46160.652579236106</v>
+      </c>
+      <c r="C49" s="8">
+        <v>46181.67646592592</v>
+      </c>
+      <c r="D49" s="8">
+        <v>46181.676467303245</v>
+      </c>
+      <c r="E49" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B49" s="8">
-        <v>46160.6525734375</v>
-      </c>
-      <c r="C49" s="8">
-        <v>46181.676427557875</v>
-      </c>
-      <c r="D49" s="8">
-        <v>46181.67642934028</v>
-      </c>
-      <c r="E49" s="9" t="s">
+      <c r="F49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="9" t="s">
-        <v>178</v>
-      </c>
       <c r="H49" s="9" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="I49" s="8">
-        <v>46176</v>
+        <v>46205</v>
       </c>
       <c r="J49" s="8">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="K49" s="9" t="s">
         <v>26</v>
@@ -4613,13 +4592,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>110</v>
+        <v>181</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>186</v>
+        <v>26</v>
       </c>
       <c r="Q49" s="9"/>
       <c r="R49" s="9"/>
@@ -4632,13 +4611,13 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46160.652579236106</v>
+        <v>46160.65258304398</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.67646592592</v>
+        <v>46181.676567789356</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.676467303245</v>
+        <v>46181.67657885417</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4647,71 +4626,81 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I50" s="5">
+        <v>46167</v>
+      </c>
+      <c r="J50" s="5">
+        <v>46177</v>
+      </c>
+      <c r="K50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N50" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="O50" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="H50" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="I50" s="5">
-        <v>46205</v>
-      </c>
-      <c r="J50" s="5">
-        <v>46205</v>
-      </c>
-      <c r="K50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M50" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N50" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="O50" s="6" t="s">
-        <v>185</v>
-      </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="6"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
+      <c r="Q50" s="5">
+        <v>46167</v>
+      </c>
+      <c r="R50" s="5">
+        <v>46177</v>
+      </c>
+      <c r="S50" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T50" s="6">
+        <v>1</v>
+      </c>
+      <c r="U50" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B51" s="8">
-        <v>46160.65258304398</v>
+        <v>46160.6525875463</v>
       </c>
       <c r="C51" s="8">
-        <v>46181.676567789356</v>
+        <v>46181.676511840276</v>
       </c>
       <c r="D51" s="8">
-        <v>46181.67657885417</v>
+        <v>46181.67651314815</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>192</v>
+        <v>103</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I51" s="8">
         <v>46167</v>
       </c>
       <c r="J51" s="8">
-        <v>46177</v>
+        <v>46168</v>
       </c>
       <c r="K51" s="9" t="s">
         <v>26</v>
@@ -4723,78 +4712,68 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>115</v>
+        <v>188</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q51" s="8">
-        <v>46167</v>
-      </c>
-      <c r="R51" s="8">
-        <v>46177</v>
-      </c>
-      <c r="S51" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="T51" s="9">
-        <v>1</v>
-      </c>
-      <c r="U51" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="Q51" s="9"/>
+      <c r="R51" s="9"/>
+      <c r="S51" s="9"/>
+      <c r="T51" s="9"/>
+      <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B52" s="5">
+        <v>46160.652593067134</v>
+      </c>
+      <c r="C52" s="5">
+        <v>46181.67655238426</v>
+      </c>
+      <c r="D52" s="5">
+        <v>46181.676553680554</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="I52" s="5">
+        <v>46169</v>
+      </c>
+      <c r="J52" s="5">
+        <v>46177</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N52" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="P52" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="B52" s="5">
-        <v>46160.6525875463</v>
-      </c>
-      <c r="C52" s="5">
-        <v>46181.676511840276</v>
-      </c>
-      <c r="D52" s="5">
-        <v>46181.67651314815</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="I52" s="5">
-        <v>46167</v>
-      </c>
-      <c r="J52" s="5">
-        <v>46168</v>
-      </c>
-      <c r="K52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N52" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="O52" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="P52" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4804,52 +4783,46 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="B53" s="8">
+        <v>46160.65225516204</v>
+      </c>
+      <c r="C53" s="8">
+        <v>46181.612413587965</v>
+      </c>
+      <c r="D53" s="8">
+        <v>46181.67858451389</v>
+      </c>
+      <c r="E53" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B53" s="8">
-        <v>46160.652593067134</v>
-      </c>
-      <c r="C53" s="8">
-        <v>46181.67655238426</v>
-      </c>
-      <c r="D53" s="8">
-        <v>46181.676553680554</v>
-      </c>
-      <c r="E53" s="9" t="s">
+      <c r="F53" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M53" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N53" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O53" s="9" t="s">
         <v>197</v>
       </c>
-      <c r="F53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G53" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="I53" s="8">
-        <v>46169</v>
-      </c>
-      <c r="J53" s="8">
-        <v>46177</v>
-      </c>
-      <c r="K53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M53" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N53" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="O53" s="9" t="s">
-        <v>107</v>
-      </c>
       <c r="P53" s="9" t="s">
-        <v>198</v>
+        <v>26</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -4859,29 +4832,35 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B54" s="5">
+        <v>46160.65259921296</v>
+      </c>
+      <c r="C54" s="5">
+        <v>46181.61232818287</v>
+      </c>
+      <c r="D54" s="5">
+        <v>46197.712640196754</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="B54" s="5">
-        <v>46160.65225516204</v>
-      </c>
-      <c r="C54" s="5">
-        <v>46181.612413587965</v>
-      </c>
-      <c r="D54" s="5">
-        <v>46181.67858451389</v>
-      </c>
-      <c r="E54" s="6" t="s">
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
+      <c r="H54" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="I54" s="5">
+        <v>46140</v>
+      </c>
+      <c r="J54" s="5">
+        <v>46147</v>
+      </c>
       <c r="K54" s="6" t="s">
         <v>26</v>
       </c>
@@ -4889,77 +4868,87 @@
         <v>26</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>26</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-      <c r="U54" s="6"/>
+        <v>202</v>
+      </c>
+      <c r="Q54" s="5">
+        <v>46140</v>
+      </c>
+      <c r="R54" s="5">
+        <v>46147</v>
+      </c>
+      <c r="S54" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T54" s="6">
+        <v>1</v>
+      </c>
+      <c r="U54" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B55" s="8">
-        <v>46160.65259921296</v>
+        <v>46160.652606006945</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.61232818287</v>
+        <v>46181.675721631946</v>
       </c>
       <c r="D55" s="8">
-        <v>46197.712640196754</v>
+        <v>46197.71267317129</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="H55" s="9" t="s">
+        <v>201</v>
+      </c>
+      <c r="I55" s="8">
+        <v>46153</v>
+      </c>
+      <c r="J55" s="8">
+        <v>46157</v>
+      </c>
+      <c r="K55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N55" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="O55" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="I55" s="8">
-        <v>46140</v>
-      </c>
-      <c r="J55" s="8">
-        <v>46147</v>
-      </c>
-      <c r="K55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N55" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="O55" s="9" t="s">
-        <v>76</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>206</v>
       </c>
       <c r="Q55" s="8">
-        <v>46140</v>
+        <v>46153</v>
       </c>
       <c r="R55" s="8">
-        <v>46147</v>
+        <v>46157</v>
       </c>
       <c r="S55" s="10" t="s">
         <v>32</v>
@@ -4976,58 +4965,58 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46160.652606006945</v>
+        <v>46160.65261409723</v>
       </c>
       <c r="C56" s="5">
-        <v>46181.675721631946</v>
+        <v>46181.67576423611</v>
       </c>
       <c r="D56" s="5">
-        <v>46197.71267317129</v>
+        <v>46181.67578048611</v>
       </c>
       <c r="E56" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="F56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="I56" s="5">
+        <v>46160</v>
+      </c>
+      <c r="J56" s="5">
+        <v>46160</v>
+      </c>
+      <c r="K56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N56" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="O56" s="6" t="s">
         <v>204</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="I56" s="5">
-        <v>46153</v>
-      </c>
-      <c r="J56" s="5">
-        <v>46157</v>
-      </c>
-      <c r="K56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M56" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N56" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="O56" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>210</v>
       </c>
       <c r="Q56" s="5">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="R56" s="5">
-        <v>46157</v>
-      </c>
-      <c r="S56" s="10" t="s">
-        <v>32</v>
+        <v>46161</v>
+      </c>
+      <c r="S56" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5041,31 +5030,31 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46160.65261409723</v>
+        <v>46160.652630983794</v>
       </c>
       <c r="C57" s="8">
-        <v>46181.67576423611</v>
+        <v>46198.56611644676</v>
       </c>
       <c r="D57" s="8">
-        <v>46181.67578048611</v>
+        <v>46198.566261608794</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>100</v>
+        <v>212</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I57" s="8">
-        <v>46160</v>
+        <v>46210</v>
       </c>
       <c r="J57" s="8">
-        <v>46160</v>
+        <v>46210</v>
       </c>
       <c r="K57" s="9" t="s">
         <v>26</v>
@@ -5077,22 +5066,22 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>214</v>
+        <v>26</v>
       </c>
       <c r="Q57" s="8">
-        <v>46160</v>
+        <v>46210</v>
       </c>
       <c r="R57" s="8">
-        <v>46161</v>
-      </c>
-      <c r="S57" s="11" t="s">
-        <v>63</v>
+        <v>46210</v>
+      </c>
+      <c r="S57" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T57" s="9">
         <v>1</v>
@@ -5103,28 +5092,28 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B58" s="5">
-        <v>46160.652630983794</v>
+        <v>46160.65263532408</v>
       </c>
       <c r="C58" s="5">
-        <v>46198.56611644676</v>
+        <v>46198.56608402778</v>
       </c>
       <c r="D58" s="5">
-        <v>46198.566261608794</v>
+        <v>46198.566085625</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="I58" s="5">
         <v>46210</v>
@@ -5142,54 +5131,44 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q58" s="5">
-        <v>46210</v>
-      </c>
-      <c r="R58" s="5">
-        <v>46210</v>
-      </c>
-      <c r="S58" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T58" s="6">
-        <v>1</v>
-      </c>
-      <c r="U58" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Q58" s="6"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="6"/>
+      <c r="T58" s="6"/>
+      <c r="U58" s="6"/>
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46160.65263532408</v>
+        <v>46160.65264069445</v>
       </c>
       <c r="C59" s="8">
-        <v>46198.56608402778</v>
+        <v>46198.566099675925</v>
       </c>
       <c r="D59" s="8">
-        <v>46198.566085625</v>
+        <v>46198.5661015625</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="I59" s="8">
         <v>46210</v>
@@ -5207,13 +5186,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5223,52 +5202,46 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B60" s="5">
+        <v>46160.652676921294</v>
+      </c>
+      <c r="C60" s="5">
+        <v>46181.612796331014</v>
+      </c>
+      <c r="D60" s="5">
+        <v>46181.67816971065</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H60" s="6"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O60" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="B60" s="5">
-        <v>46160.65264069445</v>
-      </c>
-      <c r="C60" s="5">
-        <v>46198.566099675925</v>
-      </c>
-      <c r="D60" s="5">
-        <v>46198.5661015625</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="I60" s="5">
-        <v>46210</v>
-      </c>
-      <c r="J60" s="5">
-        <v>46210</v>
-      </c>
-      <c r="K60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N60" s="6" t="s">
-        <v>216</v>
-      </c>
-      <c r="O60" s="6" t="s">
-        <v>221</v>
-      </c>
       <c r="P60" s="6" t="s">
-        <v>224</v>
+        <v>26</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5278,29 +5251,35 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B61" s="8">
+        <v>46160.65268083333</v>
+      </c>
+      <c r="C61" s="8">
+        <v>46181.67658946759</v>
+      </c>
+      <c r="D61" s="8">
+        <v>46182.19861893519</v>
+      </c>
+      <c r="E61" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="B61" s="8">
-        <v>46160.652676921294</v>
-      </c>
-      <c r="C61" s="8">
-        <v>46181.612796331014</v>
-      </c>
-      <c r="D61" s="8">
-        <v>46181.67816971065</v>
-      </c>
-      <c r="E61" s="9" t="s">
+      <c r="F61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H61" s="9"/>
-      <c r="I61" s="9"/>
-      <c r="J61" s="9"/>
+      <c r="H61" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="I61" s="8">
+        <v>46178</v>
+      </c>
+      <c r="J61" s="8">
+        <v>46181</v>
+      </c>
       <c r="K61" s="9" t="s">
         <v>26</v>
       </c>
@@ -5308,77 +5287,87 @@
         <v>26</v>
       </c>
       <c r="M61" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>26</v>
+        <v>222</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>227</v>
+        <v>162</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q61" s="9"/>
-      <c r="R61" s="9"/>
-      <c r="S61" s="9"/>
-      <c r="T61" s="9"/>
-      <c r="U61" s="9"/>
+        <v>228</v>
+      </c>
+      <c r="Q61" s="8">
+        <v>46178</v>
+      </c>
+      <c r="R61" s="8">
+        <v>46181</v>
+      </c>
+      <c r="S61" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T61" s="9">
+        <v>1</v>
+      </c>
+      <c r="U61" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B62" s="5">
-        <v>46160.65268083333</v>
+        <v>46160.652685810186</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.67658946759</v>
+        <v>46181.67668319444</v>
       </c>
       <c r="D62" s="5">
-        <v>46182.19861893519</v>
+        <v>46184.17212899306</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
       <c r="H62" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="I62" s="5">
+        <v>46182</v>
+      </c>
+      <c r="J62" s="5">
+        <v>46183</v>
+      </c>
+      <c r="K62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N62" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="O62" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="I62" s="5">
-        <v>46178</v>
-      </c>
-      <c r="J62" s="5">
-        <v>46181</v>
-      </c>
-      <c r="K62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M62" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N62" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="O62" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>232</v>
       </c>
       <c r="Q62" s="5">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="R62" s="5">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="S62" s="11" t="s">
         <v>63</v>
@@ -5395,13 +5384,13 @@
         <v>233</v>
       </c>
       <c r="B63" s="8">
-        <v>46160.652685810186</v>
+        <v>46160.65269097222</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.67668319444</v>
+        <v>46181.67660690972</v>
       </c>
       <c r="D63" s="8">
-        <v>46184.17212899306</v>
+        <v>46181.6766224537</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>234</v>
@@ -5410,16 +5399,16 @@
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="I63" s="8">
-        <v>46182</v>
+        <v>46178</v>
       </c>
       <c r="J63" s="8">
-        <v>46183</v>
+        <v>46181</v>
       </c>
       <c r="K63" s="9" t="s">
         <v>26</v>
@@ -5431,22 +5420,22 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O63" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="P63" s="9" t="s">
         <v>235</v>
       </c>
-      <c r="P63" s="9" t="s">
-        <v>236</v>
-      </c>
       <c r="Q63" s="8">
-        <v>46182</v>
+        <v>46147</v>
       </c>
       <c r="R63" s="8">
-        <v>46183</v>
-      </c>
-      <c r="S63" s="11" t="s">
-        <v>63</v>
+        <v>46150</v>
+      </c>
+      <c r="S63" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T63" s="9">
         <v>1</v>
@@ -5457,34 +5446,34 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B64" s="5">
+        <v>46160.65269633102</v>
+      </c>
+      <c r="C64" s="5">
+        <v>46181.67669797454</v>
+      </c>
+      <c r="D64" s="5">
+        <v>46184.17212899306</v>
+      </c>
+      <c r="E64" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="B64" s="5">
-        <v>46160.65269097222</v>
-      </c>
-      <c r="C64" s="5">
-        <v>46181.67660690972</v>
-      </c>
-      <c r="D64" s="5">
-        <v>46181.6766224537</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>238</v>
-      </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>231</v>
+        <v>186</v>
       </c>
       <c r="I64" s="5">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="J64" s="5">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
@@ -5496,22 +5485,22 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>174</v>
+        <v>234</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="Q64" s="5">
-        <v>46147</v>
+        <v>46182</v>
       </c>
       <c r="R64" s="5">
-        <v>46150</v>
-      </c>
-      <c r="S64" s="10" t="s">
-        <v>32</v>
+        <v>46183</v>
+      </c>
+      <c r="S64" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T64" s="6">
         <v>1</v>
@@ -5522,61 +5511,61 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B65" s="8">
+        <v>46160.65269980324</v>
+      </c>
+      <c r="C65" s="8">
+        <v>46181.67666710648</v>
+      </c>
+      <c r="D65" s="8">
+        <v>46181.67666866898</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="H65" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="I65" s="8">
+        <v>46178</v>
+      </c>
+      <c r="J65" s="8">
+        <v>46181</v>
+      </c>
+      <c r="K65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M65" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N65" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="O65" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="P65" s="9" t="s">
         <v>240</v>
       </c>
-      <c r="B65" s="8">
-        <v>46160.65269633102</v>
-      </c>
-      <c r="C65" s="8">
-        <v>46181.67669797454</v>
-      </c>
-      <c r="D65" s="8">
-        <v>46184.17212899306</v>
-      </c>
-      <c r="E65" s="9" t="s">
-        <v>241</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="I65" s="8">
-        <v>46182</v>
-      </c>
-      <c r="J65" s="8">
-        <v>46183</v>
-      </c>
-      <c r="K65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M65" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N65" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="O65" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="P65" s="9" t="s">
-        <v>219</v>
-      </c>
       <c r="Q65" s="8">
-        <v>46182</v>
+        <v>46147</v>
       </c>
       <c r="R65" s="8">
-        <v>46183</v>
-      </c>
-      <c r="S65" s="11" t="s">
-        <v>63</v>
+        <v>46150</v>
+      </c>
+      <c r="S65" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T65" s="9">
         <v>1</v>
@@ -5587,34 +5576,34 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B66" s="5">
-        <v>46160.65269980324</v>
+        <v>46160.652703935186</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.67666710648</v>
+        <v>46181.67671591435</v>
       </c>
       <c r="D66" s="5">
-        <v>46181.67666866898</v>
+        <v>46184.172129004626</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>231</v>
+        <v>186</v>
       </c>
       <c r="I66" s="5">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="J66" s="5">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="K66" s="6" t="s">
         <v>26</v>
@@ -5626,22 +5615,22 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>197</v>
+        <v>239</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="Q66" s="5">
-        <v>46147</v>
+        <v>46182</v>
       </c>
       <c r="R66" s="5">
-        <v>46150</v>
-      </c>
-      <c r="S66" s="10" t="s">
-        <v>32</v>
+        <v>46183</v>
+      </c>
+      <c r="S66" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -5652,94 +5641,84 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46160.652703935186</v>
+        <v>46160.65270767361</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.67671591435</v>
+        <v>46181.61286469907</v>
       </c>
       <c r="D67" s="8">
-        <v>46184.172129004626</v>
+        <v>46181.6781084838</v>
       </c>
       <c r="E67" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="F67" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="9"/>
+      <c r="K67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O67" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="F67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G67" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="I67" s="8">
-        <v>46182</v>
-      </c>
-      <c r="J67" s="8">
-        <v>46183</v>
-      </c>
-      <c r="K67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="O67" s="9" t="s">
-        <v>243</v>
-      </c>
       <c r="P67" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q67" s="8">
-        <v>46182</v>
-      </c>
-      <c r="R67" s="8">
-        <v>46183</v>
-      </c>
-      <c r="S67" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="T67" s="9">
-        <v>1</v>
-      </c>
-      <c r="U67" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q67" s="9"/>
+      <c r="R67" s="9"/>
+      <c r="S67" s="9"/>
+      <c r="T67" s="9"/>
+      <c r="U67" s="9"/>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B68" s="5">
+        <v>46160.65271061343</v>
+      </c>
+      <c r="C68" s="5">
+        <v>46181.676856307866</v>
+      </c>
+      <c r="D68" s="5">
+        <v>46189.195743599535</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="B68" s="5">
-        <v>46160.65270767361</v>
-      </c>
-      <c r="C68" s="5">
-        <v>46181.61286469907</v>
-      </c>
-      <c r="D68" s="5">
-        <v>46181.6781084838</v>
-      </c>
-      <c r="E68" s="6" t="s">
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H68" s="6"/>
-      <c r="I68" s="6"/>
-      <c r="J68" s="6"/>
+      <c r="H68" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="I68" s="5">
+        <v>46184</v>
+      </c>
+      <c r="J68" s="5">
+        <v>46188</v>
+      </c>
       <c r="K68" s="6" t="s">
         <v>26</v>
       </c>
@@ -5747,47 +5726,57 @@
         <v>26</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>26</v>
+        <v>243</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
+        <v>243</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>46184</v>
+      </c>
+      <c r="R68" s="5">
+        <v>46188</v>
+      </c>
+      <c r="S68" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T68" s="6">
+        <v>1</v>
+      </c>
+      <c r="U68" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46160.65271061343</v>
+        <v>46160.65271650463</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.676856307866</v>
+        <v>46181.67682665509</v>
       </c>
       <c r="D69" s="8">
-        <v>46189.195743599535</v>
+        <v>46181.67713434028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I69" s="8">
         <v>46184</v>
@@ -5805,54 +5794,44 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q69" s="8">
-        <v>46184</v>
-      </c>
-      <c r="R69" s="8">
-        <v>46188</v>
-      </c>
-      <c r="S69" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="T69" s="9">
-        <v>1</v>
-      </c>
-      <c r="U69" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="Q69" s="9"/>
+      <c r="R69" s="9"/>
+      <c r="S69" s="9"/>
+      <c r="T69" s="9"/>
+      <c r="U69" s="9"/>
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46160.65271650463</v>
+        <v>46160.65272224537</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.67682665509</v>
+        <v>46181.67684240741</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.67713434028</v>
+        <v>46181.67713509259</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I70" s="5">
         <v>46184</v>
@@ -5870,13 +5849,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>255</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>256</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5886,34 +5865,34 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="B71" s="8">
+        <v>46160.652726898144</v>
+      </c>
+      <c r="C71" s="8">
+        <v>46181.677226064814</v>
+      </c>
+      <c r="D71" s="8">
+        <v>46196.198199756946</v>
+      </c>
+      <c r="E71" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="B71" s="8">
-        <v>46160.65272224537</v>
-      </c>
-      <c r="C71" s="8">
-        <v>46181.67684240741</v>
-      </c>
-      <c r="D71" s="8">
-        <v>46181.67713509259</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>221</v>
-      </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I71" s="8">
-        <v>46184</v>
+        <v>46189</v>
       </c>
       <c r="J71" s="8">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="K71" s="9" t="s">
         <v>26</v>
@@ -5925,44 +5904,54 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="O71" s="9" t="s">
         <v>258</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q71" s="9"/>
-      <c r="R71" s="9"/>
-      <c r="S71" s="9"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
+        <v>243</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>46189</v>
+      </c>
+      <c r="R71" s="8">
+        <v>46195</v>
+      </c>
+      <c r="S71" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T71" s="9">
+        <v>1</v>
+      </c>
+      <c r="U71" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B72" s="5">
-        <v>46160.652726898144</v>
+        <v>46160.65273052083</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.677226064814</v>
+        <v>46181.677197129626</v>
       </c>
       <c r="D72" s="5">
-        <v>46196.198199756946</v>
+        <v>46181.67719854167</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I72" s="5">
         <v>46189</v>
@@ -5980,54 +5969,44 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q72" s="5">
-        <v>46189</v>
-      </c>
-      <c r="R72" s="5">
-        <v>46195</v>
-      </c>
-      <c r="S72" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="T72" s="6">
-        <v>1</v>
-      </c>
-      <c r="U72" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>261</v>
+      </c>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="6"/>
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B73" s="8">
-        <v>46160.65273052083</v>
+        <v>46160.652741620375</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.677197129626</v>
+        <v>46181.67721283565</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.67719854167</v>
+        <v>46181.67721436343</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>221</v>
+        <v>255</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I73" s="8">
         <v>46189</v>
@@ -6045,13 +6024,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="O73" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>261</v>
-      </c>
-      <c r="O73" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6061,34 +6040,34 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B74" s="5">
-        <v>46160.652741620375</v>
+        <v>46160.65274630787</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.67721283565</v>
+        <v>46181.67728712963</v>
       </c>
       <c r="D74" s="5">
-        <v>46181.67721436343</v>
+        <v>46197.19306369213</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>251</v>
+        <v>185</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>252</v>
+        <v>186</v>
       </c>
       <c r="I74" s="5">
-        <v>46189</v>
+        <v>46196</v>
       </c>
       <c r="J74" s="5">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="K74" s="6" t="s">
         <v>26</v>
@@ -6100,44 +6079,54 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q74" s="6"/>
-      <c r="R74" s="6"/>
-      <c r="S74" s="6"/>
-      <c r="T74" s="6"/>
-      <c r="U74" s="6"/>
+        <v>243</v>
+      </c>
+      <c r="Q74" s="5">
+        <v>46196</v>
+      </c>
+      <c r="R74" s="5">
+        <v>46196</v>
+      </c>
+      <c r="S74" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T74" s="6">
+        <v>1</v>
+      </c>
+      <c r="U74" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46160.65274630787</v>
+        <v>46160.65275005787</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.67728712963</v>
+        <v>46181.67726334491</v>
       </c>
       <c r="D75" s="8">
-        <v>46197.19306369213</v>
+        <v>46181.67726512731</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>268</v>
+        <v>217</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I75" s="8">
         <v>46196</v>
@@ -6155,54 +6144,44 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q75" s="8">
-        <v>46196</v>
-      </c>
-      <c r="R75" s="8">
-        <v>46196</v>
-      </c>
-      <c r="S75" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="T75" s="9">
-        <v>1</v>
-      </c>
-      <c r="U75" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="Q75" s="9"/>
+      <c r="R75" s="9"/>
+      <c r="S75" s="9"/>
+      <c r="T75" s="9"/>
+      <c r="U75" s="9"/>
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B76" s="5">
-        <v>46160.65275005787</v>
+        <v>46160.65275548611</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.67726334491</v>
+        <v>46181.67727303241</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.67726512731</v>
+        <v>46181.677274664355</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I76" s="5">
         <v>46196</v>
@@ -6220,13 +6199,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="O76" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="O76" s="6" t="s">
-        <v>264</v>
-      </c>
       <c r="P76" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6236,52 +6215,46 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="B77" s="8">
+        <v>46160.652760625</v>
+      </c>
+      <c r="C77" s="8">
+        <v>46181.6130322338</v>
+      </c>
+      <c r="D77" s="8">
+        <v>46181.67751854166</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="F77" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H77" s="9"/>
+      <c r="I77" s="9"/>
+      <c r="J77" s="9"/>
+      <c r="K77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M77" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N77" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O77" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="B77" s="8">
-        <v>46160.65275548611</v>
-      </c>
-      <c r="C77" s="8">
-        <v>46181.67727303241</v>
-      </c>
-      <c r="D77" s="8">
-        <v>46181.677274664355</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G77" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="I77" s="8">
-        <v>46196</v>
-      </c>
-      <c r="J77" s="8">
-        <v>46196</v>
-      </c>
-      <c r="K77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M77" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N77" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="O77" s="9" t="s">
-        <v>272</v>
-      </c>
       <c r="P77" s="9" t="s">
-        <v>273</v>
+        <v>26</v>
       </c>
       <c r="Q77" s="9"/>
       <c r="R77" s="9"/>
@@ -6291,83 +6264,99 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B78" s="5">
+        <v>46160.65276340277</v>
+      </c>
+      <c r="C78" s="5">
+        <v>46181.67731516204</v>
+      </c>
+      <c r="D78" s="5">
+        <v>46192.20460657407</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I78" s="5">
+        <v>46160</v>
+      </c>
+      <c r="J78" s="5">
+        <v>46160</v>
+      </c>
+      <c r="K78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N78" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="P78" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B78" s="5">
-        <v>46160.652760625</v>
-      </c>
-      <c r="C78" s="5">
-        <v>46181.6130322338</v>
-      </c>
-      <c r="D78" s="5">
-        <v>46181.67751854166</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M78" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O78" s="6" t="s">
-        <v>275</v>
-      </c>
-      <c r="P78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q78" s="6"/>
-      <c r="R78" s="6"/>
-      <c r="S78" s="6"/>
-      <c r="T78" s="6"/>
-      <c r="U78" s="6"/>
+      <c r="Q78" s="5">
+        <v>46160</v>
+      </c>
+      <c r="R78" s="5">
+        <v>46191</v>
+      </c>
+      <c r="S78" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="T78" s="6">
+        <v>1</v>
+      </c>
+      <c r="U78" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="B79" s="8">
+        <v>46160.652768831016</v>
+      </c>
+      <c r="C79" s="8">
+        <v>46181.67732524306</v>
+      </c>
+      <c r="D79" s="8">
+        <v>46181.677345034725</v>
+      </c>
+      <c r="E79" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="B79" s="8">
-        <v>46160.65276340277</v>
-      </c>
-      <c r="C79" s="8">
-        <v>46181.67731516204</v>
-      </c>
-      <c r="D79" s="8">
-        <v>46192.20460657407</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>277</v>
-      </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I79" s="8">
-        <v>46160</v>
+        <v>46141</v>
       </c>
       <c r="J79" s="8">
-        <v>46160</v>
+        <v>46141</v>
       </c>
       <c r="K79" s="9" t="s">
         <v>26</v>
@@ -6379,22 +6368,22 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="Q79" s="8">
-        <v>46160</v>
+        <v>46141</v>
       </c>
       <c r="R79" s="8">
-        <v>46191</v>
-      </c>
-      <c r="S79" s="11" t="s">
-        <v>63</v>
+        <v>46141</v>
+      </c>
+      <c r="S79" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T79" s="9">
         <v>1</v>
@@ -6405,34 +6394,34 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B80" s="5">
-        <v>46160.652768831016</v>
+        <v>46160.652774409726</v>
       </c>
       <c r="C80" s="5">
-        <v>46181.67732524306</v>
+        <v>46181.67733638889</v>
       </c>
       <c r="D80" s="5">
-        <v>46181.677345034725</v>
+        <v>46181.67735619213</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I80" s="5">
-        <v>46141</v>
+        <v>46174</v>
       </c>
       <c r="J80" s="5">
-        <v>46141</v>
+        <v>46174</v>
       </c>
       <c r="K80" s="6" t="s">
         <v>26</v>
@@ -6444,22 +6433,22 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="Q80" s="5">
-        <v>46141</v>
+        <v>46174</v>
       </c>
       <c r="R80" s="5">
-        <v>46141</v>
-      </c>
-      <c r="S80" s="10" t="s">
-        <v>32</v>
+        <v>46174</v>
+      </c>
+      <c r="S80" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T80" s="6">
         <v>1</v>
@@ -6470,61 +6459,61 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="B81" s="8">
+        <v>46160.652779745375</v>
+      </c>
+      <c r="C81" s="8">
+        <v>46181.677345601856</v>
+      </c>
+      <c r="D81" s="8">
+        <v>46199.19357225695</v>
+      </c>
+      <c r="E81" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="F81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="I81" s="8">
+        <v>46206</v>
+      </c>
+      <c r="J81" s="8">
+        <v>46206</v>
+      </c>
+      <c r="K81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N81" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="O81" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="P81" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="B81" s="8">
-        <v>46160.652774409726</v>
-      </c>
-      <c r="C81" s="8">
-        <v>46181.67733638889</v>
-      </c>
-      <c r="D81" s="8">
-        <v>46181.67735619213</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>282</v>
-      </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="I81" s="8">
-        <v>46174</v>
-      </c>
-      <c r="J81" s="8">
-        <v>46174</v>
-      </c>
-      <c r="K81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N81" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="O81" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>236</v>
-      </c>
       <c r="Q81" s="8">
-        <v>46174</v>
+        <v>46206</v>
       </c>
       <c r="R81" s="8">
-        <v>46174</v>
-      </c>
-      <c r="S81" s="11" t="s">
-        <v>63</v>
+        <v>46206</v>
+      </c>
+      <c r="S81" s="12" t="s">
+        <v>177</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>
@@ -6535,34 +6524,32 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B82" s="5">
-        <v>46160.652779745375</v>
-      </c>
-      <c r="C82" s="5">
-        <v>46181.677345601856</v>
-      </c>
+        <v>46160.657067569446</v>
+      </c>
+      <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46199.19357225695</v>
+        <v>46198.18861751157</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>284</v>
+        <v>61</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="I82" s="5">
-        <v>46206</v>
+        <v>46197</v>
       </c>
       <c r="J82" s="5">
-        <v>46206</v>
+        <v>46197</v>
       </c>
       <c r="K82" s="6" t="s">
         <v>26</v>
@@ -6574,59 +6561,55 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>185</v>
+        <v>151</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>285</v>
+        <v>58</v>
       </c>
       <c r="Q82" s="5">
-        <v>46206</v>
+        <v>46197</v>
       </c>
       <c r="R82" s="5">
-        <v>46206</v>
-      </c>
-      <c r="S82" s="12" t="s">
-        <v>181</v>
+        <v>46197</v>
+      </c>
+      <c r="S82" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T82" s="6">
-        <v>1</v>
-      </c>
-      <c r="U82" s="10" t="s">
-        <v>33</v>
+        <v>0</v>
+      </c>
+      <c r="U82" s="11" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B83" s="8">
-        <v>46160.657067569446</v>
-      </c>
-      <c r="C83" s="9"/>
+        <v>46160.65278418981</v>
+      </c>
+      <c r="C83" s="8">
+        <v>46181.617794328704</v>
+      </c>
       <c r="D83" s="8">
-        <v>46198.18861751157</v>
+        <v>46197.49724974537</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>61</v>
+        <v>284</v>
       </c>
       <c r="F83" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>230</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="I83" s="8">
-        <v>46197</v>
-      </c>
-      <c r="J83" s="8">
-        <v>46197</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H83" s="9"/>
+      <c r="I83" s="9"/>
+      <c r="J83" s="9"/>
       <c r="K83" s="9" t="s">
         <v>26</v>
       </c>
@@ -6634,108 +6617,114 @@
         <v>26</v>
       </c>
       <c r="M83" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>226</v>
+        <v>26</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>155</v>
+        <v>285</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q83" s="8">
-        <v>46197</v>
-      </c>
-      <c r="R83" s="8">
-        <v>46197</v>
-      </c>
-      <c r="S83" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="T83" s="9">
-        <v>0</v>
-      </c>
-      <c r="U83" s="11" t="s">
-        <v>51</v>
+        <v>26</v>
+      </c>
+      <c r="Q83" s="9"/>
+      <c r="R83" s="9"/>
+      <c r="S83" s="9"/>
+      <c r="T83" s="9"/>
+      <c r="U83" s="12" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B84" s="5">
+        <v>46160.65278701389</v>
+      </c>
+      <c r="C84" s="5">
+        <v>46181.67760038194</v>
+      </c>
+      <c r="D84" s="5">
+        <v>46196.17484756945</v>
+      </c>
+      <c r="E84" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="B84" s="5">
-        <v>46160.65278418981</v>
-      </c>
-      <c r="C84" s="5">
-        <v>46181.617794328704</v>
-      </c>
-      <c r="D84" s="5">
-        <v>46197.49724974537</v>
-      </c>
-      <c r="E84" s="6" t="s">
+      <c r="F84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I84" s="5">
+        <v>46197</v>
+      </c>
+      <c r="J84" s="5">
+        <v>46203</v>
+      </c>
+      <c r="K84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N84" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="O84" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F84" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="6"/>
-      <c r="K84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M84" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>289</v>
-      </c>
       <c r="P84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="6"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="12" t="s">
-        <v>82</v>
+        <v>284</v>
+      </c>
+      <c r="Q84" s="5">
+        <v>46197</v>
+      </c>
+      <c r="R84" s="5">
+        <v>46203</v>
+      </c>
+      <c r="S84" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="T84" s="6">
+        <v>1</v>
+      </c>
+      <c r="U84" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B85" s="8">
-        <v>46160.65278701389</v>
+        <v>46160.65279357639</v>
       </c>
       <c r="C85" s="8">
-        <v>46181.67760038194</v>
+        <v>46181.677674942126</v>
       </c>
       <c r="D85" s="8">
-        <v>46196.17484756945</v>
+        <v>46181.67767618055</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>291</v>
+        <v>217</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6753,54 +6742,44 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q85" s="8">
-        <v>46197</v>
-      </c>
-      <c r="R85" s="8">
-        <v>46203</v>
-      </c>
-      <c r="S85" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="T85" s="9">
-        <v>1</v>
-      </c>
-      <c r="U85" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q85" s="9"/>
+      <c r="R85" s="9"/>
+      <c r="S85" s="9"/>
+      <c r="T85" s="9"/>
+      <c r="U85" s="9"/>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B86" s="5">
-        <v>46160.65279357639</v>
+        <v>46160.65279733796</v>
       </c>
       <c r="C86" s="5">
-        <v>46181.677674942126</v>
+        <v>46181.677687511576</v>
       </c>
       <c r="D86" s="5">
-        <v>46181.67767618055</v>
+        <v>46181.677689247685</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I86" s="5">
         <v>46197</v>
@@ -6818,10 +6797,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6834,34 +6813,34 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B87" s="8">
-        <v>46160.65279733796</v>
+        <v>46160.65280108796</v>
       </c>
       <c r="C87" s="8">
-        <v>46181.677687511576</v>
+        <v>46181.67776662037</v>
       </c>
       <c r="D87" s="8">
-        <v>46181.677689247685</v>
+        <v>46197.19052525463</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>221</v>
+        <v>293</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I87" s="8">
-        <v>46197</v>
+        <v>46204</v>
       </c>
       <c r="J87" s="8">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="K87" s="9" t="s">
         <v>26</v>
@@ -6873,44 +6852,54 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>294</v>
+        <v>215</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q87" s="9"/>
-      <c r="R87" s="9"/>
-      <c r="S87" s="9"/>
-      <c r="T87" s="9"/>
-      <c r="U87" s="9"/>
+        <v>284</v>
+      </c>
+      <c r="Q87" s="8">
+        <v>46204</v>
+      </c>
+      <c r="R87" s="8">
+        <v>46204</v>
+      </c>
+      <c r="S87" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="T87" s="9">
+        <v>1</v>
+      </c>
+      <c r="U87" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
-        <v>46160.65280108796</v>
+        <v>46160.65280498842</v>
       </c>
       <c r="C88" s="5">
-        <v>46181.67776662037</v>
+        <v>46181.677741273146</v>
       </c>
       <c r="D88" s="5">
-        <v>46197.19052525463</v>
+        <v>46181.67774287037</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>297</v>
+        <v>217</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I88" s="5">
         <v>46204</v>
@@ -6928,54 +6917,44 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>219</v>
+        <v>295</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q88" s="5">
-        <v>46204</v>
-      </c>
-      <c r="R88" s="5">
-        <v>46204</v>
-      </c>
-      <c r="S88" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="T88" s="6">
-        <v>1</v>
-      </c>
-      <c r="U88" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>296</v>
+      </c>
+      <c r="Q88" s="6"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="6"/>
+      <c r="T88" s="6"/>
+      <c r="U88" s="6"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B89" s="8">
-        <v>46160.65280498842</v>
+        <v>46160.65281013889</v>
       </c>
       <c r="C89" s="8">
-        <v>46181.677741273146</v>
+        <v>46181.677753344906</v>
       </c>
       <c r="D89" s="8">
-        <v>46181.67774287037</v>
+        <v>46181.67775488426</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I89" s="8">
         <v>46204</v>
@@ -6993,13 +6972,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7009,34 +6988,34 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
-        <v>46160.65281013889</v>
+        <v>46160.65281503472</v>
       </c>
       <c r="C90" s="5">
-        <v>46181.677753344906</v>
+        <v>46181.67783773148</v>
       </c>
       <c r="D90" s="5">
-        <v>46181.67775488426</v>
+        <v>46198.20633876158</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>221</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I90" s="5">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="J90" s="5">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="K90" s="6" t="s">
         <v>26</v>
@@ -7048,48 +7027,56 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>299</v>
+        <v>215</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="6"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
+        <v>284</v>
+      </c>
+      <c r="Q90" s="5">
+        <v>46205</v>
+      </c>
+      <c r="R90" s="5">
+        <v>46205</v>
+      </c>
+      <c r="S90" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="T90" s="6">
+        <v>1</v>
+      </c>
+      <c r="U90" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B91" s="8">
-        <v>46160.65281503472</v>
+        <v>46160.65281883102</v>
       </c>
       <c r="C91" s="8">
-        <v>46181.67783773148</v>
+        <v>46181.67779599537</v>
       </c>
       <c r="D91" s="8">
-        <v>46198.20633876158</v>
+        <v>46181.677797627315</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>303</v>
+        <v>217</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="I91" s="8">
-        <v>46205</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="I91" s="9"/>
       <c r="J91" s="8">
         <v>46205</v>
       </c>
@@ -7103,54 +7090,44 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>219</v>
+        <v>301</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q91" s="8">
-        <v>46205</v>
-      </c>
-      <c r="R91" s="8">
-        <v>46205</v>
-      </c>
-      <c r="S91" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="T91" s="9">
-        <v>1</v>
-      </c>
-      <c r="U91" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="Q91" s="9"/>
+      <c r="R91" s="9"/>
+      <c r="S91" s="9"/>
+      <c r="T91" s="9"/>
+      <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B92" s="5">
-        <v>46160.65281883102</v>
+        <v>46160.65287608796</v>
       </c>
       <c r="C92" s="5">
-        <v>46181.67779599537</v>
+        <v>46181.67780578704</v>
       </c>
       <c r="D92" s="5">
-        <v>46181.677797627315</v>
+        <v>46181.67780725694</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -7166,13 +7143,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7182,32 +7159,34 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B93" s="8">
-        <v>46160.65287608796</v>
+        <v>46160.65288447917</v>
       </c>
       <c r="C93" s="8">
-        <v>46181.67780578704</v>
+        <v>46181.6778656713</v>
       </c>
       <c r="D93" s="8">
-        <v>46181.67780725694</v>
+        <v>46199.193572986114</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>221</v>
+        <v>304</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="I93" s="9"/>
+        <v>90</v>
+      </c>
+      <c r="I93" s="8">
+        <v>46206</v>
+      </c>
       <c r="J93" s="8">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="K93" s="9" t="s">
         <v>26</v>
@@ -7219,44 +7198,54 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>305</v>
+        <v>215</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="Q93" s="9"/>
-      <c r="R93" s="9"/>
-      <c r="S93" s="9"/>
-      <c r="T93" s="9"/>
-      <c r="U93" s="9"/>
+        <v>284</v>
+      </c>
+      <c r="Q93" s="8">
+        <v>46206</v>
+      </c>
+      <c r="R93" s="8">
+        <v>46206</v>
+      </c>
+      <c r="S93" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="T93" s="9">
+        <v>1</v>
+      </c>
+      <c r="U93" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B94" s="5">
-        <v>46160.65288447917</v>
+        <v>46160.65288969908</v>
       </c>
       <c r="C94" s="5">
-        <v>46181.6778656713</v>
+        <v>46181.67784234954</v>
       </c>
       <c r="D94" s="5">
-        <v>46199.193572986114</v>
+        <v>46181.67784412037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>308</v>
+        <v>217</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I94" s="5">
         <v>46206</v>
@@ -7274,54 +7263,44 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>219</v>
+        <v>306</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q94" s="5">
-        <v>46206</v>
-      </c>
-      <c r="R94" s="5">
-        <v>46206</v>
-      </c>
-      <c r="S94" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="T94" s="6">
-        <v>1</v>
-      </c>
-      <c r="U94" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="6"/>
+      <c r="T94" s="6"/>
+      <c r="U94" s="6"/>
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B95" s="8">
-        <v>46160.65288969908</v>
+        <v>46160.6528953588</v>
       </c>
       <c r="C95" s="8">
-        <v>46181.67784234954</v>
+        <v>46181.67784924769</v>
       </c>
       <c r="D95" s="8">
-        <v>46181.67784412037</v>
+        <v>46181.677850625</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I95" s="8">
         <v>46206</v>
@@ -7339,13 +7318,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7355,34 +7334,34 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B96" s="5">
-        <v>46160.6528953588</v>
+        <v>46160.652900706016</v>
       </c>
       <c r="C96" s="5">
-        <v>46181.67784924769</v>
+        <v>46181.677918587964</v>
       </c>
       <c r="D96" s="5">
-        <v>46181.677850625</v>
+        <v>46181.67793089121</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>221</v>
+        <v>310</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I96" s="5">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="J96" s="5">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="K96" s="6" t="s">
         <v>26</v>
@@ -7394,44 +7373,54 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>308</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>310</v>
+        <v>215</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q96" s="6"/>
-      <c r="R96" s="6"/>
-      <c r="S96" s="6"/>
-      <c r="T96" s="6"/>
-      <c r="U96" s="6"/>
+        <v>284</v>
+      </c>
+      <c r="Q96" s="5">
+        <v>46209</v>
+      </c>
+      <c r="R96" s="5">
+        <v>46209</v>
+      </c>
+      <c r="S96" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T96" s="6">
+        <v>1</v>
+      </c>
+      <c r="U96" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B97" s="8">
-        <v>46160.652900706016</v>
+        <v>46160.65290569444</v>
       </c>
       <c r="C97" s="8">
-        <v>46181.677918587964</v>
+        <v>46181.6778925463</v>
       </c>
       <c r="D97" s="8">
-        <v>46181.67793089121</v>
+        <v>46181.67789438658</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>314</v>
+        <v>217</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I97" s="8">
         <v>46209</v>
@@ -7449,54 +7438,44 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q97" s="8">
-        <v>46209</v>
-      </c>
-      <c r="R97" s="8">
-        <v>46209</v>
-      </c>
-      <c r="S97" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T97" s="9">
-        <v>1</v>
-      </c>
-      <c r="U97" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="Q97" s="9"/>
+      <c r="R97" s="9"/>
+      <c r="S97" s="9"/>
+      <c r="T97" s="9"/>
+      <c r="U97" s="9"/>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B98" s="5">
-        <v>46160.65290569444</v>
+        <v>46160.652911157405</v>
       </c>
       <c r="C98" s="5">
-        <v>46181.6778925463</v>
+        <v>46181.67790297454</v>
       </c>
       <c r="D98" s="5">
-        <v>46181.67789438658</v>
+        <v>46181.67790501157</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I98" s="5">
         <v>46209</v>
@@ -7514,13 +7493,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7530,34 +7509,34 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B99" s="8">
-        <v>46160.652911157405</v>
+        <v>46160.65291657408</v>
       </c>
       <c r="C99" s="8">
-        <v>46181.67790297454</v>
+        <v>46197.49723263889</v>
       </c>
       <c r="D99" s="8">
-        <v>46181.67790501157</v>
+        <v>46197.60306288194</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>221</v>
+        <v>315</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I99" s="8">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="J99" s="8">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="K99" s="9" t="s">
         <v>26</v>
@@ -7569,48 +7548,56 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>316</v>
       </c>
-      <c r="Q99" s="9"/>
-      <c r="R99" s="9"/>
-      <c r="S99" s="9"/>
-      <c r="T99" s="9"/>
-      <c r="U99" s="9"/>
+      <c r="Q99" s="8">
+        <v>46211</v>
+      </c>
+      <c r="R99" s="8">
+        <v>46211</v>
+      </c>
+      <c r="S99" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T99" s="9">
+        <v>1</v>
+      </c>
+      <c r="U99" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B100" s="5">
-        <v>46160.65291657408</v>
+        <v>46160.652921562505</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.49723263889</v>
+        <v>46197.60304642361</v>
       </c>
       <c r="D100" s="5">
-        <v>46197.60306288194</v>
+        <v>46198.56608928241</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>319</v>
+        <v>217</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I100" s="5">
-        <v>46211</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="I100" s="6"/>
       <c r="J100" s="5">
         <v>46211</v>
       </c>
@@ -7624,54 +7611,44 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q100" s="5">
-        <v>46211</v>
-      </c>
-      <c r="R100" s="5">
-        <v>46211</v>
-      </c>
-      <c r="S100" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T100" s="6">
-        <v>1</v>
-      </c>
-      <c r="U100" s="12" t="s">
-        <v>82</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="Q100" s="6"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="6"/>
+      <c r="T100" s="6"/>
+      <c r="U100" s="6"/>
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B101" s="8">
-        <v>46160.652921562505</v>
+        <v>46160.65292620371</v>
       </c>
       <c r="C101" s="8">
-        <v>46197.60304642361</v>
+        <v>46197.4972891088</v>
       </c>
       <c r="D101" s="8">
-        <v>46198.56608928241</v>
+        <v>46198.566110405096</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="8">
@@ -7687,13 +7664,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7703,50 +7680,44 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B102" s="5">
+        <v>46160.65293084491</v>
+      </c>
+      <c r="C102" s="6"/>
+      <c r="D102" s="5">
+        <v>46197.49766417824</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G102" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H102" s="6"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="6"/>
+      <c r="K102" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L102" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M102" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N102" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O102" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="B102" s="5">
-        <v>46160.65292620371</v>
-      </c>
-      <c r="C102" s="5">
-        <v>46197.4972891088</v>
-      </c>
-      <c r="D102" s="5">
-        <v>46198.566110405096</v>
-      </c>
-      <c r="E102" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="F102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G102" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="I102" s="6"/>
-      <c r="J102" s="5">
-        <v>46211</v>
-      </c>
-      <c r="K102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N102" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="O102" s="6" t="s">
-        <v>221</v>
-      </c>
       <c r="P102" s="6" t="s">
-        <v>324</v>
+        <v>26</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -7756,27 +7727,33 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B103" s="8">
-        <v>46160.65293084491</v>
+        <v>46160.65293431713</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46197.49766417824</v>
+        <v>46197.49724334491</v>
       </c>
       <c r="E103" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="9" t="s">
         <v>326</v>
       </c>
-      <c r="F103" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H103" s="9"/>
-      <c r="I103" s="9"/>
-      <c r="J103" s="9"/>
+      <c r="H103" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="I103" s="8">
+        <v>46212</v>
+      </c>
+      <c r="J103" s="8">
+        <v>46212</v>
+      </c>
       <c r="K103" s="9" t="s">
         <v>26</v>
       </c>
@@ -7784,45 +7761,55 @@
         <v>26</v>
       </c>
       <c r="M103" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>26</v>
+        <v>322</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q103" s="9"/>
-      <c r="R103" s="9"/>
-      <c r="S103" s="9"/>
-      <c r="T103" s="9"/>
-      <c r="U103" s="9"/>
+        <v>322</v>
+      </c>
+      <c r="Q103" s="8">
+        <v>46212</v>
+      </c>
+      <c r="R103" s="8">
+        <v>46212</v>
+      </c>
+      <c r="S103" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T103" s="9">
+        <v>1</v>
+      </c>
+      <c r="U103" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B104" s="5">
-        <v>46160.65293431713</v>
+        <v>46160.65293966435</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46197.49724334491</v>
+        <v>46197.60305672453</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>329</v>
+        <v>217</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I104" s="5">
         <v>46212</v>
@@ -7840,52 +7827,42 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>332</v>
+        <v>217</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q104" s="5">
-        <v>46212</v>
-      </c>
-      <c r="R104" s="5">
-        <v>46212</v>
-      </c>
-      <c r="S104" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T104" s="6">
-        <v>1</v>
-      </c>
-      <c r="U104" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="Q104" s="6"/>
+      <c r="R104" s="6"/>
+      <c r="S104" s="6"/>
+      <c r="T104" s="6"/>
+      <c r="U104" s="6"/>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B105" s="8">
-        <v>46160.65293966435</v>
+        <v>46160.652944201385</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46197.60305672453</v>
+        <v>46197.49729465278</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I105" s="8">
         <v>46212</v>
@@ -7903,13 +7880,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7919,26 +7896,26 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B106" s="5">
-        <v>46160.652944201385</v>
+        <v>46160.80816486111</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46197.49729465278</v>
+        <v>46160.817732083335</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>221</v>
+        <v>334</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I106" s="5">
         <v>46212</v>
@@ -7956,13 +7933,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>221</v>
+        <v>58</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7972,26 +7949,26 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B107" s="8">
-        <v>46160.80816486111</v>
+        <v>46160.80854525463</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46160.817732083335</v>
+        <v>46160.81773274306</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="I107" s="8">
         <v>46212</v>
@@ -8009,13 +7986,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>58</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8025,81 +8002,93 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B108" s="5">
+        <v>46160.65294850695</v>
+      </c>
+      <c r="C108" s="5">
+        <v>46197.49765626158</v>
+      </c>
+      <c r="D108" s="5">
+        <v>46197.497765231485</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="I108" s="5">
+        <v>46213</v>
+      </c>
+      <c r="J108" s="5">
+        <v>46213</v>
+      </c>
+      <c r="K108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N108" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="O108" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="B108" s="5">
-        <v>46160.80854525463</v>
-      </c>
-      <c r="C108" s="6"/>
-      <c r="D108" s="5">
-        <v>46160.81773274306</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="I108" s="5">
-        <v>46212</v>
-      </c>
-      <c r="J108" s="5">
-        <v>46212</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N108" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>58</v>
-      </c>
       <c r="P108" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="Q108" s="6"/>
-      <c r="R108" s="6"/>
-      <c r="S108" s="6"/>
-      <c r="T108" s="6"/>
-      <c r="U108" s="6"/>
+        <v>322</v>
+      </c>
+      <c r="Q108" s="5">
+        <v>46213</v>
+      </c>
+      <c r="R108" s="5">
+        <v>46213</v>
+      </c>
+      <c r="S108" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T108" s="6">
+        <v>1</v>
+      </c>
+      <c r="U108" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B109" s="8">
-        <v>46160.65294850695</v>
+        <v>46160.652952592594</v>
       </c>
       <c r="C109" s="8">
-        <v>46197.49765626158</v>
+        <v>46197.497369351855</v>
       </c>
       <c r="D109" s="8">
-        <v>46197.497765231485</v>
+        <v>46197.497371261576</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>343</v>
+        <v>217</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I109" s="8">
         <v>46213</v>
@@ -8117,54 +8106,44 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>344</v>
+        <v>217</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q109" s="8">
-        <v>46213</v>
-      </c>
-      <c r="R109" s="8">
-        <v>46213</v>
-      </c>
-      <c r="S109" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T109" s="9">
-        <v>1</v>
-      </c>
-      <c r="U109" s="12" t="s">
-        <v>82</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="Q109" s="9"/>
+      <c r="R109" s="9"/>
+      <c r="S109" s="9"/>
+      <c r="T109" s="9"/>
+      <c r="U109" s="9"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B110" s="5">
-        <v>46160.652952592594</v>
+        <v>46160.65295699074</v>
       </c>
       <c r="C110" s="5">
-        <v>46197.497369351855</v>
+        <v>46197.497530023145</v>
       </c>
       <c r="D110" s="5">
-        <v>46197.497371261576</v>
+        <v>46197.49753173611</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I110" s="5">
         <v>46213</v>
@@ -8182,13 +8161,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8198,28 +8177,26 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B111" s="8">
-        <v>46160.65295699074</v>
-      </c>
-      <c r="C111" s="8">
-        <v>46197.497530023145</v>
-      </c>
+        <v>46160.809122164355</v>
+      </c>
+      <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46197.49753173611</v>
+        <v>46197.4977528125</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>221</v>
+        <v>334</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I111" s="8">
         <v>46213</v>
@@ -8237,13 +8214,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>221</v>
+        <v>334</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8253,26 +8230,26 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B112" s="5">
-        <v>46160.809122164355</v>
+        <v>46160.809137627315</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46197.4977528125</v>
+        <v>46197.497759895836</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I112" s="5">
         <v>46213</v>
@@ -8290,13 +8267,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8306,32 +8283,32 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B113" s="8">
-        <v>46160.809137627315</v>
+        <v>46160.652961203705</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46197.497759895836</v>
+        <v>46194.05666876158</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>94</v>
+        <v>247</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>94</v>
+        <v>248</v>
       </c>
       <c r="I113" s="8">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="J113" s="8">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="K113" s="9" t="s">
         <v>26</v>
@@ -8343,46 +8320,54 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>343</v>
+        <v>322</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="Q113" s="9"/>
-      <c r="R113" s="9"/>
-      <c r="S113" s="9"/>
-      <c r="T113" s="9"/>
-      <c r="U113" s="9"/>
+        <v>322</v>
+      </c>
+      <c r="Q113" s="8">
+        <v>46216</v>
+      </c>
+      <c r="R113" s="8">
+        <v>46216</v>
+      </c>
+      <c r="S113" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T113" s="9">
+        <v>1</v>
+      </c>
+      <c r="U113" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B114" s="5">
-        <v>46160.652961203705</v>
+        <v>46160.65296532407</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46194.05666876158</v>
+        <v>46197.49737577546</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>353</v>
+        <v>217</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="I114" s="5">
-        <v>46216</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="I114" s="6"/>
       <c r="J114" s="5">
         <v>46216</v>
       </c>
@@ -8396,52 +8381,42 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>354</v>
+        <v>217</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="Q114" s="5">
-        <v>46216</v>
-      </c>
-      <c r="R114" s="5">
-        <v>46216</v>
-      </c>
-      <c r="S114" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T114" s="6">
-        <v>1</v>
-      </c>
-      <c r="U114" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="Q114" s="6"/>
+      <c r="R114" s="6"/>
+      <c r="S114" s="6"/>
+      <c r="T114" s="6"/>
+      <c r="U114" s="6"/>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B115" s="8">
-        <v>46160.65296532407</v>
+        <v>46160.65297267361</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46197.49737577546</v>
+        <v>46197.49753788194</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="8">
@@ -8457,13 +8432,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8473,26 +8448,26 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B116" s="5">
-        <v>46160.65297267361</v>
+        <v>46160.81088733797</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46197.49753788194</v>
+        <v>46197.49775597222</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>221</v>
+        <v>334</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8508,13 +8483,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>221</v>
+        <v>334</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8524,26 +8499,26 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B117" s="8">
-        <v>46160.81088733797</v>
+        <v>46160.81089606481</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46197.49775597222</v>
+        <v>46197.49776570602</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8559,13 +8534,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8575,30 +8550,32 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B118" s="5">
-        <v>46160.81089606481</v>
+        <v>46160.65297846065</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46197.49776570602</v>
+        <v>46183.89564782407</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="I118" s="6"/>
+        <v>248</v>
+      </c>
+      <c r="I118" s="5">
+        <v>46217</v>
+      </c>
       <c r="J118" s="5">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>26</v>
@@ -8610,42 +8587,52 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>353</v>
+        <v>322</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="Q118" s="6"/>
-      <c r="R118" s="6"/>
-      <c r="S118" s="6"/>
-      <c r="T118" s="6"/>
-      <c r="U118" s="6"/>
+      <c r="Q118" s="5">
+        <v>46217</v>
+      </c>
+      <c r="R118" s="5">
+        <v>46217</v>
+      </c>
+      <c r="S118" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T118" s="6">
+        <v>0</v>
+      </c>
+      <c r="U118" s="11" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B119" s="8">
-        <v>46160.65297846065</v>
+        <v>46160.652983935186</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46183.89564782407</v>
+        <v>46194.054542048616</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>363</v>
+        <v>217</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I119" s="8">
         <v>46217</v>
@@ -8663,52 +8650,42 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>326</v>
+        <v>359</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>354</v>
+        <v>217</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="Q119" s="8">
-        <v>46217</v>
-      </c>
-      <c r="R119" s="8">
-        <v>46217</v>
-      </c>
-      <c r="S119" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T119" s="9">
-        <v>0</v>
-      </c>
-      <c r="U119" s="11" t="s">
-        <v>51</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="Q119" s="9"/>
+      <c r="R119" s="9"/>
+      <c r="S119" s="9"/>
+      <c r="T119" s="9"/>
+      <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B120" s="5">
-        <v>46160.652983935186</v>
+        <v>46160.65298813657</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46194.054542048616</v>
+        <v>46194.056669247686</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I120" s="5">
         <v>46217</v>
@@ -8726,13 +8703,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8742,26 +8719,26 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B121" s="8">
-        <v>46160.65298813657</v>
+        <v>46160.81215837963</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46194.056669247686</v>
+        <v>46194.05454575231</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>221</v>
+        <v>334</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I121" s="8">
         <v>46217</v>
@@ -8779,13 +8756,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>221</v>
+        <v>334</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8795,26 +8772,26 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B122" s="5">
-        <v>46160.81215837963</v>
+        <v>46160.81220768519</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46194.05454575231</v>
+        <v>46194.05454428241</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="I122" s="5">
         <v>46217</v>
@@ -8832,13 +8809,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8848,33 +8825,27 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B123" s="8">
-        <v>46160.81220768519</v>
+        <v>46160.65302554399</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46194.05454428241</v>
+        <v>46160.8192895949</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="F123" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="I123" s="8">
-        <v>46217</v>
-      </c>
-      <c r="J123" s="8">
-        <v>46217</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H123" s="9"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="9"/>
       <c r="K123" s="9" t="s">
         <v>26</v>
       </c>
@@ -8882,16 +8853,16 @@
         <v>26</v>
       </c>
       <c r="M123" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>363</v>
+        <v>26</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>363</v>
+        <v>26</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8901,27 +8872,33 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B124" s="5">
-        <v>46160.65302554399</v>
+        <v>46160.65302895833</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46160.8192895949</v>
+        <v>46160.819199722224</v>
       </c>
       <c r="E124" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G124" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="F124" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
-      <c r="J124" s="6"/>
+      <c r="H124" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="I124" s="5">
+        <v>46218</v>
+      </c>
+      <c r="J124" s="5">
+        <v>46226</v>
+      </c>
       <c r="K124" s="6" t="s">
         <v>26</v>
       </c>
@@ -8929,33 +8906,43 @@
         <v>26</v>
       </c>
       <c r="M124" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N124" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="O124" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="P124" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q124" s="5">
+        <v>46218</v>
+      </c>
+      <c r="R124" s="5">
+        <v>46226</v>
+      </c>
+      <c r="S124" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T124" s="6">
         <v>0</v>
       </c>
-      <c r="N124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O124" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="P124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q124" s="6"/>
-      <c r="R124" s="6"/>
-      <c r="S124" s="6"/>
-      <c r="T124" s="6"/>
-      <c r="U124" s="6"/>
+      <c r="U124" s="11" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
         <v>372</v>
       </c>
       <c r="B125" s="8">
-        <v>46160.65302895833</v>
+        <v>46160.65303386574</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46160.819199722224</v>
+        <v>46199.75068079861</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>373</v>
@@ -8964,10 +8951,10 @@
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>374</v>
+        <v>36</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>375</v>
+        <v>37</v>
       </c>
       <c r="I125" s="8">
         <v>46218</v>
@@ -8985,13 +8972,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="Q125" s="8">
         <v>46218</v>
@@ -9011,33 +8998,27 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B126" s="5">
-        <v>46160.65303386574</v>
+        <v>46160.65808951389</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46160.81937795139</v>
+        <v>46160.819809513894</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I126" s="5">
-        <v>46218</v>
-      </c>
-      <c r="J126" s="5">
-        <v>46226</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H126" s="6"/>
+      <c r="I126" s="6"/>
+      <c r="J126" s="6"/>
       <c r="K126" s="6" t="s">
         <v>26</v>
       </c>
@@ -9045,23 +9026,19 @@
         <v>26</v>
       </c>
       <c r="M126" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>370</v>
+        <v>26</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="Q126" s="5">
-        <v>46218</v>
-      </c>
-      <c r="R126" s="5">
-        <v>46226</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q126" s="6"/>
+      <c r="R126" s="6"/>
       <c r="S126" s="10" t="s">
         <v>32</v>
       </c>
@@ -9074,27 +9051,33 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B127" s="8">
-        <v>46160.65808951389</v>
+        <v>46160.66095159722</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46160.819809513894</v>
+        <v>46160.81972457176</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="F127" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H127" s="9"/>
-      <c r="I127" s="9"/>
-      <c r="J127" s="9"/>
+        <v>54</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I127" s="8">
+        <v>46218</v>
+      </c>
+      <c r="J127" s="8">
+        <v>46226</v>
+      </c>
       <c r="K127" s="9" t="s">
         <v>26</v>
       </c>
@@ -9102,19 +9085,23 @@
         <v>26</v>
       </c>
       <c r="M127" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>26</v>
+        <v>375</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q127" s="9"/>
-      <c r="R127" s="9"/>
+        <v>379</v>
+      </c>
+      <c r="Q127" s="8">
+        <v>46218</v>
+      </c>
+      <c r="R127" s="8">
+        <v>46226</v>
+      </c>
       <c r="S127" s="10" t="s">
         <v>32</v>
       </c>
@@ -9127,17 +9114,17 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B128" s="5">
-        <v>46160.66095159722</v>
+        <v>46160.66107538194</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46160.81972457176</v>
+        <v>46160.8199466088</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9149,10 +9136,10 @@
         <v>55</v>
       </c>
       <c r="I128" s="5">
-        <v>46218</v>
+        <v>46227</v>
       </c>
       <c r="J128" s="5">
-        <v>46226</v>
+        <v>46237</v>
       </c>
       <c r="K128" s="6" t="s">
         <v>26</v>
@@ -9164,19 +9151,19 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="Q128" s="5">
-        <v>46218</v>
+        <v>46227</v>
       </c>
       <c r="R128" s="5">
-        <v>46226</v>
+        <v>46237</v>
       </c>
       <c r="S128" s="10" t="s">
         <v>32</v>
@@ -9185,69 +9172,6 @@
         <v>0</v>
       </c>
       <c r="U128" s="11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A129" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="B129" s="8">
-        <v>46160.66107538194</v>
-      </c>
-      <c r="C129" s="9"/>
-      <c r="D129" s="8">
-        <v>46160.8199466088</v>
-      </c>
-      <c r="E129" s="9" t="s">
-        <v>386</v>
-      </c>
-      <c r="F129" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G129" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I129" s="8">
-        <v>46227</v>
-      </c>
-      <c r="J129" s="8">
-        <v>46237</v>
-      </c>
-      <c r="K129" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L129" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M129" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N129" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="O129" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="P129" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q129" s="8">
-        <v>46227</v>
-      </c>
-      <c r="R129" s="8">
-        <v>46237</v>
-      </c>
-      <c r="S129" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T129" s="9">
-        <v>0</v>
-      </c>
-      <c r="U129" s="11" t="s">
         <v>51</v>
       </c>
     </row>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -7343,7 +7343,7 @@
         <v>46181.677918587964</v>
       </c>
       <c r="D96" s="5">
-        <v>46181.67793089121</v>
+        <v>46202.16840032407</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>310</v>
@@ -7387,8 +7387,8 @@
       <c r="R96" s="5">
         <v>46209</v>
       </c>
-      <c r="S96" s="10" t="s">
-        <v>32</v>
+      <c r="S96" s="12" t="s">
+        <v>177</v>
       </c>
       <c r="T96" s="6">
         <v>1</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -5036,7 +5036,7 @@
         <v>46198.56611644676</v>
       </c>
       <c r="D57" s="8">
-        <v>46198.566261608794</v>
+        <v>46203.199680034726</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -5080,8 +5080,8 @@
       <c r="R57" s="8">
         <v>46210</v>
       </c>
-      <c r="S57" s="10" t="s">
-        <v>32</v>
+      <c r="S57" s="12" t="s">
+        <v>177</v>
       </c>
       <c r="T57" s="9">
         <v>1</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -6647,7 +6647,7 @@
         <v>46181.67760038194</v>
       </c>
       <c r="D84" s="5">
-        <v>46196.17484756945</v>
+        <v>46204.17292415509</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6691,8 +6691,8 @@
       <c r="R84" s="5">
         <v>46203</v>
       </c>
-      <c r="S84" s="12" t="s">
-        <v>177</v>
+      <c r="S84" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T84" s="6">
         <v>1</v>
@@ -7518,7 +7518,7 @@
         <v>46197.49723263889</v>
       </c>
       <c r="D99" s="8">
-        <v>46197.60306288194</v>
+        <v>46204.17015261574</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>315</v>
@@ -7562,8 +7562,8 @@
       <c r="R99" s="8">
         <v>46211</v>
       </c>
-      <c r="S99" s="10" t="s">
-        <v>32</v>
+      <c r="S99" s="12" t="s">
+        <v>177</v>
       </c>
       <c r="T99" s="9">
         <v>1</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="383">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -1045,6 +1045,9 @@
   </si>
   <si>
     <t>1214909311722244</t>
+  </si>
+  <si>
+    <t>DESPACHADO Y FACTURADO</t>
   </si>
   <si>
     <t>Coordinacion Entrega con Cliente,OT 4313 - ZVN 1-9-45/2</t>
@@ -7734,7 +7737,7 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46197.49724334491</v>
+        <v>46204.802491932875</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>325</v>
@@ -7795,9 +7798,11 @@
       <c r="B104" s="5">
         <v>46160.65293966435</v>
       </c>
-      <c r="C104" s="6"/>
+      <c r="C104" s="5">
+        <v>46204.80222208334</v>
+      </c>
       <c r="D104" s="5">
-        <v>46197.60305672453</v>
+        <v>46204.80222355324</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>217</v>
@@ -7848,9 +7853,11 @@
       <c r="B105" s="8">
         <v>46160.652944201385</v>
       </c>
-      <c r="C105" s="9"/>
+      <c r="C105" s="8">
+        <v>46204.80248626157</v>
+      </c>
       <c r="D105" s="8">
-        <v>46197.49729465278</v>
+        <v>46204.80248778935</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>217</v>
@@ -7874,7 +7881,7 @@
         <v>26</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>26</v>
+        <v>332</v>
       </c>
       <c r="M105" s="9" t="s">
         <v>26</v>
@@ -7886,7 +7893,7 @@
         <v>217</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7896,7 +7903,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B106" s="5">
         <v>46160.80816486111</v>
@@ -7906,7 +7913,7 @@
         <v>46160.817732083335</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7939,7 +7946,7 @@
         <v>58</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7949,7 +7956,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B107" s="8">
         <v>46160.80854525463</v>
@@ -7959,7 +7966,7 @@
         <v>46160.81773274306</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7992,7 +7999,7 @@
         <v>58</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8002,7 +8009,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B108" s="5">
         <v>46160.65294850695</v>
@@ -8014,7 +8021,7 @@
         <v>46197.497765231485</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8044,7 +8051,7 @@
         <v>322</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>322</v>
@@ -8067,7 +8074,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B109" s="8">
         <v>46160.652952592594</v>
@@ -8076,7 +8083,7 @@
         <v>46197.497369351855</v>
       </c>
       <c r="D109" s="8">
-        <v>46197.497371261576</v>
+        <v>46204.80222711805</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>217</v>
@@ -8106,13 +8113,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>217</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8122,7 +8129,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B110" s="5">
         <v>46160.65295699074</v>
@@ -8131,7 +8138,7 @@
         <v>46197.497530023145</v>
       </c>
       <c r="D110" s="5">
-        <v>46197.49753173611</v>
+        <v>46204.80249248842</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>217</v>
@@ -8161,13 +8168,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>217</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8177,7 +8184,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B111" s="8">
         <v>46160.809122164355</v>
@@ -8187,7 +8194,7 @@
         <v>46197.4977528125</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8214,13 +8221,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8230,7 +8237,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B112" s="5">
         <v>46160.809137627315</v>
@@ -8240,7 +8247,7 @@
         <v>46197.497759895836</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8267,13 +8274,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8283,7 +8290,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B113" s="8">
         <v>46160.652961203705</v>
@@ -8293,7 +8300,7 @@
         <v>46194.05666876158</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8323,7 +8330,7 @@
         <v>322</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>322</v>
@@ -8346,7 +8353,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B114" s="5">
         <v>46160.65296532407</v>
@@ -8381,13 +8388,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>217</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8397,7 +8404,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B115" s="8">
         <v>46160.65297267361</v>
@@ -8432,13 +8439,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>217</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8448,7 +8455,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B116" s="5">
         <v>46160.81088733797</v>
@@ -8458,7 +8465,7 @@
         <v>46197.49775597222</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8483,13 +8490,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8499,7 +8506,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B117" s="8">
         <v>46160.81089606481</v>
@@ -8509,7 +8516,7 @@
         <v>46197.49776570602</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8534,13 +8541,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8550,7 +8557,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B118" s="5">
         <v>46160.65297846065</v>
@@ -8560,7 +8567,7 @@
         <v>46183.89564782407</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8590,10 +8597,10 @@
         <v>322</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q118" s="5">
         <v>46217</v>
@@ -8613,7 +8620,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B119" s="8">
         <v>46160.652983935186</v>
@@ -8650,13 +8657,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>217</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8666,7 +8673,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B120" s="5">
         <v>46160.65298813657</v>
@@ -8703,13 +8710,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>217</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8719,7 +8726,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B121" s="8">
         <v>46160.81215837963</v>
@@ -8729,7 +8736,7 @@
         <v>46194.05454575231</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8756,13 +8763,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8772,7 +8779,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B122" s="5">
         <v>46160.81220768519</v>
@@ -8782,7 +8789,7 @@
         <v>46194.05454428241</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8809,13 +8816,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8825,7 +8832,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B123" s="8">
         <v>46160.65302554399</v>
@@ -8835,7 +8842,7 @@
         <v>46160.8192895949</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>25</v>
@@ -8859,7 +8866,7 @@
         <v>26</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>26</v>
@@ -8872,7 +8879,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B124" s="5">
         <v>46160.65302895833</v>
@@ -8882,16 +8889,16 @@
         <v>46160.819199722224</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I124" s="5">
         <v>46218</v>
@@ -8909,13 +8916,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q124" s="5">
         <v>46218</v>
@@ -8935,7 +8942,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B125" s="8">
         <v>46160.65303386574</v>
@@ -8945,7 +8952,7 @@
         <v>46199.75068079861</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8972,13 +8979,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q125" s="8">
         <v>46218</v>
@@ -8998,7 +9005,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B126" s="5">
         <v>46160.65808951389</v>
@@ -9008,7 +9015,7 @@
         <v>46160.819809513894</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>25</v>
@@ -9032,7 +9039,7 @@
         <v>26</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -9051,7 +9058,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B127" s="8">
         <v>46160.66095159722</v>
@@ -9061,7 +9068,7 @@
         <v>46160.81972457176</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9088,13 +9095,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q127" s="8">
         <v>46218</v>
@@ -9114,7 +9121,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B128" s="5">
         <v>46160.66107538194</v>
@@ -9124,7 +9131,7 @@
         <v>46160.8199466088</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9151,13 +9158,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q128" s="5">
         <v>46227</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -1824,13 +1824,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46160.65223744213</v>
+        <v>46160.48557077546</v>
       </c>
       <c r="C4" s="5">
-        <v>46167.55836144676</v>
+        <v>46167.39169478009</v>
       </c>
       <c r="D4" s="5">
-        <v>46181.67878920139</v>
+        <v>46181.512122534725</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1873,13 +1873,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46160.65235053241</v>
+        <v>46160.48568386574</v>
       </c>
       <c r="C5" s="8">
-        <v>46167.558334305555</v>
+        <v>46167.39166763889</v>
       </c>
       <c r="D5" s="8">
-        <v>46167.55833537037</v>
+        <v>46167.391668703705</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1936,13 +1936,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46160.652354039354</v>
+        <v>46160.48568737268</v>
       </c>
       <c r="C6" s="5">
-        <v>46167.55815621528</v>
+        <v>46167.39148954861</v>
       </c>
       <c r="D6" s="5">
-        <v>46167.558157314816</v>
+        <v>46167.39149064815</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1999,13 +1999,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46160.65235689815</v>
+        <v>46160.48569023148</v>
       </c>
       <c r="C7" s="8">
-        <v>46167.55818940973</v>
+        <v>46167.391522743055</v>
       </c>
       <c r="D7" s="8">
-        <v>46167.558190428244</v>
+        <v>46167.39152376157</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -2062,13 +2062,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46160.652359687505</v>
+        <v>46160.48569302083</v>
       </c>
       <c r="C8" s="5">
-        <v>46167.558234027776</v>
+        <v>46167.39156736111</v>
       </c>
       <c r="D8" s="5">
-        <v>46167.55823541667</v>
+        <v>46167.39156875</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -2125,13 +2125,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46160.65236314815</v>
+        <v>46160.48569648148</v>
       </c>
       <c r="C9" s="8">
-        <v>46167.55834611111</v>
+        <v>46167.391679444445</v>
       </c>
       <c r="D9" s="8">
-        <v>46167.558347303246</v>
+        <v>46167.391680636574</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2188,11 +2188,11 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46160.65369118056</v>
+        <v>46160.48702451389</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46167.55829033565</v>
+        <v>46167.391623668984</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2241,13 +2241,13 @@
         <v>52</v>
       </c>
       <c r="B11" s="8">
-        <v>46160.654091874996</v>
+        <v>46160.48742520833</v>
       </c>
       <c r="C11" s="8">
-        <v>46167.55828399306</v>
+        <v>46167.391617326386</v>
       </c>
       <c r="D11" s="8">
-        <v>46167.558296180556</v>
+        <v>46167.39162951389</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>53</v>
@@ -2306,11 +2306,11 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46160.654172118055</v>
+        <v>46160.48750545139</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46199.17997571759</v>
+        <v>46199.013309050926</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2369,11 +2369,11 @@
         <v>64</v>
       </c>
       <c r="B13" s="8">
-        <v>46160.65224207176</v>
+        <v>46160.485575405095</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46199.75069068287</v>
+        <v>46199.58402401621</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>65</v>
@@ -2418,13 +2418,13 @@
         <v>68</v>
       </c>
       <c r="B14" s="5">
-        <v>46160.6523665162</v>
+        <v>46160.48569984954</v>
       </c>
       <c r="C14" s="5">
-        <v>46167.55892170139</v>
+        <v>46167.39225503472</v>
       </c>
       <c r="D14" s="5">
-        <v>46199.75068067129</v>
+        <v>46199.584014004635</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>69</v>
@@ -2483,13 +2483,13 @@
         <v>72</v>
       </c>
       <c r="B15" s="8">
-        <v>46160.65237170139</v>
+        <v>46160.48570503472</v>
       </c>
       <c r="C15" s="8">
-        <v>46167.55892672454</v>
+        <v>46167.392260057866</v>
       </c>
       <c r="D15" s="8">
-        <v>46199.75068077546</v>
+        <v>46199.5840141088</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>73</v>
@@ -2548,13 +2548,13 @@
         <v>76</v>
       </c>
       <c r="B16" s="5">
-        <v>46160.652376875005</v>
+        <v>46160.48571020833</v>
       </c>
       <c r="C16" s="5">
-        <v>46167.558934155095</v>
+        <v>46167.39226748842</v>
       </c>
       <c r="D16" s="5">
-        <v>46199.750680613426</v>
+        <v>46199.58401394676</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>77</v>
@@ -2613,13 +2613,13 @@
         <v>79</v>
       </c>
       <c r="B17" s="8">
-        <v>46160.65224614584</v>
+        <v>46160.485579479166</v>
       </c>
       <c r="C17" s="8">
-        <v>46181.61267278936</v>
+        <v>46181.446006122686</v>
       </c>
       <c r="D17" s="8">
-        <v>46181.678702233796</v>
+        <v>46181.512035567124</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>80</v>
@@ -2662,13 +2662,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46160.652389560186</v>
+        <v>46160.485722893514</v>
       </c>
       <c r="C18" s="5">
-        <v>46167.55896461806</v>
+        <v>46167.39229795139</v>
       </c>
       <c r="D18" s="5">
-        <v>46167.55897762731</v>
+        <v>46167.39231096065</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2727,13 +2727,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46160.65239491899</v>
+        <v>46160.485728252315</v>
       </c>
       <c r="C19" s="8">
-        <v>46167.55899587963</v>
+        <v>46167.39232921296</v>
       </c>
       <c r="D19" s="8">
-        <v>46167.55901266204</v>
+        <v>46167.392345995366</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2792,13 +2792,13 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46160.65240028936</v>
+        <v>46160.485733622685</v>
       </c>
       <c r="C20" s="5">
-        <v>46181.612247048615</v>
+        <v>46181.445580381944</v>
       </c>
       <c r="D20" s="5">
-        <v>46181.61226466435</v>
+        <v>46181.445597997685</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2857,13 +2857,13 @@
         <v>92</v>
       </c>
       <c r="B21" s="8">
-        <v>46160.652405636574</v>
+        <v>46160.4857389699</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.612735636576</v>
+        <v>46181.446068969904</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.67578979167</v>
+        <v>46181.509123125</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>93</v>
@@ -2922,13 +2922,13 @@
         <v>98</v>
       </c>
       <c r="B22" s="5">
-        <v>46160.65241059028</v>
+        <v>46160.48574392361</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.67582236111</v>
+        <v>46181.509155694446</v>
       </c>
       <c r="D22" s="5">
-        <v>46181.67583789352</v>
+        <v>46181.50917122685</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>99</v>
@@ -2987,13 +2987,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46160.652414490745</v>
+        <v>46160.485747824074</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.675860312505</v>
+        <v>46181.509193645834</v>
       </c>
       <c r="D23" s="8">
-        <v>46181.67587553241</v>
+        <v>46181.50920886574</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -3052,13 +3052,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46160.65241840278</v>
+        <v>46160.48575173611</v>
       </c>
       <c r="C24" s="5">
-        <v>46181.67587228009</v>
+        <v>46181.50920561343</v>
       </c>
       <c r="D24" s="5">
-        <v>46181.67588775463</v>
+        <v>46181.50922108797</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -3117,13 +3117,13 @@
         <v>107</v>
       </c>
       <c r="B25" s="8">
-        <v>46160.65857868055</v>
+        <v>46160.49191201389</v>
       </c>
       <c r="C25" s="8">
-        <v>46167.55902803241</v>
+        <v>46167.39236136574</v>
       </c>
       <c r="D25" s="8">
-        <v>46167.55904253472</v>
+        <v>46167.392375868054</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>108</v>
@@ -3182,11 +3182,11 @@
         <v>110</v>
       </c>
       <c r="B26" s="5">
-        <v>46160.65225063657</v>
+        <v>46160.48558396991</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46181.678639652775</v>
+        <v>46181.51197298611</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>111</v>
@@ -3229,13 +3229,13 @@
         <v>113</v>
       </c>
       <c r="B27" s="8">
-        <v>46160.65242274306</v>
+        <v>46160.48575607639</v>
       </c>
       <c r="C27" s="8">
-        <v>46181.67569217592</v>
+        <v>46181.50902550926</v>
       </c>
       <c r="D27" s="8">
-        <v>46181.675709143514</v>
+        <v>46181.50904247686</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>114</v>
@@ -3294,13 +3294,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46160.65242719908</v>
+        <v>46160.48576053241</v>
       </c>
       <c r="C28" s="5">
-        <v>46181.675633032406</v>
+        <v>46181.50896636574</v>
       </c>
       <c r="D28" s="5">
-        <v>46181.67563449074</v>
+        <v>46181.50896782408</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3355,13 +3355,13 @@
         <v>121</v>
       </c>
       <c r="B29" s="8">
-        <v>46160.65243181713</v>
+        <v>46160.485765150464</v>
       </c>
       <c r="C29" s="8">
-        <v>46181.67567633102</v>
+        <v>46181.509009664354</v>
       </c>
       <c r="D29" s="8">
-        <v>46181.67567790509</v>
+        <v>46181.50901123842</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3416,13 +3416,13 @@
         <v>124</v>
       </c>
       <c r="B30" s="5">
-        <v>46160.65243667824</v>
+        <v>46160.485770011575</v>
       </c>
       <c r="C30" s="5">
-        <v>46181.67561266204</v>
+        <v>46181.508945995374</v>
       </c>
       <c r="D30" s="5">
-        <v>46181.67562327546</v>
+        <v>46181.5089566088</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3481,13 +3481,13 @@
         <v>127</v>
       </c>
       <c r="B31" s="8">
-        <v>46160.65244107639</v>
+        <v>46160.485774409724</v>
       </c>
       <c r="C31" s="8">
-        <v>46181.67555267361</v>
+        <v>46181.508886006945</v>
       </c>
       <c r="D31" s="8">
-        <v>46181.67555395833</v>
+        <v>46181.50888729167</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3542,13 +3542,13 @@
         <v>130</v>
       </c>
       <c r="B32" s="5">
-        <v>46160.65244578704</v>
+        <v>46160.48577912037</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.67559679398</v>
+        <v>46181.50893012731</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.67559840278</v>
+        <v>46181.50893173611</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>131</v>
@@ -3603,13 +3603,13 @@
         <v>133</v>
       </c>
       <c r="B33" s="8">
-        <v>46160.652450625</v>
+        <v>46160.485783958335</v>
       </c>
       <c r="C33" s="8">
-        <v>46181.67547991898</v>
+        <v>46181.508813252316</v>
       </c>
       <c r="D33" s="8">
-        <v>46181.67549369213</v>
+        <v>46181.508827025464</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>134</v>
@@ -3668,13 +3668,13 @@
         <v>136</v>
       </c>
       <c r="B34" s="5">
-        <v>46160.65245552083</v>
+        <v>46160.48578885417</v>
       </c>
       <c r="C34" s="5">
-        <v>46181.67541125</v>
+        <v>46181.508744583334</v>
       </c>
       <c r="D34" s="5">
-        <v>46181.67541268519</v>
+        <v>46181.50874601852</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>137</v>
@@ -3729,13 +3729,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="8">
-        <v>46160.65246048611</v>
+        <v>46160.48579381945</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.675452662035</v>
+        <v>46181.50878599537</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.67545391204</v>
+        <v>46181.50878724537</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>140</v>
@@ -3790,13 +3790,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46160.6524655324</v>
+        <v>46160.485798865746</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.675465057866</v>
+        <v>46181.50879839121</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.67546648148</v>
+        <v>46181.508799814816</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3851,11 +3851,11 @@
         <v>145</v>
       </c>
       <c r="B37" s="8">
-        <v>46160.6566696875</v>
+        <v>46160.49000302084</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46197.19306372685</v>
+        <v>46197.02639706018</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>146</v>
@@ -3914,13 +3914,13 @@
         <v>148</v>
       </c>
       <c r="B38" s="5">
-        <v>46160.65676351852</v>
+        <v>46160.49009685185</v>
       </c>
       <c r="C38" s="5">
-        <v>46182.67674130787</v>
+        <v>46182.510074641206</v>
       </c>
       <c r="D38" s="5">
-        <v>46182.67674333333</v>
+        <v>46182.510076666666</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>109</v>
@@ -3969,11 +3969,11 @@
         <v>150</v>
       </c>
       <c r="B39" s="8">
-        <v>46160.65688415509</v>
+        <v>46160.49021748843</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46196.16898914352</v>
+        <v>46196.00232247685</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -4022,13 +4022,13 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46160.65247015047</v>
+        <v>46160.485803483796</v>
       </c>
       <c r="C40" s="5">
-        <v>46181.67623252315</v>
+        <v>46181.50956585648</v>
       </c>
       <c r="D40" s="5">
-        <v>46181.676244386574</v>
+        <v>46181.5095777199</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>154</v>
@@ -4087,13 +4087,13 @@
         <v>158</v>
       </c>
       <c r="B41" s="8">
-        <v>46160.65247482639</v>
+        <v>46160.48580815972</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.676148715276</v>
+        <v>46181.50948204861</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.67615008102</v>
+        <v>46181.50948341435</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>159</v>
@@ -4148,13 +4148,13 @@
         <v>161</v>
       </c>
       <c r="B42" s="5">
-        <v>46160.65247959491</v>
+        <v>46160.48581292824</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.67621893519</v>
+        <v>46181.509552268515</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.67622016204</v>
+        <v>46181.50955349537</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>162</v>
@@ -4209,13 +4209,13 @@
         <v>164</v>
       </c>
       <c r="B43" s="8">
-        <v>46160.65254070602</v>
+        <v>46160.485874039354</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.67635490741</v>
+        <v>46181.50968824074</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.67636662037</v>
+        <v>46181.509699953705</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>165</v>
@@ -4274,13 +4274,13 @@
         <v>167</v>
       </c>
       <c r="B44" s="5">
-        <v>46160.65254572917</v>
+        <v>46160.4858790625</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.67630011574</v>
+        <v>46181.50963344907</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.67630162037</v>
+        <v>46181.509634953705</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>100</v>
@@ -4329,13 +4329,13 @@
         <v>169</v>
       </c>
       <c r="B45" s="8">
-        <v>46160.652551377316</v>
+        <v>46160.48588471065</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.676339375</v>
+        <v>46181.50967270833</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.67634090278</v>
+        <v>46181.50967423611</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>170</v>
@@ -4384,13 +4384,13 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46160.652557152775</v>
+        <v>46160.48589048611</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.67648052084</v>
+        <v>46181.509813854165</v>
       </c>
       <c r="D46" s="5">
-        <v>46198.206338171294</v>
+        <v>46198.03967150463</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4449,13 +4449,13 @@
         <v>178</v>
       </c>
       <c r="B47" s="8">
-        <v>46160.65256162037</v>
+        <v>46160.4858949537</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.67638747685</v>
+        <v>46181.50972081019</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.67638900463</v>
+        <v>46181.50972233796</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>106</v>
@@ -4504,13 +4504,13 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46160.6525734375</v>
+        <v>46160.48590677083</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.676427557875</v>
+        <v>46181.509760891204</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.67642934028</v>
+        <v>46181.50976267361</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>181</v>
@@ -4559,13 +4559,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46160.652579236106</v>
+        <v>46160.48591256945</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.67646592592</v>
+        <v>46181.509799259264</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.676467303245</v>
+        <v>46181.50980063657</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4614,13 +4614,13 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46160.65258304398</v>
+        <v>46160.485916377314</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.676567789356</v>
+        <v>46181.509901122685</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.67657885417</v>
+        <v>46181.509912187496</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4679,13 +4679,13 @@
         <v>190</v>
       </c>
       <c r="B51" s="8">
-        <v>46160.6525875463</v>
+        <v>46160.485920879626</v>
       </c>
       <c r="C51" s="8">
-        <v>46181.676511840276</v>
+        <v>46181.50984517361</v>
       </c>
       <c r="D51" s="8">
-        <v>46181.67651314815</v>
+        <v>46181.50984648148</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>103</v>
@@ -4734,13 +4734,13 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46160.652593067134</v>
+        <v>46160.48592640046</v>
       </c>
       <c r="C52" s="5">
-        <v>46181.67655238426</v>
+        <v>46181.50988571759</v>
       </c>
       <c r="D52" s="5">
-        <v>46181.676553680554</v>
+        <v>46181.50988701389</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4789,13 +4789,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46160.65225516204</v>
+        <v>46160.48558849537</v>
       </c>
       <c r="C53" s="8">
-        <v>46181.612413587965</v>
+        <v>46181.445746921294</v>
       </c>
       <c r="D53" s="8">
-        <v>46181.67858451389</v>
+        <v>46181.51191784722</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4838,13 +4838,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46160.65259921296</v>
+        <v>46160.4859325463</v>
       </c>
       <c r="C54" s="5">
-        <v>46181.61232818287</v>
+        <v>46181.445661516205</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.712640196754</v>
+        <v>46197.5459735301</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4903,13 +4903,13 @@
         <v>203</v>
       </c>
       <c r="B55" s="8">
-        <v>46160.652606006945</v>
+        <v>46160.48593934027</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.675721631946</v>
+        <v>46181.50905496528</v>
       </c>
       <c r="D55" s="8">
-        <v>46197.71267317129</v>
+        <v>46197.54600650463</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>204</v>
@@ -4968,13 +4968,13 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46160.65261409723</v>
+        <v>46160.485947430556</v>
       </c>
       <c r="C56" s="5">
-        <v>46181.67576423611</v>
+        <v>46181.50909756945</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.67578048611</v>
+        <v>46181.50911381944</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>96</v>
@@ -5033,13 +5033,13 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46160.652630983794</v>
+        <v>46160.48596431713</v>
       </c>
       <c r="C57" s="8">
-        <v>46198.56611644676</v>
+        <v>46198.39944978009</v>
       </c>
       <c r="D57" s="8">
-        <v>46203.199680034726</v>
+        <v>46203.033013368055</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -5098,13 +5098,13 @@
         <v>216</v>
       </c>
       <c r="B58" s="5">
-        <v>46160.65263532408</v>
+        <v>46160.485968657405</v>
       </c>
       <c r="C58" s="5">
-        <v>46198.56608402778</v>
+        <v>46198.39941736111</v>
       </c>
       <c r="D58" s="5">
-        <v>46198.566085625</v>
+        <v>46198.39941895833</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>217</v>
@@ -5153,13 +5153,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46160.65264069445</v>
+        <v>46160.485974027775</v>
       </c>
       <c r="C59" s="8">
-        <v>46198.566099675925</v>
+        <v>46198.39943300926</v>
       </c>
       <c r="D59" s="8">
-        <v>46198.5661015625</v>
+        <v>46198.39943489584</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>217</v>
@@ -5208,13 +5208,13 @@
         <v>221</v>
       </c>
       <c r="B60" s="5">
-        <v>46160.652676921294</v>
+        <v>46160.48601025463</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.612796331014</v>
+        <v>46181.44612966436</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.67816971065</v>
+        <v>46181.51150304398</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>222</v>
@@ -5257,13 +5257,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46160.65268083333</v>
+        <v>46160.486014166665</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.67658946759</v>
+        <v>46181.50992280093</v>
       </c>
       <c r="D61" s="8">
-        <v>46182.19861893519</v>
+        <v>46182.03195226852</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>225</v>
@@ -5322,13 +5322,13 @@
         <v>229</v>
       </c>
       <c r="B62" s="5">
-        <v>46160.652685810186</v>
+        <v>46160.486019143515</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.67668319444</v>
+        <v>46181.510016527776</v>
       </c>
       <c r="D62" s="5">
-        <v>46184.17212899306</v>
+        <v>46184.005462326386</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>230</v>
@@ -5387,13 +5387,13 @@
         <v>233</v>
       </c>
       <c r="B63" s="8">
-        <v>46160.65269097222</v>
+        <v>46160.48602430556</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.67660690972</v>
+        <v>46181.50994024306</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.6766224537</v>
+        <v>46181.50995578704</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>234</v>
@@ -5452,13 +5452,13 @@
         <v>236</v>
       </c>
       <c r="B64" s="5">
-        <v>46160.65269633102</v>
+        <v>46160.48602966435</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.67669797454</v>
+        <v>46181.51003130787</v>
       </c>
       <c r="D64" s="5">
-        <v>46184.17212899306</v>
+        <v>46184.005462326386</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>237</v>
@@ -5517,13 +5517,13 @@
         <v>238</v>
       </c>
       <c r="B65" s="8">
-        <v>46160.65269980324</v>
+        <v>46160.48603313658</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.67666710648</v>
+        <v>46181.51000043981</v>
       </c>
       <c r="D65" s="8">
-        <v>46181.67666866898</v>
+        <v>46181.51000200232</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>239</v>
@@ -5582,13 +5582,13 @@
         <v>241</v>
       </c>
       <c r="B66" s="5">
-        <v>46160.652703935186</v>
+        <v>46160.48603726852</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.67671591435</v>
+        <v>46181.510049247685</v>
       </c>
       <c r="D66" s="5">
-        <v>46184.172129004626</v>
+        <v>46184.00546233796</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5647,13 +5647,13 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46160.65270767361</v>
+        <v>46160.486041006945</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.61286469907</v>
+        <v>46181.44619803241</v>
       </c>
       <c r="D67" s="8">
-        <v>46181.6781084838</v>
+        <v>46181.51144181713</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5696,13 +5696,13 @@
         <v>245</v>
       </c>
       <c r="B68" s="5">
-        <v>46160.65271061343</v>
+        <v>46160.48604394676</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.676856307866</v>
+        <v>46181.51018964121</v>
       </c>
       <c r="D68" s="5">
-        <v>46189.195743599535</v>
+        <v>46189.02907693287</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -5761,13 +5761,13 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46160.65271650463</v>
+        <v>46160.486049837964</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.67682665509</v>
+        <v>46181.51015998842</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.67713434028</v>
+        <v>46181.51046767361</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>217</v>
@@ -5816,13 +5816,13 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46160.65272224537</v>
+        <v>46160.4860555787</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.67684240741</v>
+        <v>46181.51017574074</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.67713509259</v>
+        <v>46181.51046842593</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>217</v>
@@ -5871,13 +5871,13 @@
         <v>256</v>
       </c>
       <c r="B71" s="8">
-        <v>46160.652726898144</v>
+        <v>46160.48606023148</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.677226064814</v>
+        <v>46181.51055939815</v>
       </c>
       <c r="D71" s="8">
-        <v>46196.198199756946</v>
+        <v>46196.03153309028</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>257</v>
@@ -5936,13 +5936,13 @@
         <v>259</v>
       </c>
       <c r="B72" s="5">
-        <v>46160.65273052083</v>
+        <v>46160.486063854165</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.677197129626</v>
+        <v>46181.51053046296</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.67719854167</v>
+        <v>46181.510531875</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>217</v>
@@ -5991,13 +5991,13 @@
         <v>262</v>
       </c>
       <c r="B73" s="8">
-        <v>46160.652741620375</v>
+        <v>46160.486074953704</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.67721283565</v>
+        <v>46181.51054616898</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.67721436343</v>
+        <v>46181.51054769676</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>255</v>
@@ -6046,13 +6046,13 @@
         <v>263</v>
       </c>
       <c r="B74" s="5">
-        <v>46160.65274630787</v>
+        <v>46160.4860796412</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.67728712963</v>
+        <v>46181.51062046296</v>
       </c>
       <c r="D74" s="5">
-        <v>46197.19306369213</v>
+        <v>46197.02639702546</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -6111,13 +6111,13 @@
         <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46160.65275005787</v>
+        <v>46160.4860833912</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.67726334491</v>
+        <v>46181.51059667824</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.67726512731</v>
+        <v>46181.51059846065</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>217</v>
@@ -6166,13 +6166,13 @@
         <v>267</v>
       </c>
       <c r="B76" s="5">
-        <v>46160.65275548611</v>
+        <v>46160.486088819445</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.67727303241</v>
+        <v>46181.510606365744</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.677274664355</v>
+        <v>46181.51060799768</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>217</v>
@@ -6221,13 +6221,13 @@
         <v>270</v>
       </c>
       <c r="B77" s="8">
-        <v>46160.652760625</v>
+        <v>46160.48609395833</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.6130322338</v>
+        <v>46181.44636556713</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.67751854166</v>
+        <v>46181.510851875</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>222</v>
@@ -6270,13 +6270,13 @@
         <v>272</v>
       </c>
       <c r="B78" s="5">
-        <v>46160.65276340277</v>
+        <v>46160.48609673612</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.67731516204</v>
+        <v>46181.51064849537</v>
       </c>
       <c r="D78" s="5">
-        <v>46192.20460657407</v>
+        <v>46192.03793990741</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>273</v>
@@ -6335,13 +6335,13 @@
         <v>275</v>
       </c>
       <c r="B79" s="8">
-        <v>46160.652768831016</v>
+        <v>46160.48610216435</v>
       </c>
       <c r="C79" s="8">
-        <v>46181.67732524306</v>
+        <v>46181.510658576386</v>
       </c>
       <c r="D79" s="8">
-        <v>46181.677345034725</v>
+        <v>46181.51067836805</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>276</v>
@@ -6400,13 +6400,13 @@
         <v>277</v>
       </c>
       <c r="B80" s="5">
-        <v>46160.652774409726</v>
+        <v>46160.486107743054</v>
       </c>
       <c r="C80" s="5">
-        <v>46181.67733638889</v>
+        <v>46181.51066972222</v>
       </c>
       <c r="D80" s="5">
-        <v>46181.67735619213</v>
+        <v>46181.51068952546</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>278</v>
@@ -6465,13 +6465,13 @@
         <v>279</v>
       </c>
       <c r="B81" s="8">
-        <v>46160.652779745375</v>
+        <v>46160.4861130787</v>
       </c>
       <c r="C81" s="8">
-        <v>46181.677345601856</v>
+        <v>46181.510678935185</v>
       </c>
       <c r="D81" s="8">
-        <v>46199.19357225695</v>
+        <v>46199.026905590275</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>280</v>
@@ -6530,11 +6530,11 @@
         <v>282</v>
       </c>
       <c r="B82" s="5">
-        <v>46160.657067569446</v>
+        <v>46160.49040090278</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.18861751157</v>
+        <v>46198.02195084491</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>61</v>
@@ -6593,13 +6593,13 @@
         <v>283</v>
       </c>
       <c r="B83" s="8">
-        <v>46160.65278418981</v>
+        <v>46160.48611752315</v>
       </c>
       <c r="C83" s="8">
-        <v>46181.617794328704</v>
+        <v>46181.45112766203</v>
       </c>
       <c r="D83" s="8">
-        <v>46197.49724974537</v>
+        <v>46197.3305830787</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>284</v>
@@ -6644,13 +6644,13 @@
         <v>286</v>
       </c>
       <c r="B84" s="5">
-        <v>46160.65278701389</v>
+        <v>46160.486120347225</v>
       </c>
       <c r="C84" s="5">
-        <v>46181.67760038194</v>
+        <v>46181.51093371528</v>
       </c>
       <c r="D84" s="5">
-        <v>46204.17292415509</v>
+        <v>46204.00625748842</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6709,13 +6709,13 @@
         <v>289</v>
       </c>
       <c r="B85" s="8">
-        <v>46160.65279357639</v>
+        <v>46160.486126909724</v>
       </c>
       <c r="C85" s="8">
-        <v>46181.677674942126</v>
+        <v>46181.51100827546</v>
       </c>
       <c r="D85" s="8">
-        <v>46181.67767618055</v>
+        <v>46181.51100951389</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>217</v>
@@ -6764,13 +6764,13 @@
         <v>291</v>
       </c>
       <c r="B86" s="5">
-        <v>46160.65279733796</v>
+        <v>46160.4861306713</v>
       </c>
       <c r="C86" s="5">
-        <v>46181.677687511576</v>
+        <v>46181.511020844904</v>
       </c>
       <c r="D86" s="5">
-        <v>46181.677689247685</v>
+        <v>46181.51102258102</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>217</v>
@@ -6819,13 +6819,13 @@
         <v>292</v>
       </c>
       <c r="B87" s="8">
-        <v>46160.65280108796</v>
+        <v>46160.4861344213</v>
       </c>
       <c r="C87" s="8">
-        <v>46181.67776662037</v>
+        <v>46181.5110999537</v>
       </c>
       <c r="D87" s="8">
-        <v>46197.19052525463</v>
+        <v>46205.015753541666</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>293</v>
@@ -6869,8 +6869,8 @@
       <c r="R87" s="8">
         <v>46204</v>
       </c>
-      <c r="S87" s="12" t="s">
-        <v>177</v>
+      <c r="S87" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -6884,13 +6884,13 @@
         <v>294</v>
       </c>
       <c r="B88" s="5">
-        <v>46160.65280498842</v>
+        <v>46160.48613832176</v>
       </c>
       <c r="C88" s="5">
-        <v>46181.677741273146</v>
+        <v>46181.51107460648</v>
       </c>
       <c r="D88" s="5">
-        <v>46181.67774287037</v>
+        <v>46181.51107620371</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>217</v>
@@ -6939,13 +6939,13 @@
         <v>297</v>
       </c>
       <c r="B89" s="8">
-        <v>46160.65281013889</v>
+        <v>46160.486143472226</v>
       </c>
       <c r="C89" s="8">
-        <v>46181.677753344906</v>
+        <v>46181.51108667824</v>
       </c>
       <c r="D89" s="8">
-        <v>46181.67775488426</v>
+        <v>46181.511088217594</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>217</v>
@@ -6994,13 +6994,13 @@
         <v>298</v>
       </c>
       <c r="B90" s="5">
-        <v>46160.65281503472</v>
+        <v>46160.48614836806</v>
       </c>
       <c r="C90" s="5">
-        <v>46181.67783773148</v>
+        <v>46181.51117106482</v>
       </c>
       <c r="D90" s="5">
-        <v>46198.20633876158</v>
+        <v>46198.03967209491</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>299</v>
@@ -7059,13 +7059,13 @@
         <v>300</v>
       </c>
       <c r="B91" s="8">
-        <v>46160.65281883102</v>
+        <v>46160.48615216435</v>
       </c>
       <c r="C91" s="8">
-        <v>46181.67779599537</v>
+        <v>46181.511129328705</v>
       </c>
       <c r="D91" s="8">
-        <v>46181.677797627315</v>
+        <v>46181.511130960644</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>217</v>
@@ -7112,13 +7112,13 @@
         <v>302</v>
       </c>
       <c r="B92" s="5">
-        <v>46160.65287608796</v>
+        <v>46160.486209421295</v>
       </c>
       <c r="C92" s="5">
-        <v>46181.67780578704</v>
+        <v>46181.51113912037</v>
       </c>
       <c r="D92" s="5">
-        <v>46181.67780725694</v>
+        <v>46181.51114059028</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>217</v>
@@ -7165,13 +7165,13 @@
         <v>303</v>
       </c>
       <c r="B93" s="8">
-        <v>46160.65288447917</v>
+        <v>46160.486217812504</v>
       </c>
       <c r="C93" s="8">
-        <v>46181.6778656713</v>
+        <v>46181.51119900463</v>
       </c>
       <c r="D93" s="8">
-        <v>46199.193572986114</v>
+        <v>46199.02690631944</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>304</v>
@@ -7230,13 +7230,13 @@
         <v>305</v>
       </c>
       <c r="B94" s="5">
-        <v>46160.65288969908</v>
+        <v>46160.48622303241</v>
       </c>
       <c r="C94" s="5">
-        <v>46181.67784234954</v>
+        <v>46181.51117568287</v>
       </c>
       <c r="D94" s="5">
-        <v>46181.67784412037</v>
+        <v>46181.51117745371</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>217</v>
@@ -7285,13 +7285,13 @@
         <v>308</v>
       </c>
       <c r="B95" s="8">
-        <v>46160.6528953588</v>
+        <v>46160.48622869213</v>
       </c>
       <c r="C95" s="8">
-        <v>46181.67784924769</v>
+        <v>46181.511182581016</v>
       </c>
       <c r="D95" s="8">
-        <v>46181.677850625</v>
+        <v>46181.51118395833</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>217</v>
@@ -7340,13 +7340,13 @@
         <v>309</v>
       </c>
       <c r="B96" s="5">
-        <v>46160.652900706016</v>
+        <v>46160.48623403935</v>
       </c>
       <c r="C96" s="5">
-        <v>46181.677918587964</v>
+        <v>46181.5112519213</v>
       </c>
       <c r="D96" s="5">
-        <v>46202.16840032407</v>
+        <v>46202.00173365741</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>310</v>
@@ -7405,13 +7405,13 @@
         <v>311</v>
       </c>
       <c r="B97" s="8">
-        <v>46160.65290569444</v>
+        <v>46160.48623902778</v>
       </c>
       <c r="C97" s="8">
-        <v>46181.6778925463</v>
+        <v>46181.51122587963</v>
       </c>
       <c r="D97" s="8">
-        <v>46181.67789438658</v>
+        <v>46181.51122771991</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>217</v>
@@ -7460,13 +7460,13 @@
         <v>313</v>
       </c>
       <c r="B98" s="5">
-        <v>46160.652911157405</v>
+        <v>46160.48624449074</v>
       </c>
       <c r="C98" s="5">
-        <v>46181.67790297454</v>
+        <v>46181.511236307866</v>
       </c>
       <c r="D98" s="5">
-        <v>46181.67790501157</v>
+        <v>46181.51123834491</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>217</v>
@@ -7515,13 +7515,13 @@
         <v>314</v>
       </c>
       <c r="B99" s="8">
-        <v>46160.65291657408</v>
+        <v>46160.48624990741</v>
       </c>
       <c r="C99" s="8">
-        <v>46197.49723263889</v>
+        <v>46197.330565972225</v>
       </c>
       <c r="D99" s="8">
-        <v>46204.17015261574</v>
+        <v>46204.00348594907</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>315</v>
@@ -7580,13 +7580,13 @@
         <v>317</v>
       </c>
       <c r="B100" s="5">
-        <v>46160.652921562505</v>
+        <v>46160.48625489583</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.60304642361</v>
+        <v>46197.436379756946</v>
       </c>
       <c r="D100" s="5">
-        <v>46198.56608928241</v>
+        <v>46198.39942261574</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>217</v>
@@ -7633,13 +7633,13 @@
         <v>319</v>
       </c>
       <c r="B101" s="8">
-        <v>46160.65292620371</v>
+        <v>46160.486259537036</v>
       </c>
       <c r="C101" s="8">
-        <v>46197.4972891088</v>
+        <v>46197.330622442125</v>
       </c>
       <c r="D101" s="8">
-        <v>46198.566110405096</v>
+        <v>46198.399443738424</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>217</v>
@@ -7686,11 +7686,11 @@
         <v>321</v>
       </c>
       <c r="B102" s="5">
-        <v>46160.65293084491</v>
+        <v>46160.48626417824</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46197.49766417824</v>
+        <v>46197.33099751157</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>322</v>
@@ -7733,11 +7733,11 @@
         <v>324</v>
       </c>
       <c r="B103" s="8">
-        <v>46160.65293431713</v>
+        <v>46160.48626765046</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46204.802491932875</v>
+        <v>46205.00763515046</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>325</v>
@@ -7781,8 +7781,8 @@
       <c r="R103" s="8">
         <v>46212</v>
       </c>
-      <c r="S103" s="10" t="s">
-        <v>32</v>
+      <c r="S103" s="12" t="s">
+        <v>177</v>
       </c>
       <c r="T103" s="9">
         <v>1</v>
@@ -7796,13 +7796,13 @@
         <v>329</v>
       </c>
       <c r="B104" s="5">
-        <v>46160.65293966435</v>
+        <v>46160.48627299769</v>
       </c>
       <c r="C104" s="5">
-        <v>46204.80222208334</v>
+        <v>46204.635555416666</v>
       </c>
       <c r="D104" s="5">
-        <v>46204.80222355324</v>
+        <v>46204.63555688657</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>217</v>
@@ -7851,13 +7851,13 @@
         <v>331</v>
       </c>
       <c r="B105" s="8">
-        <v>46160.652944201385</v>
+        <v>46160.48627753472</v>
       </c>
       <c r="C105" s="8">
-        <v>46204.80248626157</v>
+        <v>46204.63581959491</v>
       </c>
       <c r="D105" s="8">
-        <v>46204.80248778935</v>
+        <v>46204.63582112268</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>217</v>
@@ -7906,11 +7906,11 @@
         <v>334</v>
       </c>
       <c r="B106" s="5">
-        <v>46160.80816486111</v>
+        <v>46160.64149819444</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46160.817732083335</v>
+        <v>46160.65106541666</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>335</v>
@@ -7959,11 +7959,11 @@
         <v>337</v>
       </c>
       <c r="B107" s="8">
-        <v>46160.80854525463</v>
+        <v>46160.641878587965</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46160.81773274306</v>
+        <v>46160.65106607639</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>335</v>
@@ -8012,13 +8012,13 @@
         <v>339</v>
       </c>
       <c r="B108" s="5">
-        <v>46160.65294850695</v>
+        <v>46160.486281840276</v>
       </c>
       <c r="C108" s="5">
-        <v>46197.49765626158</v>
+        <v>46197.330989594906</v>
       </c>
       <c r="D108" s="5">
-        <v>46197.497765231485</v>
+        <v>46197.33109856481</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>340</v>
@@ -8077,13 +8077,13 @@
         <v>342</v>
       </c>
       <c r="B109" s="8">
-        <v>46160.652952592594</v>
+        <v>46160.48628592593</v>
       </c>
       <c r="C109" s="8">
-        <v>46197.497369351855</v>
+        <v>46197.33070268518</v>
       </c>
       <c r="D109" s="8">
-        <v>46204.80222711805</v>
+        <v>46204.63556045139</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>217</v>
@@ -8132,13 +8132,13 @@
         <v>344</v>
       </c>
       <c r="B110" s="5">
-        <v>46160.65295699074</v>
+        <v>46160.48629032407</v>
       </c>
       <c r="C110" s="5">
-        <v>46197.497530023145</v>
+        <v>46197.33086335648</v>
       </c>
       <c r="D110" s="5">
-        <v>46204.80249248842</v>
+        <v>46204.63582582176</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>217</v>
@@ -8187,11 +8187,11 @@
         <v>345</v>
       </c>
       <c r="B111" s="8">
-        <v>46160.809122164355</v>
+        <v>46160.642455497684</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46197.4977528125</v>
+        <v>46197.33108614583</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>335</v>
@@ -8240,11 +8240,11 @@
         <v>347</v>
       </c>
       <c r="B112" s="5">
-        <v>46160.809137627315</v>
+        <v>46160.64247096065</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46197.497759895836</v>
+        <v>46197.331093229164</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>348</v>
@@ -8293,11 +8293,11 @@
         <v>349</v>
       </c>
       <c r="B113" s="8">
-        <v>46160.652961203705</v>
+        <v>46160.48629453704</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46194.05666876158</v>
+        <v>46193.89000209491</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>350</v>
@@ -8356,11 +8356,11 @@
         <v>352</v>
       </c>
       <c r="B114" s="5">
-        <v>46160.65296532407</v>
+        <v>46160.48629865741</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46197.49737577546</v>
+        <v>46197.33070910879</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>217</v>
@@ -8407,11 +8407,11 @@
         <v>354</v>
       </c>
       <c r="B115" s="8">
-        <v>46160.65297267361</v>
+        <v>46160.48630600695</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46197.49753788194</v>
+        <v>46197.33087121528</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>217</v>
@@ -8458,11 +8458,11 @@
         <v>356</v>
       </c>
       <c r="B116" s="5">
-        <v>46160.81088733797</v>
+        <v>46160.644220671296</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46197.49775597222</v>
+        <v>46197.33108930556</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>335</v>
@@ -8509,11 +8509,11 @@
         <v>358</v>
       </c>
       <c r="B117" s="8">
-        <v>46160.81089606481</v>
+        <v>46160.64422939815</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46197.49776570602</v>
+        <v>46197.33109903935</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>335</v>
@@ -8560,11 +8560,11 @@
         <v>359</v>
       </c>
       <c r="B118" s="5">
-        <v>46160.65297846065</v>
+        <v>46160.48631179398</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46183.89564782407</v>
+        <v>46183.72898115741</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>360</v>
@@ -8623,11 +8623,11 @@
         <v>362</v>
       </c>
       <c r="B119" s="8">
-        <v>46160.652983935186</v>
+        <v>46160.486317268515</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46194.054542048616</v>
+        <v>46193.887875381944</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>217</v>
@@ -8676,11 +8676,11 @@
         <v>363</v>
       </c>
       <c r="B120" s="5">
-        <v>46160.65298813657</v>
+        <v>46160.48632146991</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46194.056669247686</v>
+        <v>46193.890002581014</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>217</v>
@@ -8729,11 +8729,11 @@
         <v>364</v>
       </c>
       <c r="B121" s="8">
-        <v>46160.81215837963</v>
+        <v>46160.64549171296</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46194.05454575231</v>
+        <v>46193.88787908565</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>335</v>
@@ -8782,11 +8782,11 @@
         <v>365</v>
       </c>
       <c r="B122" s="5">
-        <v>46160.81220768519</v>
+        <v>46160.645541018515</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46194.05454428241</v>
+        <v>46193.887877615736</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>335</v>
@@ -8835,11 +8835,11 @@
         <v>366</v>
       </c>
       <c r="B123" s="8">
-        <v>46160.65302554399</v>
+        <v>46160.486358877315</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46160.8192895949</v>
+        <v>46160.65262292824</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>367</v>
@@ -8882,11 +8882,11 @@
         <v>369</v>
       </c>
       <c r="B124" s="5">
-        <v>46160.65302895833</v>
+        <v>46160.48636229167</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46160.819199722224</v>
+        <v>46160.65253305556</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>370</v>
@@ -8945,11 +8945,11 @@
         <v>373</v>
       </c>
       <c r="B125" s="8">
-        <v>46160.65303386574</v>
+        <v>46160.486367199075</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46199.75068079861</v>
+        <v>46199.58401413195</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>374</v>
@@ -9008,11 +9008,11 @@
         <v>375</v>
       </c>
       <c r="B126" s="5">
-        <v>46160.65808951389</v>
+        <v>46160.49142284722</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46160.819809513894</v>
+        <v>46160.65314284722</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>376</v>
@@ -9061,11 +9061,11 @@
         <v>378</v>
       </c>
       <c r="B127" s="8">
-        <v>46160.66095159722</v>
+        <v>46160.49428493055</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46160.81972457176</v>
+        <v>46160.65305790509</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>379</v>
@@ -9124,11 +9124,11 @@
         <v>381</v>
       </c>
       <c r="B128" s="5">
-        <v>46160.66107538194</v>
+        <v>46160.494408715276</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46160.8199466088</v>
+        <v>46160.653279942126</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>382</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -1824,13 +1824,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46160.48557077546</v>
+        <v>46160.65223744213</v>
       </c>
       <c r="C4" s="5">
-        <v>46167.39169478009</v>
+        <v>46167.55836144676</v>
       </c>
       <c r="D4" s="5">
-        <v>46181.512122534725</v>
+        <v>46181.67878920139</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -1873,13 +1873,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46160.48568386574</v>
+        <v>46160.65235053241</v>
       </c>
       <c r="C5" s="8">
-        <v>46167.39166763889</v>
+        <v>46167.558334305555</v>
       </c>
       <c r="D5" s="8">
-        <v>46167.391668703705</v>
+        <v>46167.55833537037</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -1936,13 +1936,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46160.48568737268</v>
+        <v>46160.652354039354</v>
       </c>
       <c r="C6" s="5">
-        <v>46167.39148954861</v>
+        <v>46167.55815621528</v>
       </c>
       <c r="D6" s="5">
-        <v>46167.39149064815</v>
+        <v>46167.558157314816</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1999,13 +1999,13 @@
         <v>38</v>
       </c>
       <c r="B7" s="8">
-        <v>46160.48569023148</v>
+        <v>46160.65235689815</v>
       </c>
       <c r="C7" s="8">
-        <v>46167.391522743055</v>
+        <v>46167.55818940973</v>
       </c>
       <c r="D7" s="8">
-        <v>46167.39152376157</v>
+        <v>46167.558190428244</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>39</v>
@@ -2062,13 +2062,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="5">
-        <v>46160.48569302083</v>
+        <v>46160.652359687505</v>
       </c>
       <c r="C8" s="5">
-        <v>46167.39156736111</v>
+        <v>46167.558234027776</v>
       </c>
       <c r="D8" s="5">
-        <v>46167.39156875</v>
+        <v>46167.55823541667</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>42</v>
@@ -2125,13 +2125,13 @@
         <v>45</v>
       </c>
       <c r="B9" s="8">
-        <v>46160.48569648148</v>
+        <v>46160.65236314815</v>
       </c>
       <c r="C9" s="8">
-        <v>46167.391679444445</v>
+        <v>46167.55834611111</v>
       </c>
       <c r="D9" s="8">
-        <v>46167.391680636574</v>
+        <v>46167.558347303246</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>46</v>
@@ -2188,11 +2188,11 @@
         <v>48</v>
       </c>
       <c r="B10" s="5">
-        <v>46160.48702451389</v>
+        <v>46160.65369118056</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46167.391623668984</v>
+        <v>46167.55829033565</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>49</v>
@@ -2241,13 +2241,13 @@
         <v>52</v>
       </c>
       <c r="B11" s="8">
-        <v>46160.48742520833</v>
+        <v>46160.654091874996</v>
       </c>
       <c r="C11" s="8">
-        <v>46167.391617326386</v>
+        <v>46167.55828399306</v>
       </c>
       <c r="D11" s="8">
-        <v>46167.39162951389</v>
+        <v>46167.558296180556</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>53</v>
@@ -2306,11 +2306,11 @@
         <v>57</v>
       </c>
       <c r="B12" s="5">
-        <v>46160.48750545139</v>
+        <v>46160.654172118055</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46199.013309050926</v>
+        <v>46199.17997571759</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2369,11 +2369,11 @@
         <v>64</v>
       </c>
       <c r="B13" s="8">
-        <v>46160.485575405095</v>
+        <v>46160.65224207176</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46199.58402401621</v>
+        <v>46199.75069068287</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>65</v>
@@ -2418,13 +2418,13 @@
         <v>68</v>
       </c>
       <c r="B14" s="5">
-        <v>46160.48569984954</v>
+        <v>46160.6523665162</v>
       </c>
       <c r="C14" s="5">
-        <v>46167.39225503472</v>
+        <v>46167.55892170139</v>
       </c>
       <c r="D14" s="5">
-        <v>46199.584014004635</v>
+        <v>46199.75068067129</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>69</v>
@@ -2483,13 +2483,13 @@
         <v>72</v>
       </c>
       <c r="B15" s="8">
-        <v>46160.48570503472</v>
+        <v>46160.65237170139</v>
       </c>
       <c r="C15" s="8">
-        <v>46167.392260057866</v>
+        <v>46167.55892672454</v>
       </c>
       <c r="D15" s="8">
-        <v>46199.5840141088</v>
+        <v>46199.75068077546</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>73</v>
@@ -2548,13 +2548,13 @@
         <v>76</v>
       </c>
       <c r="B16" s="5">
-        <v>46160.48571020833</v>
+        <v>46160.652376875005</v>
       </c>
       <c r="C16" s="5">
-        <v>46167.39226748842</v>
+        <v>46167.558934155095</v>
       </c>
       <c r="D16" s="5">
-        <v>46199.58401394676</v>
+        <v>46199.750680613426</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>77</v>
@@ -2613,13 +2613,13 @@
         <v>79</v>
       </c>
       <c r="B17" s="8">
-        <v>46160.485579479166</v>
+        <v>46160.65224614584</v>
       </c>
       <c r="C17" s="8">
-        <v>46181.446006122686</v>
+        <v>46181.61267278936</v>
       </c>
       <c r="D17" s="8">
-        <v>46181.512035567124</v>
+        <v>46181.678702233796</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>80</v>
@@ -2662,13 +2662,13 @@
         <v>82</v>
       </c>
       <c r="B18" s="5">
-        <v>46160.485722893514</v>
+        <v>46160.652389560186</v>
       </c>
       <c r="C18" s="5">
-        <v>46167.39229795139</v>
+        <v>46167.55896461806</v>
       </c>
       <c r="D18" s="5">
-        <v>46167.39231096065</v>
+        <v>46167.55897762731</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>83</v>
@@ -2727,13 +2727,13 @@
         <v>85</v>
       </c>
       <c r="B19" s="8">
-        <v>46160.485728252315</v>
+        <v>46160.65239491899</v>
       </c>
       <c r="C19" s="8">
-        <v>46167.39232921296</v>
+        <v>46167.55899587963</v>
       </c>
       <c r="D19" s="8">
-        <v>46167.392345995366</v>
+        <v>46167.55901266204</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>86</v>
@@ -2792,13 +2792,13 @@
         <v>88</v>
       </c>
       <c r="B20" s="5">
-        <v>46160.485733622685</v>
+        <v>46160.65240028936</v>
       </c>
       <c r="C20" s="5">
-        <v>46181.445580381944</v>
+        <v>46181.612247048615</v>
       </c>
       <c r="D20" s="5">
-        <v>46181.445597997685</v>
+        <v>46181.61226466435</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>89</v>
@@ -2857,13 +2857,13 @@
         <v>92</v>
       </c>
       <c r="B21" s="8">
-        <v>46160.4857389699</v>
+        <v>46160.652405636574</v>
       </c>
       <c r="C21" s="8">
-        <v>46181.446068969904</v>
+        <v>46181.612735636576</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.509123125</v>
+        <v>46181.67578979167</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>93</v>
@@ -2922,13 +2922,13 @@
         <v>98</v>
       </c>
       <c r="B22" s="5">
-        <v>46160.48574392361</v>
+        <v>46160.65241059028</v>
       </c>
       <c r="C22" s="5">
-        <v>46181.509155694446</v>
+        <v>46181.67582236111</v>
       </c>
       <c r="D22" s="5">
-        <v>46181.50917122685</v>
+        <v>46181.67583789352</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>99</v>
@@ -2987,13 +2987,13 @@
         <v>101</v>
       </c>
       <c r="B23" s="8">
-        <v>46160.485747824074</v>
+        <v>46160.652414490745</v>
       </c>
       <c r="C23" s="8">
-        <v>46181.509193645834</v>
+        <v>46181.675860312505</v>
       </c>
       <c r="D23" s="8">
-        <v>46181.50920886574</v>
+        <v>46181.67587553241</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -3052,13 +3052,13 @@
         <v>104</v>
       </c>
       <c r="B24" s="5">
-        <v>46160.48575173611</v>
+        <v>46160.65241840278</v>
       </c>
       <c r="C24" s="5">
-        <v>46181.50920561343</v>
+        <v>46181.67587228009</v>
       </c>
       <c r="D24" s="5">
-        <v>46181.50922108797</v>
+        <v>46181.67588775463</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>
@@ -3117,13 +3117,13 @@
         <v>107</v>
       </c>
       <c r="B25" s="8">
-        <v>46160.49191201389</v>
+        <v>46160.65857868055</v>
       </c>
       <c r="C25" s="8">
-        <v>46167.39236136574</v>
+        <v>46167.55902803241</v>
       </c>
       <c r="D25" s="8">
-        <v>46167.392375868054</v>
+        <v>46167.55904253472</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>108</v>
@@ -3182,11 +3182,11 @@
         <v>110</v>
       </c>
       <c r="B26" s="5">
-        <v>46160.48558396991</v>
+        <v>46160.65225063657</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46181.51197298611</v>
+        <v>46181.678639652775</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>111</v>
@@ -3229,13 +3229,13 @@
         <v>113</v>
       </c>
       <c r="B27" s="8">
-        <v>46160.48575607639</v>
+        <v>46160.65242274306</v>
       </c>
       <c r="C27" s="8">
-        <v>46181.50902550926</v>
+        <v>46181.67569217592</v>
       </c>
       <c r="D27" s="8">
-        <v>46181.50904247686</v>
+        <v>46181.675709143514</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>114</v>
@@ -3294,13 +3294,13 @@
         <v>118</v>
       </c>
       <c r="B28" s="5">
-        <v>46160.48576053241</v>
+        <v>46160.65242719908</v>
       </c>
       <c r="C28" s="5">
-        <v>46181.50896636574</v>
+        <v>46181.675633032406</v>
       </c>
       <c r="D28" s="5">
-        <v>46181.50896782408</v>
+        <v>46181.67563449074</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>119</v>
@@ -3355,13 +3355,13 @@
         <v>121</v>
       </c>
       <c r="B29" s="8">
-        <v>46160.485765150464</v>
+        <v>46160.65243181713</v>
       </c>
       <c r="C29" s="8">
-        <v>46181.509009664354</v>
+        <v>46181.67567633102</v>
       </c>
       <c r="D29" s="8">
-        <v>46181.50901123842</v>
+        <v>46181.67567790509</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>122</v>
@@ -3416,13 +3416,13 @@
         <v>124</v>
       </c>
       <c r="B30" s="5">
-        <v>46160.485770011575</v>
+        <v>46160.65243667824</v>
       </c>
       <c r="C30" s="5">
-        <v>46181.508945995374</v>
+        <v>46181.67561266204</v>
       </c>
       <c r="D30" s="5">
-        <v>46181.5089566088</v>
+        <v>46181.67562327546</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>125</v>
@@ -3481,13 +3481,13 @@
         <v>127</v>
       </c>
       <c r="B31" s="8">
-        <v>46160.485774409724</v>
+        <v>46160.65244107639</v>
       </c>
       <c r="C31" s="8">
-        <v>46181.508886006945</v>
+        <v>46181.67555267361</v>
       </c>
       <c r="D31" s="8">
-        <v>46181.50888729167</v>
+        <v>46181.67555395833</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>128</v>
@@ -3542,13 +3542,13 @@
         <v>130</v>
       </c>
       <c r="B32" s="5">
-        <v>46160.48577912037</v>
+        <v>46160.65244578704</v>
       </c>
       <c r="C32" s="5">
-        <v>46181.50893012731</v>
+        <v>46181.67559679398</v>
       </c>
       <c r="D32" s="5">
-        <v>46181.50893173611</v>
+        <v>46181.67559840278</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>131</v>
@@ -3603,13 +3603,13 @@
         <v>133</v>
       </c>
       <c r="B33" s="8">
-        <v>46160.485783958335</v>
+        <v>46160.652450625</v>
       </c>
       <c r="C33" s="8">
-        <v>46181.508813252316</v>
+        <v>46181.67547991898</v>
       </c>
       <c r="D33" s="8">
-        <v>46181.508827025464</v>
+        <v>46181.67549369213</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>134</v>
@@ -3668,13 +3668,13 @@
         <v>136</v>
       </c>
       <c r="B34" s="5">
-        <v>46160.48578885417</v>
+        <v>46160.65245552083</v>
       </c>
       <c r="C34" s="5">
-        <v>46181.508744583334</v>
+        <v>46181.67541125</v>
       </c>
       <c r="D34" s="5">
-        <v>46181.50874601852</v>
+        <v>46181.67541268519</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>137</v>
@@ -3729,13 +3729,13 @@
         <v>139</v>
       </c>
       <c r="B35" s="8">
-        <v>46160.48579381945</v>
+        <v>46160.65246048611</v>
       </c>
       <c r="C35" s="8">
-        <v>46181.50878599537</v>
+        <v>46181.675452662035</v>
       </c>
       <c r="D35" s="8">
-        <v>46181.50878724537</v>
+        <v>46181.67545391204</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>140</v>
@@ -3790,13 +3790,13 @@
         <v>142</v>
       </c>
       <c r="B36" s="5">
-        <v>46160.485798865746</v>
+        <v>46160.6524655324</v>
       </c>
       <c r="C36" s="5">
-        <v>46181.50879839121</v>
+        <v>46181.675465057866</v>
       </c>
       <c r="D36" s="5">
-        <v>46181.508799814816</v>
+        <v>46181.67546648148</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>143</v>
@@ -3851,11 +3851,11 @@
         <v>145</v>
       </c>
       <c r="B37" s="8">
-        <v>46160.49000302084</v>
+        <v>46160.6566696875</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="8">
-        <v>46197.02639706018</v>
+        <v>46197.19306372685</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>146</v>
@@ -3914,13 +3914,13 @@
         <v>148</v>
       </c>
       <c r="B38" s="5">
-        <v>46160.49009685185</v>
+        <v>46160.65676351852</v>
       </c>
       <c r="C38" s="5">
-        <v>46182.510074641206</v>
+        <v>46182.67674130787</v>
       </c>
       <c r="D38" s="5">
-        <v>46182.510076666666</v>
+        <v>46182.67674333333</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>109</v>
@@ -3969,11 +3969,11 @@
         <v>150</v>
       </c>
       <c r="B39" s="8">
-        <v>46160.49021748843</v>
+        <v>46160.65688415509</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46196.00232247685</v>
+        <v>46196.16898914352</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>151</v>
@@ -4022,13 +4022,13 @@
         <v>153</v>
       </c>
       <c r="B40" s="5">
-        <v>46160.485803483796</v>
+        <v>46160.65247015047</v>
       </c>
       <c r="C40" s="5">
-        <v>46181.50956585648</v>
+        <v>46181.67623252315</v>
       </c>
       <c r="D40" s="5">
-        <v>46181.5095777199</v>
+        <v>46181.676244386574</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>154</v>
@@ -4087,13 +4087,13 @@
         <v>158</v>
       </c>
       <c r="B41" s="8">
-        <v>46160.48580815972</v>
+        <v>46160.65247482639</v>
       </c>
       <c r="C41" s="8">
-        <v>46181.50948204861</v>
+        <v>46181.676148715276</v>
       </c>
       <c r="D41" s="8">
-        <v>46181.50948341435</v>
+        <v>46181.67615008102</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>159</v>
@@ -4148,13 +4148,13 @@
         <v>161</v>
       </c>
       <c r="B42" s="5">
-        <v>46160.48581292824</v>
+        <v>46160.65247959491</v>
       </c>
       <c r="C42" s="5">
-        <v>46181.509552268515</v>
+        <v>46181.67621893519</v>
       </c>
       <c r="D42" s="5">
-        <v>46181.50955349537</v>
+        <v>46181.67622016204</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>162</v>
@@ -4209,13 +4209,13 @@
         <v>164</v>
       </c>
       <c r="B43" s="8">
-        <v>46160.485874039354</v>
+        <v>46160.65254070602</v>
       </c>
       <c r="C43" s="8">
-        <v>46181.50968824074</v>
+        <v>46181.67635490741</v>
       </c>
       <c r="D43" s="8">
-        <v>46181.509699953705</v>
+        <v>46181.67636662037</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>165</v>
@@ -4274,13 +4274,13 @@
         <v>167</v>
       </c>
       <c r="B44" s="5">
-        <v>46160.4858790625</v>
+        <v>46160.65254572917</v>
       </c>
       <c r="C44" s="5">
-        <v>46181.50963344907</v>
+        <v>46181.67630011574</v>
       </c>
       <c r="D44" s="5">
-        <v>46181.509634953705</v>
+        <v>46181.67630162037</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>100</v>
@@ -4329,13 +4329,13 @@
         <v>169</v>
       </c>
       <c r="B45" s="8">
-        <v>46160.48588471065</v>
+        <v>46160.652551377316</v>
       </c>
       <c r="C45" s="8">
-        <v>46181.50967270833</v>
+        <v>46181.676339375</v>
       </c>
       <c r="D45" s="8">
-        <v>46181.50967423611</v>
+        <v>46181.67634090278</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>170</v>
@@ -4384,13 +4384,13 @@
         <v>172</v>
       </c>
       <c r="B46" s="5">
-        <v>46160.48589048611</v>
+        <v>46160.652557152775</v>
       </c>
       <c r="C46" s="5">
-        <v>46181.509813854165</v>
+        <v>46181.67648052084</v>
       </c>
       <c r="D46" s="5">
-        <v>46198.03967150463</v>
+        <v>46198.206338171294</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4449,13 +4449,13 @@
         <v>178</v>
       </c>
       <c r="B47" s="8">
-        <v>46160.4858949537</v>
+        <v>46160.65256162037</v>
       </c>
       <c r="C47" s="8">
-        <v>46181.50972081019</v>
+        <v>46181.67638747685</v>
       </c>
       <c r="D47" s="8">
-        <v>46181.50972233796</v>
+        <v>46181.67638900463</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>106</v>
@@ -4504,13 +4504,13 @@
         <v>180</v>
       </c>
       <c r="B48" s="5">
-        <v>46160.48590677083</v>
+        <v>46160.6525734375</v>
       </c>
       <c r="C48" s="5">
-        <v>46181.509760891204</v>
+        <v>46181.676427557875</v>
       </c>
       <c r="D48" s="5">
-        <v>46181.50976267361</v>
+        <v>46181.67642934028</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>181</v>
@@ -4559,13 +4559,13 @@
         <v>183</v>
       </c>
       <c r="B49" s="8">
-        <v>46160.48591256945</v>
+        <v>46160.652579236106</v>
       </c>
       <c r="C49" s="8">
-        <v>46181.509799259264</v>
+        <v>46181.67646592592</v>
       </c>
       <c r="D49" s="8">
-        <v>46181.50980063657</v>
+        <v>46181.676467303245</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>184</v>
@@ -4614,13 +4614,13 @@
         <v>187</v>
       </c>
       <c r="B50" s="5">
-        <v>46160.485916377314</v>
+        <v>46160.65258304398</v>
       </c>
       <c r="C50" s="5">
-        <v>46181.509901122685</v>
+        <v>46181.676567789356</v>
       </c>
       <c r="D50" s="5">
-        <v>46181.509912187496</v>
+        <v>46181.67657885417</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>188</v>
@@ -4679,13 +4679,13 @@
         <v>190</v>
       </c>
       <c r="B51" s="8">
-        <v>46160.485920879626</v>
+        <v>46160.6525875463</v>
       </c>
       <c r="C51" s="8">
-        <v>46181.50984517361</v>
+        <v>46181.676511840276</v>
       </c>
       <c r="D51" s="8">
-        <v>46181.50984648148</v>
+        <v>46181.67651314815</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>103</v>
@@ -4734,13 +4734,13 @@
         <v>192</v>
       </c>
       <c r="B52" s="5">
-        <v>46160.48592640046</v>
+        <v>46160.652593067134</v>
       </c>
       <c r="C52" s="5">
-        <v>46181.50988571759</v>
+        <v>46181.67655238426</v>
       </c>
       <c r="D52" s="5">
-        <v>46181.50988701389</v>
+        <v>46181.676553680554</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>193</v>
@@ -4789,13 +4789,13 @@
         <v>195</v>
       </c>
       <c r="B53" s="8">
-        <v>46160.48558849537</v>
+        <v>46160.65225516204</v>
       </c>
       <c r="C53" s="8">
-        <v>46181.445746921294</v>
+        <v>46181.612413587965</v>
       </c>
       <c r="D53" s="8">
-        <v>46181.51191784722</v>
+        <v>46181.67858451389</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>196</v>
@@ -4838,13 +4838,13 @@
         <v>198</v>
       </c>
       <c r="B54" s="5">
-        <v>46160.4859325463</v>
+        <v>46160.65259921296</v>
       </c>
       <c r="C54" s="5">
-        <v>46181.445661516205</v>
+        <v>46181.61232818287</v>
       </c>
       <c r="D54" s="5">
-        <v>46197.5459735301</v>
+        <v>46197.712640196754</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>199</v>
@@ -4903,13 +4903,13 @@
         <v>203</v>
       </c>
       <c r="B55" s="8">
-        <v>46160.48593934027</v>
+        <v>46160.652606006945</v>
       </c>
       <c r="C55" s="8">
-        <v>46181.50905496528</v>
+        <v>46181.675721631946</v>
       </c>
       <c r="D55" s="8">
-        <v>46197.54600650463</v>
+        <v>46197.71267317129</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>204</v>
@@ -4968,13 +4968,13 @@
         <v>207</v>
       </c>
       <c r="B56" s="5">
-        <v>46160.485947430556</v>
+        <v>46160.65261409723</v>
       </c>
       <c r="C56" s="5">
-        <v>46181.50909756945</v>
+        <v>46181.67576423611</v>
       </c>
       <c r="D56" s="5">
-        <v>46181.50911381944</v>
+        <v>46181.67578048611</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>96</v>
@@ -5033,13 +5033,13 @@
         <v>211</v>
       </c>
       <c r="B57" s="8">
-        <v>46160.48596431713</v>
+        <v>46160.652630983794</v>
       </c>
       <c r="C57" s="8">
-        <v>46198.39944978009</v>
+        <v>46198.56611644676</v>
       </c>
       <c r="D57" s="8">
-        <v>46203.033013368055</v>
+        <v>46203.199680034726</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>212</v>
@@ -5098,13 +5098,13 @@
         <v>216</v>
       </c>
       <c r="B58" s="5">
-        <v>46160.485968657405</v>
+        <v>46160.65263532408</v>
       </c>
       <c r="C58" s="5">
-        <v>46198.39941736111</v>
+        <v>46198.56608402778</v>
       </c>
       <c r="D58" s="5">
-        <v>46198.39941895833</v>
+        <v>46198.566085625</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>217</v>
@@ -5153,13 +5153,13 @@
         <v>219</v>
       </c>
       <c r="B59" s="8">
-        <v>46160.485974027775</v>
+        <v>46160.65264069445</v>
       </c>
       <c r="C59" s="8">
-        <v>46198.39943300926</v>
+        <v>46198.566099675925</v>
       </c>
       <c r="D59" s="8">
-        <v>46198.39943489584</v>
+        <v>46198.5661015625</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>217</v>
@@ -5208,13 +5208,13 @@
         <v>221</v>
       </c>
       <c r="B60" s="5">
-        <v>46160.48601025463</v>
+        <v>46160.652676921294</v>
       </c>
       <c r="C60" s="5">
-        <v>46181.44612966436</v>
+        <v>46181.612796331014</v>
       </c>
       <c r="D60" s="5">
-        <v>46181.51150304398</v>
+        <v>46181.67816971065</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>222</v>
@@ -5257,13 +5257,13 @@
         <v>224</v>
       </c>
       <c r="B61" s="8">
-        <v>46160.486014166665</v>
+        <v>46160.65268083333</v>
       </c>
       <c r="C61" s="8">
-        <v>46181.50992280093</v>
+        <v>46181.67658946759</v>
       </c>
       <c r="D61" s="8">
-        <v>46182.03195226852</v>
+        <v>46182.19861893519</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>225</v>
@@ -5322,13 +5322,13 @@
         <v>229</v>
       </c>
       <c r="B62" s="5">
-        <v>46160.486019143515</v>
+        <v>46160.652685810186</v>
       </c>
       <c r="C62" s="5">
-        <v>46181.510016527776</v>
+        <v>46181.67668319444</v>
       </c>
       <c r="D62" s="5">
-        <v>46184.005462326386</v>
+        <v>46184.17212899306</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>230</v>
@@ -5387,13 +5387,13 @@
         <v>233</v>
       </c>
       <c r="B63" s="8">
-        <v>46160.48602430556</v>
+        <v>46160.65269097222</v>
       </c>
       <c r="C63" s="8">
-        <v>46181.50994024306</v>
+        <v>46181.67660690972</v>
       </c>
       <c r="D63" s="8">
-        <v>46181.50995578704</v>
+        <v>46181.6766224537</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>234</v>
@@ -5452,13 +5452,13 @@
         <v>236</v>
       </c>
       <c r="B64" s="5">
-        <v>46160.48602966435</v>
+        <v>46160.65269633102</v>
       </c>
       <c r="C64" s="5">
-        <v>46181.51003130787</v>
+        <v>46181.67669797454</v>
       </c>
       <c r="D64" s="5">
-        <v>46184.005462326386</v>
+        <v>46184.17212899306</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>237</v>
@@ -5517,13 +5517,13 @@
         <v>238</v>
       </c>
       <c r="B65" s="8">
-        <v>46160.48603313658</v>
+        <v>46160.65269980324</v>
       </c>
       <c r="C65" s="8">
-        <v>46181.51000043981</v>
+        <v>46181.67666710648</v>
       </c>
       <c r="D65" s="8">
-        <v>46181.51000200232</v>
+        <v>46181.67666866898</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>239</v>
@@ -5582,13 +5582,13 @@
         <v>241</v>
       </c>
       <c r="B66" s="5">
-        <v>46160.48603726852</v>
+        <v>46160.652703935186</v>
       </c>
       <c r="C66" s="5">
-        <v>46181.510049247685</v>
+        <v>46181.67671591435</v>
       </c>
       <c r="D66" s="5">
-        <v>46184.00546233796</v>
+        <v>46184.172129004626</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>240</v>
@@ -5647,13 +5647,13 @@
         <v>242</v>
       </c>
       <c r="B67" s="8">
-        <v>46160.486041006945</v>
+        <v>46160.65270767361</v>
       </c>
       <c r="C67" s="8">
-        <v>46181.44619803241</v>
+        <v>46181.61286469907</v>
       </c>
       <c r="D67" s="8">
-        <v>46181.51144181713</v>
+        <v>46181.6781084838</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5696,13 +5696,13 @@
         <v>245</v>
       </c>
       <c r="B68" s="5">
-        <v>46160.48604394676</v>
+        <v>46160.65271061343</v>
       </c>
       <c r="C68" s="5">
-        <v>46181.51018964121</v>
+        <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46189.02907693287</v>
+        <v>46189.195743599535</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -5761,13 +5761,13 @@
         <v>250</v>
       </c>
       <c r="B69" s="8">
-        <v>46160.486049837964</v>
+        <v>46160.65271650463</v>
       </c>
       <c r="C69" s="8">
-        <v>46181.51015998842</v>
+        <v>46181.67682665509</v>
       </c>
       <c r="D69" s="8">
-        <v>46181.51046767361</v>
+        <v>46181.67713434028</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>217</v>
@@ -5816,13 +5816,13 @@
         <v>253</v>
       </c>
       <c r="B70" s="5">
-        <v>46160.4860555787</v>
+        <v>46160.65272224537</v>
       </c>
       <c r="C70" s="5">
-        <v>46181.51017574074</v>
+        <v>46181.67684240741</v>
       </c>
       <c r="D70" s="5">
-        <v>46181.51046842593</v>
+        <v>46181.67713509259</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>217</v>
@@ -5871,13 +5871,13 @@
         <v>256</v>
       </c>
       <c r="B71" s="8">
-        <v>46160.48606023148</v>
+        <v>46160.652726898144</v>
       </c>
       <c r="C71" s="8">
-        <v>46181.51055939815</v>
+        <v>46181.677226064814</v>
       </c>
       <c r="D71" s="8">
-        <v>46196.03153309028</v>
+        <v>46196.198199756946</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>257</v>
@@ -5936,13 +5936,13 @@
         <v>259</v>
       </c>
       <c r="B72" s="5">
-        <v>46160.486063854165</v>
+        <v>46160.65273052083</v>
       </c>
       <c r="C72" s="5">
-        <v>46181.51053046296</v>
+        <v>46181.677197129626</v>
       </c>
       <c r="D72" s="5">
-        <v>46181.510531875</v>
+        <v>46181.67719854167</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>217</v>
@@ -5991,13 +5991,13 @@
         <v>262</v>
       </c>
       <c r="B73" s="8">
-        <v>46160.486074953704</v>
+        <v>46160.652741620375</v>
       </c>
       <c r="C73" s="8">
-        <v>46181.51054616898</v>
+        <v>46181.67721283565</v>
       </c>
       <c r="D73" s="8">
-        <v>46181.51054769676</v>
+        <v>46181.67721436343</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>255</v>
@@ -6046,13 +6046,13 @@
         <v>263</v>
       </c>
       <c r="B74" s="5">
-        <v>46160.4860796412</v>
+        <v>46160.65274630787</v>
       </c>
       <c r="C74" s="5">
-        <v>46181.51062046296</v>
+        <v>46181.67728712963</v>
       </c>
       <c r="D74" s="5">
-        <v>46197.02639702546</v>
+        <v>46197.19306369213</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>264</v>
@@ -6111,13 +6111,13 @@
         <v>265</v>
       </c>
       <c r="B75" s="8">
-        <v>46160.4860833912</v>
+        <v>46160.65275005787</v>
       </c>
       <c r="C75" s="8">
-        <v>46181.51059667824</v>
+        <v>46181.67726334491</v>
       </c>
       <c r="D75" s="8">
-        <v>46181.51059846065</v>
+        <v>46181.67726512731</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>217</v>
@@ -6166,13 +6166,13 @@
         <v>267</v>
       </c>
       <c r="B76" s="5">
-        <v>46160.486088819445</v>
+        <v>46160.65275548611</v>
       </c>
       <c r="C76" s="5">
-        <v>46181.510606365744</v>
+        <v>46181.67727303241</v>
       </c>
       <c r="D76" s="5">
-        <v>46181.51060799768</v>
+        <v>46181.677274664355</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>217</v>
@@ -6221,13 +6221,13 @@
         <v>270</v>
       </c>
       <c r="B77" s="8">
-        <v>46160.48609395833</v>
+        <v>46160.652760625</v>
       </c>
       <c r="C77" s="8">
-        <v>46181.44636556713</v>
+        <v>46181.6130322338</v>
       </c>
       <c r="D77" s="8">
-        <v>46181.510851875</v>
+        <v>46181.67751854166</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>222</v>
@@ -6270,13 +6270,13 @@
         <v>272</v>
       </c>
       <c r="B78" s="5">
-        <v>46160.48609673612</v>
+        <v>46160.65276340277</v>
       </c>
       <c r="C78" s="5">
-        <v>46181.51064849537</v>
+        <v>46181.67731516204</v>
       </c>
       <c r="D78" s="5">
-        <v>46192.03793990741</v>
+        <v>46192.20460657407</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>273</v>
@@ -6335,13 +6335,13 @@
         <v>275</v>
       </c>
       <c r="B79" s="8">
-        <v>46160.48610216435</v>
+        <v>46160.652768831016</v>
       </c>
       <c r="C79" s="8">
-        <v>46181.510658576386</v>
+        <v>46181.67732524306</v>
       </c>
       <c r="D79" s="8">
-        <v>46181.51067836805</v>
+        <v>46181.677345034725</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>276</v>
@@ -6400,13 +6400,13 @@
         <v>277</v>
       </c>
       <c r="B80" s="5">
-        <v>46160.486107743054</v>
+        <v>46160.652774409726</v>
       </c>
       <c r="C80" s="5">
-        <v>46181.51066972222</v>
+        <v>46181.67733638889</v>
       </c>
       <c r="D80" s="5">
-        <v>46181.51068952546</v>
+        <v>46181.67735619213</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>278</v>
@@ -6465,13 +6465,13 @@
         <v>279</v>
       </c>
       <c r="B81" s="8">
-        <v>46160.4861130787</v>
+        <v>46160.652779745375</v>
       </c>
       <c r="C81" s="8">
-        <v>46181.510678935185</v>
+        <v>46181.677345601856</v>
       </c>
       <c r="D81" s="8">
-        <v>46199.026905590275</v>
+        <v>46199.19357225695</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>280</v>
@@ -6530,11 +6530,11 @@
         <v>282</v>
       </c>
       <c r="B82" s="5">
-        <v>46160.49040090278</v>
+        <v>46160.657067569446</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46198.02195084491</v>
+        <v>46198.18861751157</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>61</v>
@@ -6593,13 +6593,13 @@
         <v>283</v>
       </c>
       <c r="B83" s="8">
-        <v>46160.48611752315</v>
+        <v>46160.65278418981</v>
       </c>
       <c r="C83" s="8">
-        <v>46181.45112766203</v>
+        <v>46181.617794328704</v>
       </c>
       <c r="D83" s="8">
-        <v>46197.3305830787</v>
+        <v>46197.49724974537</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>284</v>
@@ -6644,13 +6644,13 @@
         <v>286</v>
       </c>
       <c r="B84" s="5">
-        <v>46160.486120347225</v>
+        <v>46160.65278701389</v>
       </c>
       <c r="C84" s="5">
-        <v>46181.51093371528</v>
+        <v>46181.67760038194</v>
       </c>
       <c r="D84" s="5">
-        <v>46204.00625748842</v>
+        <v>46204.17292415509</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>287</v>
@@ -6709,13 +6709,13 @@
         <v>289</v>
       </c>
       <c r="B85" s="8">
-        <v>46160.486126909724</v>
+        <v>46160.65279357639</v>
       </c>
       <c r="C85" s="8">
-        <v>46181.51100827546</v>
+        <v>46181.677674942126</v>
       </c>
       <c r="D85" s="8">
-        <v>46181.51100951389</v>
+        <v>46181.67767618055</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>217</v>
@@ -6764,13 +6764,13 @@
         <v>291</v>
       </c>
       <c r="B86" s="5">
-        <v>46160.4861306713</v>
+        <v>46160.65279733796</v>
       </c>
       <c r="C86" s="5">
-        <v>46181.511020844904</v>
+        <v>46181.677687511576</v>
       </c>
       <c r="D86" s="5">
-        <v>46181.51102258102</v>
+        <v>46181.677689247685</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>217</v>
@@ -6819,13 +6819,13 @@
         <v>292</v>
       </c>
       <c r="B87" s="8">
-        <v>46160.4861344213</v>
+        <v>46160.65280108796</v>
       </c>
       <c r="C87" s="8">
-        <v>46181.5110999537</v>
+        <v>46181.67776662037</v>
       </c>
       <c r="D87" s="8">
-        <v>46205.015753541666</v>
+        <v>46205.18242020834</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>293</v>
@@ -6884,13 +6884,13 @@
         <v>294</v>
       </c>
       <c r="B88" s="5">
-        <v>46160.48613832176</v>
+        <v>46160.65280498842</v>
       </c>
       <c r="C88" s="5">
-        <v>46181.51107460648</v>
+        <v>46181.677741273146</v>
       </c>
       <c r="D88" s="5">
-        <v>46181.51107620371</v>
+        <v>46181.67774287037</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>217</v>
@@ -6939,13 +6939,13 @@
         <v>297</v>
       </c>
       <c r="B89" s="8">
-        <v>46160.486143472226</v>
+        <v>46160.65281013889</v>
       </c>
       <c r="C89" s="8">
-        <v>46181.51108667824</v>
+        <v>46181.677753344906</v>
       </c>
       <c r="D89" s="8">
-        <v>46181.511088217594</v>
+        <v>46181.67775488426</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>217</v>
@@ -6994,13 +6994,13 @@
         <v>298</v>
       </c>
       <c r="B90" s="5">
-        <v>46160.48614836806</v>
+        <v>46160.65281503472</v>
       </c>
       <c r="C90" s="5">
-        <v>46181.51117106482</v>
+        <v>46181.67783773148</v>
       </c>
       <c r="D90" s="5">
-        <v>46198.03967209491</v>
+        <v>46198.20633876158</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>299</v>
@@ -7059,13 +7059,13 @@
         <v>300</v>
       </c>
       <c r="B91" s="8">
-        <v>46160.48615216435</v>
+        <v>46160.65281883102</v>
       </c>
       <c r="C91" s="8">
-        <v>46181.511129328705</v>
+        <v>46181.67779599537</v>
       </c>
       <c r="D91" s="8">
-        <v>46181.511130960644</v>
+        <v>46181.677797627315</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>217</v>
@@ -7112,13 +7112,13 @@
         <v>302</v>
       </c>
       <c r="B92" s="5">
-        <v>46160.486209421295</v>
+        <v>46160.65287608796</v>
       </c>
       <c r="C92" s="5">
-        <v>46181.51113912037</v>
+        <v>46181.67780578704</v>
       </c>
       <c r="D92" s="5">
-        <v>46181.51114059028</v>
+        <v>46181.67780725694</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>217</v>
@@ -7165,13 +7165,13 @@
         <v>303</v>
       </c>
       <c r="B93" s="8">
-        <v>46160.486217812504</v>
+        <v>46160.65288447917</v>
       </c>
       <c r="C93" s="8">
-        <v>46181.51119900463</v>
+        <v>46181.6778656713</v>
       </c>
       <c r="D93" s="8">
-        <v>46199.02690631944</v>
+        <v>46199.193572986114</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>304</v>
@@ -7230,13 +7230,13 @@
         <v>305</v>
       </c>
       <c r="B94" s="5">
-        <v>46160.48622303241</v>
+        <v>46160.65288969908</v>
       </c>
       <c r="C94" s="5">
-        <v>46181.51117568287</v>
+        <v>46181.67784234954</v>
       </c>
       <c r="D94" s="5">
-        <v>46181.51117745371</v>
+        <v>46181.67784412037</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>217</v>
@@ -7285,13 +7285,13 @@
         <v>308</v>
       </c>
       <c r="B95" s="8">
-        <v>46160.48622869213</v>
+        <v>46160.6528953588</v>
       </c>
       <c r="C95" s="8">
-        <v>46181.511182581016</v>
+        <v>46181.67784924769</v>
       </c>
       <c r="D95" s="8">
-        <v>46181.51118395833</v>
+        <v>46181.677850625</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>217</v>
@@ -7340,13 +7340,13 @@
         <v>309</v>
       </c>
       <c r="B96" s="5">
-        <v>46160.48623403935</v>
+        <v>46160.652900706016</v>
       </c>
       <c r="C96" s="5">
-        <v>46181.5112519213</v>
+        <v>46181.677918587964</v>
       </c>
       <c r="D96" s="5">
-        <v>46202.00173365741</v>
+        <v>46202.16840032407</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>310</v>
@@ -7405,13 +7405,13 @@
         <v>311</v>
       </c>
       <c r="B97" s="8">
-        <v>46160.48623902778</v>
+        <v>46160.65290569444</v>
       </c>
       <c r="C97" s="8">
-        <v>46181.51122587963</v>
+        <v>46181.6778925463</v>
       </c>
       <c r="D97" s="8">
-        <v>46181.51122771991</v>
+        <v>46181.67789438658</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>217</v>
@@ -7460,13 +7460,13 @@
         <v>313</v>
       </c>
       <c r="B98" s="5">
-        <v>46160.48624449074</v>
+        <v>46160.652911157405</v>
       </c>
       <c r="C98" s="5">
-        <v>46181.511236307866</v>
+        <v>46181.67790297454</v>
       </c>
       <c r="D98" s="5">
-        <v>46181.51123834491</v>
+        <v>46181.67790501157</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>217</v>
@@ -7515,13 +7515,13 @@
         <v>314</v>
       </c>
       <c r="B99" s="8">
-        <v>46160.48624990741</v>
+        <v>46160.65291657408</v>
       </c>
       <c r="C99" s="8">
-        <v>46197.330565972225</v>
+        <v>46197.49723263889</v>
       </c>
       <c r="D99" s="8">
-        <v>46204.00348594907</v>
+        <v>46204.17015261574</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>315</v>
@@ -7580,13 +7580,13 @@
         <v>317</v>
       </c>
       <c r="B100" s="5">
-        <v>46160.48625489583</v>
+        <v>46160.652921562505</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.436379756946</v>
+        <v>46197.60304642361</v>
       </c>
       <c r="D100" s="5">
-        <v>46198.39942261574</v>
+        <v>46198.56608928241</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>217</v>
@@ -7633,13 +7633,13 @@
         <v>319</v>
       </c>
       <c r="B101" s="8">
-        <v>46160.486259537036</v>
+        <v>46160.65292620371</v>
       </c>
       <c r="C101" s="8">
-        <v>46197.330622442125</v>
+        <v>46197.4972891088</v>
       </c>
       <c r="D101" s="8">
-        <v>46198.399443738424</v>
+        <v>46198.566110405096</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>217</v>
@@ -7686,11 +7686,11 @@
         <v>321</v>
       </c>
       <c r="B102" s="5">
-        <v>46160.48626417824</v>
+        <v>46160.65293084491</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46197.33099751157</v>
+        <v>46197.49766417824</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>322</v>
@@ -7733,11 +7733,11 @@
         <v>324</v>
       </c>
       <c r="B103" s="8">
-        <v>46160.48626765046</v>
+        <v>46160.65293431713</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46205.00763515046</v>
+        <v>46205.174301817126</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>325</v>
@@ -7796,13 +7796,13 @@
         <v>329</v>
       </c>
       <c r="B104" s="5">
-        <v>46160.48627299769</v>
+        <v>46160.65293966435</v>
       </c>
       <c r="C104" s="5">
-        <v>46204.635555416666</v>
+        <v>46204.80222208334</v>
       </c>
       <c r="D104" s="5">
-        <v>46204.63555688657</v>
+        <v>46204.80222355324</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>217</v>
@@ -7851,13 +7851,13 @@
         <v>331</v>
       </c>
       <c r="B105" s="8">
-        <v>46160.48627753472</v>
+        <v>46160.652944201385</v>
       </c>
       <c r="C105" s="8">
-        <v>46204.63581959491</v>
+        <v>46204.80248626157</v>
       </c>
       <c r="D105" s="8">
-        <v>46204.63582112268</v>
+        <v>46204.80248778935</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>217</v>
@@ -7906,11 +7906,11 @@
         <v>334</v>
       </c>
       <c r="B106" s="5">
-        <v>46160.64149819444</v>
+        <v>46160.80816486111</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46160.65106541666</v>
+        <v>46160.817732083335</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>335</v>
@@ -7959,11 +7959,11 @@
         <v>337</v>
       </c>
       <c r="B107" s="8">
-        <v>46160.641878587965</v>
+        <v>46160.80854525463</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46160.65106607639</v>
+        <v>46160.81773274306</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>335</v>
@@ -8012,13 +8012,13 @@
         <v>339</v>
       </c>
       <c r="B108" s="5">
-        <v>46160.486281840276</v>
+        <v>46160.65294850695</v>
       </c>
       <c r="C108" s="5">
-        <v>46197.330989594906</v>
+        <v>46197.49765626158</v>
       </c>
       <c r="D108" s="5">
-        <v>46197.33109856481</v>
+        <v>46197.497765231485</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>340</v>
@@ -8077,13 +8077,13 @@
         <v>342</v>
       </c>
       <c r="B109" s="8">
-        <v>46160.48628592593</v>
+        <v>46160.652952592594</v>
       </c>
       <c r="C109" s="8">
-        <v>46197.33070268518</v>
+        <v>46197.497369351855</v>
       </c>
       <c r="D109" s="8">
-        <v>46204.63556045139</v>
+        <v>46204.80222711805</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>217</v>
@@ -8132,13 +8132,13 @@
         <v>344</v>
       </c>
       <c r="B110" s="5">
-        <v>46160.48629032407</v>
+        <v>46160.65295699074</v>
       </c>
       <c r="C110" s="5">
-        <v>46197.33086335648</v>
+        <v>46197.497530023145</v>
       </c>
       <c r="D110" s="5">
-        <v>46204.63582582176</v>
+        <v>46204.80249248842</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>217</v>
@@ -8187,11 +8187,11 @@
         <v>345</v>
       </c>
       <c r="B111" s="8">
-        <v>46160.642455497684</v>
+        <v>46160.809122164355</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46197.33108614583</v>
+        <v>46197.4977528125</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>335</v>
@@ -8240,11 +8240,11 @@
         <v>347</v>
       </c>
       <c r="B112" s="5">
-        <v>46160.64247096065</v>
+        <v>46160.809137627315</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46197.331093229164</v>
+        <v>46197.497759895836</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>348</v>
@@ -8293,11 +8293,11 @@
         <v>349</v>
       </c>
       <c r="B113" s="8">
-        <v>46160.48629453704</v>
+        <v>46160.652961203705</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46193.89000209491</v>
+        <v>46194.05666876158</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>350</v>
@@ -8356,11 +8356,11 @@
         <v>352</v>
       </c>
       <c r="B114" s="5">
-        <v>46160.48629865741</v>
+        <v>46160.65296532407</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46197.33070910879</v>
+        <v>46197.49737577546</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>217</v>
@@ -8407,11 +8407,11 @@
         <v>354</v>
       </c>
       <c r="B115" s="8">
-        <v>46160.48630600695</v>
+        <v>46160.65297267361</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46197.33087121528</v>
+        <v>46197.49753788194</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>217</v>
@@ -8458,11 +8458,11 @@
         <v>356</v>
       </c>
       <c r="B116" s="5">
-        <v>46160.644220671296</v>
+        <v>46160.81088733797</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46197.33108930556</v>
+        <v>46197.49775597222</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>335</v>
@@ -8509,11 +8509,11 @@
         <v>358</v>
       </c>
       <c r="B117" s="8">
-        <v>46160.64422939815</v>
+        <v>46160.81089606481</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46197.33109903935</v>
+        <v>46197.49776570602</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>335</v>
@@ -8560,11 +8560,11 @@
         <v>359</v>
       </c>
       <c r="B118" s="5">
-        <v>46160.48631179398</v>
+        <v>46160.65297846065</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46183.72898115741</v>
+        <v>46183.89564782407</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>360</v>
@@ -8623,11 +8623,11 @@
         <v>362</v>
       </c>
       <c r="B119" s="8">
-        <v>46160.486317268515</v>
+        <v>46160.652983935186</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46193.887875381944</v>
+        <v>46194.054542048616</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>217</v>
@@ -8676,11 +8676,11 @@
         <v>363</v>
       </c>
       <c r="B120" s="5">
-        <v>46160.48632146991</v>
+        <v>46160.65298813657</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46193.890002581014</v>
+        <v>46194.056669247686</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>217</v>
@@ -8729,11 +8729,11 @@
         <v>364</v>
       </c>
       <c r="B121" s="8">
-        <v>46160.64549171296</v>
+        <v>46160.81215837963</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46193.88787908565</v>
+        <v>46194.05454575231</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>335</v>
@@ -8782,11 +8782,11 @@
         <v>365</v>
       </c>
       <c r="B122" s="5">
-        <v>46160.645541018515</v>
+        <v>46160.81220768519</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46193.887877615736</v>
+        <v>46194.05454428241</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>335</v>
@@ -8835,11 +8835,11 @@
         <v>366</v>
       </c>
       <c r="B123" s="8">
-        <v>46160.486358877315</v>
+        <v>46160.65302554399</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46160.65262292824</v>
+        <v>46160.8192895949</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>367</v>
@@ -8882,11 +8882,11 @@
         <v>369</v>
       </c>
       <c r="B124" s="5">
-        <v>46160.48636229167</v>
+        <v>46160.65302895833</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46160.65253305556</v>
+        <v>46160.819199722224</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>370</v>
@@ -8945,11 +8945,11 @@
         <v>373</v>
       </c>
       <c r="B125" s="8">
-        <v>46160.486367199075</v>
+        <v>46160.65303386574</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46199.58401413195</v>
+        <v>46199.75068079861</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>374</v>
@@ -9008,11 +9008,11 @@
         <v>375</v>
       </c>
       <c r="B126" s="5">
-        <v>46160.49142284722</v>
+        <v>46160.65808951389</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46160.65314284722</v>
+        <v>46160.819809513894</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>376</v>
@@ -9061,11 +9061,11 @@
         <v>378</v>
       </c>
       <c r="B127" s="8">
-        <v>46160.49428493055</v>
+        <v>46160.66095159722</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46160.65305790509</v>
+        <v>46160.81972457176</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>379</v>
@@ -9124,11 +9124,11 @@
         <v>381</v>
       </c>
       <c r="B128" s="5">
-        <v>46160.494408715276</v>
+        <v>46160.66107538194</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46160.653279942126</v>
+        <v>46160.8199466088</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>382</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -582,121 +582,121 @@
     <t>Generacion OC Fabricación Externa ot 4313,Fabricación estructura proveedor externo ot 4313</t>
   </si>
   <si>
+    <t>1214909353558429</t>
+  </si>
+  <si>
+    <t>Fabricación Externa ot 4313 ,Fabricación estructura proveedor externo ot 4313</t>
+  </si>
+  <si>
+    <t>1214909353559656</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa ot 4313 ,Control de calidad fabricación externa  ot 4313,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214909353559671</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  ot 4313</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1214909353559681</t>
+  </si>
+  <si>
+    <t>Mecanizado ot 4313</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado ot 4313,Fabricación Mecanizado ot 4313</t>
+  </si>
+  <si>
+    <t>1214909311504704</t>
+  </si>
+  <si>
+    <t>Mecanizado ot 4313,Fabricación Mecanizado ot 4313</t>
+  </si>
+  <si>
+    <t>1214909311504719</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado ot 4313</t>
+  </si>
+  <si>
+    <t>Mecanizado ot 4313,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1214892476594835</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1214909595210202</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>1214909595210222</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>Planos preliminar,Planos motor proveedor ot 4313</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:,check planos</t>
+  </si>
+  <si>
+    <t>1214909462950236</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,propuesta Corte Laser ot 4313,Propuesta Corte plasma  ot 4313,Propuesta Mecanizado ot 4313 ,Propuesta Fabricación externa ot 4313,OT 4313 - ZVN 1-9-45/2,OT  4313- ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909353584079</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214909353558429</t>
-  </si>
-  <si>
-    <t>Fabricación Externa ot 4313 ,Fabricación estructura proveedor externo ot 4313</t>
-  </si>
-  <si>
-    <t>1214909353559656</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa ot 4313 ,Control de calidad fabricación externa  ot 4313,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214909353559671</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  ot 4313</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1214909353559681</t>
-  </si>
-  <si>
-    <t>Mecanizado ot 4313</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado ot 4313,Fabricación Mecanizado ot 4313</t>
-  </si>
-  <si>
-    <t>1214909311504704</t>
-  </si>
-  <si>
-    <t>Mecanizado ot 4313,Fabricación Mecanizado ot 4313</t>
-  </si>
-  <si>
-    <t>1214909311504719</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado ot 4313</t>
-  </si>
-  <si>
-    <t>Mecanizado ot 4313,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1214892476594835</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1214909595210202</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Gonzalo Javier Dávila Bade</t>
-  </si>
-  <si>
-    <t>gonzalo.davila@zitron.com</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>1214909595210222</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>Planos preliminar,Planos motor proveedor ot 4313</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:,check planos</t>
-  </si>
-  <si>
-    <t>1214909462950236</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,propuesta Corte Laser ot 4313,Propuesta Corte plasma  ot 4313,Propuesta Mecanizado ot 4313 ,Propuesta Fabricación externa ot 4313,OT 4313 - ZVN 1-9-45/2,OT  4313- ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909353584079</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
   </si>
   <si>
     <t>1214909617021015</t>
@@ -4390,7 +4390,7 @@
         <v>46181.67648052084</v>
       </c>
       <c r="D46" s="5">
-        <v>46198.206338171294</v>
+        <v>46206.17392120371</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>173</v>
@@ -4434,8 +4434,8 @@
       <c r="R46" s="5">
         <v>46205</v>
       </c>
-      <c r="S46" s="12" t="s">
-        <v>177</v>
+      <c r="S46" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>
@@ -4446,7 +4446,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B47" s="8">
         <v>46160.65256162037</v>
@@ -4491,7 +4491,7 @@
         <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4501,7 +4501,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46160.6525734375</v>
@@ -4513,7 +4513,7 @@
         <v>46181.67642934028</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4546,7 +4546,7 @@
         <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4556,7 +4556,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B49" s="8">
         <v>46160.652579236106</v>
@@ -4568,16 +4568,16 @@
         <v>46181.676467303245</v>
       </c>
       <c r="E49" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="F49" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="9" t="s">
+      <c r="H49" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="I49" s="8">
         <v>46205</v>
@@ -4598,7 +4598,7 @@
         <v>173</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4611,7 +4611,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46160.65258304398</v>
@@ -4623,7 +4623,7 @@
         <v>46181.67657885417</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -4653,7 +4653,7 @@
         <v>111</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4676,7 +4676,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8">
         <v>46160.6525875463</v>
@@ -4715,13 +4715,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>102</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4731,7 +4731,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46160.652593067134</v>
@@ -4743,7 +4743,7 @@
         <v>46181.676553680554</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
@@ -4770,13 +4770,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>103</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4786,7 +4786,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46160.65225516204</v>
@@ -4798,7 +4798,7 @@
         <v>46181.67858451389</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4822,7 +4822,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4835,7 +4835,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46160.65259921296</v>
@@ -4847,16 +4847,16 @@
         <v>46197.712640196754</v>
       </c>
       <c r="E54" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="F54" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>201</v>
       </c>
       <c r="I54" s="5">
         <v>46140</v>
@@ -4874,13 +4874,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>77</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46140</v>
@@ -4900,7 +4900,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B55" s="8">
         <v>46160.652606006945</v>
@@ -4912,16 +4912,16 @@
         <v>46197.71267317129</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="H55" s="9" t="s">
         <v>200</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="I55" s="8">
         <v>46153</v>
@@ -4939,13 +4939,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O55" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="P55" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="P55" s="9" t="s">
-        <v>206</v>
       </c>
       <c r="Q55" s="8">
         <v>46153</v>
@@ -4965,7 +4965,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46160.65261409723</v>
@@ -4983,10 +4983,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46160</v>
@@ -5004,13 +5004,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="5">
         <v>46160</v>
@@ -5030,7 +5030,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B57" s="8">
         <v>46160.652630983794</v>
@@ -5042,16 +5042,16 @@
         <v>46203.199680034726</v>
       </c>
       <c r="E57" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F57" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="9" t="s">
+      <c r="H57" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I57" s="8">
         <v>46210</v>
@@ -5069,10 +5069,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -5084,7 +5084,7 @@
         <v>46210</v>
       </c>
       <c r="S57" s="12" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="T57" s="9">
         <v>1</v>
@@ -5113,10 +5113,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>213</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>214</v>
       </c>
       <c r="I58" s="5">
         <v>46210</v>
@@ -5134,7 +5134,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>217</v>
@@ -5168,10 +5168,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H59" s="9" t="s">
         <v>213</v>
-      </c>
-      <c r="H59" s="9" t="s">
-        <v>214</v>
       </c>
       <c r="I59" s="8">
         <v>46210</v>
@@ -5189,7 +5189,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="O59" s="9" t="s">
         <v>217</v>
@@ -5337,10 +5337,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I62" s="5">
         <v>46182</v>
@@ -5467,10 +5467,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I64" s="5">
         <v>46182</v>
@@ -5494,7 +5494,7 @@
         <v>234</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q64" s="5">
         <v>46182</v>
@@ -5556,7 +5556,7 @@
         <v>222</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>240</v>
@@ -5597,10 +5597,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I66" s="5">
         <v>46182</v>
@@ -5624,7 +5624,7 @@
         <v>239</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="Q66" s="5">
         <v>46182</v>
@@ -6061,10 +6061,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I74" s="5">
         <v>46196</v>
@@ -6085,7 +6085,7 @@
         <v>243</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>243</v>
@@ -6126,10 +6126,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>185</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>186</v>
       </c>
       <c r="I75" s="8">
         <v>46196</v>
@@ -6181,10 +6181,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>185</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>186</v>
       </c>
       <c r="I76" s="5">
         <v>46196</v>
@@ -6504,7 +6504,7 @@
         <v>222</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="P81" s="9" t="s">
         <v>281</v>
@@ -6516,7 +6516,7 @@
         <v>46206</v>
       </c>
       <c r="S81" s="12" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>
@@ -6858,7 +6858,7 @@
         <v>284</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>284</v>
@@ -7000,7 +7000,7 @@
         <v>46181.67783773148</v>
       </c>
       <c r="D90" s="5">
-        <v>46198.20633876158</v>
+        <v>46206.17392120371</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>299</v>
@@ -7033,7 +7033,7 @@
         <v>284</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P90" s="6" t="s">
         <v>284</v>
@@ -7044,8 +7044,8 @@
       <c r="R90" s="5">
         <v>46205</v>
       </c>
-      <c r="S90" s="12" t="s">
-        <v>177</v>
+      <c r="S90" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T90" s="6">
         <v>1</v>
@@ -7204,7 +7204,7 @@
         <v>284</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P93" s="9" t="s">
         <v>284</v>
@@ -7216,7 +7216,7 @@
         <v>46206</v>
       </c>
       <c r="S93" s="12" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="T93" s="9">
         <v>1</v>
@@ -7379,7 +7379,7 @@
         <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>284</v>
@@ -7391,7 +7391,7 @@
         <v>46209</v>
       </c>
       <c r="S96" s="12" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="T96" s="6">
         <v>1</v>
@@ -7554,7 +7554,7 @@
         <v>284</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="P99" s="9" t="s">
         <v>316</v>
@@ -7566,7 +7566,7 @@
         <v>46211</v>
       </c>
       <c r="S99" s="12" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="T99" s="9">
         <v>1</v>
@@ -7782,7 +7782,7 @@
         <v>46212</v>
       </c>
       <c r="S103" s="12" t="s">
-        <v>177</v>
+        <v>215</v>
       </c>
       <c r="T103" s="9">
         <v>1</v>
@@ -8018,7 +8018,7 @@
         <v>46197.49765626158</v>
       </c>
       <c r="D108" s="5">
-        <v>46197.497765231485</v>
+        <v>46206.181434004626</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>340</v>
@@ -8062,8 +8062,8 @@
       <c r="R108" s="5">
         <v>46213</v>
       </c>
-      <c r="S108" s="10" t="s">
-        <v>32</v>
+      <c r="S108" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="T108" s="6">
         <v>1</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -2863,7 +2863,7 @@
         <v>46181.612735636576</v>
       </c>
       <c r="D21" s="8">
-        <v>46181.67578979167</v>
+        <v>46206.562373125</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>93</v>
@@ -2928,7 +2928,7 @@
         <v>46181.67582236111</v>
       </c>
       <c r="D22" s="5">
-        <v>46181.67583789352</v>
+        <v>46206.56247952546</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>99</v>
@@ -2993,7 +2993,7 @@
         <v>46181.675860312505</v>
       </c>
       <c r="D23" s="8">
-        <v>46181.67587553241</v>
+        <v>46206.562588877314</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>102</v>
@@ -3058,7 +3058,7 @@
         <v>46181.67587228009</v>
       </c>
       <c r="D24" s="5">
-        <v>46181.67588775463</v>
+        <v>46206.56275350694</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>105</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -6471,7 +6471,7 @@
         <v>46181.677345601856</v>
       </c>
       <c r="D81" s="8">
-        <v>46199.19357225695</v>
+        <v>46207.188708125</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>280</v>
@@ -6515,8 +6515,8 @@
       <c r="R81" s="8">
         <v>46206</v>
       </c>
-      <c r="S81" s="12" t="s">
-        <v>215</v>
+      <c r="S81" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>
@@ -7171,7 +7171,7 @@
         <v>46181.6778656713</v>
       </c>
       <c r="D93" s="8">
-        <v>46199.193572986114</v>
+        <v>46207.18870825232</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>304</v>
@@ -7215,8 +7215,8 @@
       <c r="R93" s="8">
         <v>46206</v>
       </c>
-      <c r="S93" s="12" t="s">
-        <v>215</v>
+      <c r="S93" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T93" s="9">
         <v>1</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -8297,7 +8297,7 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46194.05666876158</v>
+        <v>46209.199074965276</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>350</v>
@@ -8341,8 +8341,8 @@
       <c r="R113" s="8">
         <v>46216</v>
       </c>
-      <c r="S113" s="10" t="s">
-        <v>32</v>
+      <c r="S113" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -7346,7 +7346,7 @@
         <v>46181.677918587964</v>
       </c>
       <c r="D96" s="5">
-        <v>46202.16840032407</v>
+        <v>46210.194492256946</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>310</v>
@@ -7390,8 +7390,8 @@
       <c r="R96" s="5">
         <v>46209</v>
       </c>
-      <c r="S96" s="12" t="s">
-        <v>215</v>
+      <c r="S96" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T96" s="6">
         <v>1</v>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46183.89564782407</v>
+        <v>46210.19434488426</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>360</v>
@@ -8608,8 +8608,8 @@
       <c r="R118" s="5">
         <v>46217</v>
       </c>
-      <c r="S118" s="10" t="s">
-        <v>32</v>
+      <c r="S118" s="12" t="s">
+        <v>215</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -696,310 +696,310 @@
     <t>OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
   </si>
   <si>
+    <t>1214909617021015</t>
+  </si>
+  <si>
+    <t>OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>OT 4313 - ZVN 1-9-45/2,check pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214909617021025</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909311523649</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214909311523659</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1214909353634934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909353634954</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214909353643276</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1214909353643291</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1214909311576495</t>
+  </si>
+  <si>
+    <t>1214909311576510</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214909353651651</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909353651671</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909462990247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>OT  4313- ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909462991387</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>OT 4313 - ZVN 1-9-45/2,OT  4313- ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909462991402</t>
+  </si>
+  <si>
+    <t>OT 4313 - ZVN 1-9-45/2,check planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909462999774</t>
+  </si>
+  <si>
+    <t>1214909462999794</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214909595352637</t>
+  </si>
+  <si>
+    <t>Revestimiento,OT 4313 - ZVN 1-9-45/2,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214909595352657</t>
+  </si>
+  <si>
+    <t>OT  4313- ZVN 1-9-45/2,check planos</t>
+  </si>
+  <si>
+    <t>OT 4313 - ZVN 1-9-45/2,Revestimiento,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1214922926330543</t>
+  </si>
+  <si>
+    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214922926330553</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,Bodega:</t>
+  </si>
+  <si>
+    <t>1214909617117221</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1214909311617718</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>1214909311617738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>OT 4313 - ZVN 1-9-45/2,Revestimiento,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214889077215099</t>
+  </si>
+  <si>
+    <t>1214909463054472</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,Revestimiento,Montaje Rodete,Pruebas FAT,RE-PINTADO,Montaje motor</t>
+  </si>
+  <si>
+    <t>1214909463054482</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214909463078246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4313 - ZVN 1-9-45/2,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1214909463078261</t>
+  </si>
+  <si>
+    <t>1214909311625663</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1214909311625678</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,check planos</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909311626898</t>
+  </si>
+  <si>
+    <t>1214909463082677</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1214909463082692</t>
+  </si>
+  <si>
+    <t>OT 4313 - ZVN 1-9-45/2,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t>1214909311669543</t>
+  </si>
+  <si>
+    <t>1214909311669568</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1214909617208982</t>
+  </si>
+  <si>
+    <t>Recepcion motor,check planos</t>
+  </si>
+  <si>
+    <t>Montaje motor,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909617209002</t>
+  </si>
+  <si>
+    <t>1214909595434865</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1214909595434880</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909653715893</t>
+  </si>
+  <si>
+    <t>1214909595453558</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Montaje:,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214909617021015</t>
-  </si>
-  <si>
-    <t>OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>OT 4313 - ZVN 1-9-45/2,check pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214909617021025</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909311523649</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214909311523659</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1214909353634934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909353634954</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214909353643276</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1214909353643291</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1214909311576495</t>
-  </si>
-  <si>
-    <t>1214909311576510</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214909353651651</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909353651671</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909462990247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>OT  4313- ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909462991387</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>OT 4313 - ZVN 1-9-45/2,OT  4313- ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909462991402</t>
-  </si>
-  <si>
-    <t>OT 4313 - ZVN 1-9-45/2,check planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909462999774</t>
-  </si>
-  <si>
-    <t>1214909462999794</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214909595352637</t>
-  </si>
-  <si>
-    <t>Revestimiento,OT 4313 - ZVN 1-9-45/2,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214909595352657</t>
-  </si>
-  <si>
-    <t>OT  4313- ZVN 1-9-45/2,check planos</t>
-  </si>
-  <si>
-    <t>OT 4313 - ZVN 1-9-45/2,Revestimiento,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1214922926330543</t>
-  </si>
-  <si>
-    <t>Recepcion motor,Recepcion Rodete,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214922926330553</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,Bodega:</t>
-  </si>
-  <si>
-    <t>1214909617117221</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1214909311617718</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>1214909311617738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>OT 4313 - ZVN 1-9-45/2,Revestimiento,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214889077215099</t>
-  </si>
-  <si>
-    <t>1214909463054472</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,Revestimiento,Montaje Rodete,Pruebas FAT,RE-PINTADO,Montaje motor</t>
-  </si>
-  <si>
-    <t>1214909463054482</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214909463078246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4313 - ZVN 1-9-45/2,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1214909463078261</t>
-  </si>
-  <si>
-    <t>1214909311625663</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1214909311625678</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,check planos</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909311626898</t>
-  </si>
-  <si>
-    <t>1214909463082677</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1214909463082692</t>
-  </si>
-  <si>
-    <t>OT 4313 - ZVN 1-9-45/2,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t>1214909311669543</t>
-  </si>
-  <si>
-    <t>1214909311669568</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1214909617208982</t>
-  </si>
-  <si>
-    <t>Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>Montaje motor,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909617209002</t>
-  </si>
-  <si>
-    <t>1214909595434865</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1214909595434880</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909653715893</t>
-  </si>
-  <si>
-    <t>1214909595453558</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1214909595453573</t>
@@ -5039,7 +5039,7 @@
         <v>46198.56611644676</v>
       </c>
       <c r="D57" s="8">
-        <v>46203.199680034726</v>
+        <v>46211.169411759256</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>211</v>
@@ -5083,8 +5083,8 @@
       <c r="R57" s="8">
         <v>46210</v>
       </c>
-      <c r="S57" s="12" t="s">
-        <v>215</v>
+      <c r="S57" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T57" s="9">
         <v>1</v>
@@ -5095,7 +5095,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46160.65263532408</v>
@@ -5107,7 +5107,7 @@
         <v>46198.566085625</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5137,10 +5137,10 @@
         <v>211</v>
       </c>
       <c r="O58" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="P58" s="6" t="s">
         <v>217</v>
-      </c>
-      <c r="P58" s="6" t="s">
-        <v>218</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5150,7 +5150,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B59" s="8">
         <v>46160.65264069445</v>
@@ -5162,7 +5162,7 @@
         <v>46198.5661015625</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
@@ -5192,10 +5192,10 @@
         <v>211</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5205,7 +5205,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46160.652676921294</v>
@@ -5217,7 +5217,7 @@
         <v>46181.67816971065</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5241,7 +5241,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5254,7 +5254,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
         <v>46160.65268083333</v>
@@ -5266,16 +5266,16 @@
         <v>46182.19861893519</v>
       </c>
       <c r="E61" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="9" t="s">
         <v>225</v>
       </c>
-      <c r="F61" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G61" s="9" t="s">
+      <c r="H61" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I61" s="8">
         <v>46178</v>
@@ -5293,13 +5293,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>162</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q61" s="8">
         <v>46178</v>
@@ -5319,7 +5319,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B62" s="5">
         <v>46160.652685810186</v>
@@ -5331,7 +5331,7 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
@@ -5358,13 +5358,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O62" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="P62" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="P62" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="Q62" s="5">
         <v>46182</v>
@@ -5384,7 +5384,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B63" s="8">
         <v>46160.65269097222</v>
@@ -5396,16 +5396,16 @@
         <v>46181.6766224537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I63" s="8">
         <v>46178</v>
@@ -5423,13 +5423,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>170</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="Q63" s="8">
         <v>46147</v>
@@ -5449,7 +5449,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B64" s="5">
         <v>46160.65269633102</v>
@@ -5461,7 +5461,7 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5488,10 +5488,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>214</v>
@@ -5514,7 +5514,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B65" s="8">
         <v>46160.65269980324</v>
@@ -5526,16 +5526,16 @@
         <v>46181.67666866898</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I65" s="8">
         <v>46178</v>
@@ -5553,13 +5553,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>192</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="Q65" s="8">
         <v>46147</v>
@@ -5579,7 +5579,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5">
         <v>46160.652703935186</v>
@@ -5591,7 +5591,7 @@
         <v>46184.172129004626</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
@@ -5618,10 +5618,10 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>214</v>
@@ -5644,7 +5644,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B67" s="8">
         <v>46160.65270767361</v>
@@ -5656,7 +5656,7 @@
         <v>46181.6781084838</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5680,7 +5680,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5693,7 +5693,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B68" s="5">
         <v>46160.65271061343</v>
@@ -5705,16 +5705,16 @@
         <v>46189.195743599535</v>
       </c>
       <c r="E68" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
+      <c r="H68" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I68" s="5">
         <v>46184</v>
@@ -5732,13 +5732,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q68" s="5">
         <v>46184</v>
@@ -5758,7 +5758,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B69" s="8">
         <v>46160.65271650463</v>
@@ -5770,16 +5770,16 @@
         <v>46181.67713434028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="I69" s="8">
         <v>46184</v>
@@ -5797,13 +5797,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O69" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="P69" s="9" t="s">
         <v>251</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>252</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5813,7 +5813,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B70" s="5">
         <v>46160.65272224537</v>
@@ -5825,16 +5825,16 @@
         <v>46181.67713509259</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I70" s="5">
         <v>46184</v>
@@ -5852,13 +5852,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>254</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>255</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5868,7 +5868,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B71" s="8">
         <v>46160.652726898144</v>
@@ -5880,16 +5880,16 @@
         <v>46196.198199756946</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="I71" s="8">
         <v>46189</v>
@@ -5907,13 +5907,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q71" s="8">
         <v>46189</v>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B72" s="5">
         <v>46160.65273052083</v>
@@ -5945,16 +5945,16 @@
         <v>46181.67719854167</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I72" s="5">
         <v>46189</v>
@@ -5972,13 +5972,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>260</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>261</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B73" s="8">
         <v>46160.652741620375</v>
@@ -6000,16 +6000,16 @@
         <v>46181.67721436343</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="I73" s="8">
         <v>46189</v>
@@ -6027,13 +6027,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O73" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="P73" s="9" t="s">
         <v>260</v>
-      </c>
-      <c r="P73" s="9" t="s">
-        <v>261</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6043,7 +6043,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B74" s="5">
         <v>46160.65274630787</v>
@@ -6055,7 +6055,7 @@
         <v>46197.19306369213</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
@@ -6082,13 +6082,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>214</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="Q74" s="5">
         <v>46196</v>
@@ -6108,7 +6108,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B75" s="8">
         <v>46160.65275005787</v>
@@ -6120,7 +6120,7 @@
         <v>46181.67726512731</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
@@ -6147,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6163,7 +6163,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B76" s="5">
         <v>46160.65275548611</v>
@@ -6175,7 +6175,7 @@
         <v>46181.677274664355</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -6202,13 +6202,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="O76" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="P76" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="P76" s="6" t="s">
-        <v>269</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6218,7 +6218,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B77" s="8">
         <v>46160.652760625</v>
@@ -6230,7 +6230,7 @@
         <v>46181.67751854166</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6254,7 +6254,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6267,7 +6267,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B78" s="5">
         <v>46160.65276340277</v>
@@ -6279,16 +6279,16 @@
         <v>46192.20460657407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H78" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I78" s="5">
         <v>46160</v>
@@ -6306,13 +6306,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>131</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q78" s="5">
         <v>46160</v>
@@ -6332,7 +6332,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B79" s="8">
         <v>46160.652768831016</v>
@@ -6344,16 +6344,16 @@
         <v>46181.677345034725</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I79" s="8">
         <v>46141</v>
@@ -6371,13 +6371,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O79" s="9" t="s">
         <v>122</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q79" s="8">
         <v>46141</v>
@@ -6397,7 +6397,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B80" s="5">
         <v>46160.652774409726</v>
@@ -6409,16 +6409,16 @@
         <v>46181.67735619213</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6436,13 +6436,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>140</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6462,7 +6462,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B81" s="8">
         <v>46160.652779745375</v>
@@ -6474,16 +6474,16 @@
         <v>46207.188708125</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="I81" s="8">
         <v>46206</v>
@@ -6501,13 +6501,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>180</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="Q81" s="8">
         <v>46206</v>
@@ -6527,7 +6527,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B82" s="5">
         <v>46160.657067569446</v>
@@ -6543,10 +6543,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="I82" s="5">
         <v>46197</v>
@@ -6564,7 +6564,7 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>151</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B83" s="8">
         <v>46160.65278418981</v>
@@ -6602,7 +6602,7 @@
         <v>46197.49724974537</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>25</v>
@@ -6626,7 +6626,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>26</v>
@@ -6641,7 +6641,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B84" s="5">
         <v>46160.65278701389</v>
@@ -6653,7 +6653,7 @@
         <v>46204.17292415509</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6680,13 +6680,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q84" s="5">
         <v>46197</v>
@@ -6706,7 +6706,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B85" s="8">
         <v>46160.65279357639</v>
@@ -6718,7 +6718,7 @@
         <v>46181.67767618055</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6745,10 +6745,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6761,7 +6761,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B86" s="5">
         <v>46160.65279733796</v>
@@ -6773,7 +6773,7 @@
         <v>46181.677689247685</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6800,10 +6800,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6816,7 +6816,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B87" s="8">
         <v>46160.65280108796</v>
@@ -6828,7 +6828,7 @@
         <v>46205.18242020834</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6855,13 +6855,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>214</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -6881,7 +6881,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
         <v>46160.65280498842</v>
@@ -6893,7 +6893,7 @@
         <v>46181.67774287037</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6920,13 +6920,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O88" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>295</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6936,7 +6936,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B89" s="8">
         <v>46160.65281013889</v>
@@ -6948,7 +6948,7 @@
         <v>46181.67775488426</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6975,13 +6975,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="O89" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="P89" s="9" t="s">
         <v>295</v>
-      </c>
-      <c r="P89" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6991,7 +6991,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B90" s="5">
         <v>46160.65281503472</v>
@@ -7003,7 +7003,7 @@
         <v>46206.17392120371</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7030,13 +7030,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>214</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q90" s="5">
         <v>46205</v>
@@ -7056,7 +7056,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B91" s="8">
         <v>46160.65281883102</v>
@@ -7068,7 +7068,7 @@
         <v>46181.677797627315</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7093,13 +7093,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7109,7 +7109,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B92" s="5">
         <v>46160.65287608796</v>
@@ -7121,7 +7121,7 @@
         <v>46181.67780725694</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7146,13 +7146,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7162,7 +7162,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B93" s="8">
         <v>46160.65288447917</v>
@@ -7174,7 +7174,7 @@
         <v>46207.18870825232</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7201,13 +7201,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>214</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q93" s="8">
         <v>46206</v>
@@ -7227,7 +7227,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B94" s="5">
         <v>46160.65288969908</v>
@@ -7239,7 +7239,7 @@
         <v>46181.67784412037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7266,13 +7266,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O94" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>306</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B95" s="8">
         <v>46160.6528953588</v>
@@ -7294,7 +7294,7 @@
         <v>46181.677850625</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7321,13 +7321,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="O95" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>306</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>307</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7337,7 +7337,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B96" s="5">
         <v>46160.652900706016</v>
@@ -7349,7 +7349,7 @@
         <v>46210.194492256946</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7376,13 +7376,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>214</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Q96" s="5">
         <v>46209</v>
@@ -7402,7 +7402,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B97" s="8">
         <v>46160.65290569444</v>
@@ -7414,7 +7414,7 @@
         <v>46181.67789438658</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7441,13 +7441,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7457,7 +7457,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B98" s="5">
         <v>46160.652911157405</v>
@@ -7469,7 +7469,7 @@
         <v>46181.67790501157</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7496,13 +7496,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7512,7 +7512,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B99" s="8">
         <v>46160.65291657408</v>
@@ -7524,7 +7524,7 @@
         <v>46204.17015261574</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7551,13 +7551,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="O99" s="9" t="s">
         <v>214</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q99" s="8">
         <v>46211</v>
@@ -7566,7 +7566,7 @@
         <v>46211</v>
       </c>
       <c r="S99" s="12" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
       <c r="T99" s="9">
         <v>1</v>
@@ -7589,7 +7589,7 @@
         <v>46198.56608928241</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7614,10 +7614,10 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P100" s="6" t="s">
         <v>318</v>
@@ -7642,7 +7642,7 @@
         <v>46198.566110405096</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7667,10 +7667,10 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P101" s="9" t="s">
         <v>320</v>
@@ -7782,7 +7782,7 @@
         <v>46212</v>
       </c>
       <c r="S103" s="12" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
       <c r="T103" s="9">
         <v>1</v>
@@ -7805,7 +7805,7 @@
         <v>46204.80222355324</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7835,7 +7835,7 @@
         <v>325</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P104" s="6" t="s">
         <v>330</v>
@@ -7860,7 +7860,7 @@
         <v>46204.80248778935</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -7890,7 +7890,7 @@
         <v>325</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P105" s="9" t="s">
         <v>333</v>
@@ -8063,7 +8063,7 @@
         <v>46213</v>
       </c>
       <c r="S108" s="12" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
       <c r="T108" s="6">
         <v>1</v>
@@ -8086,7 +8086,7 @@
         <v>46204.80222711805</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8116,7 +8116,7 @@
         <v>340</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>343</v>
@@ -8141,7 +8141,7 @@
         <v>46204.80249248842</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8171,7 +8171,7 @@
         <v>340</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>343</v>
@@ -8306,10 +8306,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="H113" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="I113" s="8">
         <v>46216</v>
@@ -8342,7 +8342,7 @@
         <v>46216</v>
       </c>
       <c r="S113" s="12" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>
@@ -8363,16 +8363,16 @@
         <v>46197.49737577546</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8391,7 +8391,7 @@
         <v>350</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>353</v>
@@ -8414,16 +8414,16 @@
         <v>46197.49753788194</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="H115" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="8">
@@ -8442,7 +8442,7 @@
         <v>350</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>355</v>
@@ -8471,10 +8471,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H116" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8522,10 +8522,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="H117" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8573,10 +8573,10 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H118" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I118" s="5">
         <v>46217</v>
@@ -8609,7 +8609,7 @@
         <v>46217</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>215</v>
+        <v>316</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
@@ -8630,16 +8630,16 @@
         <v>46194.054542048616</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="H119" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="I119" s="8">
         <v>46217</v>
@@ -8660,7 +8660,7 @@
         <v>360</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P119" s="9" t="s">
         <v>360</v>
@@ -8683,16 +8683,16 @@
         <v>46194.056669247686</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H120" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I120" s="5">
         <v>46217</v>
@@ -8713,7 +8713,7 @@
         <v>360</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>360</v>
@@ -8742,10 +8742,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="H121" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="I121" s="8">
         <v>46217</v>
@@ -8795,10 +8795,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H122" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I122" s="5">
         <v>46217</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -999,43 +999,43 @@
     <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>1214909595453573</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909653727710</t>
+  </si>
+  <si>
+    <t>OT 4313 - ZVN 1-9-45/2,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1214909653727725</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Embalaje,Despacho,PACKING LIST,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1214909653727735</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>Revision Tableros,OT 4314 - VDF VLT  FC 102,OT 4314 - VDF VLT  FC 102,OT 4313 - ZVN 1-9-45/2,RE-PINTADO,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214909595453573</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909653727710</t>
-  </si>
-  <si>
-    <t>OT 4313 - ZVN 1-9-45/2,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1214909653727725</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Embalaje,Despacho,PACKING LIST,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1214909653727735</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>Revision Tableros,OT 4314 - VDF VLT  FC 102,OT 4314 - VDF VLT  FC 102,OT 4313 - ZVN 1-9-45/2,RE-PINTADO,OT 4313 - ZVN 1-9-45/2</t>
   </si>
   <si>
     <t>1214909653744388</t>
@@ -7521,7 +7521,7 @@
         <v>46197.49723263889</v>
       </c>
       <c r="D99" s="8">
-        <v>46204.17015261574</v>
+        <v>46212.190271898144</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>314</v>
@@ -7565,8 +7565,8 @@
       <c r="R99" s="8">
         <v>46211</v>
       </c>
-      <c r="S99" s="12" t="s">
-        <v>316</v>
+      <c r="S99" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T99" s="9">
         <v>1</v>
@@ -7577,7 +7577,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B100" s="5">
         <v>46160.652921562505</v>
@@ -7620,7 +7620,7 @@
         <v>216</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7630,7 +7630,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B101" s="8">
         <v>46160.65292620371</v>
@@ -7673,7 +7673,7 @@
         <v>216</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7683,7 +7683,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B102" s="5">
         <v>46160.65293084491</v>
@@ -7693,7 +7693,7 @@
         <v>46197.49766417824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7717,7 +7717,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7730,26 +7730,26 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B103" s="8">
         <v>46160.65293431713</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46205.174301817126</v>
+        <v>46212.16852481481</v>
       </c>
       <c r="E103" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="9" t="s">
         <v>325</v>
       </c>
-      <c r="F103" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G103" s="9" t="s">
+      <c r="H103" s="9" t="s">
         <v>326</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>327</v>
       </c>
       <c r="I103" s="8">
         <v>46212</v>
@@ -7767,13 +7767,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q103" s="8">
         <v>46212</v>
@@ -7782,7 +7782,7 @@
         <v>46212</v>
       </c>
       <c r="S103" s="12" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="T103" s="9">
         <v>1</v>
@@ -7811,10 +7811,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>326</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>327</v>
       </c>
       <c r="I104" s="5">
         <v>46212</v>
@@ -7832,7 +7832,7 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>216</v>
@@ -7866,10 +7866,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="H105" s="9" t="s">
         <v>326</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>327</v>
       </c>
       <c r="I105" s="8">
         <v>46212</v>
@@ -7887,7 +7887,7 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O105" s="9" t="s">
         <v>216</v>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46160.817732083335</v>
+        <v>46212.16850269676</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>335</v>
@@ -7919,10 +7919,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>326</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>327</v>
       </c>
       <c r="I106" s="5">
         <v>46212</v>
@@ -7940,7 +7940,7 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>58</v>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46160.81773274306</v>
+        <v>46212.168504710644</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>335</v>
@@ -7972,10 +7972,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="H107" s="9" t="s">
         <v>326</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>327</v>
       </c>
       <c r="I107" s="8">
         <v>46212</v>
@@ -7993,7 +7993,7 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>58</v>
@@ -8048,13 +8048,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>341</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q108" s="5">
         <v>46213</v>
@@ -8063,7 +8063,7 @@
         <v>46213</v>
       </c>
       <c r="S108" s="12" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="T108" s="6">
         <v>1</v>
@@ -8327,13 +8327,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>351</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q113" s="8">
         <v>46216</v>
@@ -8342,7 +8342,7 @@
         <v>46216</v>
       </c>
       <c r="S113" s="12" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>
@@ -8594,7 +8594,7 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>351</v>
@@ -8609,7 +8609,7 @@
         <v>46217</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -1035,46 +1035,46 @@
     <t>Revision Tableros,OT 4314 - VDF VLT  FC 102,OT 4314 - VDF VLT  FC 102,OT 4313 - ZVN 1-9-45/2,RE-PINTADO,OT 4313 - ZVN 1-9-45/2</t>
   </si>
   <si>
+    <t>1214909653744388</t>
+  </si>
+  <si>
+    <t>OT 4313 - ZVN 1-9-45/2,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1214909311722244</t>
+  </si>
+  <si>
+    <t>DESPACHADO Y FACTURADO</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214889077215247</t>
+  </si>
+  <si>
+    <t>OT 4314 - VDF VLT  FC 102</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,OT 4314 - VDF VLT  FC 102</t>
+  </si>
+  <si>
+    <t>1214889077215248</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,OT 4314- VDF VLT  FC 102</t>
+  </si>
+  <si>
+    <t>1214909311722259</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
+    <t>OT 4314- VDF VLT  FC 102,OT 4314 - VDF VLT  FC 102,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214909653744388</t>
-  </si>
-  <si>
-    <t>OT 4313 - ZVN 1-9-45/2,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1214909311722244</t>
-  </si>
-  <si>
-    <t>DESPACHADO Y FACTURADO</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214889077215247</t>
-  </si>
-  <si>
-    <t>OT 4314 - VDF VLT  FC 102</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,OT 4314 - VDF VLT  FC 102</t>
-  </si>
-  <si>
-    <t>1214889077215248</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,OT 4314- VDF VLT  FC 102</t>
-  </si>
-  <si>
-    <t>1214909311722259</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
-  </si>
-  <si>
-    <t>OT 4314- VDF VLT  FC 102,OT 4314 - VDF VLT  FC 102,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
   </si>
   <si>
     <t>1214909311722274</t>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46212.16852481481</v>
+        <v>46213.179386909724</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>324</v>
@@ -7781,8 +7781,8 @@
       <c r="R103" s="8">
         <v>46212</v>
       </c>
-      <c r="S103" s="12" t="s">
-        <v>328</v>
+      <c r="S103" s="11" t="s">
+        <v>63</v>
       </c>
       <c r="T103" s="9">
         <v>1</v>
@@ -7793,7 +7793,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B104" s="5">
         <v>46160.65293966435</v>
@@ -7838,7 +7838,7 @@
         <v>216</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7848,7 +7848,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B105" s="8">
         <v>46160.652944201385</v>
@@ -7881,7 +7881,7 @@
         <v>26</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="M105" s="9" t="s">
         <v>26</v>
@@ -7893,7 +7893,7 @@
         <v>216</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7903,7 +7903,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B106" s="5">
         <v>46160.80816486111</v>
@@ -7913,7 +7913,7 @@
         <v>46212.16850269676</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -7946,7 +7946,7 @@
         <v>58</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7956,7 +7956,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B107" s="8">
         <v>46160.80854525463</v>
@@ -7966,7 +7966,7 @@
         <v>46212.168504710644</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -7999,7 +7999,7 @@
         <v>58</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8009,7 +8009,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B108" s="5">
         <v>46160.65294850695</v>
@@ -8021,7 +8021,7 @@
         <v>46206.181434004626</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8051,7 +8051,7 @@
         <v>321</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>321</v>
@@ -8063,7 +8063,7 @@
         <v>46213</v>
       </c>
       <c r="S108" s="12" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="T108" s="6">
         <v>1</v>
@@ -8113,7 +8113,7 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>216</v>
@@ -8168,7 +8168,7 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>216</v>
@@ -8191,10 +8191,10 @@
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46197.4977528125</v>
+        <v>46213.16936128472</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8221,10 +8221,10 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>346</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46197.497759895836</v>
+        <v>46213.16936325232</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>348</v>
@@ -8274,10 +8274,10 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>346</v>
@@ -8342,7 +8342,7 @@
         <v>46216</v>
       </c>
       <c r="S113" s="12" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>
@@ -8465,7 +8465,7 @@
         <v>46197.49775597222</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8493,7 +8493,7 @@
         <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>357</v>
@@ -8516,7 +8516,7 @@
         <v>46197.49776570602</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8609,7 +8609,7 @@
         <v>46217</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
@@ -8736,7 +8736,7 @@
         <v>46194.05454575231</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8766,7 +8766,7 @@
         <v>360</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>360</v>
@@ -8789,7 +8789,7 @@
         <v>46194.05454428241</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8819,7 +8819,7 @@
         <v>360</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>360</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="384">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -125,6 +125,34 @@
   </si>
   <si>
     <t>francisca@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buen día,
+Para el pedido 1544 se tiene 2 ventiladores ZVN 1-9-45/2 para DMC Mining Servicie:
+    *    Fabricación:
+        *    Ventilador ZVN 1-9-45/2 con motor WEG.
+        *    Alcance: Tobera + Rejilla + FAR100/100 + Ventilador + FAR 100/100 + Tipo A Ø900mm.
+        *    Referencia: 300000-225
+    *    Rodete:
+        *    Rodete de placas s/plano 4999.00
+        *    Alabe s/ plano 4999.01
+        *    Z8 N590
+        *    Código 300000
+        *    hgutierrez@zitron.com, tu apoyo con la definición de calaje
+    *    Tratamiento superficial:
+        *    Preparación de superficie: Arenado SSPC-SP10
+        *    1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        *    2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    *    Datos eléctricos para el motor:
+        *    Motor WEG 45KW, 400VAC, 50 Hz, 2P, IP55, FS: 1
+        *    Plano motor adjunto.
+    *    Datos tablero eléctricos:
+        *    VDF 75 kW, IP54, 400V, 50Hz.
+        *    Marca Danfoss
+        *    Modelo VLT FC102
+        *    OC19219 VDF VLT FC102: 08-06-26
+    *    Fecha de entrega: 15-05-2026
+</t>
   </si>
   <si>
     <t>1214909594964500</t>
@@ -1942,7 +1970,7 @@
         <v>46167.55815621528</v>
       </c>
       <c r="D6" s="5">
-        <v>46167.558157314816</v>
+        <v>46213.70911188658</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -1964,7 +1992,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -1996,7 +2024,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="8">
         <v>46160.65235689815</v>
@@ -2008,7 +2036,7 @@
         <v>46167.558190428244</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>26</v>
@@ -2027,7 +2055,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>26</v>
@@ -2059,7 +2087,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="5">
         <v>46160.652359687505</v>
@@ -2071,7 +2099,7 @@
         <v>46167.55823541667</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -2090,7 +2118,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -2102,7 +2130,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q8" s="5">
         <v>46128</v>
@@ -2122,7 +2150,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B9" s="8">
         <v>46160.65236314815</v>
@@ -2134,7 +2162,7 @@
         <v>46167.558347303246</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>26</v>
@@ -2153,7 +2181,7 @@
         <v>26</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>26</v>
@@ -2185,7 +2213,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B10" s="5">
         <v>46160.65369118056</v>
@@ -2195,7 +2223,7 @@
         <v>46167.55829033565</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>25</v>
@@ -2219,7 +2247,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -2233,12 +2261,12 @@
         <v>0</v>
       </c>
       <c r="U10" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B11" s="8">
         <v>46160.654091874996</v>
@@ -2250,16 +2278,16 @@
         <v>46167.558296180556</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I11" s="8">
         <v>46129</v>
@@ -2277,13 +2305,13 @@
         <v>26</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q11" s="8">
         <v>46129</v>
@@ -2303,7 +2331,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B12" s="5">
         <v>46160.654172118055</v>
@@ -2313,16 +2341,16 @@
         <v>46199.17997571759</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I12" s="5">
         <v>46198</v>
@@ -2340,13 +2368,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q12" s="5">
         <v>46198</v>
@@ -2355,18 +2383,18 @@
         <v>46198</v>
       </c>
       <c r="S12" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T12" s="6">
         <v>0</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B13" s="8">
         <v>46160.65224207176</v>
@@ -2376,7 +2404,7 @@
         <v>46199.75069068287</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2400,7 +2428,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2410,12 +2438,12 @@
       <c r="S13" s="9"/>
       <c r="T13" s="9"/>
       <c r="U13" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" s="5">
         <v>46160.6523665162</v>
@@ -2427,7 +2455,7 @@
         <v>46199.75068067129</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2448,19 +2476,19 @@
         <v>26</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Q14" s="5">
         <v>46129</v>
@@ -2480,7 +2508,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B15" s="8">
         <v>46160.65237170139</v>
@@ -2492,7 +2520,7 @@
         <v>46199.75068077546</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2513,19 +2541,19 @@
         <v>26</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="Q15" s="8">
         <v>46129</v>
@@ -2545,7 +2573,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B16" s="5">
         <v>46160.652376875005</v>
@@ -2557,7 +2585,7 @@
         <v>46199.750680613426</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -2584,13 +2612,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q16" s="5">
         <v>46129</v>
@@ -2610,7 +2638,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B17" s="8">
         <v>46160.65224614584</v>
@@ -2622,7 +2650,7 @@
         <v>46181.678702233796</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>25</v>
@@ -2646,7 +2674,7 @@
         <v>26</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P17" s="9" t="s">
         <v>26</v>
@@ -2659,7 +2687,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B18" s="5">
         <v>46160.652389560186</v>
@@ -2671,7 +2699,7 @@
         <v>46167.55897762731</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2698,13 +2726,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="Q18" s="5">
         <v>46133</v>
@@ -2724,7 +2752,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B19" s="8">
         <v>46160.65239491899</v>
@@ -2736,7 +2764,7 @@
         <v>46167.55901266204</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2763,13 +2791,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="Q19" s="8">
         <v>46133</v>
@@ -2789,7 +2817,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B20" s="5">
         <v>46160.65240028936</v>
@@ -2801,16 +2829,16 @@
         <v>46181.61226466435</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I20" s="5">
         <v>46133</v>
@@ -2828,13 +2856,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q20" s="5">
         <v>46133</v>
@@ -2854,7 +2882,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B21" s="8">
         <v>46160.652405636574</v>
@@ -2866,16 +2894,16 @@
         <v>46206.562373125</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I21" s="8">
         <v>46162</v>
@@ -2893,13 +2921,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q21" s="8">
         <v>46162</v>
@@ -2908,18 +2936,18 @@
         <v>46164</v>
       </c>
       <c r="S21" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T21" s="9">
         <v>1</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B22" s="5">
         <v>46160.65241059028</v>
@@ -2931,16 +2959,16 @@
         <v>46206.56247952546</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I22" s="5">
         <v>46162</v>
@@ -2958,13 +2986,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -2973,7 +3001,7 @@
         <v>46164</v>
       </c>
       <c r="S22" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T22" s="6">
         <v>1</v>
@@ -2984,7 +3012,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B23" s="8">
         <v>46160.652414490745</v>
@@ -2996,16 +3024,16 @@
         <v>46206.562588877314</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" s="8">
         <v>46162</v>
@@ -3023,13 +3051,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q23" s="8">
         <v>46162</v>
@@ -3038,7 +3066,7 @@
         <v>46164</v>
       </c>
       <c r="S23" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T23" s="9">
         <v>1</v>
@@ -3049,7 +3077,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B24" s="5">
         <v>46160.65241840278</v>
@@ -3061,16 +3089,16 @@
         <v>46206.56275350694</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I24" s="5">
         <v>46162</v>
@@ -3088,13 +3116,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q24" s="5">
         <v>46162</v>
@@ -3103,7 +3131,7 @@
         <v>46164</v>
       </c>
       <c r="S24" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T24" s="6">
         <v>1</v>
@@ -3114,7 +3142,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B25" s="8">
         <v>46160.65857868055</v>
@@ -3126,7 +3154,7 @@
         <v>46167.55904253472</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -3153,13 +3181,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q25" s="8">
         <v>46134</v>
@@ -3179,7 +3207,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B26" s="5">
         <v>46160.65225063657</v>
@@ -3189,7 +3217,7 @@
         <v>46181.678639652775</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -3213,7 +3241,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -3226,7 +3254,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B27" s="8">
         <v>46160.65242274306</v>
@@ -3238,16 +3266,16 @@
         <v>46181.675709143514</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I27" s="8">
         <v>46135</v>
@@ -3265,13 +3293,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q27" s="8">
         <v>46135</v>
@@ -3291,7 +3319,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B28" s="5">
         <v>46160.65242719908</v>
@@ -3303,16 +3331,16 @@
         <v>46181.67563449074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I28" s="5">
         <v>46135</v>
@@ -3330,13 +3358,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3347,12 +3375,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B29" s="8">
         <v>46160.65243181713</v>
@@ -3364,16 +3392,16 @@
         <v>46181.67567790509</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I29" s="8">
         <v>46139</v>
@@ -3391,13 +3419,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3408,12 +3436,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B30" s="5">
         <v>46160.65243667824</v>
@@ -3425,16 +3453,16 @@
         <v>46181.67562327546</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I30" s="5">
         <v>46135</v>
@@ -3452,13 +3480,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q30" s="5">
         <v>46135</v>
@@ -3478,7 +3506,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B31" s="8">
         <v>46160.65244107639</v>
@@ -3490,16 +3518,16 @@
         <v>46181.67555395833</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I31" s="8">
         <v>46135</v>
@@ -3517,13 +3545,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3534,12 +3562,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B32" s="5">
         <v>46160.65244578704</v>
@@ -3551,16 +3579,16 @@
         <v>46181.67559840278</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I32" s="5">
         <v>46139</v>
@@ -3578,13 +3606,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3595,12 +3623,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B33" s="8">
         <v>46160.652450625</v>
@@ -3612,16 +3640,16 @@
         <v>46181.67549369213</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I33" s="8">
         <v>46133</v>
@@ -3639,13 +3667,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q33" s="8">
         <v>46133</v>
@@ -3654,7 +3682,7 @@
         <v>46171</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T33" s="9">
         <v>1</v>
@@ -3665,7 +3693,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B34" s="5">
         <v>46160.65245552083</v>
@@ -3677,16 +3705,16 @@
         <v>46181.67541268519</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I34" s="5">
         <v>46133</v>
@@ -3704,13 +3732,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3721,12 +3749,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B35" s="8">
         <v>46160.65246048611</v>
@@ -3738,16 +3766,16 @@
         <v>46181.67545391204</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I35" s="8">
         <v>46142</v>
@@ -3765,13 +3793,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3782,12 +3810,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B36" s="5">
         <v>46160.6524655324</v>
@@ -3799,16 +3827,16 @@
         <v>46181.67546648148</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I36" s="5">
         <v>46141</v>
@@ -3826,13 +3854,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3843,12 +3871,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B37" s="8">
         <v>46160.6566696875</v>
@@ -3858,16 +3886,16 @@
         <v>46197.19306372685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I37" s="8">
         <v>46136</v>
@@ -3885,10 +3913,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>26</v>
@@ -3900,18 +3928,18 @@
         <v>46196</v>
       </c>
       <c r="S37" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B38" s="5">
         <v>46160.65676351852</v>
@@ -3923,16 +3951,16 @@
         <v>46182.67674333333</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I38" s="5">
         <v>46136</v>
@@ -3950,13 +3978,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3966,7 +3994,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" s="8">
         <v>46160.65688415509</v>
@@ -3976,16 +4004,16 @@
         <v>46196.16898914352</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I39" s="8">
         <v>46148</v>
@@ -4003,13 +4031,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4019,7 +4047,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
         <v>46160.65247015047</v>
@@ -4031,16 +4059,16 @@
         <v>46181.676244386574</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I40" s="5">
         <v>46167</v>
@@ -4058,13 +4086,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q40" s="5">
         <v>46167</v>
@@ -4073,7 +4101,7 @@
         <v>46177</v>
       </c>
       <c r="S40" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T40" s="6">
         <v>1</v>
@@ -4084,7 +4112,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B41" s="8">
         <v>46160.65247482639</v>
@@ -4096,16 +4124,16 @@
         <v>46181.67615008102</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I41" s="8">
         <v>46167</v>
@@ -4123,13 +4151,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4140,12 +4168,12 @@
         <v>0</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B42" s="5">
         <v>46160.65247959491</v>
@@ -4157,16 +4185,16 @@
         <v>46181.67622016204</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46169</v>
@@ -4184,13 +4212,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4201,12 +4229,12 @@
         <v>0</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B43" s="8">
         <v>46160.65254070602</v>
@@ -4218,16 +4246,16 @@
         <v>46181.67636662037</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I43" s="8">
         <v>46167</v>
@@ -4245,10 +4273,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4260,7 +4288,7 @@
         <v>46177</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4271,7 +4299,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B44" s="5">
         <v>46160.65254572917</v>
@@ -4283,16 +4311,16 @@
         <v>46181.67630162037</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I44" s="5">
         <v>46167</v>
@@ -4310,13 +4338,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4326,7 +4354,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B45" s="8">
         <v>46160.652551377316</v>
@@ -4338,16 +4366,16 @@
         <v>46181.67634090278</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I45" s="8">
         <v>46169</v>
@@ -4365,13 +4393,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4381,7 +4409,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B46" s="5">
         <v>46160.652557152775</v>
@@ -4393,16 +4421,16 @@
         <v>46206.17392120371</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I46" s="5">
         <v>46167</v>
@@ -4420,10 +4448,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4435,7 +4463,7 @@
         <v>46205</v>
       </c>
       <c r="S46" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>
@@ -4446,7 +4474,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B47" s="8">
         <v>46160.65256162037</v>
@@ -4458,16 +4486,16 @@
         <v>46181.67638900463</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4485,13 +4513,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4501,7 +4529,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46160.6525734375</v>
@@ -4513,16 +4541,16 @@
         <v>46181.67642934028</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46176</v>
@@ -4540,13 +4568,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4556,7 +4584,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="8">
         <v>46160.652579236106</v>
@@ -4568,16 +4596,16 @@
         <v>46181.676467303245</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I49" s="8">
         <v>46205</v>
@@ -4595,10 +4623,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4611,7 +4639,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46160.65258304398</v>
@@ -4623,16 +4651,16 @@
         <v>46181.67657885417</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I50" s="5">
         <v>46167</v>
@@ -4650,10 +4678,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4665,7 +4693,7 @@
         <v>46177</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T50" s="6">
         <v>1</v>
@@ -4676,7 +4704,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="8">
         <v>46160.6525875463</v>
@@ -4688,16 +4716,16 @@
         <v>46181.67651314815</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I51" s="8">
         <v>46167</v>
@@ -4715,13 +4743,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4731,7 +4759,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46160.652593067134</v>
@@ -4743,16 +4771,16 @@
         <v>46181.676553680554</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I52" s="5">
         <v>46169</v>
@@ -4770,13 +4798,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4786,7 +4814,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46160.65225516204</v>
@@ -4798,7 +4826,7 @@
         <v>46181.67858451389</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4822,7 +4850,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4835,7 +4863,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46160.65259921296</v>
@@ -4847,16 +4875,16 @@
         <v>46197.712640196754</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I54" s="5">
         <v>46140</v>
@@ -4874,13 +4902,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46140</v>
@@ -4900,7 +4928,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B55" s="8">
         <v>46160.652606006945</v>
@@ -4912,16 +4940,16 @@
         <v>46197.71267317129</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I55" s="8">
         <v>46153</v>
@@ -4939,13 +4967,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q55" s="8">
         <v>46153</v>
@@ -4965,7 +4993,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46160.65261409723</v>
@@ -4977,16 +5005,16 @@
         <v>46181.67578048611</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46160</v>
@@ -5004,13 +5032,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46160</v>
@@ -5019,7 +5047,7 @@
         <v>46161</v>
       </c>
       <c r="S56" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5030,7 +5058,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46160.652630983794</v>
@@ -5042,16 +5070,16 @@
         <v>46211.169411759256</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I57" s="8">
         <v>46210</v>
@@ -5069,10 +5097,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -5084,7 +5112,7 @@
         <v>46210</v>
       </c>
       <c r="S57" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T57" s="9">
         <v>1</v>
@@ -5095,7 +5123,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B58" s="5">
         <v>46160.65263532408</v>
@@ -5107,16 +5135,16 @@
         <v>46198.566085625</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I58" s="5">
         <v>46210</v>
@@ -5134,13 +5162,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5150,7 +5178,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B59" s="8">
         <v>46160.65264069445</v>
@@ -5162,16 +5190,16 @@
         <v>46198.5661015625</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I59" s="8">
         <v>46210</v>
@@ -5189,13 +5217,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5205,7 +5233,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B60" s="5">
         <v>46160.652676921294</v>
@@ -5217,7 +5245,7 @@
         <v>46181.67816971065</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5241,7 +5269,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5254,7 +5282,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B61" s="8">
         <v>46160.65268083333</v>
@@ -5266,16 +5294,16 @@
         <v>46182.19861893519</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I61" s="8">
         <v>46178</v>
@@ -5293,13 +5321,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q61" s="8">
         <v>46178</v>
@@ -5308,7 +5336,7 @@
         <v>46181</v>
       </c>
       <c r="S61" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T61" s="9">
         <v>1</v>
@@ -5319,7 +5347,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B62" s="5">
         <v>46160.652685810186</v>
@@ -5331,16 +5359,16 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I62" s="5">
         <v>46182</v>
@@ -5358,13 +5386,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q62" s="5">
         <v>46182</v>
@@ -5373,7 +5401,7 @@
         <v>46183</v>
       </c>
       <c r="S62" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T62" s="6">
         <v>1</v>
@@ -5384,7 +5412,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B63" s="8">
         <v>46160.65269097222</v>
@@ -5396,16 +5424,16 @@
         <v>46181.6766224537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I63" s="8">
         <v>46178</v>
@@ -5423,13 +5451,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q63" s="8">
         <v>46147</v>
@@ -5449,7 +5477,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B64" s="5">
         <v>46160.65269633102</v>
@@ -5461,16 +5489,16 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I64" s="5">
         <v>46182</v>
@@ -5488,13 +5516,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q64" s="5">
         <v>46182</v>
@@ -5503,7 +5531,7 @@
         <v>46183</v>
       </c>
       <c r="S64" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T64" s="6">
         <v>1</v>
@@ -5514,7 +5542,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B65" s="8">
         <v>46160.65269980324</v>
@@ -5526,16 +5554,16 @@
         <v>46181.67666866898</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I65" s="8">
         <v>46178</v>
@@ -5553,13 +5581,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q65" s="8">
         <v>46147</v>
@@ -5579,7 +5607,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B66" s="5">
         <v>46160.652703935186</v>
@@ -5591,16 +5619,16 @@
         <v>46184.172129004626</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I66" s="5">
         <v>46182</v>
@@ -5618,13 +5646,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q66" s="5">
         <v>46182</v>
@@ -5633,7 +5661,7 @@
         <v>46183</v>
       </c>
       <c r="S66" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -5644,7 +5672,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B67" s="8">
         <v>46160.65270767361</v>
@@ -5656,7 +5684,7 @@
         <v>46181.6781084838</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5680,7 +5708,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5693,7 +5721,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B68" s="5">
         <v>46160.65271061343</v>
@@ -5705,16 +5733,16 @@
         <v>46189.195743599535</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I68" s="5">
         <v>46184</v>
@@ -5732,13 +5760,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q68" s="5">
         <v>46184</v>
@@ -5747,7 +5775,7 @@
         <v>46188</v>
       </c>
       <c r="S68" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T68" s="6">
         <v>1</v>
@@ -5758,7 +5786,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B69" s="8">
         <v>46160.65271650463</v>
@@ -5770,16 +5798,16 @@
         <v>46181.67713434028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I69" s="8">
         <v>46184</v>
@@ -5797,13 +5825,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5813,7 +5841,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B70" s="5">
         <v>46160.65272224537</v>
@@ -5825,16 +5853,16 @@
         <v>46181.67713509259</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I70" s="5">
         <v>46184</v>
@@ -5852,13 +5880,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5868,7 +5896,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B71" s="8">
         <v>46160.652726898144</v>
@@ -5880,16 +5908,16 @@
         <v>46196.198199756946</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I71" s="8">
         <v>46189</v>
@@ -5907,13 +5935,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q71" s="8">
         <v>46189</v>
@@ -5922,7 +5950,7 @@
         <v>46195</v>
       </c>
       <c r="S71" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T71" s="9">
         <v>1</v>
@@ -5933,7 +5961,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B72" s="5">
         <v>46160.65273052083</v>
@@ -5945,16 +5973,16 @@
         <v>46181.67719854167</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I72" s="5">
         <v>46189</v>
@@ -5972,13 +6000,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5988,7 +6016,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B73" s="8">
         <v>46160.652741620375</v>
@@ -6000,16 +6028,16 @@
         <v>46181.67721436343</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I73" s="8">
         <v>46189</v>
@@ -6027,13 +6055,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6043,7 +6071,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B74" s="5">
         <v>46160.65274630787</v>
@@ -6055,16 +6083,16 @@
         <v>46197.19306369213</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I74" s="5">
         <v>46196</v>
@@ -6082,13 +6110,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="5">
         <v>46196</v>
@@ -6097,7 +6125,7 @@
         <v>46196</v>
       </c>
       <c r="S74" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T74" s="6">
         <v>1</v>
@@ -6108,7 +6136,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B75" s="8">
         <v>46160.65275005787</v>
@@ -6120,16 +6148,16 @@
         <v>46181.67726512731</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I75" s="8">
         <v>46196</v>
@@ -6147,13 +6175,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6163,7 +6191,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B76" s="5">
         <v>46160.65275548611</v>
@@ -6175,16 +6203,16 @@
         <v>46181.677274664355</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I76" s="5">
         <v>46196</v>
@@ -6202,13 +6230,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6218,7 +6246,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B77" s="8">
         <v>46160.652760625</v>
@@ -6230,7 +6258,7 @@
         <v>46181.67751854166</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6254,7 +6282,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6267,7 +6295,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B78" s="5">
         <v>46160.65276340277</v>
@@ -6279,16 +6307,16 @@
         <v>46192.20460657407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I78" s="5">
         <v>46160</v>
@@ -6306,13 +6334,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q78" s="5">
         <v>46160</v>
@@ -6321,7 +6349,7 @@
         <v>46191</v>
       </c>
       <c r="S78" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -6332,7 +6360,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B79" s="8">
         <v>46160.652768831016</v>
@@ -6344,16 +6372,16 @@
         <v>46181.677345034725</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I79" s="8">
         <v>46141</v>
@@ -6371,13 +6399,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q79" s="8">
         <v>46141</v>
@@ -6397,7 +6425,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B80" s="5">
         <v>46160.652774409726</v>
@@ -6409,16 +6437,16 @@
         <v>46181.67735619213</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6436,13 +6464,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6451,7 +6479,7 @@
         <v>46174</v>
       </c>
       <c r="S80" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T80" s="6">
         <v>1</v>
@@ -6462,7 +6490,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B81" s="8">
         <v>46160.652779745375</v>
@@ -6474,16 +6502,16 @@
         <v>46207.188708125</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I81" s="8">
         <v>46206</v>
@@ -6501,13 +6529,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q81" s="8">
         <v>46206</v>
@@ -6516,7 +6544,7 @@
         <v>46206</v>
       </c>
       <c r="S81" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T81" s="9">
         <v>1</v>
@@ -6527,7 +6555,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B82" s="5">
         <v>46160.657067569446</v>
@@ -6537,16 +6565,16 @@
         <v>46198.18861751157</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I82" s="5">
         <v>46197</v>
@@ -6564,13 +6592,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q82" s="5">
         <v>46197</v>
@@ -6579,18 +6607,18 @@
         <v>46197</v>
       </c>
       <c r="S82" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T82" s="6">
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B83" s="8">
         <v>46160.65278418981</v>
@@ -6602,7 +6630,7 @@
         <v>46197.49724974537</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>25</v>
@@ -6626,7 +6654,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>26</v>
@@ -6636,12 +6664,12 @@
       <c r="S83" s="9"/>
       <c r="T83" s="9"/>
       <c r="U83" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B84" s="5">
         <v>46160.65278701389</v>
@@ -6653,16 +6681,16 @@
         <v>46204.17292415509</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I84" s="5">
         <v>46197</v>
@@ -6680,13 +6708,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="5">
         <v>46197</v>
@@ -6695,7 +6723,7 @@
         <v>46203</v>
       </c>
       <c r="S84" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T84" s="6">
         <v>1</v>
@@ -6706,7 +6734,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B85" s="8">
         <v>46160.65279357639</v>
@@ -6718,16 +6746,16 @@
         <v>46181.67767618055</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6745,10 +6773,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6761,7 +6789,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B86" s="5">
         <v>46160.65279733796</v>
@@ -6773,16 +6801,16 @@
         <v>46181.677689247685</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I86" s="5">
         <v>46197</v>
@@ -6800,10 +6828,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6816,7 +6844,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="8">
         <v>46160.65280108796</v>
@@ -6828,16 +6856,16 @@
         <v>46205.18242020834</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I87" s="8">
         <v>46204</v>
@@ -6855,13 +6883,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -6870,7 +6898,7 @@
         <v>46204</v>
       </c>
       <c r="S87" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -6881,7 +6909,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46160.65280498842</v>
@@ -6893,16 +6921,16 @@
         <v>46181.67774287037</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I88" s="5">
         <v>46204</v>
@@ -6920,13 +6948,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6936,7 +6964,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B89" s="8">
         <v>46160.65281013889</v>
@@ -6948,16 +6976,16 @@
         <v>46181.67775488426</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I89" s="8">
         <v>46204</v>
@@ -6975,13 +7003,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6991,7 +7019,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46160.65281503472</v>
@@ -7003,16 +7031,16 @@
         <v>46206.17392120371</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I90" s="5">
         <v>46205</v>
@@ -7030,13 +7058,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q90" s="5">
         <v>46205</v>
@@ -7045,7 +7073,7 @@
         <v>46205</v>
       </c>
       <c r="S90" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T90" s="6">
         <v>1</v>
@@ -7056,7 +7084,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B91" s="8">
         <v>46160.65281883102</v>
@@ -7068,16 +7096,16 @@
         <v>46181.677797627315</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="8">
@@ -7093,13 +7121,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7109,7 +7137,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B92" s="5">
         <v>46160.65287608796</v>
@@ -7121,16 +7149,16 @@
         <v>46181.67780725694</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -7146,13 +7174,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7162,7 +7190,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B93" s="8">
         <v>46160.65288447917</v>
@@ -7174,16 +7202,16 @@
         <v>46207.18870825232</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I93" s="8">
         <v>46206</v>
@@ -7201,13 +7229,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q93" s="8">
         <v>46206</v>
@@ -7216,7 +7244,7 @@
         <v>46206</v>
       </c>
       <c r="S93" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T93" s="9">
         <v>1</v>
@@ -7227,7 +7255,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B94" s="5">
         <v>46160.65288969908</v>
@@ -7239,16 +7267,16 @@
         <v>46181.67784412037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I94" s="5">
         <v>46206</v>
@@ -7266,13 +7294,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7282,7 +7310,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B95" s="8">
         <v>46160.6528953588</v>
@@ -7294,16 +7322,16 @@
         <v>46181.677850625</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I95" s="8">
         <v>46206</v>
@@ -7321,13 +7349,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7337,7 +7365,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B96" s="5">
         <v>46160.652900706016</v>
@@ -7349,16 +7377,16 @@
         <v>46210.194492256946</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I96" s="5">
         <v>46209</v>
@@ -7376,13 +7404,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q96" s="5">
         <v>46209</v>
@@ -7391,7 +7419,7 @@
         <v>46209</v>
       </c>
       <c r="S96" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T96" s="6">
         <v>1</v>
@@ -7402,7 +7430,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B97" s="8">
         <v>46160.65290569444</v>
@@ -7414,16 +7442,16 @@
         <v>46181.67789438658</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I97" s="8">
         <v>46209</v>
@@ -7441,13 +7469,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7457,7 +7485,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B98" s="5">
         <v>46160.652911157405</v>
@@ -7469,16 +7497,16 @@
         <v>46181.67790501157</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I98" s="5">
         <v>46209</v>
@@ -7496,13 +7524,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7512,7 +7540,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B99" s="8">
         <v>46160.65291657408</v>
@@ -7524,16 +7552,16 @@
         <v>46212.190271898144</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I99" s="8">
         <v>46211</v>
@@ -7551,13 +7579,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q99" s="8">
         <v>46211</v>
@@ -7566,18 +7594,18 @@
         <v>46211</v>
       </c>
       <c r="S99" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T99" s="9">
         <v>1</v>
       </c>
       <c r="U99" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B100" s="5">
         <v>46160.652921562505</v>
@@ -7589,16 +7617,16 @@
         <v>46198.56608928241</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7614,13 +7642,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7630,7 +7658,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B101" s="8">
         <v>46160.65292620371</v>
@@ -7642,16 +7670,16 @@
         <v>46198.566110405096</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="8">
@@ -7667,13 +7695,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7683,7 +7711,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B102" s="5">
         <v>46160.65293084491</v>
@@ -7693,7 +7721,7 @@
         <v>46197.49766417824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7717,7 +7745,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7730,7 +7758,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B103" s="8">
         <v>46160.65293431713</v>
@@ -7740,16 +7768,16 @@
         <v>46213.179386909724</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I103" s="8">
         <v>46212</v>
@@ -7767,13 +7795,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q103" s="8">
         <v>46212</v>
@@ -7782,7 +7810,7 @@
         <v>46212</v>
       </c>
       <c r="S103" s="11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="T103" s="9">
         <v>1</v>
@@ -7793,7 +7821,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B104" s="5">
         <v>46160.65293966435</v>
@@ -7805,16 +7833,16 @@
         <v>46204.80222355324</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I104" s="5">
         <v>46212</v>
@@ -7832,13 +7860,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7848,7 +7876,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B105" s="8">
         <v>46160.652944201385</v>
@@ -7860,16 +7888,16 @@
         <v>46204.80248778935</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I105" s="8">
         <v>46212</v>
@@ -7881,19 +7909,19 @@
         <v>26</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7903,7 +7931,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B106" s="5">
         <v>46160.80816486111</v>
@@ -7913,16 +7941,16 @@
         <v>46212.16850269676</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I106" s="5">
         <v>46212</v>
@@ -7940,13 +7968,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7956,7 +7984,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B107" s="8">
         <v>46160.80854525463</v>
@@ -7966,16 +7994,16 @@
         <v>46212.168504710644</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I107" s="8">
         <v>46212</v>
@@ -7993,13 +8021,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8009,7 +8037,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B108" s="5">
         <v>46160.65294850695</v>
@@ -8021,16 +8049,16 @@
         <v>46206.181434004626</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I108" s="5">
         <v>46213</v>
@@ -8048,13 +8076,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q108" s="5">
         <v>46213</v>
@@ -8063,18 +8091,18 @@
         <v>46213</v>
       </c>
       <c r="S108" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="T108" s="6">
         <v>1</v>
       </c>
       <c r="U108" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B109" s="8">
         <v>46160.652952592594</v>
@@ -8086,16 +8114,16 @@
         <v>46204.80222711805</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I109" s="8">
         <v>46213</v>
@@ -8113,13 +8141,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8129,7 +8157,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B110" s="5">
         <v>46160.65295699074</v>
@@ -8141,16 +8169,16 @@
         <v>46204.80249248842</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I110" s="5">
         <v>46213</v>
@@ -8168,13 +8196,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8184,7 +8212,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B111" s="8">
         <v>46160.809122164355</v>
@@ -8194,16 +8222,16 @@
         <v>46213.16936128472</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I111" s="8">
         <v>46213</v>
@@ -8221,13 +8249,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8237,7 +8265,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B112" s="5">
         <v>46160.809137627315</v>
@@ -8247,16 +8275,16 @@
         <v>46213.16936325232</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I112" s="5">
         <v>46213</v>
@@ -8274,13 +8302,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8290,7 +8318,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B113" s="8">
         <v>46160.652961203705</v>
@@ -8300,16 +8328,16 @@
         <v>46209.199074965276</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I113" s="8">
         <v>46216</v>
@@ -8327,13 +8355,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q113" s="8">
         <v>46216</v>
@@ -8342,7 +8370,7 @@
         <v>46216</v>
       </c>
       <c r="S113" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>
@@ -8353,7 +8381,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B114" s="5">
         <v>46160.65296532407</v>
@@ -8363,16 +8391,16 @@
         <v>46197.49737577546</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8388,13 +8416,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8404,7 +8432,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B115" s="8">
         <v>46160.65297267361</v>
@@ -8414,16 +8442,16 @@
         <v>46197.49753788194</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="8">
@@ -8439,13 +8467,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8455,7 +8483,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B116" s="5">
         <v>46160.81088733797</v>
@@ -8465,16 +8493,16 @@
         <v>46197.49775597222</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8490,13 +8518,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8506,7 +8534,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B117" s="8">
         <v>46160.81089606481</v>
@@ -8516,16 +8544,16 @@
         <v>46197.49776570602</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8541,13 +8569,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8557,7 +8585,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B118" s="5">
         <v>46160.65297846065</v>
@@ -8567,16 +8595,16 @@
         <v>46210.19434488426</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I118" s="5">
         <v>46217</v>
@@ -8594,13 +8622,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q118" s="5">
         <v>46217</v>
@@ -8609,18 +8637,18 @@
         <v>46217</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
       </c>
       <c r="U118" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B119" s="8">
         <v>46160.652983935186</v>
@@ -8630,16 +8658,16 @@
         <v>46194.054542048616</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I119" s="8">
         <v>46217</v>
@@ -8657,13 +8685,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8673,7 +8701,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B120" s="5">
         <v>46160.65298813657</v>
@@ -8683,16 +8711,16 @@
         <v>46194.056669247686</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I120" s="5">
         <v>46217</v>
@@ -8710,13 +8738,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8726,7 +8754,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B121" s="8">
         <v>46160.81215837963</v>
@@ -8736,16 +8764,16 @@
         <v>46194.05454575231</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I121" s="8">
         <v>46217</v>
@@ -8763,13 +8791,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8779,7 +8807,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B122" s="5">
         <v>46160.81220768519</v>
@@ -8789,16 +8817,16 @@
         <v>46194.05454428241</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I122" s="5">
         <v>46217</v>
@@ -8816,13 +8844,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8832,7 +8860,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B123" s="8">
         <v>46160.65302554399</v>
@@ -8842,7 +8870,7 @@
         <v>46160.8192895949</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>25</v>
@@ -8866,7 +8894,7 @@
         <v>26</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>26</v>
@@ -8879,7 +8907,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B124" s="5">
         <v>46160.65302895833</v>
@@ -8889,16 +8917,16 @@
         <v>46160.819199722224</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I124" s="5">
         <v>46218</v>
@@ -8916,13 +8944,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q124" s="5">
         <v>46218</v>
@@ -8937,12 +8965,12 @@
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B125" s="8">
         <v>46160.65303386574</v>
@@ -8952,7 +8980,7 @@
         <v>46199.75068079861</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8979,13 +9007,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q125" s="8">
         <v>46218</v>
@@ -9000,12 +9028,12 @@
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B126" s="5">
         <v>46160.65808951389</v>
@@ -9015,7 +9043,7 @@
         <v>46160.819809513894</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>25</v>
@@ -9039,7 +9067,7 @@
         <v>26</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -9053,12 +9081,12 @@
         <v>0</v>
       </c>
       <c r="U126" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B127" s="8">
         <v>46160.66095159722</v>
@@ -9068,16 +9096,16 @@
         <v>46160.81972457176</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I127" s="8">
         <v>46218</v>
@@ -9095,13 +9123,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q127" s="8">
         <v>46218</v>
@@ -9116,12 +9144,12 @@
         <v>0</v>
       </c>
       <c r="U127" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B128" s="5">
         <v>46160.66107538194</v>
@@ -9131,16 +9159,16 @@
         <v>46160.8199466088</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I128" s="5">
         <v>46227</v>
@@ -9158,13 +9186,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q128" s="5">
         <v>46227</v>
@@ -9179,7 +9207,7 @@
         <v>0</v>
       </c>
       <c r="U128" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -1102,37 +1102,37 @@
     <t>OT 4314- VDF VLT  FC 102,OT 4314 - VDF VLT  FC 102,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
   </si>
   <si>
+    <t>1214909311722274</t>
+  </si>
+  <si>
+    <t>Embalaje,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909463204974</t>
+  </si>
+  <si>
+    <t>1214889077215251</t>
+  </si>
+  <si>
+    <t>Embalaje,OT 4314 - VDF VLT  FC 102</t>
+  </si>
+  <si>
+    <t>1214889077215252</t>
+  </si>
+  <si>
+    <t>OT 4314- VDF VLT  FC 102</t>
+  </si>
+  <si>
+    <t>1214909463204989</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
+    <t>OT 4314 - VDF VLT  FC 102,OT 4314 - VDF VLT  FC 102,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214909311722274</t>
-  </si>
-  <si>
-    <t>Embalaje,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909463204974</t>
-  </si>
-  <si>
-    <t>1214889077215251</t>
-  </si>
-  <si>
-    <t>Embalaje,OT 4314 - VDF VLT  FC 102</t>
-  </si>
-  <si>
-    <t>1214889077215252</t>
-  </si>
-  <si>
-    <t>OT 4314- VDF VLT  FC 102</t>
-  </si>
-  <si>
-    <t>1214909463204989</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
-  </si>
-  <si>
-    <t>OT 4314 - VDF VLT  FC 102,OT 4314 - VDF VLT  FC 102,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
   </si>
   <si>
     <t>1214909595482433</t>
@@ -8046,7 +8046,7 @@
         <v>46197.49765626158</v>
       </c>
       <c r="D108" s="5">
-        <v>46206.181434004626</v>
+        <v>46214.19955962963</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>340</v>
@@ -8090,8 +8090,8 @@
       <c r="R108" s="5">
         <v>46213</v>
       </c>
-      <c r="S108" s="12" t="s">
-        <v>342</v>
+      <c r="S108" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="T108" s="6">
         <v>1</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B109" s="8">
         <v>46160.652952592594</v>
@@ -8147,7 +8147,7 @@
         <v>217</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8157,7 +8157,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B110" s="5">
         <v>46160.65295699074</v>
@@ -8202,7 +8202,7 @@
         <v>217</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8212,7 +8212,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B111" s="8">
         <v>46160.809122164355</v>
@@ -8255,7 +8255,7 @@
         <v>335</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8265,7 +8265,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B112" s="5">
         <v>46160.809137627315</v>
@@ -8275,7 +8275,7 @@
         <v>46213.16936325232</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8308,7 +8308,7 @@
         <v>335</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8318,7 +8318,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B113" s="8">
         <v>46160.652961203705</v>
@@ -8328,7 +8328,7 @@
         <v>46209.199074965276</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8358,7 +8358,7 @@
         <v>322</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>322</v>
@@ -8370,7 +8370,7 @@
         <v>46216</v>
       </c>
       <c r="S113" s="12" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>
@@ -8416,7 +8416,7 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>217</v>
@@ -8467,7 +8467,7 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>217</v>
@@ -8518,7 +8518,7 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>335</v>
@@ -8569,10 +8569,10 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="P117" s="9" t="s">
         <v>358</v>
@@ -8625,7 +8625,7 @@
         <v>322</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="P118" s="6" t="s">
         <v>362</v>
@@ -8637,7 +8637,7 @@
         <v>46217</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -8325,7 +8325,7 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46209.199074965276</v>
+        <v>46216.168956863425</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>350</v>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46197.49737577546</v>
+        <v>46216.168960752315</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>217</v>
@@ -8439,7 +8439,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46197.49753788194</v>
+        <v>46216.16895939814</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>217</v>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46197.49775597222</v>
+        <v>46216.16896737269</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>335</v>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46197.49776570602</v>
+        <v>46216.168969085644</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>335</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -1132,37 +1132,37 @@
     <t>OT 4314 - VDF VLT  FC 102,OT 4314 - VDF VLT  FC 102,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2</t>
   </si>
   <si>
+    <t>1214909595482433</t>
+  </si>
+  <si>
+    <t>PACKING LIST,Planos Preliminar,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214909463222754</t>
+  </si>
+  <si>
+    <t>Planos Preliminar,PACKING LIST,OT 4313 - ZVN 1-9-45/2</t>
+  </si>
+  <si>
+    <t>1214889077215260</t>
+  </si>
+  <si>
+    <t>PACKING LIST,OT 4314 - VDF VLT  FC 102</t>
+  </si>
+  <si>
+    <t>1214889077215261</t>
+  </si>
+  <si>
+    <t>1214909463222774</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>Instalación componentes,Gestion,Logistica:,Costos</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214909595482433</t>
-  </si>
-  <si>
-    <t>PACKING LIST,Planos Preliminar,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214909463222754</t>
-  </si>
-  <si>
-    <t>Planos Preliminar,PACKING LIST,OT 4313 - ZVN 1-9-45/2</t>
-  </si>
-  <si>
-    <t>1214889077215260</t>
-  </si>
-  <si>
-    <t>PACKING LIST,OT 4314 - VDF VLT  FC 102</t>
-  </si>
-  <si>
-    <t>1214889077215261</t>
-  </si>
-  <si>
-    <t>1214909463222774</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>Instalación componentes,Gestion,Logistica:,Costos</t>
   </si>
   <si>
     <t>1214909617251339</t>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46216.168956863425</v>
+        <v>46217.178433506946</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>350</v>
@@ -8369,8 +8369,8 @@
       <c r="R113" s="8">
         <v>46216</v>
       </c>
-      <c r="S113" s="12" t="s">
-        <v>352</v>
+      <c r="S113" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>
@@ -8381,7 +8381,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B114" s="5">
         <v>46160.65296532407</v>
@@ -8422,7 +8422,7 @@
         <v>217</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8432,7 +8432,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B115" s="8">
         <v>46160.65297267361</v>
@@ -8473,7 +8473,7 @@
         <v>217</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8483,7 +8483,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B116" s="5">
         <v>46160.81088733797</v>
@@ -8524,7 +8524,7 @@
         <v>335</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8534,7 +8534,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B117" s="8">
         <v>46160.81089606481</v>
@@ -8575,7 +8575,7 @@
         <v>348</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8585,17 +8585,17 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B118" s="5">
         <v>46160.65297846065</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46210.19434488426</v>
+        <v>46217.16843122685</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8628,7 +8628,7 @@
         <v>351</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q118" s="5">
         <v>46217</v>
@@ -8637,7 +8637,7 @@
         <v>46217</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
@@ -8655,7 +8655,7 @@
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46194.054542048616</v>
+        <v>46217.16843326389</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>217</v>
@@ -8685,13 +8685,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O119" s="9" t="s">
         <v>217</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8708,7 +8708,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46194.056669247686</v>
+        <v>46217.16837645833</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>217</v>
@@ -8738,13 +8738,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>217</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46194.05454575231</v>
+        <v>46217.168417002315</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>335</v>
@@ -8791,13 +8791,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>335</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8814,7 +8814,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46194.05454428241</v>
+        <v>46217.16841864583</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>335</v>
@@ -8844,13 +8844,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>335</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8947,7 +8947,7 @@
         <v>368</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P124" s="6" t="s">
         <v>368</v>
@@ -9010,7 +9010,7 @@
         <v>368</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>368</v>
@@ -9126,7 +9126,7 @@
         <v>377</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="P127" s="9" t="s">
         <v>381</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="383">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -1160,9 +1160,6 @@
   </si>
   <si>
     <t>Instalación componentes,Gestion,Logistica:,Costos</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1214909617251339</t>
@@ -8592,7 +8589,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46217.16843122685</v>
+        <v>46218.17912671296</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>360</v>
@@ -8636,8 +8633,8 @@
       <c r="R118" s="5">
         <v>46217</v>
       </c>
-      <c r="S118" s="12" t="s">
-        <v>362</v>
+      <c r="S118" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="T118" s="6">
         <v>0</v>
@@ -8648,7 +8645,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B119" s="8">
         <v>46160.652983935186</v>
@@ -8701,7 +8698,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B120" s="5">
         <v>46160.65298813657</v>
@@ -8754,7 +8751,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B121" s="8">
         <v>46160.81215837963</v>
@@ -8807,7 +8804,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B122" s="5">
         <v>46160.81220768519</v>
@@ -8860,7 +8857,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B123" s="8">
         <v>46160.65302554399</v>
@@ -8870,7 +8867,7 @@
         <v>46160.8192895949</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>25</v>
@@ -8894,7 +8891,7 @@
         <v>26</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>26</v>
@@ -8907,7 +8904,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B124" s="5">
         <v>46160.65302895833</v>
@@ -8917,16 +8914,16 @@
         <v>46160.819199722224</v>
       </c>
       <c r="E124" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G124" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="F124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G124" s="6" t="s">
+      <c r="H124" s="6" t="s">
         <v>372</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>373</v>
       </c>
       <c r="I124" s="5">
         <v>46218</v>
@@ -8944,13 +8941,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>360</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q124" s="5">
         <v>46218</v>
@@ -8970,7 +8967,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B125" s="8">
         <v>46160.65303386574</v>
@@ -8980,7 +8977,7 @@
         <v>46199.75068079861</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9007,13 +9004,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="O125" s="9" t="s">
         <v>360</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q125" s="8">
         <v>46218</v>
@@ -9033,7 +9030,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B126" s="5">
         <v>46160.65808951389</v>
@@ -9043,7 +9040,7 @@
         <v>46160.819809513894</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>25</v>
@@ -9067,7 +9064,7 @@
         <v>26</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -9086,7 +9083,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B127" s="8">
         <v>46160.66095159722</v>
@@ -9096,7 +9093,7 @@
         <v>46160.81972457176</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9123,13 +9120,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>360</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q127" s="8">
         <v>46218</v>
@@ -9149,7 +9146,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B128" s="5">
         <v>46160.66107538194</v>
@@ -9159,7 +9156,7 @@
         <v>46160.8199466088</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9186,13 +9183,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q128" s="5">
         <v>46227</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="380">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -349,9 +349,6 @@
     <t>propuesta nucleo rodete ot 4313</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Generación OC Rodete ot 4313,Propuesta compras:</t>
   </si>
   <si>
@@ -359,12 +356,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser ot 4313</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -2832,11 +2823,9 @@
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H20" s="6"/>
       <c r="I20" s="5">
         <v>46133</v>
       </c>
@@ -2859,7 +2848,7 @@
         <v>74</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="Q20" s="5">
         <v>46133</v>
@@ -2879,7 +2868,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B21" s="8">
         <v>46160.652405636574</v>
@@ -2891,17 +2880,15 @@
         <v>46206.562373125</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>96</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H21" s="9"/>
       <c r="I21" s="8">
         <v>46162</v>
       </c>
@@ -2921,10 +2908,10 @@
         <v>81</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q21" s="8">
         <v>46162</v>
@@ -2944,7 +2931,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B22" s="5">
         <v>46160.65241059028</v>
@@ -2956,17 +2943,15 @@
         <v>46206.56247952546</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>96</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H22" s="6"/>
       <c r="I22" s="5">
         <v>46162</v>
       </c>
@@ -2986,10 +2971,10 @@
         <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -3009,7 +2994,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B23" s="8">
         <v>46160.652414490745</v>
@@ -3021,17 +3006,15 @@
         <v>46206.562588877314</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>96</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H23" s="9"/>
       <c r="I23" s="8">
         <v>46162</v>
       </c>
@@ -3051,10 +3034,10 @@
         <v>81</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q23" s="8">
         <v>46162</v>
@@ -3074,7 +3057,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B24" s="5">
         <v>46160.65241840278</v>
@@ -3086,17 +3069,15 @@
         <v>46206.56275350694</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>96</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H24" s="6"/>
       <c r="I24" s="5">
         <v>46162</v>
       </c>
@@ -3116,10 +3097,10 @@
         <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Q24" s="5">
         <v>46162</v>
@@ -3139,7 +3120,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B25" s="8">
         <v>46160.65857868055</v>
@@ -3151,7 +3132,7 @@
         <v>46167.55904253472</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -3184,7 +3165,7 @@
         <v>54</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q25" s="8">
         <v>46134</v>
@@ -3204,7 +3185,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B26" s="5">
         <v>46160.65225063657</v>
@@ -3214,7 +3195,7 @@
         <v>46181.678639652775</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -3238,7 +3219,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -3251,7 +3232,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B27" s="8">
         <v>46160.65242274306</v>
@@ -3263,16 +3244,16 @@
         <v>46181.675709143514</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I27" s="8">
         <v>46135</v>
@@ -3290,13 +3271,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q27" s="8">
         <v>46135</v>
@@ -3316,7 +3297,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B28" s="5">
         <v>46160.65242719908</v>
@@ -3328,16 +3309,16 @@
         <v>46181.67563449074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I28" s="5">
         <v>46135</v>
@@ -3355,13 +3336,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3377,7 +3358,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B29" s="8">
         <v>46160.65243181713</v>
@@ -3389,16 +3370,16 @@
         <v>46181.67567790509</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I29" s="8">
         <v>46139</v>
@@ -3416,13 +3397,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3438,7 +3419,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B30" s="5">
         <v>46160.65243667824</v>
@@ -3450,16 +3431,16 @@
         <v>46181.67562327546</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I30" s="5">
         <v>46135</v>
@@ -3477,13 +3458,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q30" s="5">
         <v>46135</v>
@@ -3503,7 +3484,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B31" s="8">
         <v>46160.65244107639</v>
@@ -3515,16 +3496,16 @@
         <v>46181.67555395833</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I31" s="8">
         <v>46135</v>
@@ -3542,13 +3523,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3564,7 +3545,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B32" s="5">
         <v>46160.65244578704</v>
@@ -3576,16 +3557,16 @@
         <v>46181.67559840278</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I32" s="5">
         <v>46139</v>
@@ -3603,13 +3584,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="O32" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="O32" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="P32" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3625,7 +3606,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B33" s="8">
         <v>46160.652450625</v>
@@ -3637,16 +3618,16 @@
         <v>46181.67549369213</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I33" s="8">
         <v>46133</v>
@@ -3664,13 +3645,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q33" s="8">
         <v>46133</v>
@@ -3690,7 +3671,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B34" s="5">
         <v>46160.65245552083</v>
@@ -3702,16 +3683,16 @@
         <v>46181.67541268519</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I34" s="5">
         <v>46133</v>
@@ -3729,13 +3710,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3751,7 +3732,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B35" s="8">
         <v>46160.65246048611</v>
@@ -3763,16 +3744,16 @@
         <v>46181.67545391204</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I35" s="8">
         <v>46142</v>
@@ -3790,13 +3771,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="O35" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="O35" s="9" t="s">
-        <v>138</v>
-      </c>
       <c r="P35" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3812,7 +3793,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B36" s="5">
         <v>46160.6524655324</v>
@@ -3824,16 +3805,16 @@
         <v>46181.67546648148</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I36" s="5">
         <v>46141</v>
@@ -3851,13 +3832,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="O36" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="O36" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="P36" s="6" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3873,7 +3854,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B37" s="8">
         <v>46160.6566696875</v>
@@ -3883,16 +3864,16 @@
         <v>46197.19306372685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I37" s="8">
         <v>46136</v>
@@ -3910,10 +3891,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>26</v>
@@ -3936,7 +3917,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B38" s="5">
         <v>46160.65676351852</v>
@@ -3948,16 +3929,16 @@
         <v>46182.67674333333</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I38" s="5">
         <v>46136</v>
@@ -3975,13 +3956,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="P38" s="6" t="s">
         <v>147</v>
-      </c>
-      <c r="O38" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="P38" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3991,7 +3972,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B39" s="8">
         <v>46160.65688415509</v>
@@ -4001,16 +3982,16 @@
         <v>46196.16898914352</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="I39" s="8">
         <v>46148</v>
@@ -4028,13 +4009,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4044,7 +4025,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B40" s="5">
         <v>46160.65247015047</v>
@@ -4056,16 +4037,16 @@
         <v>46181.676244386574</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I40" s="5">
         <v>46167</v>
@@ -4083,13 +4064,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q40" s="5">
         <v>46167</v>
@@ -4109,7 +4090,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B41" s="8">
         <v>46160.65247482639</v>
@@ -4121,16 +4102,16 @@
         <v>46181.67615008102</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I41" s="8">
         <v>46167</v>
@@ -4148,13 +4129,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4170,7 +4151,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B42" s="5">
         <v>46160.65247959491</v>
@@ -4182,16 +4163,16 @@
         <v>46181.67622016204</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I42" s="5">
         <v>46169</v>
@@ -4209,13 +4190,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4231,7 +4212,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B43" s="8">
         <v>46160.65254070602</v>
@@ -4243,16 +4224,16 @@
         <v>46181.67636662037</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I43" s="8">
         <v>46167</v>
@@ -4270,10 +4251,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4296,7 +4277,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B44" s="5">
         <v>46160.65254572917</v>
@@ -4308,16 +4289,16 @@
         <v>46181.67630162037</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I44" s="5">
         <v>46167</v>
@@ -4335,13 +4316,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="P44" s="6" t="s">
         <v>166</v>
-      </c>
-      <c r="O44" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="P44" s="6" t="s">
-        <v>169</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4351,7 +4332,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B45" s="8">
         <v>46160.652551377316</v>
@@ -4363,16 +4344,16 @@
         <v>46181.67634090278</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I45" s="8">
         <v>46169</v>
@@ -4390,13 +4371,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4406,7 +4387,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B46" s="5">
         <v>46160.652557152775</v>
@@ -4418,16 +4399,16 @@
         <v>46206.17392120371</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I46" s="5">
         <v>46167</v>
@@ -4445,10 +4426,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4471,7 +4452,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B47" s="8">
         <v>46160.65256162037</v>
@@ -4483,16 +4464,16 @@
         <v>46181.67638900463</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4510,13 +4491,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4526,7 +4507,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B48" s="5">
         <v>46160.6525734375</v>
@@ -4538,16 +4519,16 @@
         <v>46181.67642934028</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="I48" s="5">
         <v>46176</v>
@@ -4565,13 +4546,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4581,7 +4562,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B49" s="8">
         <v>46160.652579236106</v>
@@ -4593,16 +4574,16 @@
         <v>46181.676467303245</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I49" s="8">
         <v>46205</v>
@@ -4620,10 +4601,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4636,7 +4617,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B50" s="5">
         <v>46160.65258304398</v>
@@ -4648,16 +4629,16 @@
         <v>46181.67657885417</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I50" s="5">
         <v>46167</v>
@@ -4675,10 +4656,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4701,7 +4682,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B51" s="8">
         <v>46160.6525875463</v>
@@ -4713,16 +4694,16 @@
         <v>46181.67651314815</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I51" s="8">
         <v>46167</v>
@@ -4740,13 +4721,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="O51" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="P51" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="O51" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="P51" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4756,7 +4737,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B52" s="5">
         <v>46160.652593067134</v>
@@ -4768,16 +4749,16 @@
         <v>46181.676553680554</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="I52" s="5">
         <v>46169</v>
@@ -4795,13 +4776,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4811,7 +4792,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B53" s="8">
         <v>46160.65225516204</v>
@@ -4823,7 +4804,7 @@
         <v>46181.67858451389</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4847,7 +4828,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4860,7 +4841,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B54" s="5">
         <v>46160.65259921296</v>
@@ -4872,16 +4853,16 @@
         <v>46197.712640196754</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I54" s="5">
         <v>46140</v>
@@ -4899,13 +4880,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="Q54" s="5">
         <v>46140</v>
@@ -4925,7 +4906,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B55" s="8">
         <v>46160.652606006945</v>
@@ -4937,16 +4918,16 @@
         <v>46197.71267317129</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="I55" s="8">
         <v>46153</v>
@@ -4964,13 +4945,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Q55" s="8">
         <v>46153</v>
@@ -4990,7 +4971,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B56" s="5">
         <v>46160.65261409723</v>
@@ -5002,16 +4983,16 @@
         <v>46181.67578048611</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I56" s="5">
         <v>46160</v>
@@ -5029,13 +5010,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="Q56" s="5">
         <v>46160</v>
@@ -5055,7 +5036,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B57" s="8">
         <v>46160.652630983794</v>
@@ -5067,16 +5048,16 @@
         <v>46211.169411759256</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I57" s="8">
         <v>46210</v>
@@ -5094,10 +5075,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -5120,7 +5101,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B58" s="5">
         <v>46160.65263532408</v>
@@ -5132,16 +5113,16 @@
         <v>46198.566085625</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I58" s="5">
         <v>46210</v>
@@ -5159,13 +5140,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5175,7 +5156,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B59" s="8">
         <v>46160.65264069445</v>
@@ -5187,16 +5168,16 @@
         <v>46198.5661015625</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I59" s="8">
         <v>46210</v>
@@ -5214,13 +5195,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="O59" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="P59" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="P59" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5230,7 +5211,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B60" s="5">
         <v>46160.652676921294</v>
@@ -5242,7 +5223,7 @@
         <v>46181.67816971065</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5266,7 +5247,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5279,7 +5260,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B61" s="8">
         <v>46160.65268083333</v>
@@ -5291,16 +5272,16 @@
         <v>46182.19861893519</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I61" s="8">
         <v>46178</v>
@@ -5318,13 +5299,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="Q61" s="8">
         <v>46178</v>
@@ -5344,7 +5325,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B62" s="5">
         <v>46160.652685810186</v>
@@ -5356,16 +5337,16 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I62" s="5">
         <v>46182</v>
@@ -5383,13 +5364,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q62" s="5">
         <v>46182</v>
@@ -5409,7 +5390,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B63" s="8">
         <v>46160.65269097222</v>
@@ -5421,16 +5402,16 @@
         <v>46181.6766224537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I63" s="8">
         <v>46178</v>
@@ -5448,13 +5429,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="Q63" s="8">
         <v>46147</v>
@@ -5474,7 +5455,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B64" s="5">
         <v>46160.65269633102</v>
@@ -5486,16 +5467,16 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I64" s="5">
         <v>46182</v>
@@ -5513,13 +5494,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q64" s="5">
         <v>46182</v>
@@ -5539,7 +5520,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B65" s="8">
         <v>46160.65269980324</v>
@@ -5551,16 +5532,16 @@
         <v>46181.67666866898</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I65" s="8">
         <v>46178</v>
@@ -5578,13 +5559,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q65" s="8">
         <v>46147</v>
@@ -5604,7 +5585,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B66" s="5">
         <v>46160.652703935186</v>
@@ -5616,16 +5597,16 @@
         <v>46184.172129004626</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I66" s="5">
         <v>46182</v>
@@ -5643,13 +5624,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q66" s="5">
         <v>46182</v>
@@ -5669,7 +5650,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B67" s="8">
         <v>46160.65270767361</v>
@@ -5681,7 +5662,7 @@
         <v>46181.6781084838</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5705,7 +5686,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5718,7 +5699,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B68" s="5">
         <v>46160.65271061343</v>
@@ -5730,16 +5711,16 @@
         <v>46189.195743599535</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I68" s="5">
         <v>46184</v>
@@ -5757,13 +5738,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Q68" s="5">
         <v>46184</v>
@@ -5783,7 +5764,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B69" s="8">
         <v>46160.65271650463</v>
@@ -5795,16 +5776,16 @@
         <v>46181.67713434028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I69" s="8">
         <v>46184</v>
@@ -5822,13 +5803,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5838,7 +5819,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B70" s="5">
         <v>46160.65272224537</v>
@@ -5850,16 +5831,16 @@
         <v>46181.67713509259</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I70" s="5">
         <v>46184</v>
@@ -5877,13 +5858,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5893,7 +5874,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B71" s="8">
         <v>46160.652726898144</v>
@@ -5905,16 +5886,16 @@
         <v>46196.198199756946</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I71" s="8">
         <v>46189</v>
@@ -5932,13 +5913,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Q71" s="8">
         <v>46189</v>
@@ -5958,7 +5939,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B72" s="5">
         <v>46160.65273052083</v>
@@ -5970,16 +5951,16 @@
         <v>46181.67719854167</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I72" s="5">
         <v>46189</v>
@@ -5997,13 +5978,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="O72" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="O72" s="6" t="s">
-        <v>260</v>
-      </c>
       <c r="P72" s="6" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6013,7 +5994,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B73" s="8">
         <v>46160.652741620375</v>
@@ -6025,16 +6006,16 @@
         <v>46181.67721436343</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I73" s="8">
         <v>46189</v>
@@ -6052,13 +6033,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="O73" s="9" t="s">
         <v>257</v>
       </c>
-      <c r="O73" s="9" t="s">
-        <v>260</v>
-      </c>
       <c r="P73" s="9" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6068,7 +6049,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B74" s="5">
         <v>46160.65274630787</v>
@@ -6080,16 +6061,16 @@
         <v>46197.19306369213</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I74" s="5">
         <v>46196</v>
@@ -6107,13 +6088,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="Q74" s="5">
         <v>46196</v>
@@ -6133,7 +6114,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B75" s="8">
         <v>46160.65275005787</v>
@@ -6145,16 +6126,16 @@
         <v>46181.67726512731</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I75" s="8">
         <v>46196</v>
@@ -6172,13 +6153,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6188,7 +6169,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B76" s="5">
         <v>46160.65275548611</v>
@@ -6200,16 +6181,16 @@
         <v>46181.677274664355</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I76" s="5">
         <v>46196</v>
@@ -6227,13 +6208,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6243,7 +6224,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B77" s="8">
         <v>46160.652760625</v>
@@ -6255,7 +6236,7 @@
         <v>46181.67751854166</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6279,7 +6260,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6292,7 +6273,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B78" s="5">
         <v>46160.65276340277</v>
@@ -6304,16 +6285,16 @@
         <v>46192.20460657407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I78" s="5">
         <v>46160</v>
@@ -6331,13 +6312,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q78" s="5">
         <v>46160</v>
@@ -6357,7 +6338,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B79" s="8">
         <v>46160.652768831016</v>
@@ -6369,16 +6350,16 @@
         <v>46181.677345034725</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I79" s="8">
         <v>46141</v>
@@ -6396,13 +6377,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Q79" s="8">
         <v>46141</v>
@@ -6422,7 +6403,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B80" s="5">
         <v>46160.652774409726</v>
@@ -6434,16 +6415,16 @@
         <v>46181.67735619213</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6461,13 +6442,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6487,7 +6468,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B81" s="8">
         <v>46160.652779745375</v>
@@ -6499,16 +6480,16 @@
         <v>46207.188708125</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I81" s="8">
         <v>46206</v>
@@ -6526,13 +6507,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Q81" s="8">
         <v>46206</v>
@@ -6552,7 +6533,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B82" s="5">
         <v>46160.657067569446</v>
@@ -6568,10 +6549,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I82" s="5">
         <v>46197</v>
@@ -6589,10 +6570,10 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>59</v>
@@ -6615,7 +6596,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B83" s="8">
         <v>46160.65278418981</v>
@@ -6627,7 +6608,7 @@
         <v>46197.49724974537</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>25</v>
@@ -6651,7 +6632,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>26</v>
@@ -6666,7 +6647,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B84" s="5">
         <v>46160.65278701389</v>
@@ -6678,17 +6659,15 @@
         <v>46204.17292415509</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H84" s="6"/>
       <c r="I84" s="5">
         <v>46197</v>
       </c>
@@ -6705,13 +6684,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q84" s="5">
         <v>46197</v>
@@ -6731,7 +6710,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B85" s="8">
         <v>46160.65279357639</v>
@@ -6743,17 +6722,15 @@
         <v>46181.67767618055</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H85" s="9"/>
       <c r="I85" s="8">
         <v>46197</v>
       </c>
@@ -6770,10 +6747,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="O85" s="9" t="s">
         <v>287</v>
-      </c>
-      <c r="O85" s="9" t="s">
-        <v>290</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6786,7 +6763,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B86" s="5">
         <v>46160.65279733796</v>
@@ -6798,17 +6775,15 @@
         <v>46181.677689247685</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H86" s="6"/>
       <c r="I86" s="5">
         <v>46197</v>
       </c>
@@ -6825,10 +6800,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="O86" s="6" t="s">
         <v>287</v>
-      </c>
-      <c r="O86" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6841,7 +6816,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B87" s="8">
         <v>46160.65280108796</v>
@@ -6853,17 +6828,15 @@
         <v>46205.18242020834</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H87" s="9"/>
       <c r="I87" s="8">
         <v>46204</v>
       </c>
@@ -6880,13 +6853,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -6906,7 +6879,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B88" s="5">
         <v>46160.65280498842</v>
@@ -6918,17 +6891,15 @@
         <v>46181.67774287037</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
       <c r="I88" s="5">
         <v>46204</v>
       </c>
@@ -6945,13 +6916,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="P88" s="6" t="s">
         <v>293</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="P88" s="6" t="s">
-        <v>296</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6961,7 +6932,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B89" s="8">
         <v>46160.65281013889</v>
@@ -6973,17 +6944,15 @@
         <v>46181.67775488426</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H89" s="9"/>
       <c r="I89" s="8">
         <v>46204</v>
       </c>
@@ -7000,13 +6969,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="O89" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="P89" s="9" t="s">
         <v>293</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>295</v>
-      </c>
-      <c r="P89" s="9" t="s">
-        <v>296</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7016,7 +6985,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B90" s="5">
         <v>46160.65281503472</v>
@@ -7028,17 +6997,15 @@
         <v>46206.17392120371</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H90" s="6"/>
       <c r="I90" s="5">
         <v>46205</v>
       </c>
@@ -7055,13 +7022,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q90" s="5">
         <v>46205</v>
@@ -7081,7 +7048,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B91" s="8">
         <v>46160.65281883102</v>
@@ -7093,17 +7060,15 @@
         <v>46181.677797627315</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H91" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H91" s="9"/>
       <c r="I91" s="9"/>
       <c r="J91" s="8">
         <v>46205</v>
@@ -7118,13 +7083,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7134,7 +7099,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B92" s="5">
         <v>46160.65287608796</v>
@@ -7146,17 +7111,15 @@
         <v>46181.67780725694</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H92" s="6"/>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
         <v>46205</v>
@@ -7171,13 +7134,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7187,7 +7150,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B93" s="8">
         <v>46160.65288447917</v>
@@ -7199,17 +7162,15 @@
         <v>46207.18870825232</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H93" s="9"/>
       <c r="I93" s="8">
         <v>46206</v>
       </c>
@@ -7226,13 +7187,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q93" s="8">
         <v>46206</v>
@@ -7252,7 +7213,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B94" s="5">
         <v>46160.65288969908</v>
@@ -7264,17 +7225,15 @@
         <v>46181.67784412037</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H94" s="6"/>
       <c r="I94" s="5">
         <v>46206</v>
       </c>
@@ -7291,13 +7250,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="P94" s="6" t="s">
         <v>304</v>
-      </c>
-      <c r="O94" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="P94" s="6" t="s">
-        <v>307</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7307,7 +7266,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="B95" s="8">
         <v>46160.6528953588</v>
@@ -7319,17 +7278,15 @@
         <v>46181.677850625</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H95" s="9"/>
       <c r="I95" s="8">
         <v>46206</v>
       </c>
@@ -7346,13 +7303,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="O95" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>304</v>
-      </c>
-      <c r="O95" s="9" t="s">
-        <v>306</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>307</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7362,7 +7319,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B96" s="5">
         <v>46160.652900706016</v>
@@ -7374,17 +7331,15 @@
         <v>46210.194492256946</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H96" s="6"/>
       <c r="I96" s="5">
         <v>46209</v>
       </c>
@@ -7401,13 +7356,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Q96" s="5">
         <v>46209</v>
@@ -7427,7 +7382,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B97" s="8">
         <v>46160.65290569444</v>
@@ -7439,17 +7394,15 @@
         <v>46181.67789438658</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H97" s="9"/>
       <c r="I97" s="8">
         <v>46209</v>
       </c>
@@ -7466,13 +7419,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7482,7 +7435,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B98" s="5">
         <v>46160.652911157405</v>
@@ -7494,17 +7447,15 @@
         <v>46181.67790501157</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H98" s="6"/>
       <c r="I98" s="5">
         <v>46209</v>
       </c>
@@ -7521,13 +7472,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7537,7 +7488,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B99" s="8">
         <v>46160.65291657408</v>
@@ -7549,17 +7500,15 @@
         <v>46212.190271898144</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H99" s="9"/>
       <c r="I99" s="8">
         <v>46211</v>
       </c>
@@ -7576,13 +7525,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="Q99" s="8">
         <v>46211</v>
@@ -7602,7 +7551,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B100" s="5">
         <v>46160.652921562505</v>
@@ -7614,17 +7563,15 @@
         <v>46198.56608928241</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H100" s="6"/>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
         <v>46211</v>
@@ -7639,13 +7586,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="P100" s="6" t="s">
         <v>315</v>
-      </c>
-      <c r="O100" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>318</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7655,7 +7602,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B101" s="8">
         <v>46160.65292620371</v>
@@ -7667,17 +7614,15 @@
         <v>46198.566110405096</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H101" s="9"/>
       <c r="I101" s="9"/>
       <c r="J101" s="8">
         <v>46211</v>
@@ -7692,13 +7637,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7708,7 +7653,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B102" s="5">
         <v>46160.65293084491</v>
@@ -7718,7 +7663,7 @@
         <v>46197.49766417824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7742,7 +7687,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7755,7 +7700,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B103" s="8">
         <v>46160.65293431713</v>
@@ -7765,16 +7710,16 @@
         <v>46213.179386909724</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I103" s="8">
         <v>46212</v>
@@ -7792,13 +7737,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q103" s="8">
         <v>46212</v>
@@ -7818,7 +7763,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B104" s="5">
         <v>46160.65293966435</v>
@@ -7830,16 +7775,16 @@
         <v>46204.80222355324</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I104" s="5">
         <v>46212</v>
@@ -7857,13 +7802,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7873,7 +7818,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B105" s="8">
         <v>46160.652944201385</v>
@@ -7885,16 +7830,16 @@
         <v>46204.80248778935</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I105" s="8">
         <v>46212</v>
@@ -7906,19 +7851,19 @@
         <v>26</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="M105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7928,7 +7873,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B106" s="5">
         <v>46160.80816486111</v>
@@ -7938,16 +7883,16 @@
         <v>46212.16850269676</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I106" s="5">
         <v>46212</v>
@@ -7965,13 +7910,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7981,7 +7926,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B107" s="8">
         <v>46160.80854525463</v>
@@ -7991,16 +7936,16 @@
         <v>46212.168504710644</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="I107" s="8">
         <v>46212</v>
@@ -8018,13 +7963,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8034,7 +7979,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B108" s="5">
         <v>46160.65294850695</v>
@@ -8046,17 +7991,15 @@
         <v>46214.19955962963</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H108" s="6"/>
       <c r="I108" s="5">
         <v>46213</v>
       </c>
@@ -8073,13 +8016,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q108" s="5">
         <v>46213</v>
@@ -8099,7 +8042,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B109" s="8">
         <v>46160.652952592594</v>
@@ -8111,17 +8054,15 @@
         <v>46204.80222711805</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H109" s="9"/>
       <c r="I109" s="8">
         <v>46213</v>
       </c>
@@ -8138,13 +8079,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
+        <v>337</v>
+      </c>
+      <c r="O109" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="P109" s="9" t="s">
         <v>340</v>
-      </c>
-      <c r="O109" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="P109" s="9" t="s">
-        <v>343</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8154,7 +8095,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B110" s="5">
         <v>46160.65295699074</v>
@@ -8166,17 +8107,15 @@
         <v>46204.80249248842</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H110" s="6"/>
       <c r="I110" s="5">
         <v>46213</v>
       </c>
@@ -8193,13 +8132,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="O110" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="P110" s="6" t="s">
         <v>340</v>
-      </c>
-      <c r="O110" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="P110" s="6" t="s">
-        <v>343</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8209,7 +8148,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B111" s="8">
         <v>46160.809122164355</v>
@@ -8219,17 +8158,15 @@
         <v>46213.16936128472</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H111" s="9"/>
       <c r="I111" s="8">
         <v>46213</v>
       </c>
@@ -8246,13 +8183,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8262,7 +8199,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B112" s="5">
         <v>46160.809137627315</v>
@@ -8272,17 +8209,15 @@
         <v>46213.16936325232</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>91</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H112" s="6"/>
       <c r="I112" s="5">
         <v>46213</v>
       </c>
@@ -8299,13 +8234,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8315,7 +8250,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B113" s="8">
         <v>46160.652961203705</v>
@@ -8325,16 +8260,16 @@
         <v>46217.178433506946</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I113" s="8">
         <v>46216</v>
@@ -8352,13 +8287,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="Q113" s="8">
         <v>46216</v>
@@ -8378,7 +8313,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B114" s="5">
         <v>46160.65296532407</v>
@@ -8388,16 +8323,16 @@
         <v>46216.168960752315</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8413,13 +8348,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="O114" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="P114" s="6" t="s">
         <v>350</v>
-      </c>
-      <c r="O114" s="6" t="s">
-        <v>217</v>
-      </c>
-      <c r="P114" s="6" t="s">
-        <v>353</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8429,7 +8364,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B115" s="8">
         <v>46160.65297267361</v>
@@ -8439,16 +8374,16 @@
         <v>46216.16895939814</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="8">
@@ -8464,13 +8399,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8480,7 +8415,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B116" s="5">
         <v>46160.81088733797</v>
@@ -8490,16 +8425,16 @@
         <v>46216.16896737269</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8515,13 +8450,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8531,7 +8466,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B117" s="8">
         <v>46160.81089606481</v>
@@ -8541,16 +8476,16 @@
         <v>46216.168969085644</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8566,13 +8501,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8582,7 +8517,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B118" s="5">
         <v>46160.65297846065</v>
@@ -8592,16 +8527,16 @@
         <v>46218.17912671296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I118" s="5">
         <v>46217</v>
@@ -8619,13 +8554,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="Q118" s="5">
         <v>46217</v>
@@ -8645,7 +8580,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B119" s="8">
         <v>46160.652983935186</v>
@@ -8655,16 +8590,16 @@
         <v>46217.16843326389</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I119" s="8">
         <v>46217</v>
@@ -8682,13 +8617,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8698,7 +8633,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B120" s="5">
         <v>46160.65298813657</v>
@@ -8708,16 +8643,16 @@
         <v>46217.16837645833</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I120" s="5">
         <v>46217</v>
@@ -8735,13 +8670,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8751,7 +8686,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B121" s="8">
         <v>46160.81215837963</v>
@@ -8761,16 +8696,16 @@
         <v>46217.168417002315</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I121" s="8">
         <v>46217</v>
@@ -8788,13 +8723,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8804,7 +8739,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B122" s="5">
         <v>46160.81220768519</v>
@@ -8814,16 +8749,16 @@
         <v>46217.16841864583</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="I122" s="5">
         <v>46217</v>
@@ -8841,13 +8776,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8857,7 +8792,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B123" s="8">
         <v>46160.65302554399</v>
@@ -8867,7 +8802,7 @@
         <v>46160.8192895949</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>25</v>
@@ -8891,7 +8826,7 @@
         <v>26</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>26</v>
@@ -8904,7 +8839,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B124" s="5">
         <v>46160.65302895833</v>
@@ -8914,16 +8849,16 @@
         <v>46160.819199722224</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I124" s="5">
         <v>46218</v>
@@ -8941,13 +8876,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Q124" s="5">
         <v>46218</v>
@@ -8967,7 +8902,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B125" s="8">
         <v>46160.65303386574</v>
@@ -8977,7 +8912,7 @@
         <v>46199.75068079861</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9004,13 +8939,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Q125" s="8">
         <v>46218</v>
@@ -9030,7 +8965,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B126" s="5">
         <v>46160.65808951389</v>
@@ -9040,7 +8975,7 @@
         <v>46160.819809513894</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>25</v>
@@ -9064,7 +8999,7 @@
         <v>26</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -9083,7 +9018,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B127" s="8">
         <v>46160.66095159722</v>
@@ -9093,7 +9028,7 @@
         <v>46160.81972457176</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9120,13 +9055,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="Q127" s="8">
         <v>46218</v>
@@ -9146,7 +9081,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B128" s="5">
         <v>46160.66107538194</v>
@@ -9156,7 +9091,7 @@
         <v>46160.8199466088</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9183,13 +9118,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="O128" s="6" t="s">
         <v>376</v>
       </c>
-      <c r="O128" s="6" t="s">
-        <v>379</v>
-      </c>
       <c r="P128" s="6" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="Q128" s="5">
         <v>46227</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="381">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -1184,6 +1184,9 @@
   </si>
   <si>
     <t>nicolas.tello@zitron.com</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1214909653811621</t>
@@ -8846,7 +8849,7 @@
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46160.819199722224</v>
+        <v>46219.173083553236</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>367</v>
@@ -8890,8 +8893,8 @@
       <c r="R124" s="5">
         <v>46226</v>
       </c>
-      <c r="S124" s="10" t="s">
-        <v>32</v>
+      <c r="S124" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="T124" s="6">
         <v>0</v>
@@ -8902,17 +8905,17 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B125" s="8">
         <v>46160.65303386574</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46199.75068079861</v>
+        <v>46219.17308424768</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8953,8 +8956,8 @@
       <c r="R125" s="8">
         <v>46226</v>
       </c>
-      <c r="S125" s="10" t="s">
-        <v>32</v>
+      <c r="S125" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
@@ -8965,7 +8968,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B126" s="5">
         <v>46160.65808951389</v>
@@ -8975,7 +8978,7 @@
         <v>46160.819809513894</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>25</v>
@@ -8999,7 +9002,7 @@
         <v>26</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -9018,17 +9021,17 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B127" s="8">
         <v>46160.66095159722</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46160.81972457176</v>
+        <v>46219.173089097225</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9055,13 +9058,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>357</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q127" s="8">
         <v>46218</v>
@@ -9069,8 +9072,8 @@
       <c r="R127" s="8">
         <v>46226</v>
       </c>
-      <c r="S127" s="10" t="s">
-        <v>32</v>
+      <c r="S127" s="12" t="s">
+        <v>370</v>
       </c>
       <c r="T127" s="9">
         <v>0</v>
@@ -9081,7 +9084,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B128" s="5">
         <v>46160.66107538194</v>
@@ -9091,7 +9094,7 @@
         <v>46160.8199466088</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9118,13 +9121,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q128" s="5">
         <v>46227</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="382">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>propuesta nucleo rodete ot 4313</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
   </si>
   <si>
     <t>Generación OC Rodete ot 4313,Propuesta compras:</t>
@@ -2817,7 +2820,7 @@
         <v>46181.612247048615</v>
       </c>
       <c r="D20" s="5">
-        <v>46181.61226466435</v>
+        <v>46223.58043689815</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>90</v>
@@ -2826,9 +2829,11 @@
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I20" s="5">
         <v>46133</v>
       </c>
@@ -2851,7 +2856,7 @@
         <v>74</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q20" s="5">
         <v>46133</v>
@@ -2871,7 +2876,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B21" s="8">
         <v>46160.652405636574</v>
@@ -2880,18 +2885,20 @@
         <v>46181.612735636576</v>
       </c>
       <c r="D21" s="8">
-        <v>46206.562373125</v>
+        <v>46223.58043296296</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H21" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I21" s="8">
         <v>46162</v>
       </c>
@@ -2911,10 +2918,10 @@
         <v>81</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q21" s="8">
         <v>46162</v>
@@ -2934,7 +2941,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B22" s="5">
         <v>46160.65241059028</v>
@@ -2943,18 +2950,20 @@
         <v>46181.67582236111</v>
       </c>
       <c r="D22" s="5">
-        <v>46206.56247952546</v>
+        <v>46223.58042920139</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H22" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I22" s="5">
         <v>46162</v>
       </c>
@@ -2974,10 +2983,10 @@
         <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -2997,7 +3006,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B23" s="8">
         <v>46160.652414490745</v>
@@ -3006,18 +3015,20 @@
         <v>46181.675860312505</v>
       </c>
       <c r="D23" s="8">
-        <v>46206.562588877314</v>
+        <v>46223.58042574074</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H23" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I23" s="8">
         <v>46162</v>
       </c>
@@ -3037,10 +3048,10 @@
         <v>81</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q23" s="8">
         <v>46162</v>
@@ -3060,7 +3071,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B24" s="5">
         <v>46160.65241840278</v>
@@ -3069,18 +3080,20 @@
         <v>46181.67587228009</v>
       </c>
       <c r="D24" s="5">
-        <v>46206.56275350694</v>
+        <v>46223.58041997685</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I24" s="5">
         <v>46162</v>
       </c>
@@ -3100,10 +3113,10 @@
         <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q24" s="5">
         <v>46162</v>
@@ -3123,7 +3136,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B25" s="8">
         <v>46160.65857868055</v>
@@ -3135,7 +3148,7 @@
         <v>46167.55904253472</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -3168,7 +3181,7 @@
         <v>54</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q25" s="8">
         <v>46134</v>
@@ -3188,7 +3201,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B26" s="5">
         <v>46160.65225063657</v>
@@ -3198,7 +3211,7 @@
         <v>46181.678639652775</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -3222,7 +3235,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -3235,7 +3248,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B27" s="8">
         <v>46160.65242274306</v>
@@ -3247,16 +3260,16 @@
         <v>46181.675709143514</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I27" s="8">
         <v>46135</v>
@@ -3274,13 +3287,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q27" s="8">
         <v>46135</v>
@@ -3300,7 +3313,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B28" s="5">
         <v>46160.65242719908</v>
@@ -3312,16 +3325,16 @@
         <v>46181.67563449074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I28" s="5">
         <v>46135</v>
@@ -3339,13 +3352,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3361,7 +3374,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B29" s="8">
         <v>46160.65243181713</v>
@@ -3373,16 +3386,16 @@
         <v>46181.67567790509</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I29" s="8">
         <v>46139</v>
@@ -3400,13 +3413,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3422,7 +3435,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B30" s="5">
         <v>46160.65243667824</v>
@@ -3434,16 +3447,16 @@
         <v>46181.67562327546</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I30" s="5">
         <v>46135</v>
@@ -3461,13 +3474,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q30" s="5">
         <v>46135</v>
@@ -3487,7 +3500,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B31" s="8">
         <v>46160.65244107639</v>
@@ -3499,16 +3512,16 @@
         <v>46181.67555395833</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I31" s="8">
         <v>46135</v>
@@ -3526,13 +3539,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3548,7 +3561,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B32" s="5">
         <v>46160.65244578704</v>
@@ -3560,16 +3573,16 @@
         <v>46181.67559840278</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I32" s="5">
         <v>46139</v>
@@ -3587,13 +3600,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3609,7 +3622,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B33" s="8">
         <v>46160.652450625</v>
@@ -3621,16 +3634,16 @@
         <v>46181.67549369213</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I33" s="8">
         <v>46133</v>
@@ -3648,13 +3661,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q33" s="8">
         <v>46133</v>
@@ -3674,7 +3687,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B34" s="5">
         <v>46160.65245552083</v>
@@ -3686,16 +3699,16 @@
         <v>46181.67541268519</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I34" s="5">
         <v>46133</v>
@@ -3713,13 +3726,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3735,7 +3748,7 @@
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B35" s="8">
         <v>46160.65246048611</v>
@@ -3747,16 +3760,16 @@
         <v>46181.67545391204</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I35" s="8">
         <v>46142</v>
@@ -3774,13 +3787,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3796,7 +3809,7 @@
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B36" s="5">
         <v>46160.6524655324</v>
@@ -3808,16 +3821,16 @@
         <v>46181.67546648148</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I36" s="5">
         <v>46141</v>
@@ -3835,13 +3848,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3857,7 +3870,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B37" s="8">
         <v>46160.6566696875</v>
@@ -3867,16 +3880,16 @@
         <v>46197.19306372685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I37" s="8">
         <v>46136</v>
@@ -3894,10 +3907,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>26</v>
@@ -3920,7 +3933,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B38" s="5">
         <v>46160.65676351852</v>
@@ -3932,16 +3945,16 @@
         <v>46182.67674333333</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I38" s="5">
         <v>46136</v>
@@ -3959,13 +3972,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3975,7 +3988,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B39" s="8">
         <v>46160.65688415509</v>
@@ -3985,16 +3998,16 @@
         <v>46196.16898914352</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I39" s="8">
         <v>46148</v>
@@ -4012,13 +4025,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4028,7 +4041,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
         <v>46160.65247015047</v>
@@ -4040,16 +4053,16 @@
         <v>46181.676244386574</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I40" s="5">
         <v>46167</v>
@@ -4067,13 +4080,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q40" s="5">
         <v>46167</v>
@@ -4093,7 +4106,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B41" s="8">
         <v>46160.65247482639</v>
@@ -4105,16 +4118,16 @@
         <v>46181.67615008102</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I41" s="8">
         <v>46167</v>
@@ -4132,13 +4145,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4154,7 +4167,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B42" s="5">
         <v>46160.65247959491</v>
@@ -4166,16 +4179,16 @@
         <v>46181.67622016204</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I42" s="5">
         <v>46169</v>
@@ -4193,13 +4206,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4215,7 +4228,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B43" s="8">
         <v>46160.65254070602</v>
@@ -4227,16 +4240,16 @@
         <v>46181.67636662037</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I43" s="8">
         <v>46167</v>
@@ -4254,10 +4267,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4280,7 +4293,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B44" s="5">
         <v>46160.65254572917</v>
@@ -4292,16 +4305,16 @@
         <v>46181.67630162037</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I44" s="5">
         <v>46167</v>
@@ -4319,13 +4332,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4335,7 +4348,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B45" s="8">
         <v>46160.652551377316</v>
@@ -4347,16 +4360,16 @@
         <v>46181.67634090278</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I45" s="8">
         <v>46169</v>
@@ -4374,13 +4387,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4390,7 +4403,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B46" s="5">
         <v>46160.652557152775</v>
@@ -4402,16 +4415,16 @@
         <v>46206.17392120371</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I46" s="5">
         <v>46167</v>
@@ -4429,10 +4442,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4455,7 +4468,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B47" s="8">
         <v>46160.65256162037</v>
@@ -4467,16 +4480,16 @@
         <v>46181.67638900463</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4494,13 +4507,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4510,7 +4523,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B48" s="5">
         <v>46160.6525734375</v>
@@ -4522,16 +4535,16 @@
         <v>46181.67642934028</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I48" s="5">
         <v>46176</v>
@@ -4549,13 +4562,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4565,7 +4578,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B49" s="8">
         <v>46160.652579236106</v>
@@ -4577,16 +4590,16 @@
         <v>46181.676467303245</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I49" s="8">
         <v>46205</v>
@@ -4604,10 +4617,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4620,7 +4633,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B50" s="5">
         <v>46160.65258304398</v>
@@ -4632,16 +4645,16 @@
         <v>46181.67657885417</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I50" s="5">
         <v>46167</v>
@@ -4659,10 +4672,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4685,7 +4698,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B51" s="8">
         <v>46160.6525875463</v>
@@ -4697,16 +4710,16 @@
         <v>46181.67651314815</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I51" s="8">
         <v>46167</v>
@@ -4724,13 +4737,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4740,7 +4753,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B52" s="5">
         <v>46160.652593067134</v>
@@ -4752,16 +4765,16 @@
         <v>46181.676553680554</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I52" s="5">
         <v>46169</v>
@@ -4779,13 +4792,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4795,7 +4808,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B53" s="8">
         <v>46160.65225516204</v>
@@ -4807,7 +4820,7 @@
         <v>46181.67858451389</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4831,7 +4844,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4844,7 +4857,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B54" s="5">
         <v>46160.65259921296</v>
@@ -4856,16 +4869,16 @@
         <v>46197.712640196754</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I54" s="5">
         <v>46140</v>
@@ -4883,13 +4896,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q54" s="5">
         <v>46140</v>
@@ -4909,7 +4922,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B55" s="8">
         <v>46160.652606006945</v>
@@ -4921,16 +4934,16 @@
         <v>46197.71267317129</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I55" s="8">
         <v>46153</v>
@@ -4948,13 +4961,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q55" s="8">
         <v>46153</v>
@@ -4974,7 +4987,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B56" s="5">
         <v>46160.65261409723</v>
@@ -4986,16 +4999,16 @@
         <v>46181.67578048611</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I56" s="5">
         <v>46160</v>
@@ -5013,13 +5026,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="Q56" s="5">
         <v>46160</v>
@@ -5039,7 +5052,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B57" s="8">
         <v>46160.652630983794</v>
@@ -5051,16 +5064,16 @@
         <v>46211.169411759256</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I57" s="8">
         <v>46210</v>
@@ -5078,10 +5091,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -5104,7 +5117,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B58" s="5">
         <v>46160.65263532408</v>
@@ -5116,16 +5129,16 @@
         <v>46198.566085625</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I58" s="5">
         <v>46210</v>
@@ -5143,13 +5156,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5159,7 +5172,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B59" s="8">
         <v>46160.65264069445</v>
@@ -5171,16 +5184,16 @@
         <v>46198.5661015625</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="I59" s="8">
         <v>46210</v>
@@ -5198,13 +5211,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5214,7 +5227,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B60" s="5">
         <v>46160.652676921294</v>
@@ -5226,7 +5239,7 @@
         <v>46181.67816971065</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5250,7 +5263,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5263,7 +5276,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B61" s="8">
         <v>46160.65268083333</v>
@@ -5275,16 +5288,16 @@
         <v>46182.19861893519</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I61" s="8">
         <v>46178</v>
@@ -5302,13 +5315,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q61" s="8">
         <v>46178</v>
@@ -5328,7 +5341,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B62" s="5">
         <v>46160.652685810186</v>
@@ -5340,16 +5353,16 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I62" s="5">
         <v>46182</v>
@@ -5367,13 +5380,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q62" s="5">
         <v>46182</v>
@@ -5393,7 +5406,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B63" s="8">
         <v>46160.65269097222</v>
@@ -5405,16 +5418,16 @@
         <v>46181.6766224537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I63" s="8">
         <v>46178</v>
@@ -5432,13 +5445,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q63" s="8">
         <v>46147</v>
@@ -5458,7 +5471,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B64" s="5">
         <v>46160.65269633102</v>
@@ -5470,16 +5483,16 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I64" s="5">
         <v>46182</v>
@@ -5497,13 +5510,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q64" s="5">
         <v>46182</v>
@@ -5523,7 +5536,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B65" s="8">
         <v>46160.65269980324</v>
@@ -5535,16 +5548,16 @@
         <v>46181.67666866898</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I65" s="8">
         <v>46178</v>
@@ -5562,13 +5575,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q65" s="8">
         <v>46147</v>
@@ -5588,7 +5601,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B66" s="5">
         <v>46160.652703935186</v>
@@ -5600,16 +5613,16 @@
         <v>46184.172129004626</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I66" s="5">
         <v>46182</v>
@@ -5627,13 +5640,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q66" s="5">
         <v>46182</v>
@@ -5653,7 +5666,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B67" s="8">
         <v>46160.65270767361</v>
@@ -5665,7 +5678,7 @@
         <v>46181.6781084838</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5689,7 +5702,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5702,7 +5715,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B68" s="5">
         <v>46160.65271061343</v>
@@ -5714,16 +5727,16 @@
         <v>46189.195743599535</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I68" s="5">
         <v>46184</v>
@@ -5741,13 +5754,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q68" s="5">
         <v>46184</v>
@@ -5767,7 +5780,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B69" s="8">
         <v>46160.65271650463</v>
@@ -5779,16 +5792,16 @@
         <v>46181.67713434028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I69" s="8">
         <v>46184</v>
@@ -5806,13 +5819,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5822,7 +5835,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B70" s="5">
         <v>46160.65272224537</v>
@@ -5834,16 +5847,16 @@
         <v>46181.67713509259</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I70" s="5">
         <v>46184</v>
@@ -5861,13 +5874,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5877,7 +5890,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B71" s="8">
         <v>46160.652726898144</v>
@@ -5889,16 +5902,16 @@
         <v>46196.198199756946</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I71" s="8">
         <v>46189</v>
@@ -5916,13 +5929,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q71" s="8">
         <v>46189</v>
@@ -5942,7 +5955,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B72" s="5">
         <v>46160.65273052083</v>
@@ -5954,16 +5967,16 @@
         <v>46181.67719854167</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I72" s="5">
         <v>46189</v>
@@ -5981,13 +5994,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -5997,7 +6010,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B73" s="8">
         <v>46160.652741620375</v>
@@ -6009,16 +6022,16 @@
         <v>46181.67721436343</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I73" s="8">
         <v>46189</v>
@@ -6036,13 +6049,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6052,7 +6065,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B74" s="5">
         <v>46160.65274630787</v>
@@ -6064,16 +6077,16 @@
         <v>46197.19306369213</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I74" s="5">
         <v>46196</v>
@@ -6091,13 +6104,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q74" s="5">
         <v>46196</v>
@@ -6117,7 +6130,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B75" s="8">
         <v>46160.65275005787</v>
@@ -6129,16 +6142,16 @@
         <v>46181.67726512731</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I75" s="8">
         <v>46196</v>
@@ -6156,13 +6169,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6172,7 +6185,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B76" s="5">
         <v>46160.65275548611</v>
@@ -6184,16 +6197,16 @@
         <v>46181.677274664355</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I76" s="5">
         <v>46196</v>
@@ -6211,13 +6224,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6227,7 +6240,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B77" s="8">
         <v>46160.652760625</v>
@@ -6239,7 +6252,7 @@
         <v>46181.67751854166</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6263,7 +6276,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6276,7 +6289,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B78" s="5">
         <v>46160.65276340277</v>
@@ -6288,16 +6301,16 @@
         <v>46192.20460657407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I78" s="5">
         <v>46160</v>
@@ -6315,13 +6328,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q78" s="5">
         <v>46160</v>
@@ -6341,7 +6354,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B79" s="8">
         <v>46160.652768831016</v>
@@ -6353,16 +6366,16 @@
         <v>46181.677345034725</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I79" s="8">
         <v>46141</v>
@@ -6380,13 +6393,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q79" s="8">
         <v>46141</v>
@@ -6406,7 +6419,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B80" s="5">
         <v>46160.652774409726</v>
@@ -6418,16 +6431,16 @@
         <v>46181.67735619213</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6445,13 +6458,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6471,7 +6484,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B81" s="8">
         <v>46160.652779745375</v>
@@ -6483,16 +6496,16 @@
         <v>46207.188708125</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I81" s="8">
         <v>46206</v>
@@ -6510,13 +6523,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q81" s="8">
         <v>46206</v>
@@ -6536,7 +6549,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B82" s="5">
         <v>46160.657067569446</v>
@@ -6552,10 +6565,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I82" s="5">
         <v>46197</v>
@@ -6573,10 +6586,10 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>59</v>
@@ -6599,7 +6612,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B83" s="8">
         <v>46160.65278418981</v>
@@ -6611,7 +6624,7 @@
         <v>46197.49724974537</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>25</v>
@@ -6635,7 +6648,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>26</v>
@@ -6650,7 +6663,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B84" s="5">
         <v>46160.65278701389</v>
@@ -6659,18 +6672,20 @@
         <v>46181.67760038194</v>
       </c>
       <c r="D84" s="5">
-        <v>46204.17292415509</v>
+        <v>46223.58112633102</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I84" s="5">
         <v>46197</v>
       </c>
@@ -6687,13 +6702,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q84" s="5">
         <v>46197</v>
@@ -6713,7 +6728,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B85" s="8">
         <v>46160.65279357639</v>
@@ -6722,18 +6737,20 @@
         <v>46181.677674942126</v>
       </c>
       <c r="D85" s="8">
-        <v>46181.67767618055</v>
+        <v>46223.58052726852</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H85" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H85" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I85" s="8">
         <v>46197</v>
       </c>
@@ -6750,10 +6767,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6766,7 +6783,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B86" s="5">
         <v>46160.65279733796</v>
@@ -6775,18 +6792,20 @@
         <v>46181.677687511576</v>
       </c>
       <c r="D86" s="5">
-        <v>46181.677689247685</v>
+        <v>46223.58052398148</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H86" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I86" s="5">
         <v>46197</v>
       </c>
@@ -6803,10 +6822,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6819,7 +6838,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B87" s="8">
         <v>46160.65280108796</v>
@@ -6828,18 +6847,20 @@
         <v>46181.67776662037</v>
       </c>
       <c r="D87" s="8">
-        <v>46205.18242020834</v>
+        <v>46223.5811225</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I87" s="8">
         <v>46204</v>
       </c>
@@ -6856,13 +6877,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -6882,7 +6903,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B88" s="5">
         <v>46160.65280498842</v>
@@ -6891,18 +6912,20 @@
         <v>46181.677741273146</v>
       </c>
       <c r="D88" s="5">
-        <v>46181.67774287037</v>
+        <v>46223.58062439815</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H88" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I88" s="5">
         <v>46204</v>
       </c>
@@ -6919,13 +6942,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6935,7 +6958,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B89" s="8">
         <v>46160.65281013889</v>
@@ -6944,18 +6967,20 @@
         <v>46181.677753344906</v>
       </c>
       <c r="D89" s="8">
-        <v>46181.67775488426</v>
+        <v>46223.5806209375</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H89" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I89" s="8">
         <v>46204</v>
       </c>
@@ -6972,13 +6997,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -6988,7 +7013,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B90" s="5">
         <v>46160.65281503472</v>
@@ -6997,18 +7022,20 @@
         <v>46181.67783773148</v>
       </c>
       <c r="D90" s="5">
-        <v>46206.17392120371</v>
+        <v>46223.581118692135</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H90" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I90" s="5">
         <v>46205</v>
       </c>
@@ -7025,13 +7052,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q90" s="5">
         <v>46205</v>
@@ -7051,7 +7078,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B91" s="8">
         <v>46160.65281883102</v>
@@ -7060,18 +7087,20 @@
         <v>46181.67779599537</v>
       </c>
       <c r="D91" s="8">
-        <v>46181.677797627315</v>
+        <v>46223.5807081713</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H91" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H91" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I91" s="9"/>
       <c r="J91" s="8">
         <v>46205</v>
@@ -7086,13 +7115,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7102,7 +7131,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B92" s="5">
         <v>46160.65287608796</v>
@@ -7111,18 +7140,20 @@
         <v>46181.67780578704</v>
       </c>
       <c r="D92" s="5">
-        <v>46181.67780725694</v>
+        <v>46223.580704803244</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
         <v>46205</v>
@@ -7137,13 +7168,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7153,7 +7184,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B93" s="8">
         <v>46160.65288447917</v>
@@ -7162,18 +7193,20 @@
         <v>46181.6778656713</v>
       </c>
       <c r="D93" s="8">
-        <v>46207.18870825232</v>
+        <v>46223.58111460648</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H93" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H93" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I93" s="8">
         <v>46206</v>
       </c>
@@ -7190,13 +7223,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q93" s="8">
         <v>46206</v>
@@ -7216,7 +7249,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B94" s="5">
         <v>46160.65288969908</v>
@@ -7225,18 +7258,20 @@
         <v>46181.67784234954</v>
       </c>
       <c r="D94" s="5">
-        <v>46181.67784412037</v>
+        <v>46223.58079063657</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H94" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I94" s="5">
         <v>46206</v>
       </c>
@@ -7253,13 +7288,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7269,7 +7304,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B95" s="8">
         <v>46160.6528953588</v>
@@ -7278,18 +7313,20 @@
         <v>46181.67784924769</v>
       </c>
       <c r="D95" s="8">
-        <v>46181.677850625</v>
+        <v>46223.58078703703</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I95" s="8">
         <v>46206</v>
       </c>
@@ -7306,13 +7343,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7322,7 +7359,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B96" s="5">
         <v>46160.652900706016</v>
@@ -7331,18 +7368,20 @@
         <v>46181.677918587964</v>
       </c>
       <c r="D96" s="5">
-        <v>46210.194492256946</v>
+        <v>46223.58111108796</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I96" s="5">
         <v>46209</v>
       </c>
@@ -7359,13 +7398,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q96" s="5">
         <v>46209</v>
@@ -7385,7 +7424,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B97" s="8">
         <v>46160.65290569444</v>
@@ -7394,18 +7433,20 @@
         <v>46181.6778925463</v>
       </c>
       <c r="D97" s="8">
-        <v>46181.67789438658</v>
+        <v>46223.58087722222</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H97" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I97" s="8">
         <v>46209</v>
       </c>
@@ -7422,13 +7463,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7438,7 +7479,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B98" s="5">
         <v>46160.652911157405</v>
@@ -7447,18 +7488,20 @@
         <v>46181.67790297454</v>
       </c>
       <c r="D98" s="5">
-        <v>46181.67790501157</v>
+        <v>46223.58087362269</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H98" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I98" s="5">
         <v>46209</v>
       </c>
@@ -7475,13 +7518,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7491,7 +7534,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B99" s="8">
         <v>46160.65291657408</v>
@@ -7500,18 +7543,20 @@
         <v>46197.49723263889</v>
       </c>
       <c r="D99" s="8">
-        <v>46212.190271898144</v>
+        <v>46223.58110539352</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H99" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I99" s="8">
         <v>46211</v>
       </c>
@@ -7528,13 +7573,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q99" s="8">
         <v>46211</v>
@@ -7554,7 +7599,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B100" s="5">
         <v>46160.652921562505</v>
@@ -7563,18 +7608,20 @@
         <v>46197.60304642361</v>
       </c>
       <c r="D100" s="5">
-        <v>46198.56608928241</v>
+        <v>46223.58100638889</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H100" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
         <v>46211</v>
@@ -7589,13 +7636,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7605,27 +7652,29 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B101" s="8">
         <v>46160.65292620371</v>
       </c>
       <c r="C101" s="8">
-        <v>46197.4972891088</v>
+        <v>46223.58093487268</v>
       </c>
       <c r="D101" s="8">
-        <v>46198.566110405096</v>
+        <v>46223.581002708335</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H101" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I101" s="9"/>
       <c r="J101" s="8">
         <v>46211</v>
@@ -7640,13 +7689,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7656,7 +7705,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B102" s="5">
         <v>46160.65293084491</v>
@@ -7666,7 +7715,7 @@
         <v>46197.49766417824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7690,7 +7739,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7703,7 +7752,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B103" s="8">
         <v>46160.65293431713</v>
@@ -7713,16 +7762,16 @@
         <v>46213.179386909724</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I103" s="8">
         <v>46212</v>
@@ -7740,13 +7789,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q103" s="8">
         <v>46212</v>
@@ -7766,7 +7815,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B104" s="5">
         <v>46160.65293966435</v>
@@ -7778,16 +7827,16 @@
         <v>46204.80222355324</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I104" s="5">
         <v>46212</v>
@@ -7805,13 +7854,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7821,7 +7870,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B105" s="8">
         <v>46160.652944201385</v>
@@ -7830,19 +7879,19 @@
         <v>46204.80248626157</v>
       </c>
       <c r="D105" s="8">
-        <v>46204.80248778935</v>
+        <v>46223.580941493055</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I105" s="8">
         <v>46212</v>
@@ -7854,19 +7903,19 @@
         <v>26</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7876,7 +7925,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B106" s="5">
         <v>46160.80816486111</v>
@@ -7886,16 +7935,16 @@
         <v>46212.16850269676</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I106" s="5">
         <v>46212</v>
@@ -7913,13 +7962,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>59</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7929,7 +7978,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B107" s="8">
         <v>46160.80854525463</v>
@@ -7939,16 +7988,16 @@
         <v>46212.168504710644</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I107" s="8">
         <v>46212</v>
@@ -7966,13 +8015,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>59</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -7982,7 +8031,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B108" s="5">
         <v>46160.65294850695</v>
@@ -7991,18 +8040,20 @@
         <v>46197.49765626158</v>
       </c>
       <c r="D108" s="5">
-        <v>46214.19955962963</v>
+        <v>46223.58126640046</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H108" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I108" s="5">
         <v>46213</v>
       </c>
@@ -8019,13 +8070,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q108" s="5">
         <v>46213</v>
@@ -8045,7 +8096,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B109" s="8">
         <v>46160.652952592594</v>
@@ -8054,18 +8105,20 @@
         <v>46197.497369351855</v>
       </c>
       <c r="D109" s="8">
-        <v>46204.80222711805</v>
+        <v>46223.58121423611</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H109" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H109" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I109" s="8">
         <v>46213</v>
       </c>
@@ -8082,13 +8135,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8098,7 +8151,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B110" s="5">
         <v>46160.65295699074</v>
@@ -8107,18 +8160,20 @@
         <v>46197.497530023145</v>
       </c>
       <c r="D110" s="5">
-        <v>46204.80249248842</v>
+        <v>46223.581210069446</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H110" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I110" s="5">
         <v>46213</v>
       </c>
@@ -8135,13 +8190,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8151,25 +8206,27 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B111" s="8">
         <v>46160.809122164355</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46213.16936128472</v>
+        <v>46223.58120212963</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H111" s="9"/>
+        <v>91</v>
+      </c>
+      <c r="H111" s="9" t="s">
+        <v>91</v>
+      </c>
       <c r="I111" s="8">
         <v>46213</v>
       </c>
@@ -8186,13 +8243,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8202,25 +8259,27 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B112" s="5">
         <v>46160.809137627315</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46213.16936325232</v>
+        <v>46223.58120152778</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H112" s="6"/>
+        <v>91</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>91</v>
+      </c>
       <c r="I112" s="5">
         <v>46213</v>
       </c>
@@ -8237,13 +8296,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8253,7 +8312,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B113" s="8">
         <v>46160.652961203705</v>
@@ -8263,16 +8322,16 @@
         <v>46217.178433506946</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I113" s="8">
         <v>46216</v>
@@ -8290,13 +8349,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q113" s="8">
         <v>46216</v>
@@ -8316,7 +8375,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B114" s="5">
         <v>46160.65296532407</v>
@@ -8326,16 +8385,16 @@
         <v>46216.168960752315</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8351,13 +8410,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8367,7 +8426,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B115" s="8">
         <v>46160.65297267361</v>
@@ -8377,16 +8436,16 @@
         <v>46216.16895939814</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="8">
@@ -8402,13 +8461,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8418,7 +8477,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B116" s="5">
         <v>46160.81088733797</v>
@@ -8428,16 +8487,16 @@
         <v>46216.16896737269</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8453,13 +8512,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8469,7 +8528,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B117" s="8">
         <v>46160.81089606481</v>
@@ -8479,16 +8538,16 @@
         <v>46216.168969085644</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8504,13 +8563,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8520,7 +8579,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B118" s="5">
         <v>46160.65297846065</v>
@@ -8530,16 +8589,16 @@
         <v>46218.17912671296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I118" s="5">
         <v>46217</v>
@@ -8557,13 +8616,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q118" s="5">
         <v>46217</v>
@@ -8583,7 +8642,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B119" s="8">
         <v>46160.652983935186</v>
@@ -8593,16 +8652,16 @@
         <v>46217.16843326389</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I119" s="8">
         <v>46217</v>
@@ -8620,13 +8679,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8636,7 +8695,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B120" s="5">
         <v>46160.65298813657</v>
@@ -8646,16 +8705,16 @@
         <v>46217.16837645833</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I120" s="5">
         <v>46217</v>
@@ -8673,13 +8732,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8689,7 +8748,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B121" s="8">
         <v>46160.81215837963</v>
@@ -8699,16 +8758,16 @@
         <v>46217.168417002315</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I121" s="8">
         <v>46217</v>
@@ -8726,13 +8785,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8742,7 +8801,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B122" s="5">
         <v>46160.81220768519</v>
@@ -8752,16 +8811,16 @@
         <v>46217.16841864583</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I122" s="5">
         <v>46217</v>
@@ -8779,13 +8838,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8795,7 +8854,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B123" s="8">
         <v>46160.65302554399</v>
@@ -8805,7 +8864,7 @@
         <v>46160.8192895949</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>25</v>
@@ -8829,7 +8888,7 @@
         <v>26</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>26</v>
@@ -8842,7 +8901,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B124" s="5">
         <v>46160.65302895833</v>
@@ -8852,16 +8911,16 @@
         <v>46219.173083553236</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="I124" s="5">
         <v>46218</v>
@@ -8879,13 +8938,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q124" s="5">
         <v>46218</v>
@@ -8894,7 +8953,7 @@
         <v>46226</v>
       </c>
       <c r="S124" s="12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="T124" s="6">
         <v>0</v>
@@ -8905,7 +8964,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B125" s="8">
         <v>46160.65303386574</v>
@@ -8915,7 +8974,7 @@
         <v>46219.17308424768</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -8942,13 +9001,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q125" s="8">
         <v>46218</v>
@@ -8957,7 +9016,7 @@
         <v>46226</v>
       </c>
       <c r="S125" s="12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
@@ -8968,7 +9027,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B126" s="5">
         <v>46160.65808951389</v>
@@ -8978,7 +9037,7 @@
         <v>46160.819809513894</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>25</v>
@@ -9002,7 +9061,7 @@
         <v>26</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -9021,7 +9080,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B127" s="8">
         <v>46160.66095159722</v>
@@ -9031,7 +9090,7 @@
         <v>46219.173089097225</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9058,13 +9117,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q127" s="8">
         <v>46218</v>
@@ -9073,7 +9132,7 @@
         <v>46226</v>
       </c>
       <c r="S127" s="12" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="T127" s="9">
         <v>0</v>
@@ -9084,7 +9143,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B128" s="5">
         <v>46160.66107538194</v>
@@ -9094,7 +9153,7 @@
         <v>46160.8199466088</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9121,13 +9180,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q128" s="5">
         <v>46227</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="383">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -226,9 +226,6 @@
     <t>Ingenieria Electrica,Revision Tableros</t>
   </si>
   <si>
-    <t>Tarea sin iniciar</t>
-  </si>
-  <si>
     <t>1214889077215084</t>
   </si>
   <si>
@@ -254,6 +251,9 @@
   </si>
   <si>
     <t>sergio.saavedra@zitron.com</t>
+  </si>
+  <si>
+    <t>º</t>
   </si>
   <si>
     <t>Recepcion Tableros</t>
@@ -436,6 +436,9 @@
     <t>Alabe ot 4313,Fabricación Alabe ot 4313</t>
   </si>
   <si>
+    <t>Tarea sin iniciar</t>
+  </si>
+  <si>
     <t>1214909311361505</t>
   </si>
   <si>
@@ -817,7 +820,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -2212,9 +2215,11 @@
       <c r="B10" s="5">
         <v>46160.65369118056</v>
       </c>
-      <c r="C10" s="6"/>
+      <c r="C10" s="5">
+        <v>46224.79339478009</v>
+      </c>
       <c r="D10" s="5">
-        <v>46167.55829033565</v>
+        <v>46224.793407743055</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
@@ -2252,15 +2257,15 @@
         <v>32</v>
       </c>
       <c r="T10" s="6">
-        <v>0</v>
-      </c>
-      <c r="U10" s="11" t="s">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="U10" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="8">
         <v>46160.654091874996</v>
@@ -2272,16 +2277,16 @@
         <v>46167.558296180556</v>
       </c>
       <c r="E11" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G11" s="9" t="s">
+      <c r="H11" s="9" t="s">
         <v>55</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>56</v>
       </c>
       <c r="I11" s="8">
         <v>46129</v>
@@ -2305,7 +2310,7 @@
         <v>43</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q11" s="8">
         <v>46129</v>
@@ -2325,26 +2330,28 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B12" s="5">
         <v>46160.654172118055</v>
       </c>
-      <c r="C12" s="6"/>
+      <c r="C12" s="5">
+        <v>46224.79337738426</v>
+      </c>
       <c r="D12" s="5">
-        <v>46199.17997571759</v>
+        <v>46224.79337954861</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="I12" s="5">
         <v>46198</v>
@@ -2356,7 +2363,7 @@
         <v>26</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>26</v>
@@ -2380,10 +2387,10 @@
         <v>64</v>
       </c>
       <c r="T12" s="6">
-        <v>0</v>
-      </c>
-      <c r="U12" s="11" t="s">
-        <v>52</v>
+        <v>1</v>
+      </c>
+      <c r="U12" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
@@ -3178,7 +3185,7 @@
         <v>81</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>108</v>
@@ -3369,12 +3376,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B29" s="8">
         <v>46160.65243181713</v>
@@ -3386,7 +3393,7 @@
         <v>46181.67567790509</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3419,7 +3426,7 @@
         <v>118</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3430,12 +3437,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B30" s="5">
         <v>46160.65243667824</v>
@@ -3447,7 +3454,7 @@
         <v>46181.67562327546</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3477,7 +3484,7 @@
         <v>110</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>110</v>
@@ -3500,7 +3507,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B31" s="8">
         <v>46160.65244107639</v>
@@ -3512,7 +3519,7 @@
         <v>46181.67555395833</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3539,13 +3546,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3556,12 +3563,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B32" s="5">
         <v>46160.65244578704</v>
@@ -3573,7 +3580,7 @@
         <v>46181.67559840278</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
@@ -3600,13 +3607,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3617,12 +3624,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B33" s="8">
         <v>46160.652450625</v>
@@ -3634,7 +3641,7 @@
         <v>46181.67549369213</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
@@ -3664,7 +3671,7 @@
         <v>110</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>110</v>
@@ -3687,7 +3694,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B34" s="5">
         <v>46160.65245552083</v>
@@ -3699,7 +3706,7 @@
         <v>46181.67541268519</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
@@ -3726,13 +3733,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3743,12 +3750,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B35" s="8">
         <v>46160.65246048611</v>
@@ -3760,7 +3767,7 @@
         <v>46181.67545391204</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
@@ -3787,13 +3794,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3804,12 +3811,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B36" s="5">
         <v>46160.6524655324</v>
@@ -3821,7 +3828,7 @@
         <v>46181.67546648148</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
@@ -3848,13 +3855,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3865,12 +3872,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B37" s="8">
         <v>46160.6566696875</v>
@@ -3880,7 +3887,7 @@
         <v>46197.19306372685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
@@ -3910,7 +3917,7 @@
         <v>110</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>26</v>
@@ -3928,12 +3935,12 @@
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B38" s="5">
         <v>46160.65676351852</v>
@@ -3972,13 +3979,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>107</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3988,7 +3995,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B39" s="8">
         <v>46160.65688415509</v>
@@ -3998,7 +4005,7 @@
         <v>46196.16898914352</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
@@ -4025,13 +4032,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O39" s="9" t="s">
         <v>108</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4041,7 +4048,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B40" s="5">
         <v>46160.65247015047</v>
@@ -4053,16 +4060,16 @@
         <v>46181.676244386574</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I40" s="5">
         <v>46167</v>
@@ -4083,7 +4090,7 @@
         <v>110</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>110</v>
@@ -4106,7 +4113,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B41" s="8">
         <v>46160.65247482639</v>
@@ -4118,16 +4125,16 @@
         <v>46181.67615008102</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I41" s="8">
         <v>46167</v>
@@ -4145,13 +4152,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>94</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4162,12 +4169,12 @@
         <v>0</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B42" s="5">
         <v>46160.65247959491</v>
@@ -4179,16 +4186,16 @@
         <v>46181.67622016204</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I42" s="5">
         <v>46169</v>
@@ -4206,13 +4213,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4223,12 +4230,12 @@
         <v>0</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B43" s="8">
         <v>46160.65254070602</v>
@@ -4240,16 +4247,16 @@
         <v>46181.67636662037</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I43" s="8">
         <v>46167</v>
@@ -4270,7 +4277,7 @@
         <v>110</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4293,7 +4300,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B44" s="5">
         <v>46160.65254572917</v>
@@ -4311,10 +4318,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I44" s="5">
         <v>46167</v>
@@ -4332,13 +4339,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>98</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4348,7 +4355,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B45" s="8">
         <v>46160.652551377316</v>
@@ -4360,16 +4367,16 @@
         <v>46181.67634090278</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I45" s="8">
         <v>46169</v>
@@ -4387,13 +4394,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>99</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4403,7 +4410,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B46" s="5">
         <v>46160.652557152775</v>
@@ -4415,16 +4422,16 @@
         <v>46206.17392120371</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I46" s="5">
         <v>46167</v>
@@ -4445,7 +4452,7 @@
         <v>110</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4468,7 +4475,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B47" s="8">
         <v>46160.65256162037</v>
@@ -4486,10 +4493,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4507,13 +4514,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>104</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4523,7 +4530,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B48" s="5">
         <v>46160.6525734375</v>
@@ -4535,16 +4542,16 @@
         <v>46181.67642934028</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I48" s="5">
         <v>46176</v>
@@ -4562,13 +4569,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>105</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4578,7 +4585,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B49" s="8">
         <v>46160.652579236106</v>
@@ -4590,16 +4597,16 @@
         <v>46181.676467303245</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I49" s="8">
         <v>46205</v>
@@ -4617,10 +4624,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4633,7 +4640,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B50" s="5">
         <v>46160.65258304398</v>
@@ -4645,16 +4652,16 @@
         <v>46181.67657885417</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I50" s="5">
         <v>46167</v>
@@ -4675,7 +4682,7 @@
         <v>110</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4698,7 +4705,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B51" s="8">
         <v>46160.6525875463</v>
@@ -4716,10 +4723,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I51" s="8">
         <v>46167</v>
@@ -4737,13 +4744,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>101</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4753,7 +4760,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B52" s="5">
         <v>46160.652593067134</v>
@@ -4765,16 +4772,16 @@
         <v>46181.676553680554</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I52" s="5">
         <v>46169</v>
@@ -4792,13 +4799,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>102</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4808,7 +4815,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B53" s="8">
         <v>46160.65225516204</v>
@@ -4820,7 +4827,7 @@
         <v>46181.67858451389</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4844,7 +4851,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4857,7 +4864,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B54" s="5">
         <v>46160.65259921296</v>
@@ -4869,16 +4876,16 @@
         <v>46197.712640196754</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I54" s="5">
         <v>46140</v>
@@ -4896,13 +4903,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q54" s="5">
         <v>46140</v>
@@ -4922,7 +4929,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B55" s="8">
         <v>46160.652606006945</v>
@@ -4934,16 +4941,16 @@
         <v>46197.71267317129</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I55" s="8">
         <v>46153</v>
@@ -4961,13 +4968,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q55" s="8">
         <v>46153</v>
@@ -4987,7 +4994,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B56" s="5">
         <v>46160.65261409723</v>
@@ -5005,10 +5012,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I56" s="5">
         <v>46160</v>
@@ -5026,13 +5033,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Q56" s="5">
         <v>46160</v>
@@ -5052,7 +5059,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B57" s="8">
         <v>46160.652630983794</v>
@@ -5064,16 +5071,16 @@
         <v>46211.169411759256</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I57" s="8">
         <v>46210</v>
@@ -5091,10 +5098,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -5117,7 +5124,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B58" s="5">
         <v>46160.65263532408</v>
@@ -5129,16 +5136,16 @@
         <v>46198.566085625</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I58" s="5">
         <v>46210</v>
@@ -5156,13 +5163,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5172,7 +5179,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B59" s="8">
         <v>46160.65264069445</v>
@@ -5184,16 +5191,16 @@
         <v>46198.5661015625</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="I59" s="8">
         <v>46210</v>
@@ -5211,13 +5218,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5227,7 +5234,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B60" s="5">
         <v>46160.652676921294</v>
@@ -5239,7 +5246,7 @@
         <v>46181.67816971065</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5263,7 +5270,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5276,7 +5283,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B61" s="8">
         <v>46160.65268083333</v>
@@ -5288,16 +5295,16 @@
         <v>46182.19861893519</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I61" s="8">
         <v>46178</v>
@@ -5315,13 +5322,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q61" s="8">
         <v>46178</v>
@@ -5341,7 +5348,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B62" s="5">
         <v>46160.652685810186</v>
@@ -5353,16 +5360,16 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I62" s="5">
         <v>46182</v>
@@ -5380,13 +5387,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q62" s="5">
         <v>46182</v>
@@ -5406,7 +5413,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B63" s="8">
         <v>46160.65269097222</v>
@@ -5418,16 +5425,16 @@
         <v>46181.6766224537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I63" s="8">
         <v>46178</v>
@@ -5445,13 +5452,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q63" s="8">
         <v>46147</v>
@@ -5471,7 +5478,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B64" s="5">
         <v>46160.65269633102</v>
@@ -5483,16 +5490,16 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I64" s="5">
         <v>46182</v>
@@ -5510,13 +5517,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q64" s="5">
         <v>46182</v>
@@ -5536,7 +5543,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B65" s="8">
         <v>46160.65269980324</v>
@@ -5548,16 +5555,16 @@
         <v>46181.67666866898</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I65" s="8">
         <v>46178</v>
@@ -5575,13 +5582,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q65" s="8">
         <v>46147</v>
@@ -5601,7 +5608,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B66" s="5">
         <v>46160.652703935186</v>
@@ -5613,16 +5620,16 @@
         <v>46184.172129004626</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I66" s="5">
         <v>46182</v>
@@ -5640,13 +5647,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q66" s="5">
         <v>46182</v>
@@ -5666,7 +5673,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B67" s="8">
         <v>46160.65270767361</v>
@@ -5678,7 +5685,7 @@
         <v>46181.6781084838</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5702,7 +5709,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5715,7 +5722,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B68" s="5">
         <v>46160.65271061343</v>
@@ -5724,19 +5731,19 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46189.195743599535</v>
+        <v>46224.87838538195</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I68" s="5">
         <v>46184</v>
@@ -5754,13 +5761,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q68" s="5">
         <v>46184</v>
@@ -5780,7 +5787,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B69" s="8">
         <v>46160.65271650463</v>
@@ -5792,16 +5799,16 @@
         <v>46181.67713434028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I69" s="8">
         <v>46184</v>
@@ -5819,13 +5826,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5835,7 +5842,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B70" s="5">
         <v>46160.65272224537</v>
@@ -5847,16 +5854,16 @@
         <v>46181.67713509259</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I70" s="5">
         <v>46184</v>
@@ -5874,13 +5881,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5890,7 +5897,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B71" s="8">
         <v>46160.652726898144</v>
@@ -5902,16 +5909,16 @@
         <v>46196.198199756946</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I71" s="8">
         <v>46189</v>
@@ -5929,13 +5936,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q71" s="8">
         <v>46189</v>
@@ -5955,7 +5962,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B72" s="5">
         <v>46160.65273052083</v>
@@ -5967,16 +5974,16 @@
         <v>46181.67719854167</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I72" s="5">
         <v>46189</v>
@@ -5994,13 +6001,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6010,7 +6017,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B73" s="8">
         <v>46160.652741620375</v>
@@ -6022,16 +6029,16 @@
         <v>46181.67721436343</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I73" s="8">
         <v>46189</v>
@@ -6049,13 +6056,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6065,7 +6072,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B74" s="5">
         <v>46160.65274630787</v>
@@ -6077,16 +6084,16 @@
         <v>46197.19306369213</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I74" s="5">
         <v>46196</v>
@@ -6104,13 +6111,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q74" s="5">
         <v>46196</v>
@@ -6130,7 +6137,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B75" s="8">
         <v>46160.65275005787</v>
@@ -6142,16 +6149,16 @@
         <v>46181.67726512731</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I75" s="8">
         <v>46196</v>
@@ -6169,13 +6176,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6185,7 +6192,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B76" s="5">
         <v>46160.65275548611</v>
@@ -6197,16 +6204,16 @@
         <v>46181.677274664355</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I76" s="5">
         <v>46196</v>
@@ -6224,13 +6231,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6240,7 +6247,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B77" s="8">
         <v>46160.652760625</v>
@@ -6252,7 +6259,7 @@
         <v>46181.67751854166</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6276,7 +6283,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6289,7 +6296,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B78" s="5">
         <v>46160.65276340277</v>
@@ -6301,16 +6308,16 @@
         <v>46192.20460657407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I78" s="5">
         <v>46160</v>
@@ -6328,13 +6335,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q78" s="5">
         <v>46160</v>
@@ -6354,7 +6361,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B79" s="8">
         <v>46160.652768831016</v>
@@ -6366,16 +6373,16 @@
         <v>46181.677345034725</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I79" s="8">
         <v>46141</v>
@@ -6393,13 +6400,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q79" s="8">
         <v>46141</v>
@@ -6419,7 +6426,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B80" s="5">
         <v>46160.652774409726</v>
@@ -6431,16 +6438,16 @@
         <v>46181.67735619213</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6458,13 +6465,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6484,7 +6491,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B81" s="8">
         <v>46160.652779745375</v>
@@ -6496,16 +6503,16 @@
         <v>46207.188708125</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I81" s="8">
         <v>46206</v>
@@ -6523,13 +6530,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q81" s="8">
         <v>46206</v>
@@ -6549,7 +6556,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B82" s="5">
         <v>46160.657067569446</v>
@@ -6565,10 +6572,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I82" s="5">
         <v>46197</v>
@@ -6586,13 +6593,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="Q82" s="5">
         <v>46197</v>
@@ -6607,12 +6614,12 @@
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B83" s="8">
         <v>46160.65278418981</v>
@@ -6624,7 +6631,7 @@
         <v>46197.49724974537</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>25</v>
@@ -6648,7 +6655,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>26</v>
@@ -6663,7 +6670,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B84" s="5">
         <v>46160.65278701389</v>
@@ -6675,7 +6682,7 @@
         <v>46223.58112633102</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6702,13 +6709,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q84" s="5">
         <v>46197</v>
@@ -6728,7 +6735,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B85" s="8">
         <v>46160.65279357639</v>
@@ -6740,7 +6747,7 @@
         <v>46223.58052726852</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6767,10 +6774,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6783,7 +6790,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B86" s="5">
         <v>46160.65279733796</v>
@@ -6795,7 +6802,7 @@
         <v>46223.58052398148</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6822,10 +6829,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6838,7 +6845,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B87" s="8">
         <v>46160.65280108796</v>
@@ -6850,7 +6857,7 @@
         <v>46223.5811225</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6877,13 +6884,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -6903,7 +6910,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B88" s="5">
         <v>46160.65280498842</v>
@@ -6915,7 +6922,7 @@
         <v>46223.58062439815</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6942,13 +6949,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6958,7 +6965,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B89" s="8">
         <v>46160.65281013889</v>
@@ -6970,7 +6977,7 @@
         <v>46223.5806209375</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6997,13 +7004,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7013,7 +7020,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B90" s="5">
         <v>46160.65281503472</v>
@@ -7025,7 +7032,7 @@
         <v>46223.581118692135</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7052,13 +7059,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q90" s="5">
         <v>46205</v>
@@ -7078,7 +7085,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B91" s="8">
         <v>46160.65281883102</v>
@@ -7090,7 +7097,7 @@
         <v>46223.5807081713</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7115,13 +7122,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7131,7 +7138,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B92" s="5">
         <v>46160.65287608796</v>
@@ -7143,7 +7150,7 @@
         <v>46223.580704803244</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7168,13 +7175,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7184,7 +7191,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B93" s="8">
         <v>46160.65288447917</v>
@@ -7196,7 +7203,7 @@
         <v>46223.58111460648</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7223,13 +7230,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q93" s="8">
         <v>46206</v>
@@ -7249,7 +7256,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B94" s="5">
         <v>46160.65288969908</v>
@@ -7261,7 +7268,7 @@
         <v>46223.58079063657</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7288,13 +7295,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7304,7 +7311,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B95" s="8">
         <v>46160.6528953588</v>
@@ -7316,7 +7323,7 @@
         <v>46223.58078703703</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7343,13 +7350,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7359,7 +7366,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B96" s="5">
         <v>46160.652900706016</v>
@@ -7371,7 +7378,7 @@
         <v>46223.58111108796</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7398,13 +7405,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q96" s="5">
         <v>46209</v>
@@ -7424,7 +7431,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B97" s="8">
         <v>46160.65290569444</v>
@@ -7436,7 +7443,7 @@
         <v>46223.58087722222</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7463,13 +7470,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7479,7 +7486,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B98" s="5">
         <v>46160.652911157405</v>
@@ -7491,7 +7498,7 @@
         <v>46223.58087362269</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7518,13 +7525,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7534,7 +7541,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B99" s="8">
         <v>46160.65291657408</v>
@@ -7546,7 +7553,7 @@
         <v>46223.58110539352</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7573,13 +7580,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q99" s="8">
         <v>46211</v>
@@ -7599,7 +7606,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B100" s="5">
         <v>46160.652921562505</v>
@@ -7611,7 +7618,7 @@
         <v>46223.58100638889</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7636,13 +7643,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7652,7 +7659,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B101" s="8">
         <v>46160.65292620371</v>
@@ -7664,7 +7671,7 @@
         <v>46223.581002708335</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7689,13 +7696,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7705,7 +7712,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B102" s="5">
         <v>46160.65293084491</v>
@@ -7715,7 +7722,7 @@
         <v>46197.49766417824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7739,7 +7746,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7752,26 +7759,26 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B103" s="8">
         <v>46160.65293431713</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46213.179386909724</v>
+        <v>46224.79338295139</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I103" s="8">
         <v>46212</v>
@@ -7789,13 +7796,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q103" s="8">
         <v>46212</v>
@@ -7815,7 +7822,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B104" s="5">
         <v>46160.65293966435</v>
@@ -7827,16 +7834,16 @@
         <v>46204.80222355324</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I104" s="5">
         <v>46212</v>
@@ -7854,13 +7861,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7870,7 +7877,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B105" s="8">
         <v>46160.652944201385</v>
@@ -7882,16 +7889,16 @@
         <v>46223.580941493055</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I105" s="8">
         <v>46212</v>
@@ -7903,19 +7910,19 @@
         <v>26</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7925,26 +7932,26 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B106" s="5">
         <v>46160.80816486111</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46212.16850269676</v>
+        <v>46224.793388101854</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I106" s="5">
         <v>46212</v>
@@ -7962,13 +7969,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7978,26 +7985,26 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B107" s="8">
         <v>46160.80854525463</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46212.168504710644</v>
+        <v>46224.79338983796</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I107" s="8">
         <v>46212</v>
@@ -8015,13 +8022,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8031,7 +8038,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B108" s="5">
         <v>46160.65294850695</v>
@@ -8043,7 +8050,7 @@
         <v>46223.58126640046</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8070,13 +8077,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q108" s="5">
         <v>46213</v>
@@ -8096,7 +8103,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B109" s="8">
         <v>46160.652952592594</v>
@@ -8108,7 +8115,7 @@
         <v>46223.58121423611</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8135,13 +8142,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8151,7 +8158,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B110" s="5">
         <v>46160.65295699074</v>
@@ -8163,7 +8170,7 @@
         <v>46223.581210069446</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8190,13 +8197,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8206,7 +8213,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B111" s="8">
         <v>46160.809122164355</v>
@@ -8216,7 +8223,7 @@
         <v>46223.58120212963</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8243,13 +8250,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8259,7 +8266,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" s="5">
         <v>46160.809137627315</v>
@@ -8269,7 +8276,7 @@
         <v>46223.58120152778</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8296,13 +8303,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8312,7 +8319,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B113" s="8">
         <v>46160.652961203705</v>
@@ -8322,16 +8329,16 @@
         <v>46217.178433506946</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I113" s="8">
         <v>46216</v>
@@ -8349,13 +8356,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q113" s="8">
         <v>46216</v>
@@ -8375,7 +8382,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B114" s="5">
         <v>46160.65296532407</v>
@@ -8385,16 +8392,16 @@
         <v>46216.168960752315</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8410,13 +8417,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8426,7 +8433,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B115" s="8">
         <v>46160.65297267361</v>
@@ -8436,16 +8443,16 @@
         <v>46216.16895939814</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="8">
@@ -8461,13 +8468,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8477,7 +8484,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B116" s="5">
         <v>46160.81088733797</v>
@@ -8487,16 +8494,16 @@
         <v>46216.16896737269</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8512,13 +8519,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8528,7 +8535,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B117" s="8">
         <v>46160.81089606481</v>
@@ -8538,16 +8545,16 @@
         <v>46216.168969085644</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8563,13 +8570,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8579,7 +8586,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B118" s="5">
         <v>46160.65297846065</v>
@@ -8589,16 +8596,16 @@
         <v>46218.17912671296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I118" s="5">
         <v>46217</v>
@@ -8616,13 +8623,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q118" s="5">
         <v>46217</v>
@@ -8637,12 +8644,12 @@
         <v>0</v>
       </c>
       <c r="U118" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B119" s="8">
         <v>46160.652983935186</v>
@@ -8652,16 +8659,16 @@
         <v>46217.16843326389</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I119" s="8">
         <v>46217</v>
@@ -8679,13 +8686,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8695,7 +8702,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B120" s="5">
         <v>46160.65298813657</v>
@@ -8705,16 +8712,16 @@
         <v>46217.16837645833</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I120" s="5">
         <v>46217</v>
@@ -8732,13 +8739,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8748,7 +8755,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B121" s="8">
         <v>46160.81215837963</v>
@@ -8758,16 +8765,16 @@
         <v>46217.168417002315</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I121" s="8">
         <v>46217</v>
@@ -8785,13 +8792,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8801,7 +8808,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B122" s="5">
         <v>46160.81220768519</v>
@@ -8811,16 +8818,16 @@
         <v>46217.16841864583</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I122" s="5">
         <v>46217</v>
@@ -8838,13 +8845,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8854,7 +8861,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B123" s="8">
         <v>46160.65302554399</v>
@@ -8864,7 +8871,7 @@
         <v>46160.8192895949</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>25</v>
@@ -8888,7 +8895,7 @@
         <v>26</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>26</v>
@@ -8901,7 +8908,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B124" s="5">
         <v>46160.65302895833</v>
@@ -8911,16 +8918,16 @@
         <v>46219.173083553236</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="I124" s="5">
         <v>46218</v>
@@ -8938,13 +8945,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q124" s="5">
         <v>46218</v>
@@ -8953,18 +8960,18 @@
         <v>46226</v>
       </c>
       <c r="S124" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="T124" s="6">
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B125" s="8">
         <v>46160.65303386574</v>
@@ -8974,7 +8981,7 @@
         <v>46219.17308424768</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9001,13 +9008,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q125" s="8">
         <v>46218</v>
@@ -9016,18 +9023,18 @@
         <v>46226</v>
       </c>
       <c r="S125" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B126" s="5">
         <v>46160.65808951389</v>
@@ -9037,7 +9044,7 @@
         <v>46160.819809513894</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>25</v>
@@ -9061,7 +9068,7 @@
         <v>26</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -9075,12 +9082,12 @@
         <v>0</v>
       </c>
       <c r="U126" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B127" s="8">
         <v>46160.66095159722</v>
@@ -9090,16 +9097,16 @@
         <v>46219.173089097225</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H127" s="9" t="s">
         <v>55</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>56</v>
       </c>
       <c r="I127" s="8">
         <v>46218</v>
@@ -9117,13 +9124,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q127" s="8">
         <v>46218</v>
@@ -9132,18 +9139,18 @@
         <v>46226</v>
       </c>
       <c r="S127" s="12" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="T127" s="9">
         <v>0</v>
       </c>
       <c r="U127" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B128" s="5">
         <v>46160.66107538194</v>
@@ -9153,16 +9160,16 @@
         <v>46160.8199466088</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="H128" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="I128" s="5">
         <v>46227</v>
@@ -9180,13 +9187,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q128" s="5">
         <v>46227</v>
@@ -9201,7 +9208,7 @@
         <v>0</v>
       </c>
       <c r="U128" s="11" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -820,7 +820,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -5731,7 +5731,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46224.87838538195</v>
+        <v>46225.009610821755</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="384">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -1082,6 +1082,9 @@
   </si>
   <si>
     <t>Coordinacion Entrega con Cliente,OT 4314 - VDF VLT  FC 102</t>
+  </si>
+  <si>
+    <t>1216786101186166</t>
   </si>
   <si>
     <t>1214889077215248</t>
@@ -1746,7 +1749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U128"/>
+  <dimension ref="A1:U129"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -7766,7 +7769,7 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46224.79338295139</v>
+        <v>46225.55379075231</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>324</v>
@@ -7937,9 +7940,11 @@
       <c r="B106" s="5">
         <v>46160.80816486111</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="5">
+        <v>46225.55378449074</v>
+      </c>
       <c r="D106" s="5">
-        <v>46224.793388101854</v>
+        <v>46225.55378673611</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>334</v>
@@ -7988,47 +7993,41 @@
         <v>336</v>
       </c>
       <c r="B107" s="8">
-        <v>46160.80854525463</v>
+        <v>46225.55376708333</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46224.79338983796</v>
+        <v>46225.553774409724</v>
       </c>
       <c r="E107" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F107" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G107" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H107" s="9"/>
+      <c r="I107" s="9"/>
+      <c r="J107" s="9"/>
+      <c r="K107" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L107" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M107" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N107" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="F107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G107" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>326</v>
-      </c>
-      <c r="I107" s="8">
-        <v>46212</v>
-      </c>
-      <c r="J107" s="8">
-        <v>46212</v>
-      </c>
-      <c r="K107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N107" s="9" t="s">
-        <v>324</v>
-      </c>
       <c r="O107" s="9" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>337</v>
+        <v>26</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8038,84 +8037,72 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B108" s="5">
+        <v>46160.80854525463</v>
+      </c>
+      <c r="C108" s="6"/>
+      <c r="D108" s="5">
+        <v>46224.79338983796</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G108" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="I108" s="5">
+        <v>46212</v>
+      </c>
+      <c r="J108" s="5">
+        <v>46212</v>
+      </c>
+      <c r="K108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N108" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="O108" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P108" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="B108" s="5">
-        <v>46160.65294850695</v>
-      </c>
-      <c r="C108" s="5">
-        <v>46197.49765626158</v>
-      </c>
-      <c r="D108" s="5">
-        <v>46223.58126640046</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G108" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I108" s="5">
-        <v>46213</v>
-      </c>
-      <c r="J108" s="5">
-        <v>46213</v>
-      </c>
-      <c r="K108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N108" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q108" s="5">
-        <v>46213</v>
-      </c>
-      <c r="R108" s="5">
-        <v>46213</v>
-      </c>
-      <c r="S108" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T108" s="6">
-        <v>1</v>
-      </c>
-      <c r="U108" s="12" t="s">
-        <v>68</v>
-      </c>
+      <c r="Q108" s="6"/>
+      <c r="R108" s="6"/>
+      <c r="S108" s="6"/>
+      <c r="T108" s="6"/>
+      <c r="U108" s="6"/>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B109" s="8">
-        <v>46160.652952592594</v>
+        <v>46160.65294850695</v>
       </c>
       <c r="C109" s="8">
-        <v>46197.497369351855</v>
+        <v>46197.49765626158</v>
       </c>
       <c r="D109" s="8">
-        <v>46223.58121423611</v>
+        <v>46223.58126640046</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>216</v>
+        <v>340</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8142,32 +8129,42 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>339</v>
+        <v>321</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>216</v>
+        <v>341</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="Q109" s="9"/>
-      <c r="R109" s="9"/>
-      <c r="S109" s="9"/>
-      <c r="T109" s="9"/>
-      <c r="U109" s="9"/>
+        <v>321</v>
+      </c>
+      <c r="Q109" s="8">
+        <v>46213</v>
+      </c>
+      <c r="R109" s="8">
+        <v>46213</v>
+      </c>
+      <c r="S109" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="T109" s="9">
+        <v>1</v>
+      </c>
+      <c r="U109" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B110" s="5">
-        <v>46160.65295699074</v>
+        <v>46160.652952592594</v>
       </c>
       <c r="C110" s="5">
-        <v>46197.497530023145</v>
+        <v>46197.497369351855</v>
       </c>
       <c r="D110" s="5">
-        <v>46223.581210069446</v>
+        <v>46223.58121423611</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>216</v>
@@ -8197,13 +8194,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>216</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8216,14 +8213,16 @@
         <v>344</v>
       </c>
       <c r="B111" s="8">
-        <v>46160.809122164355</v>
-      </c>
-      <c r="C111" s="9"/>
+        <v>46160.65295699074</v>
+      </c>
+      <c r="C111" s="8">
+        <v>46197.497530023145</v>
+      </c>
       <c r="D111" s="8">
-        <v>46223.58120212963</v>
+        <v>46223.581210069446</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>334</v>
+        <v>216</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8250,13 +8249,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>334</v>
+        <v>216</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8266,17 +8265,17 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B112" s="5">
-        <v>46160.809137627315</v>
+        <v>46160.809122164355</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46223.58120152778</v>
+        <v>46225.55379164351</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8303,13 +8302,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>334</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8319,32 +8318,32 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B113" s="8">
-        <v>46160.652961203705</v>
+        <v>46160.809137627315</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46217.178433506946</v>
+        <v>46223.58120152778</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>246</v>
+        <v>91</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>247</v>
+        <v>91</v>
       </c>
       <c r="I113" s="8">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="J113" s="8">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="K113" s="9" t="s">
         <v>26</v>
@@ -8356,43 +8355,33 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>321</v>
+        <v>340</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q113" s="8">
-        <v>46216</v>
-      </c>
-      <c r="R113" s="8">
-        <v>46216</v>
-      </c>
-      <c r="S113" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T113" s="9">
-        <v>1</v>
-      </c>
-      <c r="U113" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="Q113" s="9"/>
+      <c r="R113" s="9"/>
+      <c r="S113" s="9"/>
+      <c r="T113" s="9"/>
+      <c r="U113" s="9"/>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B114" s="5">
-        <v>46160.65296532407</v>
+        <v>46160.652961203705</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46216.168960752315</v>
+        <v>46217.178433506946</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>216</v>
+        <v>350</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8403,7 +8392,9 @@
       <c r="H114" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="I114" s="6"/>
+      <c r="I114" s="5">
+        <v>46216</v>
+      </c>
       <c r="J114" s="5">
         <v>46216</v>
       </c>
@@ -8417,30 +8408,40 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>349</v>
+        <v>321</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>216</v>
+        <v>351</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="Q114" s="6"/>
-      <c r="R114" s="6"/>
-      <c r="S114" s="6"/>
-      <c r="T114" s="6"/>
-      <c r="U114" s="6"/>
+        <v>321</v>
+      </c>
+      <c r="Q114" s="5">
+        <v>46216</v>
+      </c>
+      <c r="R114" s="5">
+        <v>46216</v>
+      </c>
+      <c r="S114" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="T114" s="6">
+        <v>1</v>
+      </c>
+      <c r="U114" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B115" s="8">
-        <v>46160.65297267361</v>
+        <v>46160.65296532407</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46216.16895939814</v>
+        <v>46216.168960752315</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>216</v>
@@ -8468,13 +8469,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>216</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8484,17 +8485,17 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B116" s="5">
-        <v>46160.81088733797</v>
+        <v>46160.65297267361</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46216.16896737269</v>
+        <v>46216.16895939814</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>334</v>
+        <v>216</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8519,13 +8520,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>334</v>
+        <v>216</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8535,14 +8536,14 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B117" s="8">
-        <v>46160.81089606481</v>
+        <v>46160.81088733797</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46216.168969085644</v>
+        <v>46216.16896737269</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>334</v>
@@ -8570,13 +8571,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8589,14 +8590,14 @@
         <v>358</v>
       </c>
       <c r="B118" s="5">
-        <v>46160.65297846065</v>
+        <v>46160.81089606481</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46218.17912671296</v>
+        <v>46216.168969085644</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>359</v>
+        <v>334</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8607,11 +8608,9 @@
       <c r="H118" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="I118" s="5">
-        <v>46217</v>
-      </c>
+      <c r="I118" s="6"/>
       <c r="J118" s="5">
-        <v>46217</v>
+        <v>46216</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>26</v>
@@ -8623,43 +8622,33 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="Q118" s="5">
-        <v>46217</v>
-      </c>
-      <c r="R118" s="5">
-        <v>46217</v>
-      </c>
-      <c r="S118" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T118" s="6">
-        <v>0</v>
-      </c>
-      <c r="U118" s="11" t="s">
-        <v>120</v>
-      </c>
+        <v>357</v>
+      </c>
+      <c r="Q118" s="6"/>
+      <c r="R118" s="6"/>
+      <c r="S118" s="6"/>
+      <c r="T118" s="6"/>
+      <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B119" s="8">
-        <v>46160.652983935186</v>
+        <v>46160.65297846065</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46217.16843326389</v>
+        <v>46218.17912671296</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>216</v>
+        <v>360</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8686,30 +8675,40 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>359</v>
+        <v>321</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>216</v>
+        <v>351</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>359</v>
-      </c>
-      <c r="Q119" s="9"/>
-      <c r="R119" s="9"/>
-      <c r="S119" s="9"/>
-      <c r="T119" s="9"/>
-      <c r="U119" s="9"/>
+        <v>361</v>
+      </c>
+      <c r="Q119" s="8">
+        <v>46217</v>
+      </c>
+      <c r="R119" s="8">
+        <v>46217</v>
+      </c>
+      <c r="S119" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="T119" s="9">
+        <v>0</v>
+      </c>
+      <c r="U119" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>362</v>
       </c>
       <c r="B120" s="5">
-        <v>46160.65298813657</v>
+        <v>46160.652983935186</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46217.16837645833</v>
+        <v>46217.16843326389</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>216</v>
@@ -8739,13 +8738,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>216</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8758,14 +8757,14 @@
         <v>363</v>
       </c>
       <c r="B121" s="8">
-        <v>46160.81215837963</v>
+        <v>46160.65298813657</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46217.168417002315</v>
+        <v>46217.16837645833</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>334</v>
+        <v>216</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8792,13 +8791,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>334</v>
+        <v>216</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8811,11 +8810,11 @@
         <v>364</v>
       </c>
       <c r="B122" s="5">
-        <v>46160.81220768519</v>
+        <v>46160.81215837963</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46217.16841864583</v>
+        <v>46217.168417002315</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>334</v>
@@ -8845,13 +8844,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>334</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8864,24 +8863,30 @@
         <v>365</v>
       </c>
       <c r="B123" s="8">
-        <v>46160.65302554399</v>
+        <v>46160.81220768519</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46160.8192895949</v>
+        <v>46217.16841864583</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>366</v>
+        <v>334</v>
       </c>
       <c r="F123" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="9"/>
-      <c r="I123" s="9"/>
-      <c r="J123" s="9"/>
+        <v>246</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="I123" s="8">
+        <v>46217</v>
+      </c>
+      <c r="J123" s="8">
+        <v>46217</v>
+      </c>
       <c r="K123" s="9" t="s">
         <v>26</v>
       </c>
@@ -8889,16 +8894,16 @@
         <v>26</v>
       </c>
       <c r="M123" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>26</v>
+        <v>360</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>367</v>
+        <v>334</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>26</v>
+        <v>360</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8908,33 +8913,27 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B124" s="5">
-        <v>46160.65302895833</v>
+        <v>46160.65302554399</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46219.173083553236</v>
+        <v>46160.8192895949</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="I124" s="5">
-        <v>46218</v>
-      </c>
-      <c r="J124" s="5">
-        <v>46226</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H124" s="6"/>
+      <c r="I124" s="6"/>
+      <c r="J124" s="6"/>
       <c r="K124" s="6" t="s">
         <v>26</v>
       </c>
@@ -8942,55 +8941,45 @@
         <v>26</v>
       </c>
       <c r="M124" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>366</v>
+        <v>26</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>366</v>
-      </c>
-      <c r="Q124" s="5">
-        <v>46218</v>
-      </c>
-      <c r="R124" s="5">
-        <v>46226</v>
-      </c>
-      <c r="S124" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="T124" s="6">
-        <v>0</v>
-      </c>
-      <c r="U124" s="11" t="s">
-        <v>120</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q124" s="6"/>
+      <c r="R124" s="6"/>
+      <c r="S124" s="6"/>
+      <c r="T124" s="6"/>
+      <c r="U124" s="6"/>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B125" s="8">
-        <v>46160.65303386574</v>
+        <v>46160.65302895833</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46219.17308424768</v>
+        <v>46219.173083553236</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>36</v>
+        <v>371</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>37</v>
+        <v>372</v>
       </c>
       <c r="I125" s="8">
         <v>46218</v>
@@ -9008,13 +8997,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q125" s="8">
         <v>46218</v>
@@ -9023,7 +9012,7 @@
         <v>46226</v>
       </c>
       <c r="S125" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
@@ -9034,27 +9023,33 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B126" s="5">
-        <v>46160.65808951389</v>
+        <v>46160.65303386574</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46160.819809513894</v>
+        <v>46219.17308424768</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
+        <v>36</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I126" s="5">
+        <v>46218</v>
+      </c>
+      <c r="J126" s="5">
+        <v>46226</v>
+      </c>
       <c r="K126" s="6" t="s">
         <v>26</v>
       </c>
@@ -9062,21 +9057,25 @@
         <v>26</v>
       </c>
       <c r="M126" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>26</v>
+        <v>367</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q126" s="6"/>
-      <c r="R126" s="6"/>
-      <c r="S126" s="10" t="s">
-        <v>32</v>
+        <v>367</v>
+      </c>
+      <c r="Q126" s="5">
+        <v>46218</v>
+      </c>
+      <c r="R126" s="5">
+        <v>46226</v>
+      </c>
+      <c r="S126" s="12" t="s">
+        <v>373</v>
       </c>
       <c r="T126" s="6">
         <v>0</v>
@@ -9087,33 +9086,27 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B127" s="8">
-        <v>46160.66095159722</v>
+        <v>46160.65808951389</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46219.173089097225</v>
+        <v>46160.819809513894</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F127" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I127" s="8">
-        <v>46218</v>
-      </c>
-      <c r="J127" s="8">
-        <v>46226</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H127" s="9"/>
+      <c r="I127" s="9"/>
+      <c r="J127" s="9"/>
       <c r="K127" s="9" t="s">
         <v>26</v>
       </c>
@@ -9121,25 +9114,21 @@
         <v>26</v>
       </c>
       <c r="M127" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>376</v>
+        <v>26</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q127" s="8">
-        <v>46218</v>
-      </c>
-      <c r="R127" s="8">
-        <v>46226</v>
-      </c>
-      <c r="S127" s="12" t="s">
-        <v>372</v>
+        <v>26</v>
+      </c>
+      <c r="Q127" s="9"/>
+      <c r="R127" s="9"/>
+      <c r="S127" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T127" s="9">
         <v>0</v>
@@ -9150,17 +9139,17 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B128" s="5">
-        <v>46160.66107538194</v>
+        <v>46160.66095159722</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46160.8199466088</v>
+        <v>46219.173089097225</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9172,10 +9161,10 @@
         <v>55</v>
       </c>
       <c r="I128" s="5">
-        <v>46227</v>
+        <v>46218</v>
       </c>
       <c r="J128" s="5">
-        <v>46237</v>
+        <v>46226</v>
       </c>
       <c r="K128" s="6" t="s">
         <v>26</v>
@@ -9187,27 +9176,90 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="Q128" s="5">
-        <v>46227</v>
+        <v>46218</v>
       </c>
       <c r="R128" s="5">
-        <v>46237</v>
-      </c>
-      <c r="S128" s="10" t="s">
-        <v>32</v>
+        <v>46226</v>
+      </c>
+      <c r="S128" s="12" t="s">
+        <v>373</v>
       </c>
       <c r="T128" s="6">
         <v>0</v>
       </c>
       <c r="U128" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A129" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="B129" s="8">
+        <v>46160.66107538194</v>
+      </c>
+      <c r="C129" s="9"/>
+      <c r="D129" s="8">
+        <v>46160.8199466088</v>
+      </c>
+      <c r="E129" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G129" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I129" s="8">
+        <v>46227</v>
+      </c>
+      <c r="J129" s="8">
+        <v>46237</v>
+      </c>
+      <c r="K129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M129" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N129" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="O129" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="P129" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="Q129" s="8">
+        <v>46227</v>
+      </c>
+      <c r="R129" s="8">
+        <v>46237</v>
+      </c>
+      <c r="S129" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="T129" s="9">
+        <v>0</v>
+      </c>
+      <c r="U129" s="11" t="s">
         <v>120</v>
       </c>
     </row>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -820,7 +820,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -2342,7 +2342,7 @@
         <v>46224.79337738426</v>
       </c>
       <c r="D12" s="5">
-        <v>46224.79337954861</v>
+        <v>46225.58331327546</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -5734,7 +5734,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46225.009610821755</v>
+        <v>46225.58945353009</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>245</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1535" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="383">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -1082,9 +1082,6 @@
   </si>
   <si>
     <t>Coordinacion Entrega con Cliente,OT 4314 - VDF VLT  FC 102</t>
-  </si>
-  <si>
-    <t>1216786101186166</t>
   </si>
   <si>
     <t>1214889077215248</t>
@@ -1749,7 +1746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U129"/>
+  <dimension ref="A1:U128"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -7993,24 +7990,30 @@
         <v>336</v>
       </c>
       <c r="B107" s="8">
-        <v>46225.55376708333</v>
+        <v>46160.80854525463</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46225.553774409724</v>
+        <v>46224.79338983796</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>26</v>
+        <v>334</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H107" s="9"/>
-      <c r="I107" s="9"/>
-      <c r="J107" s="9"/>
+        <v>325</v>
+      </c>
+      <c r="H107" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="I107" s="8">
+        <v>46212</v>
+      </c>
+      <c r="J107" s="8">
+        <v>46212</v>
+      </c>
       <c r="K107" s="9" t="s">
         <v>26</v>
       </c>
@@ -8021,13 +8024,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>26</v>
+        <v>337</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8037,32 +8040,34 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B108" s="5">
-        <v>46160.80854525463</v>
-      </c>
-      <c r="C108" s="6"/>
+        <v>46160.65294850695</v>
+      </c>
+      <c r="C108" s="5">
+        <v>46197.49765626158</v>
+      </c>
       <c r="D108" s="5">
-        <v>46224.79338983796</v>
+        <v>46223.58126640046</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>325</v>
+        <v>91</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>326</v>
+        <v>91</v>
       </c>
       <c r="I108" s="5">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="J108" s="5">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="K108" s="6" t="s">
         <v>26</v>
@@ -8074,35 +8079,45 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>58</v>
+        <v>340</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q108" s="6"/>
-      <c r="R108" s="6"/>
-      <c r="S108" s="6"/>
-      <c r="T108" s="6"/>
-      <c r="U108" s="6"/>
+        <v>321</v>
+      </c>
+      <c r="Q108" s="5">
+        <v>46213</v>
+      </c>
+      <c r="R108" s="5">
+        <v>46213</v>
+      </c>
+      <c r="S108" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="T108" s="6">
+        <v>1</v>
+      </c>
+      <c r="U108" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B109" s="8">
-        <v>46160.65294850695</v>
+        <v>46160.652952592594</v>
       </c>
       <c r="C109" s="8">
-        <v>46197.49765626158</v>
+        <v>46197.497369351855</v>
       </c>
       <c r="D109" s="8">
-        <v>46223.58126640046</v>
+        <v>46223.58121423611</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>340</v>
+        <v>216</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8129,42 +8144,32 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>341</v>
+        <v>216</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q109" s="8">
-        <v>46213</v>
-      </c>
-      <c r="R109" s="8">
-        <v>46213</v>
-      </c>
-      <c r="S109" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T109" s="9">
-        <v>1</v>
-      </c>
-      <c r="U109" s="12" t="s">
-        <v>68</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="Q109" s="9"/>
+      <c r="R109" s="9"/>
+      <c r="S109" s="9"/>
+      <c r="T109" s="9"/>
+      <c r="U109" s="9"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B110" s="5">
-        <v>46160.652952592594</v>
+        <v>46160.65295699074</v>
       </c>
       <c r="C110" s="5">
-        <v>46197.497369351855</v>
+        <v>46197.497530023145</v>
       </c>
       <c r="D110" s="5">
-        <v>46223.58121423611</v>
+        <v>46223.581210069446</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>216</v>
@@ -8194,13 +8199,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>216</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8213,16 +8218,14 @@
         <v>344</v>
       </c>
       <c r="B111" s="8">
-        <v>46160.65295699074</v>
-      </c>
-      <c r="C111" s="8">
-        <v>46197.497530023145</v>
-      </c>
+        <v>46160.809122164355</v>
+      </c>
+      <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46223.581210069446</v>
+        <v>46225.55379164351</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>216</v>
+        <v>334</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8249,13 +8252,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>216</v>
+        <v>334</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8265,17 +8268,17 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B112" s="5">
-        <v>46160.809122164355</v>
+        <v>46160.809137627315</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46225.55379164351</v>
+        <v>46223.58120152778</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8302,13 +8305,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>334</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8318,32 +8321,32 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B113" s="8">
-        <v>46160.809137627315</v>
+        <v>46160.652961203705</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46223.58120152778</v>
+        <v>46217.178433506946</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>91</v>
+        <v>246</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>91</v>
+        <v>247</v>
       </c>
       <c r="I113" s="8">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="J113" s="8">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="K113" s="9" t="s">
         <v>26</v>
@@ -8355,33 +8358,43 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>340</v>
+        <v>321</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="Q113" s="9"/>
-      <c r="R113" s="9"/>
-      <c r="S113" s="9"/>
-      <c r="T113" s="9"/>
-      <c r="U113" s="9"/>
+        <v>321</v>
+      </c>
+      <c r="Q113" s="8">
+        <v>46216</v>
+      </c>
+      <c r="R113" s="8">
+        <v>46216</v>
+      </c>
+      <c r="S113" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="T113" s="9">
+        <v>1</v>
+      </c>
+      <c r="U113" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B114" s="5">
-        <v>46160.652961203705</v>
+        <v>46160.65296532407</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46217.178433506946</v>
+        <v>46216.168960752315</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>350</v>
+        <v>216</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8392,9 +8405,7 @@
       <c r="H114" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="I114" s="5">
-        <v>46216</v>
-      </c>
+      <c r="I114" s="6"/>
       <c r="J114" s="5">
         <v>46216</v>
       </c>
@@ -8408,40 +8419,30 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>321</v>
+        <v>349</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>351</v>
+        <v>216</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q114" s="5">
-        <v>46216</v>
-      </c>
-      <c r="R114" s="5">
-        <v>46216</v>
-      </c>
-      <c r="S114" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T114" s="6">
-        <v>1</v>
-      </c>
-      <c r="U114" s="10" t="s">
-        <v>33</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="Q114" s="6"/>
+      <c r="R114" s="6"/>
+      <c r="S114" s="6"/>
+      <c r="T114" s="6"/>
+      <c r="U114" s="6"/>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B115" s="8">
-        <v>46160.65296532407</v>
+        <v>46160.65297267361</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46216.168960752315</v>
+        <v>46216.16895939814</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>216</v>
@@ -8469,13 +8470,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>216</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8485,17 +8486,17 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B116" s="5">
-        <v>46160.65297267361</v>
+        <v>46160.81088733797</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46216.16895939814</v>
+        <v>46216.16896737269</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>216</v>
+        <v>334</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8520,13 +8521,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>216</v>
+        <v>334</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8536,14 +8537,14 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B117" s="8">
-        <v>46160.81088733797</v>
+        <v>46160.81089606481</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46216.16896737269</v>
+        <v>46216.168969085644</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>334</v>
@@ -8571,13 +8572,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8590,14 +8591,14 @@
         <v>358</v>
       </c>
       <c r="B118" s="5">
-        <v>46160.81089606481</v>
+        <v>46160.65297846065</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46216.168969085644</v>
+        <v>46218.17912671296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>334</v>
+        <v>359</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8608,9 +8609,11 @@
       <c r="H118" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="I118" s="6"/>
+      <c r="I118" s="5">
+        <v>46217</v>
+      </c>
       <c r="J118" s="5">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>26</v>
@@ -8622,33 +8625,43 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="O118" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="O118" s="6" t="s">
-        <v>348</v>
-      </c>
       <c r="P118" s="6" t="s">
-        <v>357</v>
-      </c>
-      <c r="Q118" s="6"/>
-      <c r="R118" s="6"/>
-      <c r="S118" s="6"/>
-      <c r="T118" s="6"/>
-      <c r="U118" s="6"/>
+        <v>360</v>
+      </c>
+      <c r="Q118" s="5">
+        <v>46217</v>
+      </c>
+      <c r="R118" s="5">
+        <v>46217</v>
+      </c>
+      <c r="S118" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="T118" s="6">
+        <v>0</v>
+      </c>
+      <c r="U118" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B119" s="8">
-        <v>46160.65297846065</v>
+        <v>46160.652983935186</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46218.17912671296</v>
+        <v>46217.16843326389</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>360</v>
+        <v>216</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8675,40 +8688,30 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>321</v>
+        <v>359</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>351</v>
+        <v>216</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>361</v>
-      </c>
-      <c r="Q119" s="8">
-        <v>46217</v>
-      </c>
-      <c r="R119" s="8">
-        <v>46217</v>
-      </c>
-      <c r="S119" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T119" s="9">
-        <v>0</v>
-      </c>
-      <c r="U119" s="11" t="s">
-        <v>120</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="Q119" s="9"/>
+      <c r="R119" s="9"/>
+      <c r="S119" s="9"/>
+      <c r="T119" s="9"/>
+      <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>362</v>
       </c>
       <c r="B120" s="5">
-        <v>46160.652983935186</v>
+        <v>46160.65298813657</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46217.16843326389</v>
+        <v>46217.16837645833</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>216</v>
@@ -8738,13 +8741,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>216</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8757,14 +8760,14 @@
         <v>363</v>
       </c>
       <c r="B121" s="8">
-        <v>46160.65298813657</v>
+        <v>46160.81215837963</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46217.16837645833</v>
+        <v>46217.168417002315</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>216</v>
+        <v>334</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8791,13 +8794,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>216</v>
+        <v>334</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8810,11 +8813,11 @@
         <v>364</v>
       </c>
       <c r="B122" s="5">
-        <v>46160.81215837963</v>
+        <v>46160.81220768519</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46217.168417002315</v>
+        <v>46217.16841864583</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>334</v>
@@ -8844,13 +8847,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>334</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8863,30 +8866,24 @@
         <v>365</v>
       </c>
       <c r="B123" s="8">
-        <v>46160.81220768519</v>
+        <v>46160.65302554399</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46217.16841864583</v>
+        <v>46160.8192895949</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>334</v>
+        <v>366</v>
       </c>
       <c r="F123" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>246</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>247</v>
-      </c>
-      <c r="I123" s="8">
-        <v>46217</v>
-      </c>
-      <c r="J123" s="8">
-        <v>46217</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H123" s="9"/>
+      <c r="I123" s="9"/>
+      <c r="J123" s="9"/>
       <c r="K123" s="9" t="s">
         <v>26</v>
       </c>
@@ -8894,16 +8891,16 @@
         <v>26</v>
       </c>
       <c r="M123" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>360</v>
+        <v>26</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>334</v>
+        <v>367</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>360</v>
+        <v>26</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -8913,27 +8910,33 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B124" s="5">
-        <v>46160.65302554399</v>
+        <v>46160.65302895833</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46160.8192895949</v>
+        <v>46219.173083553236</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="6"/>
-      <c r="I124" s="6"/>
-      <c r="J124" s="6"/>
+        <v>370</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="I124" s="5">
+        <v>46218</v>
+      </c>
+      <c r="J124" s="5">
+        <v>46226</v>
+      </c>
       <c r="K124" s="6" t="s">
         <v>26</v>
       </c>
@@ -8941,45 +8944,55 @@
         <v>26</v>
       </c>
       <c r="M124" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N124" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="O124" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="P124" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q124" s="5">
+        <v>46218</v>
+      </c>
+      <c r="R124" s="5">
+        <v>46226</v>
+      </c>
+      <c r="S124" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="T124" s="6">
         <v>0</v>
       </c>
-      <c r="N124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O124" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="P124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q124" s="6"/>
-      <c r="R124" s="6"/>
-      <c r="S124" s="6"/>
-      <c r="T124" s="6"/>
-      <c r="U124" s="6"/>
+      <c r="U124" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B125" s="8">
-        <v>46160.65302895833</v>
+        <v>46160.65303386574</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46219.173083553236</v>
+        <v>46219.17308424768</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>371</v>
+        <v>36</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>372</v>
+        <v>37</v>
       </c>
       <c r="I125" s="8">
         <v>46218</v>
@@ -8997,13 +9010,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q125" s="8">
         <v>46218</v>
@@ -9012,7 +9025,7 @@
         <v>46226</v>
       </c>
       <c r="S125" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
@@ -9023,33 +9036,27 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B126" s="5">
-        <v>46160.65303386574</v>
+        <v>46160.65808951389</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46219.17308424768</v>
+        <v>46160.819809513894</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I126" s="5">
-        <v>46218</v>
-      </c>
-      <c r="J126" s="5">
-        <v>46226</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H126" s="6"/>
+      <c r="I126" s="6"/>
+      <c r="J126" s="6"/>
       <c r="K126" s="6" t="s">
         <v>26</v>
       </c>
@@ -9057,25 +9064,21 @@
         <v>26</v>
       </c>
       <c r="M126" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>367</v>
+        <v>26</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="Q126" s="5">
-        <v>46218</v>
-      </c>
-      <c r="R126" s="5">
-        <v>46226</v>
-      </c>
-      <c r="S126" s="12" t="s">
-        <v>373</v>
+        <v>26</v>
+      </c>
+      <c r="Q126" s="6"/>
+      <c r="R126" s="6"/>
+      <c r="S126" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T126" s="6">
         <v>0</v>
@@ -9086,27 +9089,33 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B127" s="8">
-        <v>46160.65808951389</v>
+        <v>46160.66095159722</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46160.819809513894</v>
+        <v>46219.173089097225</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F127" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H127" s="9"/>
-      <c r="I127" s="9"/>
-      <c r="J127" s="9"/>
+        <v>54</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I127" s="8">
+        <v>46218</v>
+      </c>
+      <c r="J127" s="8">
+        <v>46226</v>
+      </c>
       <c r="K127" s="9" t="s">
         <v>26</v>
       </c>
@@ -9114,21 +9123,25 @@
         <v>26</v>
       </c>
       <c r="M127" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>26</v>
+        <v>376</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q127" s="9"/>
-      <c r="R127" s="9"/>
-      <c r="S127" s="10" t="s">
-        <v>32</v>
+        <v>380</v>
+      </c>
+      <c r="Q127" s="8">
+        <v>46218</v>
+      </c>
+      <c r="R127" s="8">
+        <v>46226</v>
+      </c>
+      <c r="S127" s="12" t="s">
+        <v>372</v>
       </c>
       <c r="T127" s="9">
         <v>0</v>
@@ -9139,17 +9152,17 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B128" s="5">
-        <v>46160.66095159722</v>
+        <v>46160.66107538194</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46219.173089097225</v>
+        <v>46160.8199466088</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9161,10 +9174,10 @@
         <v>55</v>
       </c>
       <c r="I128" s="5">
-        <v>46218</v>
+        <v>46227</v>
       </c>
       <c r="J128" s="5">
-        <v>46226</v>
+        <v>46237</v>
       </c>
       <c r="K128" s="6" t="s">
         <v>26</v>
@@ -9176,90 +9189,27 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="Q128" s="5">
-        <v>46218</v>
+        <v>46227</v>
       </c>
       <c r="R128" s="5">
-        <v>46226</v>
-      </c>
-      <c r="S128" s="12" t="s">
-        <v>373</v>
+        <v>46237</v>
+      </c>
+      <c r="S128" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="T128" s="6">
         <v>0</v>
       </c>
       <c r="U128" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="129" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A129" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="B129" s="8">
-        <v>46160.66107538194</v>
-      </c>
-      <c r="C129" s="9"/>
-      <c r="D129" s="8">
-        <v>46160.8199466088</v>
-      </c>
-      <c r="E129" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="F129" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G129" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I129" s="8">
-        <v>46227</v>
-      </c>
-      <c r="J129" s="8">
-        <v>46237</v>
-      </c>
-      <c r="K129" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L129" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M129" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N129" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="O129" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="P129" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q129" s="8">
-        <v>46227</v>
-      </c>
-      <c r="R129" s="8">
-        <v>46237</v>
-      </c>
-      <c r="S129" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T129" s="9">
-        <v>0</v>
-      </c>
-      <c r="U129" s="11" t="s">
         <v>120</v>
       </c>
     </row>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="384">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -349,6 +349,9 @@
     <t>propuesta nucleo rodete ot 4313</t>
   </si>
   <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
     <t>nespinoza@zitron.com</t>
   </si>
   <si>
@@ -820,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -2839,7 +2842,7 @@
         <v>91</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I20" s="5">
         <v>46133</v>
@@ -2863,7 +2866,7 @@
         <v>74</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q20" s="5">
         <v>46133</v>
@@ -2883,7 +2886,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B21" s="8">
         <v>46160.652405636574</v>
@@ -2895,7 +2898,7 @@
         <v>46223.58043296296</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -2904,7 +2907,7 @@
         <v>91</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I21" s="8">
         <v>46162</v>
@@ -2925,10 +2928,10 @@
         <v>81</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q21" s="8">
         <v>46162</v>
@@ -2948,7 +2951,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B22" s="5">
         <v>46160.65241059028</v>
@@ -2960,7 +2963,7 @@
         <v>46223.58042920139</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
@@ -2969,7 +2972,7 @@
         <v>91</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I22" s="5">
         <v>46162</v>
@@ -2990,10 +2993,10 @@
         <v>81</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q22" s="5">
         <v>46162</v>
@@ -3013,7 +3016,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B23" s="8">
         <v>46160.652414490745</v>
@@ -3025,7 +3028,7 @@
         <v>46223.58042574074</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -3034,7 +3037,7 @@
         <v>91</v>
       </c>
       <c r="H23" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I23" s="8">
         <v>46162</v>
@@ -3055,10 +3058,10 @@
         <v>81</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q23" s="8">
         <v>46162</v>
@@ -3078,7 +3081,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B24" s="5">
         <v>46160.65241840278</v>
@@ -3090,7 +3093,7 @@
         <v>46223.58041997685</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3099,7 +3102,7 @@
         <v>91</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I24" s="5">
         <v>46162</v>
@@ -3120,10 +3123,10 @@
         <v>81</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Q24" s="5">
         <v>46162</v>
@@ -3143,7 +3146,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B25" s="8">
         <v>46160.65857868055</v>
@@ -3155,7 +3158,7 @@
         <v>46167.55904253472</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -3188,7 +3191,7 @@
         <v>53</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q25" s="8">
         <v>46134</v>
@@ -3208,7 +3211,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B26" s="5">
         <v>46160.65225063657</v>
@@ -3218,7 +3221,7 @@
         <v>46181.678639652775</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>25</v>
@@ -3242,7 +3245,7 @@
         <v>26</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>26</v>
@@ -3255,7 +3258,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B27" s="8">
         <v>46160.65242274306</v>
@@ -3267,16 +3270,16 @@
         <v>46181.675709143514</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I27" s="8">
         <v>46135</v>
@@ -3294,13 +3297,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q27" s="8">
         <v>46135</v>
@@ -3320,7 +3323,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B28" s="5">
         <v>46160.65242719908</v>
@@ -3332,16 +3335,16 @@
         <v>46181.67563449074</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I28" s="5">
         <v>46135</v>
@@ -3359,13 +3362,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>87</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q28" s="6"/>
       <c r="R28" s="6"/>
@@ -3376,12 +3379,12 @@
         <v>0</v>
       </c>
       <c r="U28" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B29" s="8">
         <v>46160.65243181713</v>
@@ -3393,16 +3396,16 @@
         <v>46181.67567790509</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I29" s="8">
         <v>46139</v>
@@ -3420,13 +3423,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="Q29" s="9"/>
       <c r="R29" s="9"/>
@@ -3437,12 +3440,12 @@
         <v>0</v>
       </c>
       <c r="U29" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B30" s="5">
         <v>46160.65243667824</v>
@@ -3454,16 +3457,16 @@
         <v>46181.67562327546</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I30" s="5">
         <v>46135</v>
@@ -3481,13 +3484,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q30" s="5">
         <v>46135</v>
@@ -3507,7 +3510,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B31" s="8">
         <v>46160.65244107639</v>
@@ -3519,16 +3522,16 @@
         <v>46181.67555395833</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I31" s="8">
         <v>46135</v>
@@ -3546,13 +3549,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
@@ -3563,12 +3566,12 @@
         <v>0</v>
       </c>
       <c r="U31" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B32" s="5">
         <v>46160.65244578704</v>
@@ -3580,16 +3583,16 @@
         <v>46181.67559840278</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I32" s="5">
         <v>46139</v>
@@ -3607,13 +3610,13 @@
         <v>26</v>
       </c>
       <c r="N32" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P32" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
@@ -3624,12 +3627,12 @@
         <v>0</v>
       </c>
       <c r="U32" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B33" s="8">
         <v>46160.652450625</v>
@@ -3641,16 +3644,16 @@
         <v>46181.67549369213</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I33" s="8">
         <v>46133</v>
@@ -3668,13 +3671,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q33" s="8">
         <v>46133</v>
@@ -3694,7 +3697,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B34" s="5">
         <v>46160.65245552083</v>
@@ -3706,16 +3709,16 @@
         <v>46181.67541268519</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I34" s="5">
         <v>46133</v>
@@ -3733,13 +3736,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -3750,12 +3753,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B35" s="8">
         <v>46160.65246048611</v>
@@ -3767,16 +3770,16 @@
         <v>46181.67545391204</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I35" s="8">
         <v>46142</v>
@@ -3794,13 +3797,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -3811,12 +3814,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B36" s="5">
         <v>46160.6524655324</v>
@@ -3828,16 +3831,16 @@
         <v>46181.67546648148</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I36" s="5">
         <v>46141</v>
@@ -3855,13 +3858,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Q36" s="6"/>
       <c r="R36" s="6"/>
@@ -3872,12 +3875,12 @@
         <v>0</v>
       </c>
       <c r="U36" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B37" s="8">
         <v>46160.6566696875</v>
@@ -3887,16 +3890,16 @@
         <v>46197.19306372685</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I37" s="8">
         <v>46136</v>
@@ -3914,10 +3917,10 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>26</v>
@@ -3935,12 +3938,12 @@
         <v>0</v>
       </c>
       <c r="U37" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B38" s="5">
         <v>46160.65676351852</v>
@@ -3952,16 +3955,16 @@
         <v>46182.67674333333</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I38" s="5">
         <v>46136</v>
@@ -3979,13 +3982,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -3995,7 +3998,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B39" s="8">
         <v>46160.65688415509</v>
@@ -4005,16 +4008,16 @@
         <v>46196.16898914352</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I39" s="8">
         <v>46148</v>
@@ -4032,13 +4035,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4048,7 +4051,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B40" s="5">
         <v>46160.65247015047</v>
@@ -4060,16 +4063,16 @@
         <v>46181.676244386574</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I40" s="5">
         <v>46167</v>
@@ -4087,13 +4090,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q40" s="5">
         <v>46167</v>
@@ -4113,7 +4116,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B41" s="8">
         <v>46160.65247482639</v>
@@ -4125,16 +4128,16 @@
         <v>46181.67615008102</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I41" s="8">
         <v>46167</v>
@@ -4152,13 +4155,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4169,12 +4172,12 @@
         <v>0</v>
       </c>
       <c r="U41" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B42" s="5">
         <v>46160.65247959491</v>
@@ -4186,16 +4189,16 @@
         <v>46181.67622016204</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I42" s="5">
         <v>46169</v>
@@ -4213,13 +4216,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4230,12 +4233,12 @@
         <v>0</v>
       </c>
       <c r="U42" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B43" s="8">
         <v>46160.65254070602</v>
@@ -4247,16 +4250,16 @@
         <v>46181.67636662037</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I43" s="8">
         <v>46167</v>
@@ -4274,10 +4277,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4300,7 +4303,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B44" s="5">
         <v>46160.65254572917</v>
@@ -4312,16 +4315,16 @@
         <v>46181.67630162037</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I44" s="5">
         <v>46167</v>
@@ -4339,13 +4342,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4355,7 +4358,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B45" s="8">
         <v>46160.652551377316</v>
@@ -4367,16 +4370,16 @@
         <v>46181.67634090278</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I45" s="8">
         <v>46169</v>
@@ -4394,13 +4397,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4410,7 +4413,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B46" s="5">
         <v>46160.652557152775</v>
@@ -4422,16 +4425,16 @@
         <v>46206.17392120371</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I46" s="5">
         <v>46167</v>
@@ -4449,10 +4452,10 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>26</v>
@@ -4475,7 +4478,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B47" s="8">
         <v>46160.65256162037</v>
@@ -4487,16 +4490,16 @@
         <v>46181.67638900463</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I47" s="8">
         <v>46167</v>
@@ -4514,13 +4517,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4530,7 +4533,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B48" s="5">
         <v>46160.6525734375</v>
@@ -4542,16 +4545,16 @@
         <v>46181.67642934028</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I48" s="5">
         <v>46176</v>
@@ -4569,13 +4572,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -4585,7 +4588,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B49" s="8">
         <v>46160.652579236106</v>
@@ -4597,16 +4600,16 @@
         <v>46181.676467303245</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I49" s="8">
         <v>46205</v>
@@ -4624,10 +4627,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -4640,7 +4643,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B50" s="5">
         <v>46160.65258304398</v>
@@ -4652,16 +4655,16 @@
         <v>46181.67657885417</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I50" s="5">
         <v>46167</v>
@@ -4679,10 +4682,10 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>26</v>
@@ -4705,7 +4708,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B51" s="8">
         <v>46160.6525875463</v>
@@ -4717,16 +4720,16 @@
         <v>46181.67651314815</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I51" s="8">
         <v>46167</v>
@@ -4744,13 +4747,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -4760,7 +4763,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B52" s="5">
         <v>46160.652593067134</v>
@@ -4772,16 +4775,16 @@
         <v>46181.676553680554</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I52" s="5">
         <v>46169</v>
@@ -4799,13 +4802,13 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="Q52" s="6"/>
       <c r="R52" s="6"/>
@@ -4815,7 +4818,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B53" s="8">
         <v>46160.65225516204</v>
@@ -4827,7 +4830,7 @@
         <v>46181.67858451389</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>25</v>
@@ -4851,7 +4854,7 @@
         <v>26</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>26</v>
@@ -4864,7 +4867,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B54" s="5">
         <v>46160.65259921296</v>
@@ -4876,16 +4879,16 @@
         <v>46197.712640196754</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I54" s="5">
         <v>46140</v>
@@ -4903,13 +4906,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>78</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q54" s="5">
         <v>46140</v>
@@ -4929,7 +4932,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B55" s="8">
         <v>46160.652606006945</v>
@@ -4941,16 +4944,16 @@
         <v>46197.71267317129</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I55" s="8">
         <v>46153</v>
@@ -4968,13 +4971,13 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P55" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q55" s="8">
         <v>46153</v>
@@ -4994,7 +4997,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B56" s="5">
         <v>46160.65261409723</v>
@@ -5006,16 +5009,16 @@
         <v>46181.67578048611</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I56" s="5">
         <v>46160</v>
@@ -5033,13 +5036,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="Q56" s="5">
         <v>46160</v>
@@ -5059,7 +5062,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B57" s="8">
         <v>46160.652630983794</v>
@@ -5071,16 +5074,16 @@
         <v>46211.169411759256</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I57" s="8">
         <v>46210</v>
@@ -5098,10 +5101,10 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>26</v>
@@ -5124,7 +5127,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B58" s="5">
         <v>46160.65263532408</v>
@@ -5136,16 +5139,16 @@
         <v>46198.566085625</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I58" s="5">
         <v>46210</v>
@@ -5163,13 +5166,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5179,7 +5182,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B59" s="8">
         <v>46160.65264069445</v>
@@ -5191,16 +5194,16 @@
         <v>46198.5661015625</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="I59" s="8">
         <v>46210</v>
@@ -5218,13 +5221,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5234,7 +5237,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B60" s="5">
         <v>46160.652676921294</v>
@@ -5246,7 +5249,7 @@
         <v>46181.67816971065</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>25</v>
@@ -5270,7 +5273,7 @@
         <v>26</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>26</v>
@@ -5283,7 +5286,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B61" s="8">
         <v>46160.65268083333</v>
@@ -5295,16 +5298,16 @@
         <v>46182.19861893519</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I61" s="8">
         <v>46178</v>
@@ -5322,13 +5325,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q61" s="8">
         <v>46178</v>
@@ -5348,7 +5351,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B62" s="5">
         <v>46160.652685810186</v>
@@ -5360,16 +5363,16 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I62" s="5">
         <v>46182</v>
@@ -5387,13 +5390,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q62" s="5">
         <v>46182</v>
@@ -5413,7 +5416,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B63" s="8">
         <v>46160.65269097222</v>
@@ -5425,16 +5428,16 @@
         <v>46181.6766224537</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I63" s="8">
         <v>46178</v>
@@ -5452,13 +5455,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q63" s="8">
         <v>46147</v>
@@ -5478,7 +5481,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B64" s="5">
         <v>46160.65269633102</v>
@@ -5490,16 +5493,16 @@
         <v>46184.17212899306</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I64" s="5">
         <v>46182</v>
@@ -5517,13 +5520,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q64" s="5">
         <v>46182</v>
@@ -5543,7 +5546,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B65" s="8">
         <v>46160.65269980324</v>
@@ -5555,16 +5558,16 @@
         <v>46181.67666866898</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I65" s="8">
         <v>46178</v>
@@ -5582,13 +5585,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q65" s="8">
         <v>46147</v>
@@ -5608,7 +5611,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B66" s="5">
         <v>46160.652703935186</v>
@@ -5620,16 +5623,16 @@
         <v>46184.172129004626</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I66" s="5">
         <v>46182</v>
@@ -5647,13 +5650,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q66" s="5">
         <v>46182</v>
@@ -5673,7 +5676,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B67" s="8">
         <v>46160.65270767361</v>
@@ -5685,7 +5688,7 @@
         <v>46181.6781084838</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5709,7 +5712,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5722,7 +5725,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B68" s="5">
         <v>46160.65271061343</v>
@@ -5731,19 +5734,19 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46225.58945353009</v>
+        <v>46225.86189206019</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I68" s="5">
         <v>46184</v>
@@ -5761,13 +5764,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q68" s="5">
         <v>46184</v>
@@ -5787,7 +5790,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B69" s="8">
         <v>46160.65271650463</v>
@@ -5799,16 +5802,16 @@
         <v>46181.67713434028</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I69" s="8">
         <v>46184</v>
@@ -5826,13 +5829,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5842,7 +5845,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B70" s="5">
         <v>46160.65272224537</v>
@@ -5854,16 +5857,16 @@
         <v>46181.67713509259</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I70" s="5">
         <v>46184</v>
@@ -5881,13 +5884,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -5897,7 +5900,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B71" s="8">
         <v>46160.652726898144</v>
@@ -5909,16 +5912,16 @@
         <v>46196.198199756946</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I71" s="8">
         <v>46189</v>
@@ -5936,13 +5939,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q71" s="8">
         <v>46189</v>
@@ -5962,7 +5965,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B72" s="5">
         <v>46160.65273052083</v>
@@ -5974,16 +5977,16 @@
         <v>46181.67719854167</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I72" s="5">
         <v>46189</v>
@@ -6001,13 +6004,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6017,7 +6020,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B73" s="8">
         <v>46160.652741620375</v>
@@ -6029,16 +6032,16 @@
         <v>46181.67721436343</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I73" s="8">
         <v>46189</v>
@@ -6056,13 +6059,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6072,7 +6075,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B74" s="5">
         <v>46160.65274630787</v>
@@ -6084,16 +6087,16 @@
         <v>46197.19306369213</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I74" s="5">
         <v>46196</v>
@@ -6111,13 +6114,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q74" s="5">
         <v>46196</v>
@@ -6137,7 +6140,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B75" s="8">
         <v>46160.65275005787</v>
@@ -6149,16 +6152,16 @@
         <v>46181.67726512731</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I75" s="8">
         <v>46196</v>
@@ -6176,13 +6179,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6192,7 +6195,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B76" s="5">
         <v>46160.65275548611</v>
@@ -6204,16 +6207,16 @@
         <v>46181.677274664355</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I76" s="5">
         <v>46196</v>
@@ -6231,13 +6234,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6247,7 +6250,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B77" s="8">
         <v>46160.652760625</v>
@@ -6259,7 +6262,7 @@
         <v>46181.67751854166</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>25</v>
@@ -6283,7 +6286,7 @@
         <v>26</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6296,7 +6299,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B78" s="5">
         <v>46160.65276340277</v>
@@ -6308,16 +6311,16 @@
         <v>46192.20460657407</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I78" s="5">
         <v>46160</v>
@@ -6335,13 +6338,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q78" s="5">
         <v>46160</v>
@@ -6361,7 +6364,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B79" s="8">
         <v>46160.652768831016</v>
@@ -6373,16 +6376,16 @@
         <v>46181.677345034725</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I79" s="8">
         <v>46141</v>
@@ -6400,13 +6403,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q79" s="8">
         <v>46141</v>
@@ -6426,7 +6429,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B80" s="5">
         <v>46160.652774409726</v>
@@ -6438,16 +6441,16 @@
         <v>46181.67735619213</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I80" s="5">
         <v>46174</v>
@@ -6465,13 +6468,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q80" s="5">
         <v>46174</v>
@@ -6491,7 +6494,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B81" s="8">
         <v>46160.652779745375</v>
@@ -6503,16 +6506,16 @@
         <v>46207.188708125</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I81" s="8">
         <v>46206</v>
@@ -6530,13 +6533,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q81" s="8">
         <v>46206</v>
@@ -6556,7 +6559,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B82" s="5">
         <v>46160.657067569446</v>
@@ -6572,10 +6575,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I82" s="5">
         <v>46197</v>
@@ -6593,10 +6596,10 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P82" s="6" t="s">
         <v>58</v>
@@ -6614,12 +6617,12 @@
         <v>0</v>
       </c>
       <c r="U82" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B83" s="8">
         <v>46160.65278418981</v>
@@ -6631,7 +6634,7 @@
         <v>46197.49724974537</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>25</v>
@@ -6655,7 +6658,7 @@
         <v>26</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P83" s="9" t="s">
         <v>26</v>
@@ -6670,7 +6673,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B84" s="5">
         <v>46160.65278701389</v>
@@ -6682,7 +6685,7 @@
         <v>46223.58112633102</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6691,7 +6694,7 @@
         <v>91</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I84" s="5">
         <v>46197</v>
@@ -6709,13 +6712,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q84" s="5">
         <v>46197</v>
@@ -6735,7 +6738,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B85" s="8">
         <v>46160.65279357639</v>
@@ -6747,7 +6750,7 @@
         <v>46223.58052726852</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6756,7 +6759,7 @@
         <v>91</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I85" s="8">
         <v>46197</v>
@@ -6774,10 +6777,10 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>26</v>
@@ -6790,7 +6793,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B86" s="5">
         <v>46160.65279733796</v>
@@ -6802,7 +6805,7 @@
         <v>46223.58052398148</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6811,7 +6814,7 @@
         <v>91</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I86" s="5">
         <v>46197</v>
@@ -6829,10 +6832,10 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P86" s="6" t="s">
         <v>26</v>
@@ -6845,7 +6848,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B87" s="8">
         <v>46160.65280108796</v>
@@ -6857,7 +6860,7 @@
         <v>46223.5811225</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -6866,7 +6869,7 @@
         <v>91</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I87" s="8">
         <v>46204</v>
@@ -6884,13 +6887,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -6910,7 +6913,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B88" s="5">
         <v>46160.65280498842</v>
@@ -6922,7 +6925,7 @@
         <v>46223.58062439815</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -6931,7 +6934,7 @@
         <v>91</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I88" s="5">
         <v>46204</v>
@@ -6949,13 +6952,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q88" s="6"/>
       <c r="R88" s="6"/>
@@ -6965,7 +6968,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B89" s="8">
         <v>46160.65281013889</v>
@@ -6977,7 +6980,7 @@
         <v>46223.5806209375</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -6986,7 +6989,7 @@
         <v>91</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I89" s="8">
         <v>46204</v>
@@ -7004,13 +7007,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q89" s="9"/>
       <c r="R89" s="9"/>
@@ -7020,7 +7023,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B90" s="5">
         <v>46160.65281503472</v>
@@ -7032,7 +7035,7 @@
         <v>46223.581118692135</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7041,7 +7044,7 @@
         <v>91</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I90" s="5">
         <v>46205</v>
@@ -7059,13 +7062,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q90" s="5">
         <v>46205</v>
@@ -7085,7 +7088,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B91" s="8">
         <v>46160.65281883102</v>
@@ -7097,7 +7100,7 @@
         <v>46223.5807081713</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
@@ -7106,7 +7109,7 @@
         <v>91</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I91" s="9"/>
       <c r="J91" s="8">
@@ -7122,13 +7125,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7138,7 +7141,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B92" s="5">
         <v>46160.65287608796</v>
@@ -7150,7 +7153,7 @@
         <v>46223.580704803244</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
@@ -7159,7 +7162,7 @@
         <v>91</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I92" s="6"/>
       <c r="J92" s="5">
@@ -7175,13 +7178,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7191,7 +7194,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B93" s="8">
         <v>46160.65288447917</v>
@@ -7203,7 +7206,7 @@
         <v>46223.58111460648</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7212,7 +7215,7 @@
         <v>91</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I93" s="8">
         <v>46206</v>
@@ -7230,13 +7233,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q93" s="8">
         <v>46206</v>
@@ -7256,7 +7259,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B94" s="5">
         <v>46160.65288969908</v>
@@ -7268,7 +7271,7 @@
         <v>46223.58079063657</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7277,7 +7280,7 @@
         <v>91</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I94" s="5">
         <v>46206</v>
@@ -7295,13 +7298,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7311,7 +7314,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B95" s="8">
         <v>46160.6528953588</v>
@@ -7323,7 +7326,7 @@
         <v>46223.58078703703</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7332,7 +7335,7 @@
         <v>91</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I95" s="8">
         <v>46206</v>
@@ -7350,13 +7353,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7366,7 +7369,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B96" s="5">
         <v>46160.652900706016</v>
@@ -7378,7 +7381,7 @@
         <v>46223.58111108796</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7387,7 +7390,7 @@
         <v>91</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I96" s="5">
         <v>46209</v>
@@ -7405,13 +7408,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q96" s="5">
         <v>46209</v>
@@ -7431,7 +7434,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B97" s="8">
         <v>46160.65290569444</v>
@@ -7443,7 +7446,7 @@
         <v>46223.58087722222</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7452,7 +7455,7 @@
         <v>91</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I97" s="8">
         <v>46209</v>
@@ -7470,13 +7473,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7486,7 +7489,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B98" s="5">
         <v>46160.652911157405</v>
@@ -7498,7 +7501,7 @@
         <v>46223.58087362269</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
@@ -7507,7 +7510,7 @@
         <v>91</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I98" s="5">
         <v>46209</v>
@@ -7525,13 +7528,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q98" s="6"/>
       <c r="R98" s="6"/>
@@ -7541,7 +7544,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B99" s="8">
         <v>46160.65291657408</v>
@@ -7553,7 +7556,7 @@
         <v>46223.58110539352</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7562,7 +7565,7 @@
         <v>91</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I99" s="8">
         <v>46211</v>
@@ -7580,13 +7583,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q99" s="8">
         <v>46211</v>
@@ -7606,7 +7609,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B100" s="5">
         <v>46160.652921562505</v>
@@ -7618,7 +7621,7 @@
         <v>46223.58100638889</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7627,7 +7630,7 @@
         <v>91</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I100" s="6"/>
       <c r="J100" s="5">
@@ -7643,13 +7646,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -7659,7 +7662,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B101" s="8">
         <v>46160.65292620371</v>
@@ -7671,7 +7674,7 @@
         <v>46223.581002708335</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -7680,7 +7683,7 @@
         <v>91</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I101" s="9"/>
       <c r="J101" s="8">
@@ -7696,13 +7699,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -7712,7 +7715,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B102" s="5">
         <v>46160.65293084491</v>
@@ -7722,7 +7725,7 @@
         <v>46197.49766417824</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>25</v>
@@ -7746,7 +7749,7 @@
         <v>26</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>26</v>
@@ -7759,26 +7762,26 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B103" s="8">
         <v>46160.65293431713</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46225.55379075231</v>
+        <v>46225.80626024306</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I103" s="8">
         <v>46212</v>
@@ -7796,13 +7799,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q103" s="8">
         <v>46212</v>
@@ -7822,7 +7825,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B104" s="5">
         <v>46160.65293966435</v>
@@ -7834,16 +7837,16 @@
         <v>46204.80222355324</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I104" s="5">
         <v>46212</v>
@@ -7861,13 +7864,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q104" s="6"/>
       <c r="R104" s="6"/>
@@ -7877,28 +7880,26 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B105" s="8">
         <v>46160.652944201385</v>
       </c>
-      <c r="C105" s="8">
-        <v>46204.80248626157</v>
-      </c>
+      <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46223.580941493055</v>
+        <v>46225.806255972224</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I105" s="8">
         <v>46212</v>
@@ -7910,19 +7911,19 @@
         <v>26</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -7932,7 +7933,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B106" s="5">
         <v>46160.80816486111</v>
@@ -7944,16 +7945,16 @@
         <v>46225.55378673611</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I106" s="5">
         <v>46212</v>
@@ -7971,13 +7972,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>58</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -7987,7 +7988,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B107" s="8">
         <v>46160.80854525463</v>
@@ -7997,16 +7998,16 @@
         <v>46224.79338983796</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="I107" s="8">
         <v>46212</v>
@@ -8024,13 +8025,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>58</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8040,7 +8041,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B108" s="5">
         <v>46160.65294850695</v>
@@ -8052,7 +8053,7 @@
         <v>46223.58126640046</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8061,7 +8062,7 @@
         <v>91</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I108" s="5">
         <v>46213</v>
@@ -8079,13 +8080,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q108" s="5">
         <v>46213</v>
@@ -8105,7 +8106,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B109" s="8">
         <v>46160.652952592594</v>
@@ -8117,7 +8118,7 @@
         <v>46223.58121423611</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8126,7 +8127,7 @@
         <v>91</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I109" s="8">
         <v>46213</v>
@@ -8144,13 +8145,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8160,7 +8161,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B110" s="5">
         <v>46160.65295699074</v>
@@ -8169,10 +8170,10 @@
         <v>46197.497530023145</v>
       </c>
       <c r="D110" s="5">
-        <v>46223.581210069446</v>
+        <v>46225.80626063657</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8181,7 +8182,7 @@
         <v>91</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I110" s="5">
         <v>46213</v>
@@ -8199,13 +8200,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
@@ -8215,7 +8216,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B111" s="8">
         <v>46160.809122164355</v>
@@ -8225,7 +8226,7 @@
         <v>46225.55379164351</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8234,7 +8235,7 @@
         <v>91</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I111" s="8">
         <v>46213</v>
@@ -8252,13 +8253,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8268,7 +8269,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B112" s="5">
         <v>46160.809137627315</v>
@@ -8278,7 +8279,7 @@
         <v>46223.58120152778</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8287,7 +8288,7 @@
         <v>91</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I112" s="5">
         <v>46213</v>
@@ -8305,13 +8306,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8321,7 +8322,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B113" s="8">
         <v>46160.652961203705</v>
@@ -8331,16 +8332,16 @@
         <v>46217.178433506946</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I113" s="8">
         <v>46216</v>
@@ -8358,13 +8359,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q113" s="8">
         <v>46216</v>
@@ -8384,7 +8385,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B114" s="5">
         <v>46160.65296532407</v>
@@ -8394,16 +8395,16 @@
         <v>46216.168960752315</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I114" s="6"/>
       <c r="J114" s="5">
@@ -8419,13 +8420,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8435,7 +8436,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B115" s="8">
         <v>46160.65297267361</v>
@@ -8445,16 +8446,16 @@
         <v>46216.16895939814</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="8">
@@ -8470,13 +8471,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8486,7 +8487,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B116" s="5">
         <v>46160.81088733797</v>
@@ -8496,16 +8497,16 @@
         <v>46216.16896737269</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I116" s="6"/>
       <c r="J116" s="5">
@@ -8521,13 +8522,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
@@ -8537,7 +8538,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B117" s="8">
         <v>46160.81089606481</v>
@@ -8547,16 +8548,16 @@
         <v>46216.168969085644</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="8">
@@ -8572,13 +8573,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8588,7 +8589,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B118" s="5">
         <v>46160.65297846065</v>
@@ -8598,16 +8599,16 @@
         <v>46218.17912671296</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I118" s="5">
         <v>46217</v>
@@ -8625,13 +8626,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q118" s="5">
         <v>46217</v>
@@ -8646,12 +8647,12 @@
         <v>0</v>
       </c>
       <c r="U118" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B119" s="8">
         <v>46160.652983935186</v>
@@ -8661,16 +8662,16 @@
         <v>46217.16843326389</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I119" s="8">
         <v>46217</v>
@@ -8688,13 +8689,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -8704,7 +8705,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B120" s="5">
         <v>46160.65298813657</v>
@@ -8714,16 +8715,16 @@
         <v>46217.16837645833</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I120" s="5">
         <v>46217</v>
@@ -8741,13 +8742,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8757,7 +8758,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B121" s="8">
         <v>46160.81215837963</v>
@@ -8767,16 +8768,16 @@
         <v>46217.168417002315</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I121" s="8">
         <v>46217</v>
@@ -8794,13 +8795,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -8810,7 +8811,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B122" s="5">
         <v>46160.81220768519</v>
@@ -8820,16 +8821,16 @@
         <v>46217.16841864583</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I122" s="5">
         <v>46217</v>
@@ -8847,13 +8848,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -8863,7 +8864,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B123" s="8">
         <v>46160.65302554399</v>
@@ -8873,7 +8874,7 @@
         <v>46160.8192895949</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>25</v>
@@ -8897,7 +8898,7 @@
         <v>26</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P123" s="9" t="s">
         <v>26</v>
@@ -8910,7 +8911,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B124" s="5">
         <v>46160.65302895833</v>
@@ -8920,16 +8921,16 @@
         <v>46219.173083553236</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="I124" s="5">
         <v>46218</v>
@@ -8947,13 +8948,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q124" s="5">
         <v>46218</v>
@@ -8962,18 +8963,18 @@
         <v>46226</v>
       </c>
       <c r="S124" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T124" s="6">
         <v>0</v>
       </c>
       <c r="U124" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B125" s="8">
         <v>46160.65303386574</v>
@@ -8983,7 +8984,7 @@
         <v>46219.17308424768</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9010,13 +9011,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q125" s="8">
         <v>46218</v>
@@ -9025,18 +9026,18 @@
         <v>46226</v>
       </c>
       <c r="S125" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
       </c>
       <c r="U125" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B126" s="5">
         <v>46160.65808951389</v>
@@ -9046,7 +9047,7 @@
         <v>46160.819809513894</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>25</v>
@@ -9070,7 +9071,7 @@
         <v>26</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -9084,12 +9085,12 @@
         <v>0</v>
       </c>
       <c r="U126" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B127" s="8">
         <v>46160.66095159722</v>
@@ -9099,7 +9100,7 @@
         <v>46219.173089097225</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9126,13 +9127,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q127" s="8">
         <v>46218</v>
@@ -9141,18 +9142,18 @@
         <v>46226</v>
       </c>
       <c r="S127" s="12" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="T127" s="9">
         <v>0</v>
       </c>
       <c r="U127" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B128" s="5">
         <v>46160.66107538194</v>
@@ -9162,7 +9163,7 @@
         <v>46160.8199466088</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9189,13 +9190,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q128" s="5">
         <v>46227</v>
@@ -9210,7 +9211,7 @@
         <v>0</v>
       </c>
       <c r="U128" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -8918,7 +8918,7 @@
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46219.173083553236</v>
+        <v>46226.1680884838</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>370</v>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46219.17308424768</v>
+        <v>46226.16809032408</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>375</v>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46219.173089097225</v>
+        <v>46226.16806592593</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>380</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1525" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="384">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -265,6 +265,9 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1214892476594829</t>
   </si>
   <si>
@@ -272,9 +275,6 @@
   </si>
   <si>
     <t>Ingenieria basica Rodete,Ingenieria Detalle,Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1214909462744422</t>
@@ -1195,37 +1195,37 @@
     <t>nicolas.tello@zitron.com</t>
   </si>
   <si>
+    <t>1214909653811621</t>
+  </si>
+  <si>
+    <t>Costos</t>
+  </si>
+  <si>
+    <t>1214889077215100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puesta En Marcha </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instalación componentes,Pruebas de Instalacion Componentes </t>
+  </si>
+  <si>
+    <t>1214889077215114</t>
+  </si>
+  <si>
+    <t>Instalación componentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pruebas de Instalacion Componentes ,Puesta En Marcha </t>
+  </si>
+  <si>
+    <t>1214889077215116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pruebas de Instalacion Componentes </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1214909653811621</t>
-  </si>
-  <si>
-    <t>Costos</t>
-  </si>
-  <si>
-    <t>1214889077215100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta En Marcha </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalación componentes,Pruebas de Instalacion Componentes </t>
-  </si>
-  <si>
-    <t>1214889077215114</t>
-  </si>
-  <si>
-    <t>Instalación componentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de Instalacion Componentes ,Puesta En Marcha </t>
-  </si>
-  <si>
-    <t>1214889077215116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de Instalacion Componentes </t>
   </si>
 </sst>
 </file>
@@ -2342,7 +2342,7 @@
         <v>46224.79337738426</v>
       </c>
       <c r="D12" s="5">
-        <v>46225.58331327546</v>
+        <v>46227.57633402778</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>58</v>
@@ -2392,13 +2392,13 @@
       <c r="T12" s="6">
         <v>1</v>
       </c>
-      <c r="U12" s="10" t="s">
-        <v>33</v>
+      <c r="U12" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" s="8">
         <v>46160.65224207176</v>
@@ -2408,7 +2408,7 @@
         <v>46199.75069068287</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>25</v>
@@ -2432,7 +2432,7 @@
         <v>26</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P13" s="9" t="s">
         <v>26</v>
@@ -2442,7 +2442,7 @@
       <c r="S13" s="9"/>
       <c r="T13" s="9"/>
       <c r="U13" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -2486,7 +2486,7 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>43</v>
@@ -2551,7 +2551,7 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>43</v>
@@ -2616,7 +2616,7 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>43</v>
@@ -2946,7 +2946,7 @@
         <v>1</v>
       </c>
       <c r="U21" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -6564,9 +6564,11 @@
       <c r="B82" s="5">
         <v>46160.657067569446</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46227.576312812496</v>
+      </c>
       <c r="D82" s="5">
-        <v>46198.18861751157</v>
+        <v>46227.57633418981</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>62</v>
@@ -6614,10 +6616,10 @@
         <v>64</v>
       </c>
       <c r="T82" s="6">
-        <v>0</v>
-      </c>
-      <c r="U82" s="11" t="s">
-        <v>121</v>
+        <v>1</v>
+      </c>
+      <c r="U82" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -6668,7 +6670,7 @@
       <c r="S83" s="9"/>
       <c r="T83" s="9"/>
       <c r="U83" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
@@ -7604,7 +7606,7 @@
         <v>1</v>
       </c>
       <c r="U99" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -7722,7 +7724,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46197.49766417824</v>
+        <v>46227.57668873842</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>322</v>
@@ -7758,7 +7760,9 @@
       <c r="R102" s="6"/>
       <c r="S102" s="6"/>
       <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
+      <c r="U102" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
@@ -7767,9 +7771,11 @@
       <c r="B103" s="8">
         <v>46160.65293431713</v>
       </c>
-      <c r="C103" s="9"/>
+      <c r="C103" s="8">
+        <v>46227.576506400466</v>
+      </c>
       <c r="D103" s="8">
-        <v>46225.80626024306</v>
+        <v>46227.57650934027</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>325</v>
@@ -7819,8 +7825,8 @@
       <c r="T103" s="9">
         <v>1</v>
       </c>
-      <c r="U103" s="10" t="s">
-        <v>33</v>
+      <c r="U103" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -7885,9 +7891,11 @@
       <c r="B105" s="8">
         <v>46160.652944201385</v>
       </c>
-      <c r="C105" s="9"/>
+      <c r="C105" s="8">
+        <v>46227.57636880787</v>
+      </c>
       <c r="D105" s="8">
-        <v>46225.806255972224</v>
+        <v>46227.57637015046</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>217</v>
@@ -7993,9 +8001,11 @@
       <c r="B107" s="8">
         <v>46160.80854525463</v>
       </c>
-      <c r="C107" s="9"/>
+      <c r="C107" s="8">
+        <v>46227.57648959491</v>
+      </c>
       <c r="D107" s="8">
-        <v>46224.79338983796</v>
+        <v>46227.57649270834</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>335</v>
@@ -8050,7 +8060,7 @@
         <v>46197.49765626158</v>
       </c>
       <c r="D108" s="5">
-        <v>46223.58126640046</v>
+        <v>46227.576563599534</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>340</v>
@@ -8101,7 +8111,7 @@
         <v>1</v>
       </c>
       <c r="U108" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -8170,7 +8180,7 @@
         <v>46197.497530023145</v>
       </c>
       <c r="D110" s="5">
-        <v>46225.80626063657</v>
+        <v>46227.576376701385</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>217</v>
@@ -8221,9 +8231,11 @@
       <c r="B111" s="8">
         <v>46160.809122164355</v>
       </c>
-      <c r="C111" s="9"/>
+      <c r="C111" s="8">
+        <v>46227.57655219907</v>
+      </c>
       <c r="D111" s="8">
-        <v>46225.55379164351</v>
+        <v>46227.57655346065</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>335</v>
@@ -8274,9 +8286,11 @@
       <c r="B112" s="5">
         <v>46160.809137627315</v>
       </c>
-      <c r="C112" s="6"/>
+      <c r="C112" s="5">
+        <v>46227.5765587037</v>
+      </c>
       <c r="D112" s="5">
-        <v>46223.58120152778</v>
+        <v>46227.57656003472</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>348</v>
@@ -8327,9 +8341,11 @@
       <c r="B113" s="8">
         <v>46160.652961203705</v>
       </c>
-      <c r="C113" s="9"/>
+      <c r="C113" s="8">
+        <v>46227.57661524306</v>
+      </c>
       <c r="D113" s="8">
-        <v>46217.178433506946</v>
+        <v>46227.57662746528</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>350</v>
@@ -8390,9 +8406,11 @@
       <c r="B114" s="5">
         <v>46160.65296532407</v>
       </c>
-      <c r="C114" s="6"/>
+      <c r="C114" s="5">
+        <v>46227.576415682866</v>
+      </c>
       <c r="D114" s="5">
-        <v>46216.168960752315</v>
+        <v>46227.576417372686</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>217</v>
@@ -8441,9 +8459,11 @@
       <c r="B115" s="8">
         <v>46160.65297267361</v>
       </c>
-      <c r="C115" s="9"/>
+      <c r="C115" s="8">
+        <v>46227.57642085648</v>
+      </c>
       <c r="D115" s="8">
-        <v>46216.16895939814</v>
+        <v>46227.57642239583</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>217</v>
@@ -8492,9 +8512,11 @@
       <c r="B116" s="5">
         <v>46160.81088733797</v>
       </c>
-      <c r="C116" s="6"/>
+      <c r="C116" s="5">
+        <v>46227.57658846065</v>
+      </c>
       <c r="D116" s="5">
-        <v>46216.16896737269</v>
+        <v>46227.57658972222</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>335</v>
@@ -8543,9 +8565,11 @@
       <c r="B117" s="8">
         <v>46160.81089606481</v>
       </c>
-      <c r="C117" s="9"/>
+      <c r="C117" s="8">
+        <v>46227.57659865741</v>
+      </c>
       <c r="D117" s="8">
-        <v>46216.168969085644</v>
+        <v>46227.57660032407</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>335</v>
@@ -8594,9 +8618,11 @@
       <c r="B118" s="5">
         <v>46160.65297846065</v>
       </c>
-      <c r="C118" s="6"/>
+      <c r="C118" s="5">
+        <v>46227.576661388885</v>
+      </c>
       <c r="D118" s="5">
-        <v>46218.17912671296</v>
+        <v>46227.57667334491</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>360</v>
@@ -8644,10 +8670,10 @@
         <v>64</v>
       </c>
       <c r="T118" s="6">
-        <v>0</v>
-      </c>
-      <c r="U118" s="11" t="s">
-        <v>121</v>
+        <v>1</v>
+      </c>
+      <c r="U118" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -8657,9 +8683,11 @@
       <c r="B119" s="8">
         <v>46160.652983935186</v>
       </c>
-      <c r="C119" s="9"/>
+      <c r="C119" s="8">
+        <v>46227.5766281713</v>
+      </c>
       <c r="D119" s="8">
-        <v>46217.16843326389</v>
+        <v>46227.57662950231</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>217</v>
@@ -8710,9 +8738,11 @@
       <c r="B120" s="5">
         <v>46160.65298813657</v>
       </c>
-      <c r="C120" s="6"/>
+      <c r="C120" s="5">
+        <v>46227.57663413194</v>
+      </c>
       <c r="D120" s="5">
-        <v>46217.16837645833</v>
+        <v>46227.576636087964</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>217</v>
@@ -8763,9 +8793,11 @@
       <c r="B121" s="8">
         <v>46160.81215837963</v>
       </c>
-      <c r="C121" s="9"/>
+      <c r="C121" s="8">
+        <v>46227.57663981481</v>
+      </c>
       <c r="D121" s="8">
-        <v>46217.168417002315</v>
+        <v>46227.57664136574</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>335</v>
@@ -8816,9 +8848,11 @@
       <c r="B122" s="5">
         <v>46160.81220768519</v>
       </c>
-      <c r="C122" s="6"/>
+      <c r="C122" s="5">
+        <v>46227.57664462963</v>
+      </c>
       <c r="D122" s="5">
-        <v>46217.16841864583</v>
+        <v>46227.57664626157</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>335</v>
@@ -8918,7 +8952,7 @@
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46226.1680884838</v>
+        <v>46227.57669</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>370</v>
@@ -8962,29 +8996,29 @@
       <c r="R124" s="5">
         <v>46226</v>
       </c>
-      <c r="S124" s="12" t="s">
-        <v>373</v>
+      <c r="S124" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="T124" s="6">
         <v>0</v>
       </c>
-      <c r="U124" s="11" t="s">
-        <v>121</v>
+      <c r="U124" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B125" s="8">
         <v>46160.65303386574</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46226.16809032408</v>
+        <v>46227.57669174769</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9025,19 +9059,19 @@
       <c r="R125" s="8">
         <v>46226</v>
       </c>
-      <c r="S125" s="12" t="s">
-        <v>373</v>
+      <c r="S125" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="T125" s="9">
         <v>0</v>
       </c>
-      <c r="U125" s="11" t="s">
-        <v>121</v>
+      <c r="U125" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B126" s="5">
         <v>46160.65808951389</v>
@@ -9047,7 +9081,7 @@
         <v>46160.819809513894</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>25</v>
@@ -9071,7 +9105,7 @@
         <v>26</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="P126" s="6" t="s">
         <v>26</v>
@@ -9090,17 +9124,17 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B127" s="8">
         <v>46160.66095159722</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46226.16806592593</v>
+        <v>46227.57668935185</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9127,13 +9161,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>360</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="Q127" s="8">
         <v>46218</v>
@@ -9141,29 +9175,29 @@
       <c r="R127" s="8">
         <v>46226</v>
       </c>
-      <c r="S127" s="12" t="s">
-        <v>373</v>
+      <c r="S127" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="T127" s="9">
         <v>0</v>
       </c>
-      <c r="U127" s="11" t="s">
-        <v>121</v>
+      <c r="U127" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B128" s="5">
         <v>46160.66107538194</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46160.8199466088</v>
+        <v>46230.17763240741</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9190,13 +9224,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q128" s="5">
         <v>46227</v>
@@ -9204,8 +9238,8 @@
       <c r="R128" s="5">
         <v>46237</v>
       </c>
-      <c r="S128" s="10" t="s">
-        <v>32</v>
+      <c r="S128" s="12" t="s">
+        <v>383</v>
       </c>
       <c r="T128" s="6">
         <v>0</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -5734,7 +5734,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46225.86189206019</v>
+        <v>46231.560373796296</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -5734,7 +5734,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46231.560373796296</v>
+        <v>46231.653098587965</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="384">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -2403,9 +2403,11 @@
       <c r="B13" s="8">
         <v>46160.65224207176</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="8">
+        <v>46232.66265292824</v>
+      </c>
       <c r="D13" s="8">
-        <v>46199.75069068287</v>
+        <v>46232.66266767361</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>67</v>
@@ -2440,9 +2442,11 @@
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
       <c r="S13" s="9"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="12" t="s">
-        <v>65</v>
+      <c r="T13" s="9">
+        <v>1</v>
+      </c>
+      <c r="U13" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
@@ -3216,9 +3220,11 @@
       <c r="B26" s="5">
         <v>46160.65225063657</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46232.66259045139</v>
+      </c>
       <c r="D26" s="5">
-        <v>46181.678639652775</v>
+        <v>46232.66259146991</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>111</v>
@@ -3253,8 +3259,12 @@
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
       <c r="S26" s="6"/>
-      <c r="T26" s="6"/>
-      <c r="U26" s="6"/>
+      <c r="T26" s="6">
+        <v>1</v>
+      </c>
+      <c r="U26" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
@@ -3885,9 +3895,11 @@
       <c r="B37" s="8">
         <v>46160.6566696875</v>
       </c>
-      <c r="C37" s="9"/>
+      <c r="C37" s="8">
+        <v>46232.662501388884</v>
+      </c>
       <c r="D37" s="8">
-        <v>46197.19306372685</v>
+        <v>46232.66254853009</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>147</v>
@@ -3935,10 +3947,10 @@
         <v>64</v>
       </c>
       <c r="T37" s="9">
-        <v>0</v>
-      </c>
-      <c r="U37" s="11" t="s">
-        <v>121</v>
+        <v>1</v>
+      </c>
+      <c r="U37" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
@@ -4003,9 +4015,11 @@
       <c r="B39" s="8">
         <v>46160.65688415509</v>
       </c>
-      <c r="C39" s="9"/>
+      <c r="C39" s="8">
+        <v>46232.66253019676</v>
+      </c>
       <c r="D39" s="8">
-        <v>46196.16898914352</v>
+        <v>46232.662531759255</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>152</v>
@@ -5734,7 +5748,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46231.653098587965</v>
+        <v>46232.83599255787</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -6568,7 +6582,7 @@
         <v>46227.576312812496</v>
       </c>
       <c r="D82" s="5">
-        <v>46227.57633418981</v>
+        <v>46232.66254844907</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>62</v>
@@ -6618,8 +6632,8 @@
       <c r="T82" s="6">
         <v>1</v>
       </c>
-      <c r="U82" s="10" t="s">
-        <v>33</v>
+      <c r="U82" s="12" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
@@ -7722,9 +7736,11 @@
       <c r="B102" s="5">
         <v>46160.65293084491</v>
       </c>
-      <c r="C102" s="6"/>
+      <c r="C102" s="5">
+        <v>46232.662692094906</v>
+      </c>
       <c r="D102" s="5">
-        <v>46227.57668873842</v>
+        <v>46232.662708495365</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>322</v>
@@ -7759,9 +7775,11 @@
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
       <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="12" t="s">
-        <v>65</v>
+      <c r="T102" s="6">
+        <v>1</v>
+      </c>
+      <c r="U102" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
@@ -8903,9 +8921,11 @@
       <c r="B123" s="8">
         <v>46160.65302554399</v>
       </c>
-      <c r="C123" s="9"/>
+      <c r="C123" s="8">
+        <v>46232.66273488426</v>
+      </c>
       <c r="D123" s="8">
-        <v>46160.8192895949</v>
+        <v>46232.66274789352</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>367</v>
@@ -8940,8 +8960,12 @@
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
       <c r="S123" s="9"/>
-      <c r="T123" s="9"/>
-      <c r="U123" s="9"/>
+      <c r="T123" s="9">
+        <v>1</v>
+      </c>
+      <c r="U123" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
@@ -8950,9 +8974,11 @@
       <c r="B124" s="5">
         <v>46160.65302895833</v>
       </c>
-      <c r="C124" s="6"/>
+      <c r="C124" s="5">
+        <v>46232.6627083912</v>
+      </c>
       <c r="D124" s="5">
-        <v>46227.57669</v>
+        <v>46232.66272603009</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>370</v>
@@ -9000,10 +9026,10 @@
         <v>64</v>
       </c>
       <c r="T124" s="6">
-        <v>0</v>
-      </c>
-      <c r="U124" s="12" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="U124" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
@@ -9013,9 +9039,11 @@
       <c r="B125" s="8">
         <v>46160.65303386574</v>
       </c>
-      <c r="C125" s="9"/>
+      <c r="C125" s="8">
+        <v>46232.66271616898</v>
+      </c>
       <c r="D125" s="8">
-        <v>46227.57669174769</v>
+        <v>46232.66273621528</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>374</v>
@@ -9063,10 +9091,10 @@
         <v>64</v>
       </c>
       <c r="T125" s="9">
-        <v>0</v>
-      </c>
-      <c r="U125" s="12" t="s">
-        <v>65</v>
+        <v>1</v>
+      </c>
+      <c r="U125" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
   </si>
   <si>
     <t>1214909353651671</t>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -5748,7 +5748,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46232.83599255787</v>
+        <v>46233.648261504626</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -2899,7 +2899,7 @@
         <v>46181.612735636576</v>
       </c>
       <c r="D21" s="8">
-        <v>46223.58043296296</v>
+        <v>46237.53890778935</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>95</v>
@@ -2949,8 +2949,8 @@
       <c r="T21" s="9">
         <v>1</v>
       </c>
-      <c r="U21" s="12" t="s">
-        <v>65</v>
+      <c r="U21" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
@@ -7569,7 +7569,7 @@
         <v>46197.49723263889</v>
       </c>
       <c r="D99" s="8">
-        <v>46223.58110539352</v>
+        <v>46237.53942605324</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>315</v>
@@ -7619,8 +7619,8 @@
       <c r="T99" s="9">
         <v>1</v>
       </c>
-      <c r="U99" s="12" t="s">
-        <v>65</v>
+      <c r="U99" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -8078,7 +8078,7 @@
         <v>46197.49765626158</v>
       </c>
       <c r="D108" s="5">
-        <v>46227.576563599534</v>
+        <v>46237.53939438658</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>340</v>
@@ -8128,8 +8128,8 @@
       <c r="T108" s="6">
         <v>1</v>
       </c>
-      <c r="U108" s="12" t="s">
-        <v>65</v>
+      <c r="U108" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46230.17763240741</v>
+        <v>46237.16913130787</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>382</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -5748,7 +5748,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46233.648261504626</v>
+        <v>46237.570501423615</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -5748,7 +5748,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46237.570501423615</v>
+        <v>46237.810159872686</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="383">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -1223,9 +1223,6 @@
   </si>
   <si>
     <t xml:space="preserve">Pruebas de Instalacion Componentes </t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
 </sst>
 </file>
@@ -9222,7 +9219,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46237.16913130787</v>
+        <v>46238.18810939815</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>382</v>
@@ -9266,8 +9263,8 @@
       <c r="R128" s="5">
         <v>46237</v>
       </c>
-      <c r="S128" s="12" t="s">
-        <v>383</v>
+      <c r="S128" s="11" t="s">
+        <v>64</v>
       </c>
       <c r="T128" s="6">
         <v>0</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -5745,7 +5745,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46237.810159872686</v>
+        <v>46239.57424583333</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1214909353651671</t>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -5745,7 +5745,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46239.57424583333</v>
+        <v>46240.58270828704</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1528" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1490" uniqueCount="375">
   <si>
     <t xml:space="preserve"> 50001544 - DMC MINING SERVICES </t>
   </si>
@@ -1159,7 +1159,7 @@
     <t>Despacho</t>
   </si>
   <si>
-    <t>Instalación componentes,Gestion,Logistica:,Costos</t>
+    <t>Gestion,Logistica:,Costos</t>
   </si>
   <si>
     <t>1214909617251339</t>
@@ -1199,30 +1199,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>1214889077215100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta En Marcha </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Instalación componentes,Pruebas de Instalacion Componentes </t>
-  </si>
-  <si>
-    <t>1214889077215114</t>
-  </si>
-  <si>
-    <t>Instalación componentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de Instalacion Componentes ,Puesta En Marcha </t>
-  </si>
-  <si>
-    <t>1214889077215116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de Instalacion Componentes </t>
   </si>
 </sst>
 </file>
@@ -1746,7 +1722,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U128"/>
+  <dimension ref="A1:U125"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -8637,7 +8613,7 @@
         <v>46227.576661388885</v>
       </c>
       <c r="D118" s="5">
-        <v>46227.57667334491</v>
+        <v>46240.71833400463</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>360</v>
@@ -9092,185 +9068,6 @@
       </c>
       <c r="U125" s="10" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="126" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A126" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="B126" s="5">
-        <v>46160.65808951389</v>
-      </c>
-      <c r="C126" s="6"/>
-      <c r="D126" s="5">
-        <v>46160.819809513894</v>
-      </c>
-      <c r="E126" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="F126" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126" s="6"/>
-      <c r="I126" s="6"/>
-      <c r="J126" s="6"/>
-      <c r="K126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M126" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="N126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="O126" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="P126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q126" s="6"/>
-      <c r="R126" s="6"/>
-      <c r="S126" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T126" s="6">
-        <v>0</v>
-      </c>
-      <c r="U126" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="127" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A127" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="B127" s="8">
-        <v>46160.66095159722</v>
-      </c>
-      <c r="C127" s="9"/>
-      <c r="D127" s="8">
-        <v>46227.57668935185</v>
-      </c>
-      <c r="E127" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="F127" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G127" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I127" s="8">
-        <v>46218</v>
-      </c>
-      <c r="J127" s="8">
-        <v>46226</v>
-      </c>
-      <c r="K127" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L127" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M127" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N127" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="O127" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="P127" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="Q127" s="8">
-        <v>46218</v>
-      </c>
-      <c r="R127" s="8">
-        <v>46226</v>
-      </c>
-      <c r="S127" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T127" s="9">
-        <v>0</v>
-      </c>
-      <c r="U127" s="12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="128" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A128" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="B128" s="5">
-        <v>46160.66107538194</v>
-      </c>
-      <c r="C128" s="6"/>
-      <c r="D128" s="5">
-        <v>46238.18810939815</v>
-      </c>
-      <c r="E128" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="F128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G128" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="I128" s="5">
-        <v>46227</v>
-      </c>
-      <c r="J128" s="5">
-        <v>46237</v>
-      </c>
-      <c r="K128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N128" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="O128" s="6" t="s">
-        <v>379</v>
-      </c>
-      <c r="P128" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="Q128" s="5">
-        <v>46227</v>
-      </c>
-      <c r="R128" s="5">
-        <v>46237</v>
-      </c>
-      <c r="S128" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="T128" s="6">
-        <v>0</v>
-      </c>
-      <c r="U128" s="11" t="s">
-        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -5672,7 +5672,7 @@
         <v>46181.61286469907</v>
       </c>
       <c r="D67" s="8">
-        <v>46181.6781084838</v>
+        <v>46244.27301119213</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>
@@ -5721,7 +5721,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46240.58270828704</v>
+        <v>46244.58203497685</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>
@@ -6620,7 +6620,7 @@
         <v>46181.617794328704</v>
       </c>
       <c r="D83" s="8">
-        <v>46197.49724974537</v>
+        <v>46244.28636982639</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>284</v>
@@ -7713,7 +7713,7 @@
         <v>46232.662692094906</v>
       </c>
       <c r="D102" s="5">
-        <v>46232.662708495365</v>
+        <v>46244.28857741898</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>322</v>
@@ -8898,7 +8898,7 @@
         <v>46232.66273488426</v>
       </c>
       <c r="D123" s="8">
-        <v>46232.66274789352</v>
+        <v>46244.24096070602</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>367</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -5721,7 +5721,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46244.58203497685</v>
+        <v>46244.816475879634</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -5721,7 +5721,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46244.816475879634</v>
+        <v>46244.91622331018</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -5721,7 +5721,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46244.91622331018</v>
+        <v>46252.55709418982</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -5721,7 +5721,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46252.55709418982</v>
+        <v>46252.69803043982</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -5672,7 +5672,7 @@
         <v>46181.61286469907</v>
       </c>
       <c r="D67" s="8">
-        <v>46244.27301119213</v>
+        <v>46256.783416990744</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>243</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -5721,7 +5721,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46252.69803043982</v>
+        <v>46258.6493202662</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -5721,7 +5721,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46258.6493202662</v>
+        <v>46260.679553379625</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -823,7 +823,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t xml:space="preserve">OT2 4307 ZVN 1-9-86/2 ,OT 4313 - ZVN 1-9-45/2,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
   </si>
   <si>
     <t>1214909353651671</t>
@@ -5721,7 +5721,7 @@
         <v>46181.676856307866</v>
       </c>
       <c r="D68" s="5">
-        <v>46260.679553379625</v>
+        <v>46261.6008246412</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>246</v>

--- a/data/50001544 - DMC MINING SERVICES.xlsx
+++ b/data/50001544 - DMC MINING SERVICES.xlsx
@@ -2380,7 +2380,7 @@
         <v>46232.66265292824</v>
       </c>
       <c r="D13" s="8">
-        <v>46232.66266767361</v>
+        <v>46264.78718804398</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>67</v>
